--- a/data/excel/Thiết kế game.xlsx
+++ b/data/excel/Thiết kế game.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Giai đoạn phát triên" sheetId="2" r:id="rId2"/>
     <sheet name="Combat mechanic" sheetId="3" r:id="rId3"/>
     <sheet name="Term" sheetId="4" r:id="rId4"/>
-    <sheet name="Combat power" sheetId="10" r:id="rId5"/>
+    <sheet name="dummy Combat power" sheetId="10" r:id="rId5"/>
     <sheet name="Item" sheetId="9" r:id="rId6"/>
     <sheet name="Formula" sheetId="5" r:id="rId7"/>
     <sheet name="status" sheetId="7" r:id="rId8"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="575">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="582">
   <si>
     <t>Tên game</t>
   </si>
@@ -1829,7 +1829,7 @@
     <t>Full line</t>
   </si>
   <si>
-    <t>Subtarget 1: -50%. Sub target 2: -25%</t>
+    <t>Subtarget 1: -50%. Sub target 2: -75%</t>
   </si>
   <si>
     <t>Base Penetration chance</t>
@@ -1878,6 +1878,71 @@
   </si>
   <si>
     <t>Base Critical damage bonus</t>
+  </si>
+  <si>
+    <t>Each character has four equipment slots: one weapon slot, equipped with one of the available weapon types; one body armor slot; one accessory slot; and one off-hand slot, equipped with exactly one of the following: Rune Enhancement, Shield, Focus, or Ammunition. Only one item can occupy each slot.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Attack Target determines which enemies may be selected as the primary target: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Front</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> allows only the frontmost living enemy in each column, while </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Any</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> allows any living enemy, including protected enemies and the main character. </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Area of Attack determines which additional positions are hit: Single affects only the primary target; Row Adjacent also hits immediately adjacent positions in the same row; Line Adjacent also hits the position immediately behind the primary target in the same column; Full Line hits the primary target and all positions behind it in that column; and Cross also hits immediately adjacent positions above, below, left, and right. </t>
+  </si>
+  <si>
+    <t>The primary target uses 100% Attack; each secondary target uses the listed Attack modifier before its own mitigation is calculated—for example, −50% means 50% Attack and −25% means 75% Attack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empty positions and defeated targets are skipped without redistributing damage. </t>
+  </si>
+  <si>
+    <t>The attack area remains fixed around the primary target’s original position for all hits: if the primary target dies, subsequent hits still affect surviving secondary targets without selecting a new primary target.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> If either main character dies, the battle ends immediately and all remaining hits are canceled.</t>
   </si>
   <si>
     <t>Status</t>
@@ -6056,7 +6121,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7142857142857" style="5" customWidth="1"/>
@@ -6239,18 +6304,18 @@
       </c>
       <c r="F7" s="15">
         <f>I7/H7</f>
-        <v>1964.28571428571</v>
+        <v>2678.57142857143</v>
       </c>
       <c r="G7" s="16">
         <f>F7/1000</f>
-        <v>1.96428571428571</v>
+        <v>2.67857142857143</v>
       </c>
       <c r="H7" s="17">
         <v>8.4</v>
       </c>
       <c r="I7" s="15">
-        <f>17900-I8</f>
-        <v>16500</v>
+        <f>17900-I8-I9</f>
+        <v>22500</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -6716,10 +6781,7 @@
       <c r="F27" s="29">
         <v>0.2</v>
       </c>
-      <c r="G27" s="16">
-        <f>F27/1000</f>
-        <v>0.0002</v>
-      </c>
+      <c r="G27" s="16"/>
       <c r="H27" s="17">
         <v>140</v>
       </c>
@@ -6804,7 +6866,7 @@
       <c r="C31" s="13"/>
       <c r="D31" s="14"/>
       <c r="E31" s="15" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="F31" s="28">
         <f>I31/H31</f>
@@ -6981,6 +7043,41 @@
       </c>
       <c r="I39" s="15">
         <v>6000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="4" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="5" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="5" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="5" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="5" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="5" t="s">
+        <v>526</v>
       </c>
     </row>
   </sheetData>
@@ -7066,130 +7163,130 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>522</v>
+        <v>529</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>526</v>
+        <v>533</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
-        <v>532</v>
+        <v>539</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>536</v>
+        <v>543</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2" t="s">
-        <v>542</v>
+        <v>549</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2" t="s">
-        <v>544</v>
+        <v>551</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2" t="s">
-        <v>546</v>
+        <v>553</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2" t="s">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -7200,16 +7297,16 @@
         <v>5</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>549</v>
+        <v>556</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -7225,18 +7322,18 @@
         <v>1</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>552</v>
+        <v>559</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c r="B19" s="2">
         <v>3</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>554</v>
+        <v>561</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -7245,96 +7342,96 @@
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2" t="s">
-        <v>555</v>
+        <v>562</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>556</v>
+        <v>563</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2" t="s">
-        <v>557</v>
+        <v>564</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2" t="s">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2" t="s">
-        <v>559</v>
+        <v>566</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2" t="s">
-        <v>561</v>
+        <v>568</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2" t="s">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2" t="s">
-        <v>563</v>
+        <v>570</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2" t="s">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="2" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2" t="s">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2" t="s">
-        <v>567</v>
+        <v>574</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2" t="s">
-        <v>568</v>
+        <v>575</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2" t="s">
-        <v>569</v>
+        <v>576</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2" t="s">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="2" t="s">
-        <v>571</v>
+        <v>578</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2" t="s">
-        <v>572</v>
+        <v>579</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" s="2" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>572</v>
+        <v>579</v>
       </c>
       <c r="C30" t="s">
-        <v>574</v>
+        <v>581</v>
       </c>
     </row>
   </sheetData>

--- a/data/excel/Thiết kế game.xlsx
+++ b/data/excel/Thiết kế game.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12180" activeTab="5"/>
+    <workbookView windowWidth="27945" windowHeight="12180" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Ý tưởng chung" sheetId="1" r:id="rId1"/>
     <sheet name="Giai đoạn phát triên" sheetId="2" r:id="rId2"/>
     <sheet name="Combat mechanic" sheetId="3" r:id="rId3"/>
-    <sheet name="Term" sheetId="4" r:id="rId4"/>
+    <sheet name="Termynology" sheetId="4" r:id="rId4"/>
     <sheet name="dummy Combat power" sheetId="10" r:id="rId5"/>
     <sheet name="Item" sheetId="9" r:id="rId6"/>
     <sheet name="Formula" sheetId="5" r:id="rId7"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="582">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="581">
   <si>
     <t>Tên game</t>
   </si>
@@ -2105,9 +2105,6 @@
   </si>
   <si>
     <t>Allows the character to act, but prevents manual control.</t>
-  </si>
-  <si>
-    <t>Nhân vật vẫn có thể hành động nhưng không thể điều khiển thủ công</t>
   </si>
 </sst>
 </file>
@@ -7153,7 +7150,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="18.7142857142857" customWidth="1"/>
@@ -7319,7 +7316,7 @@
         <v>460</v>
       </c>
       <c r="B18" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>559</v>
@@ -7332,8 +7329,10 @@
       <c r="B19" s="2">
         <v>3</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>561</v>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Has no direct effect. Each target can gain at most 1 Stun Count stack per global turn, regardless of the number of hits or sources. All stacks share a 3-global-turn duration; gaining a stack refreshes the shared duration to 3 global turns. When the duration expires, all stacks reset to 0. Reaching Stun Threshold triggers Stun. Stun Count resets to 0 and cannot increase while stunned.</t>
+        </is>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -7424,14 +7423,6 @@
       <c r="B29" s="2"/>
       <c r="C29" s="2" t="s">
         <v>580</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" t="s">
-        <v>579</v>
-      </c>
-      <c r="C30" t="s">
-        <v>581</v>
       </c>
     </row>
   </sheetData>

--- a/data/excel/Thiết kế game.xlsx
+++ b/data/excel/Thiết kế game.xlsx
@@ -6118,7 +6118,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7142857142857" style="5" customWidth="1"/>
@@ -7075,6 +7075,13 @@
     <row r="48" spans="1:1">
       <c r="A48" s="5" t="s">
         <v>526</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Weapon Attack Target, Area of Attack, and secondary-target Attack modifiers apply only to normal attacks. Each skill defines its own target selection and area of effect and does not inherit these weapon targeting rules or secondary-target Attack modifiers.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/excel/Thiết kế game.xlsx
+++ b/data/excel/Thiết kế game.xlsx
@@ -4,18 +4,17 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12180" activeTab="7"/>
+    <workbookView windowWidth="27945" windowHeight="12180" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Ý tưởng chung" sheetId="1" r:id="rId1"/>
     <sheet name="Giai đoạn phát triên" sheetId="2" r:id="rId2"/>
     <sheet name="Combat mechanic" sheetId="3" r:id="rId3"/>
     <sheet name="Termynology" sheetId="4" r:id="rId4"/>
-    <sheet name="dummy Combat power" sheetId="10" r:id="rId5"/>
-    <sheet name="Item" sheetId="9" r:id="rId6"/>
-    <sheet name="Formula" sheetId="5" r:id="rId7"/>
-    <sheet name="status" sheetId="7" r:id="rId8"/>
-    <sheet name="Character" sheetId="8" r:id="rId9"/>
+    <sheet name="Balanced Dummy " sheetId="5" r:id="rId5"/>
+    <sheet name="Destroyer class" sheetId="6" r:id="rId6"/>
+    <sheet name="Item" sheetId="7" r:id="rId7"/>
+    <sheet name="status" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="626">
   <si>
     <t>Tên game</t>
   </si>
@@ -112,27 +111,7 @@
     <t>tạo combat demo với đồ họa đơn giản</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Avatar War</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> is a turn-based strategy game where you command a main character and eight avatars in a 3×3 formation, aiming to defeat the enemy’s main character while protecting your own. Teams alternate turns, with the higher-AP team acting first and action slots gradually increasing from two to four, then five. Reposition your characters, defend to pass an action slot to an ally, or commit to an attack or skill. Every move costs AP, and pushing a character into negative AP can secure an immediate advantage at the cost of delaying their next opportunity to act. Victory depends on teamwork, positioning, and timing.</t>
-    </r>
+    <t>Avatar War is a turn-based strategy game where you command a main character and eight avatars in a 3×3 formation, aiming to defeat the enemy’s main character while protecting your own. Teams alternate turns, with the higher-AP team acting first and action slots gradually increasing from two to four, then five. Reposition your characters, defend to pass an action slot to an ally, or commit to an attack or skill. Every move costs AP, and pushing a character into negative AP can secure an immediate advantage at the cost of delaying their next opportunity to act. Victory depends on teamwork, positioning, and timing.</t>
   </si>
   <si>
     <t>Section</t>
@@ -1236,222 +1215,28 @@
     <t>1. Reference Conditions</t>
   </si>
   <si>
-    <r>
-      <t>1 HP = 1 CP.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> MP uses the same CP value as HP.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">HP: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>40,000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Attack: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2,000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Defense and Skill Defense: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>1,000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> each.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Power Constant, K: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>1,000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Skill Attack: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>4,800</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Reference rotation: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>one normal attack followed by one skill</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Accuracy: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>100%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">; Evasion: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>0%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
+    <t>1 HP = 1 CP. MP uses the same CP value as HP.</t>
+  </si>
+  <si>
+    <t>HP: 40,000.</t>
+  </si>
+  <si>
+    <t>Attack: 2,000.</t>
+  </si>
+  <si>
+    <t>Defense and Skill Defense: 1,000 each.</t>
+  </si>
+  <si>
+    <t>Power Constant, K: 1,000.</t>
+  </si>
+  <si>
+    <t>Skill Attack: 4,800.</t>
+  </si>
+  <si>
+    <t>Reference rotation: one normal attack followed by one skill.</t>
+  </si>
+  <si>
+    <t>Accuracy: 100%; Evasion: 0%.</t>
   </si>
   <si>
     <t>Multi-Hit, Penetration, and Critical Hits apply only to normal attacks.</t>
@@ -1526,56 +1311,10 @@
     <t>Equivalent HP = 40,000 × (2,064 / New Incoming Mixed Damage − 1)</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Since </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>1 HP = 1 CP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, Equivalent HP equals CP Gain.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">For percentage stats, each pricing unit means </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>one percentage point</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, such as an increase from 20% to 21%.</t>
-    </r>
+    <t>Since 1 HP = 1 CP, Equivalent HP equals CP Gain.</t>
+  </si>
+  <si>
+    <t>For percentage stats, each pricing unit means one percentage point, such as an increase from 20% to 21%.</t>
   </si>
   <si>
     <t>4. CP per Stat</t>
@@ -1701,30 +1440,7 @@
     <t>The CP value assumes sufficient opportunities to spend recovered AP. Extra AP does not automatically create action slots or bypass skill cooldowns.</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">The value uses a hypothetical healing reference because the benchmark duel contains no healing. Default Healing Amplification is </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>0%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, meaning no additional healing received.</t>
-    </r>
+    <t>The value uses a hypothetical healing reference because the benchmark duel contains no healing. Default Healing Amplification is 0%, meaning no additional healing received.</t>
   </si>
   <si>
     <t>6. Character and Item CP</t>
@@ -1757,6 +1473,211 @@
     <t>These coefficients are reference prices derived at the Balanced Dummy baseline. Applying them to all base stats is a budgeting convention; actual combat value may change with stat combinations, opponents, and battle duration.</t>
   </si>
   <si>
+    <t>Class</t>
+  </si>
+  <si>
+    <t>Destroyer</t>
+  </si>
+  <si>
+    <t>Character</t>
+  </si>
+  <si>
+    <t>Bluetooth</t>
+  </si>
+  <si>
+    <t>Weapon</t>
+  </si>
+  <si>
+    <t>Destroyer weapon</t>
+  </si>
+  <si>
+    <t>Offhand</t>
+  </si>
+  <si>
+    <t>Rune enhancement</t>
+  </si>
+  <si>
+    <t>Body armour</t>
+  </si>
+  <si>
+    <t>Accessory</t>
+  </si>
+  <si>
+    <t>Base character CP</t>
+  </si>
+  <si>
+    <t>Spare</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>Area of Effect</t>
+  </si>
+  <si>
+    <t>Formula (base)</t>
+  </si>
+  <si>
+    <t>Stat at SL 5</t>
+  </si>
+  <si>
+    <t>Frozen Axe</t>
+  </si>
+  <si>
+    <t>Deals initial skill damage, applies damage over time, and inflicts Freeze on enemies in the target row.</t>
+  </si>
+  <si>
+    <t>Front</t>
+  </si>
+  <si>
+    <t>Full Row</t>
+  </si>
+  <si>
+    <t>Initial Satk</t>
+  </si>
+  <si>
+    <t>4.8*K*2%*SL</t>
+  </si>
+  <si>
+    <t>DOT Satk</t>
+  </si>
+  <si>
+    <t>Deadly Strike</t>
+  </si>
+  <si>
+    <t>Deals heavy skill damage to one Front target. Usable only while the caster’s current HP is below 50% of Max HP.</t>
+  </si>
+  <si>
+    <t>Single</t>
+  </si>
+  <si>
+    <t>SAtk</t>
+  </si>
+  <si>
+    <t>4.8*K*70%*SL</t>
+  </si>
+  <si>
+    <t>Bluetooth Connection</t>
+  </si>
+  <si>
+    <t>Passive</t>
+  </si>
+  <si>
+    <t>At the start of each team turn, links with the two allies with the lowest HP to share damage. Grants Fortify and Resistance based on Bluetooth’s current DEF and SDEF, respectively.</t>
+  </si>
+  <si>
+    <t>2 Lowest health teamates</t>
+  </si>
+  <si>
+    <t>Shared damage before migation</t>
+  </si>
+  <si>
+    <t>10%*SL</t>
+  </si>
+  <si>
+    <t>Fortify</t>
+  </si>
+  <si>
+    <t>6%*SL</t>
+  </si>
+  <si>
+    <t>Resistance</t>
+  </si>
+  <si>
+    <t>3%*SL</t>
+  </si>
+  <si>
+    <t>Specialization 1</t>
+  </si>
+  <si>
+    <t>The Viking Conqueror</t>
+  </si>
+  <si>
+    <t>Crushes enemy formations with brute force, sweeping attacks, and a devastating finishing strike.</t>
+  </si>
+  <si>
+    <t>S1
+Unlock skill Deadly strike</t>
+  </si>
+  <si>
+    <t>S1.1.1 
+Base AP recovery +10</t>
+  </si>
+  <si>
+    <t>S1.1.2 
+Sub target damage penalty - 25%</t>
+  </si>
+  <si>
+    <t>S1.1.3 
+Attack effectiveness + 25%</t>
+  </si>
+  <si>
+    <t>S1.1.4 Increased AP recovery +20%</t>
+  </si>
+  <si>
+    <t>S1.2.1 1
+Base AP recovery +10</t>
+  </si>
+  <si>
+    <t>S1.2.2 
+Base MHR +25%</t>
+  </si>
+  <si>
+    <t>S1.2.3 
+Base CHC + 25%</t>
+  </si>
+  <si>
+    <t>S1.2.4 
+Base MHR + 15%
+Base CHC + 25%
+Base CDB + 70%</t>
+  </si>
+  <si>
+    <t>Specialization 2</t>
+  </si>
+  <si>
+    <t>The Viking Unifier</t>
+  </si>
+  <si>
+    <t>Links and protects allies, weakens enemies, and sustains the team through shared strength.</t>
+  </si>
+  <si>
+    <t>S2
+Unlock skill Bluetooth connection</t>
+  </si>
+  <si>
+    <t>S2.1.1 
+Base DEF +700</t>
+  </si>
+  <si>
+    <t>S2.1.2 
+Base SDEF + 350</t>
+  </si>
+  <si>
+    <t>S2.1.3
+Frozen Axe DOT effectiveness +100%</t>
+  </si>
+  <si>
+    <t>S2.1.4
+Skill Bluetooth connection effectiveness +20%</t>
+  </si>
+  <si>
+    <t>S2.2.1
+Base HA + 20%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2.2.2
+Frozen Axe applied Sunder -20% </t>
+  </si>
+  <si>
+    <t>S2.2.3
+Each team turn, restores 5% Max HP</t>
+  </si>
+  <si>
+    <t>S2.2.4
+When attacked, has 20% chance to restore 1%  Max HP</t>
+  </si>
+  <si>
     <t>Item</t>
   </si>
   <si>
@@ -1766,7 +1687,10 @@
     <t>Area of attack</t>
   </si>
   <si>
-    <t>Item reduced Attack for sub target</t>
+    <t>Sub-target Damage penalty</t>
+  </si>
+  <si>
+    <t>Value</t>
   </si>
   <si>
     <t>K relative</t>
@@ -1781,24 +1705,6 @@
     <t>Warrior weapon</t>
   </si>
   <si>
-    <t>Front</t>
-  </si>
-  <si>
-    <t>Single</t>
-  </si>
-  <si>
-    <t>Base Attack</t>
-  </si>
-  <si>
-    <t>Skill point</t>
-  </si>
-  <si>
-    <t>Base AP recovery</t>
-  </si>
-  <si>
-    <t>Destroyer weapon</t>
-  </si>
-  <si>
     <t>Row adjection</t>
   </si>
   <si>
@@ -1808,31 +1714,19 @@
     <t>Line adjection</t>
   </si>
   <si>
-    <t>Base critical hit chance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base AP recovery </t>
-  </si>
-  <si>
     <t>Ranger weapon</t>
   </si>
   <si>
     <t>Any</t>
   </si>
   <si>
-    <t>Base Multi hit rate</t>
-  </si>
-  <si>
-    <t>Penetrator weapon</t>
+    <t>Piercer weapon</t>
   </si>
   <si>
     <t>Full line</t>
   </si>
   <si>
-    <t>Subtarget 1: -50%. Sub target 2: -75%</t>
-  </si>
-  <si>
-    <t>Base Penetration chance</t>
+    <t>Subtarget 1: 50%. Sub target 2: 75%</t>
   </si>
   <si>
     <t>Devastator weapon</t>
@@ -1841,33 +1735,12 @@
     <t>Cross</t>
   </si>
   <si>
-    <t>Base Stun Count</t>
-  </si>
-  <si>
     <t>Caster weapon</t>
   </si>
   <si>
-    <t>Body armour</t>
-  </si>
-  <si>
-    <t>Base Defense</t>
-  </si>
-  <si>
-    <t>Base HP</t>
-  </si>
-  <si>
-    <t>Accessory</t>
-  </si>
-  <si>
-    <t>Base MP</t>
-  </si>
-  <si>
     <t>Rune Enhancement</t>
   </si>
   <si>
-    <t>Base Skill Defense</t>
-  </si>
-  <si>
     <t>Shield</t>
   </si>
   <si>
@@ -1877,57 +1750,13 @@
     <t>Ammunition</t>
   </si>
   <si>
-    <t>Base Critical damage bonus</t>
+    <t>Arrow</t>
   </si>
   <si>
     <t>Each character has four equipment slots: one weapon slot, equipped with one of the available weapon types; one body armor slot; one accessory slot; and one off-hand slot, equipped with exactly one of the following: Rune Enhancement, Shield, Focus, or Ammunition. Only one item can occupy each slot.</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Attack Target determines which enemies may be selected as the primary target: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Front</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> allows only the frontmost living enemy in each column, while </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Any</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> allows any living enemy, including protected enemies and the main character. </t>
-    </r>
+    <t xml:space="preserve">Attack Target determines which enemies may be selected as the primary target: Front allows only the frontmost living enemy in each column, while Any allows any living enemy, including protected enemies and the main character. </t>
   </si>
   <si>
     <t xml:space="preserve">Area of Attack determines which additional positions are hit: Single affects only the primary target; Row Adjacent also hits immediately adjacent positions in the same row; Line Adjacent also hits the position immediately behind the primary target in the same column; Full Line hits the primary target and all positions behind it in that column; and Cross also hits immediately adjacent positions above, below, left, and right. </t>
@@ -1945,6 +1774,9 @@
     <t xml:space="preserve"> If either main character dies, the battle ends immediately and all remaining hits are canceled.</t>
   </si>
   <si>
+    <t>Weapon Attack Target, Area of Attack, and secondary-target Attack modifiers apply only to normal attacks. Each skill defines its own target selection and area of effect and does not inherit these weapon targeting rules or secondary-target Attack modifiers.</t>
+  </si>
+  <si>
     <t>Status</t>
   </si>
   <si>
@@ -1966,15 +1798,9 @@
     <t>Increases Skill Attack.</t>
   </si>
   <si>
-    <t>Fortify</t>
-  </si>
-  <si>
     <t>Increases Defense.</t>
   </si>
   <si>
-    <t>Resistance</t>
-  </si>
-  <si>
     <t>Increases Skill Defense.</t>
   </si>
   <si>
@@ -2038,7 +1864,7 @@
     <t>Damage over Time</t>
   </si>
   <si>
-    <t>Deals damage at the start of each global turn.</t>
+    <t xml:space="preserve">Deals damage at the start of each global turn </t>
   </si>
   <si>
     <t>Prevents receiving action slots and performing voluntary actions, including attacks, defending, swaps, and active skills. Sets Character Base AP Recovery to 0. Passive skills remain usable.</t>
@@ -2047,7 +1873,7 @@
     <t>Stun Count</t>
   </si>
   <si>
-    <t>Has no direct effect. Reaching Stun Threshold triggers Stun. Stun Count resets to 0 and cannot increase while stunned.</t>
+    <t>Has no direct effect. Each target can gain at most 1 Stun Count stack per global turn, regardless of the number of hits or sources. All stacks share a 3-global-turn duration; gaining a stack refreshes the shared duration to 3 global turns. When the duration expires, all stacks reset to 0. Reaching Stun Threshold triggers Stun. Stun Count resets to 0 and cannot increase while stunned.</t>
   </si>
   <si>
     <t>The number of Stun Count stacks required to trigger Stun.</t>
@@ -2111,7 +1937,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="7">
+  <numFmts count="9">
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
@@ -2119,8 +1945,10 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ * #,##0.0_ ;_ * \-#,##0.0_ ;_ * &quot;-&quot;??.0_ ;_ @_ "/>
     <numFmt numFmtId="180" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??.00_ ;_ @_ "/>
+    <numFmt numFmtId="181" formatCode="#,##0;[Red]\-#,##0;&quot;-&quot;"/>
+    <numFmt numFmtId="182" formatCode="#,##0.00;[Red]\-#,##0.00;&quot;-&quot;"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2157,7 +1985,7 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2165,14 +1993,14 @@
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2188,7 +2016,7 @@
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2219,7 +2047,7 @@
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2227,7 +2055,7 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2235,7 +2063,7 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2243,57 +2071,42 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2354,19 +2167,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2378,19 +2191,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2402,19 +2215,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2426,19 +2239,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2450,19 +2263,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2474,19 +2287,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2521,19 +2334,6 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -2549,6 +2349,19 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -2580,7 +2393,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4" tint="0.49998"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2652,159 +2465,157 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="10">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyAlignment="1"/>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1"/>
@@ -2813,7 +2624,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="179" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2824,68 +2635,123 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2941,7 +2807,221 @@
     <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -3079,23 +3159,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="67000"/>
                 <a:lumMod val="110000"/>
                 <a:satMod val="105000"/>
-                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:tint val="73000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="103000"/>
-                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:tint val="81000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="109000"/>
-                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -3105,23 +3185,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="94000"/>
+                <a:lumMod val="102000"/>
                 <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:shade val="100000"/>
+                <a:lumMod val="100000"/>
                 <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:shade val="78000"/>
                 <a:lumMod val="99000"/>
                 <a:satMod val="120000"/>
-                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -3129,26 +3209,23 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -3183,17 +3260,17 @@
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -3346,7 +3423,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -3362,238 +3439,236 @@
     <col min="3" max="3" width="161.714285714286" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="61" customHeight="1" spans="1:3">
-      <c r="A1" s="48" t="s">
+    <row r="1" customFormat="1" ht="61" customHeight="1" spans="1:1">
+      <c r="A1" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="49" t="s">
+      <c r="B3" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="C3" s="23" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="49" t="s">
+      <c r="A4" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="49" t="s">
+      <c r="B4" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="49" t="s">
+      <c r="C4" s="23" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="49" t="s">
+      <c r="A5" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="49" t="s">
+      <c r="B5" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="49" t="s">
+      <c r="C5" s="23" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="49" t="s">
+      <c r="A6" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="49" t="s">
+      <c r="B6" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="49" t="s">
+      <c r="C6" s="23" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="49" t="s">
+      <c r="A7" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="49" t="s">
+      <c r="B7" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="49" t="s">
+      <c r="C7" s="23" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="49" t="s">
+      <c r="A8" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="49" t="s">
+      <c r="B8" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="49" t="s">
+      <c r="C8" s="23" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="49" t="s">
+      <c r="A9" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="B9" s="49" t="s">
+      <c r="B9" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="49" t="s">
+      <c r="C9" s="23" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="49" t="s">
+      <c r="A10" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="49" t="s">
+      <c r="B10" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="49" t="s">
+      <c r="C10" s="23" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="49" t="s">
+      <c r="A11" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="49" t="s">
+      <c r="B11" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="49" t="s">
+      <c r="C11" s="23" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="49" t="s">
+      <c r="A12" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="49" t="s">
+      <c r="B12" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="49" t="s">
+      <c r="C12" s="23" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="49" t="s">
+      <c r="A13" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="49" t="s">
+      <c r="B13" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="C13" s="49" t="s">
+      <c r="C13" s="23" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="49" t="s">
+      <c r="A14" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="49" t="s">
+      <c r="B14" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="49" t="s">
+      <c r="C14" s="23" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="49" t="s">
+      <c r="A15" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="B15" s="49" t="s">
+      <c r="B15" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="C15" s="49" t="s">
+      <c r="C15" s="23" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="49" t="s">
+      <c r="A16" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="B16" s="49" t="s">
+      <c r="B16" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="C16" s="49" t="s">
+      <c r="C16" s="23" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="49" t="s">
+      <c r="A17" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="B17" s="49" t="s">
+      <c r="B17" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="C17" s="49" t="s">
+      <c r="C17" s="23" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="49" t="s">
+      <c r="A18" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="B18" s="49" t="s">
+      <c r="B18" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="C18" s="49" t="s">
+      <c r="C18" s="23" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="49" t="s">
+      <c r="A19" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="B19" s="49" t="s">
+      <c r="B19" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="C19" s="49" t="s">
+      <c r="C19" s="23" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="49" t="s">
+      <c r="A20" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="B20" s="49" t="s">
+      <c r="B20" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="C20" s="49" t="s">
+      <c r="C20" s="23" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="49" t="s">
+      <c r="A21" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="B21" s="49" t="s">
+      <c r="B21" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="C21" s="49" t="s">
+      <c r="C21" s="23" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="49" t="s">
+      <c r="A22" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="B22" s="49" t="s">
+      <c r="B22" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="C22" s="49" t="s">
+      <c r="C22" s="23" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="49" t="s">
+      <c r="A23" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="B23" s="49" t="s">
+      <c r="B23" s="23" t="s">
         <v>72</v>
       </c>
       <c r="C23" t="s">
@@ -3601,186 +3676,186 @@
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="49" t="s">
+      <c r="A24" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="B24" s="49" t="s">
+      <c r="B24" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="C24" s="49" t="s">
+      <c r="C24" s="23" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="49" t="s">
+      <c r="A25" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="B25" s="49" t="s">
+      <c r="B25" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="C25" s="49" t="s">
+      <c r="C25" s="23" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="49" t="s">
+      <c r="A26" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="B26" s="49" t="s">
+      <c r="B26" s="23" t="s">
         <v>79</v>
       </c>
-      <c r="C26" s="49" t="s">
+      <c r="C26" s="23" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="49" t="s">
+      <c r="A27" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="B27" s="49" t="s">
+      <c r="B27" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="C27" s="49" t="s">
+      <c r="C27" s="23" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="49" t="s">
+      <c r="A28" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="B28" s="49" t="s">
+      <c r="B28" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="C28" s="49" t="s">
+      <c r="C28" s="23" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="49" t="s">
+      <c r="A29" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="B29" s="49" t="s">
+      <c r="B29" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="C29" s="49" t="s">
+      <c r="C29" s="23" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="49" t="s">
+      <c r="A30" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="B30" s="49" t="s">
+      <c r="B30" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="C30" s="49" t="s">
+      <c r="C30" s="23" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="49" t="s">
+      <c r="A31" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="B31" s="49" t="s">
+      <c r="B31" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="C31" s="49" t="s">
+      <c r="C31" s="23" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="49" t="s">
+      <c r="A32" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="B32" s="49" t="s">
+      <c r="B32" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="C32" s="49" t="s">
+      <c r="C32" s="23" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="49" t="s">
+      <c r="A33" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="B33" s="49" t="s">
+      <c r="B33" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="C33" s="49" t="s">
+      <c r="C33" s="23" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="49" t="s">
+      <c r="A34" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="B34" s="49" t="s">
+      <c r="B34" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="C34" s="49" t="s">
+      <c r="C34" s="23" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="49" t="s">
+      <c r="A35" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="B35" s="49" t="s">
+      <c r="B35" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="C35" s="49" t="s">
+      <c r="C35" s="23" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="49" t="s">
+      <c r="A36" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="B36" s="49" t="s">
+      <c r="B36" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="C36" s="49" t="s">
+      <c r="C36" s="23" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="49" t="s">
+      <c r="A37" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="B37" s="49" t="s">
+      <c r="B37" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="C37" s="49" t="s">
+      <c r="C37" s="23" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38" s="49" t="s">
+      <c r="A38" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="B38" s="49" t="s">
+      <c r="B38" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="C38" s="49" t="s">
+      <c r="C38" s="23" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="49" t="s">
+      <c r="A39" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="B39" s="49" t="s">
+      <c r="B39" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="C39" s="49" t="s">
+      <c r="C39" s="23" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="49" t="s">
+      <c r="A40" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="B40" s="49" t="s">
+      <c r="B40" s="23" t="s">
         <v>107</v>
       </c>
       <c r="C40" t="s">
@@ -3788,10 +3863,10 @@
       </c>
     </row>
     <row r="41" spans="1:3">
-      <c r="A41" s="49" t="s">
+      <c r="A41" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="B41" s="49" t="s">
+      <c r="B41" s="23" t="s">
         <v>109</v>
       </c>
       <c r="C41" t="s">
@@ -3799,10 +3874,10 @@
       </c>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="49" t="s">
+      <c r="A42" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="B42" s="49" t="s">
+      <c r="B42" s="23" t="s">
         <v>111</v>
       </c>
       <c r="C42" t="s">
@@ -3810,120 +3885,120 @@
       </c>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="49" t="s">
+      <c r="A43" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="B43" s="49" t="s">
+      <c r="B43" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="C43" s="49" t="s">
+      <c r="C43" s="23" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="44" spans="1:3">
-      <c r="A44" s="49" t="s">
+      <c r="A44" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="B44" s="49" t="s">
+      <c r="B44" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="C44" s="49" t="s">
+      <c r="C44" s="23" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="45" spans="1:3">
-      <c r="A45" s="49" t="s">
+      <c r="A45" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="B45" s="49" t="s">
+      <c r="B45" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="C45" s="49" t="s">
+      <c r="C45" s="23" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="46" spans="1:3">
-      <c r="A46" s="49" t="s">
+      <c r="A46" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="B46" s="49" t="s">
+      <c r="B46" s="23" t="s">
         <v>119</v>
       </c>
-      <c r="C46" s="49" t="s">
+      <c r="C46" s="23" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="49" t="s">
+      <c r="A47" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="B47" s="49" t="s">
+      <c r="B47" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="C47" s="49" t="s">
+      <c r="C47" s="23" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="48" spans="1:3">
-      <c r="A48" s="49" t="s">
+      <c r="A48" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="B48" s="49" t="s">
+      <c r="B48" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="C48" s="49" t="s">
+      <c r="C48" s="23" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="49" spans="1:3">
-      <c r="A49" s="49" t="s">
+      <c r="A49" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="B49" s="49" t="s">
+      <c r="B49" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="C49" s="49" t="s">
+      <c r="C49" s="23" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="49" t="s">
+      <c r="A50" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="B50" s="49" t="s">
+      <c r="B50" s="23" t="s">
         <v>127</v>
       </c>
-      <c r="C50" s="49" t="s">
+      <c r="C50" s="23" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="49" t="s">
+      <c r="A51" s="23" t="s">
         <v>129</v>
       </c>
-      <c r="B51" s="49" t="s">
+      <c r="B51" s="23" t="s">
         <v>130</v>
       </c>
-      <c r="C51" s="49" t="s">
+      <c r="C51" s="23" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="52" spans="1:3">
-      <c r="A52" s="49" t="s">
+      <c r="A52" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="B52" s="49" t="s">
+      <c r="B52" s="23" t="s">
         <v>133</v>
       </c>
-      <c r="C52" s="49" t="s">
+      <c r="C52" s="23" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="53" spans="1:3">
-      <c r="A53" s="49" t="s">
+      <c r="A53" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="B53" s="49" t="s">
+      <c r="B53" s="23" t="s">
         <v>135</v>
       </c>
       <c r="C53" t="s">
@@ -3931,24 +4006,24 @@
       </c>
     </row>
     <row r="54" spans="1:3">
-      <c r="A54" s="49" t="s">
+      <c r="A54" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="B54" s="49" t="s">
+      <c r="B54" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="C54" s="49" t="s">
+      <c r="C54" s="23" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="55" spans="1:3">
-      <c r="A55" s="49" t="s">
+      <c r="A55" s="23" t="s">
         <v>139</v>
       </c>
-      <c r="B55" s="49" t="s">
+      <c r="B55" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="C55" s="49" t="s">
+      <c r="C55" s="23" t="s">
         <v>140</v>
       </c>
     </row>
@@ -3964,79 +4039,79 @@
       </c>
     </row>
     <row r="57" spans="1:3">
-      <c r="A57" s="50" t="s">
+      <c r="A57" s="65" t="s">
         <v>143</v>
       </c>
-      <c r="B57" s="50" t="s">
+      <c r="B57" s="65" t="s">
         <v>144</v>
       </c>
-      <c r="C57" s="50" t="s">
+      <c r="C57" s="65" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="58" ht="30" spans="1:3">
-      <c r="A58" s="50" t="s">
+    <row r="58" customFormat="1" ht="30" customHeight="1" spans="1:3">
+      <c r="A58" s="65" t="s">
         <v>143</v>
       </c>
-      <c r="B58" s="50" t="s">
+      <c r="B58" s="65" t="s">
         <v>146</v>
       </c>
-      <c r="C58" s="50" t="s">
+      <c r="C58" s="65" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="59" ht="30" spans="1:3">
-      <c r="A59" s="50" t="s">
+    <row r="59" customFormat="1" ht="30" customHeight="1" spans="1:3">
+      <c r="A59" s="65" t="s">
         <v>143</v>
       </c>
-      <c r="B59" s="50" t="s">
+      <c r="B59" s="65" t="s">
         <v>148</v>
       </c>
-      <c r="C59" s="50" t="s">
+      <c r="C59" s="65" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="60" ht="30" spans="1:3">
-      <c r="A60" s="50" t="s">
+    <row r="60" customFormat="1" ht="30" customHeight="1" spans="1:3">
+      <c r="A60" s="65" t="s">
         <v>150</v>
       </c>
-      <c r="B60" s="50" t="s">
+      <c r="B60" s="65" t="s">
         <v>151</v>
       </c>
-      <c r="C60" s="50" t="s">
+      <c r="C60" s="65" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="61" ht="30" spans="1:3">
-      <c r="A61" s="50" t="s">
+    <row r="61" customFormat="1" ht="30" customHeight="1" spans="1:3">
+      <c r="A61" s="65" t="s">
         <v>150</v>
       </c>
-      <c r="B61" s="50" t="s">
+      <c r="B61" s="65" t="s">
         <v>153</v>
       </c>
-      <c r="C61" s="50" t="s">
+      <c r="C61" s="65" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="62" ht="30" spans="1:3">
-      <c r="A62" s="50" t="s">
+    <row r="62" customFormat="1" ht="30" customHeight="1" spans="1:3">
+      <c r="A62" s="65" t="s">
         <v>150</v>
       </c>
-      <c r="B62" s="50" t="s">
+      <c r="B62" s="65" t="s">
         <v>155</v>
       </c>
-      <c r="C62" s="50" t="s">
+      <c r="C62" s="65" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="63" ht="30" spans="1:3">
-      <c r="A63" s="50" t="s">
+    <row r="63" customFormat="1" ht="30" customHeight="1" spans="1:3">
+      <c r="A63" s="65" t="s">
         <v>150</v>
       </c>
-      <c r="B63" s="50" t="s">
+      <c r="B63" s="65" t="s">
         <v>157</v>
       </c>
-      <c r="C63" s="50" t="s">
+      <c r="C63" s="65" t="s">
         <v>158</v>
       </c>
     </row>
@@ -4044,7 +4119,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -4314,19 +4389,19 @@
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="2" t="s">
+      <c r="A16" t="s">
         <v>219</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" t="s">
         <v>220</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" t="s">
         <v>200</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" t="s">
         <v>221</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" t="s">
         <v>222</v>
       </c>
     </row>
@@ -4348,28 +4423,21 @@
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="2" t="s">
+      <c r="A18" t="s">
         <v>227</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" t="s">
         <v>228</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" t="s">
         <v>200</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" t="s">
         <v>229</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
@@ -4897,75 +4965,75 @@
       </c>
     </row>
     <row r="56" spans="1:5">
-      <c r="A56" s="2" t="s">
+      <c r="A56" t="s">
         <v>195</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="B56" t="s">
         <v>196</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C56" t="s">
         <v>165</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="D56" t="s">
         <v>350</v>
       </c>
-      <c r="E56" s="2" t="s">
+      <c r="E56" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="57" spans="1:5">
-      <c r="A57" s="2" t="s">
+      <c r="A57" t="s">
         <v>352</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="B57" t="s">
         <v>353</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C57" t="s">
         <v>354</v>
       </c>
-      <c r="D57" s="2" t="s">
+      <c r="D57" t="s">
         <v>355</v>
       </c>
-      <c r="E57" s="2" t="s">
+      <c r="E57" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="58" spans="1:5">
-      <c r="A58" s="2" t="s">
+      <c r="A58" t="s">
         <v>357</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="B58" t="s">
         <v>358</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C58" t="s">
         <v>354</v>
       </c>
-      <c r="D58" s="2" t="s">
+      <c r="D58" t="s">
         <v>359</v>
       </c>
-      <c r="E58" s="2" t="s">
+      <c r="E58" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="59" spans="1:5">
-      <c r="A59" s="2" t="s">
+      <c r="A59" t="s">
         <v>361</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B59" t="s">
         <v>362</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" t="s">
         <v>363</v>
       </c>
-      <c r="D59" s="2" t="s">
+      <c r="D59" t="s">
         <v>364</v>
       </c>
-      <c r="E59" s="2" t="s">
+      <c r="E59" t="s">
         <v>365</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -4995,47 +5063,47 @@
     <col min="17" max="17" width="12.1428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="30" customFormat="1" spans="1:17">
-      <c r="A1" s="30" t="s">
+    <row r="1" s="28" customFormat="1" spans="1:17">
+      <c r="A1" s="28" t="s">
         <v>366</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="29" t="s">
         <v>367</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="29" t="s">
         <v>368</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="29" t="s">
         <v>369</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="29" t="s">
         <v>370</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="28" t="s">
         <v>371</v>
       </c>
-      <c r="G1" s="30" t="s">
+      <c r="G1" s="28" t="s">
         <v>372</v>
       </c>
-      <c r="H1" s="30" t="s">
+      <c r="H1" s="28" t="s">
         <v>373</v>
       </c>
       <c r="J1" t="s">
         <v>374</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="3" t="s">
         <v>278</v>
       </c>
       <c r="P1" t="s">
@@ -5046,86 +5114,86 @@
       </c>
     </row>
     <row r="2" spans="1:17">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
         <v>164</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="3">
         <v>40000</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="3">
         <v>20000</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="3">
         <f>C2*G2</f>
         <v>20000</v>
       </c>
-      <c r="E2" s="32">
-        <f>B2-C2</f>
+      <c r="E2" s="37">
+        <f t="shared" ref="E2:E17" si="0">B2-C2</f>
         <v>20000</v>
       </c>
-      <c r="F2" s="33">
+      <c r="F2" s="3">
         <f>E2*G2</f>
         <v>20000</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
-      <c r="H2" s="34">
+      <c r="H2" s="37">
         <f>G2*B2</f>
         <v>40000</v>
       </c>
       <c r="J2" t="s">
         <v>378</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="3">
         <v>100</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2" s="3">
         <v>4</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="N2" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="O2" s="3" t="s">
         <v>380</v>
       </c>
       <c r="P2" t="s">
         <v>381</v>
       </c>
-      <c r="Q2" s="4">
+      <c r="Q2">
         <f>1000*10*0.48</f>
         <v>4800</v>
       </c>
     </row>
     <row r="3" spans="1:17">
-      <c r="A3" s="2" t="s">
+      <c r="A3" t="s">
         <v>169</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="3">
         <v>40000</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="3">
         <v>20000</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="3">
         <f>C3*G3</f>
         <v>20000</v>
       </c>
-      <c r="E3" s="32">
-        <f>B3-C3</f>
+      <c r="E3" s="37">
+        <f t="shared" si="0"/>
         <v>20000</v>
       </c>
-      <c r="F3" s="33">
+      <c r="F3" s="3">
         <f>E3*G3</f>
         <v>20000</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
-      <c r="H3" s="34">
+      <c r="H3" s="37">
         <f>G3*B3</f>
         <v>40000</v>
       </c>
@@ -5140,121 +5208,121 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="2" t="s">
+      <c r="A4" t="s">
         <v>172</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="3">
         <v>2000</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="3">
         <v>1000</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="3">
         <f>C4*G4</f>
         <v>8400</v>
       </c>
-      <c r="E4" s="32">
-        <f>B4-C4</f>
+      <c r="E4" s="37">
+        <f t="shared" si="0"/>
         <v>1000</v>
       </c>
-      <c r="F4" s="33">
+      <c r="F4" s="3">
         <f>E4*G4</f>
         <v>8400</v>
       </c>
       <c r="G4">
         <v>8.4</v>
       </c>
-      <c r="H4" s="34">
+      <c r="H4" s="37">
         <f>G4*B4</f>
         <v>16800</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="2" t="s">
+      <c r="A5" t="s">
         <v>176</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="3">
         <v>1000</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="3">
         <v>500</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="3">
         <f>C5*G5</f>
         <v>2800</v>
       </c>
-      <c r="E5" s="32">
-        <f>B5-C5</f>
+      <c r="E5" s="37">
+        <f t="shared" si="0"/>
         <v>500</v>
       </c>
-      <c r="F5" s="33">
+      <c r="F5" s="3">
         <f>E5*G5</f>
         <v>2800</v>
       </c>
       <c r="G5">
         <v>5.6</v>
       </c>
-      <c r="H5" s="34">
+      <c r="H5" s="37">
         <f>G5*B5</f>
         <v>5600</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="2" t="s">
+      <c r="A6" t="s">
         <v>184</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="3">
         <v>1000</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="3">
         <v>500</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="3">
         <f>C6*G6</f>
         <v>5800</v>
       </c>
-      <c r="E6" s="32">
-        <f>B6-C6</f>
+      <c r="E6" s="37">
+        <f t="shared" si="0"/>
         <v>500</v>
       </c>
-      <c r="F6" s="33">
+      <c r="F6" s="3">
         <f>E6*G6</f>
         <v>5800</v>
       </c>
       <c r="G6">
         <v>11.6</v>
       </c>
-      <c r="H6" s="34">
+      <c r="H6" s="37">
         <f>G6*B6</f>
         <v>11600</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="2" t="s">
+      <c r="A7" t="s">
         <v>207</v>
       </c>
-      <c r="B7" s="35">
+      <c r="B7" s="4">
         <v>1.2</v>
       </c>
-      <c r="C7" s="35">
+      <c r="C7" s="4">
         <v>1</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="3">
         <f>C7*G7*100</f>
         <v>14000</v>
       </c>
-      <c r="E7" s="36">
-        <f>B7-C7</f>
+      <c r="E7" s="4">
+        <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
-      <c r="F7" s="33">
+      <c r="F7" s="3">
         <f>E7*G7*100</f>
         <v>2800</v>
       </c>
       <c r="G7">
         <v>140</v>
       </c>
-      <c r="H7" s="34">
+      <c r="H7" s="37">
         <f>G7*B7*100</f>
         <v>16800</v>
       </c>
@@ -5263,118 +5331,118 @@
       <c r="A8" t="s">
         <v>384</v>
       </c>
-      <c r="B8" s="35">
+      <c r="B8" s="4">
         <v>0.2</v>
       </c>
-      <c r="C8" s="35">
+      <c r="C8" s="4">
         <v>0</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="3">
         <f>C8*G8*100</f>
         <v>0</v>
       </c>
-      <c r="E8" s="36">
-        <f>B8-C8</f>
+      <c r="E8" s="4">
+        <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
-      <c r="F8" s="33">
+      <c r="F8" s="3">
         <f>E8*G8*100</f>
         <v>2800</v>
       </c>
       <c r="G8">
         <v>140</v>
       </c>
-      <c r="H8" s="34">
+      <c r="H8" s="37">
         <f>G8*B8*100</f>
         <v>2800</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="2" t="s">
+      <c r="A9" t="s">
         <v>198</v>
       </c>
-      <c r="B9" s="35">
+      <c r="B9" s="4">
         <v>0.2</v>
       </c>
-      <c r="C9" s="35">
+      <c r="C9" s="4">
         <v>0</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="3">
         <f>C9*G9*100</f>
         <v>0</v>
       </c>
-      <c r="E9" s="36">
-        <f>B9-C9</f>
+      <c r="E9" s="4">
+        <f t="shared" si="0"/>
         <v>0.2</v>
       </c>
-      <c r="F9" s="33">
+      <c r="F9" s="3">
         <f>E9*G9*100</f>
         <v>2800</v>
       </c>
       <c r="G9">
         <v>140</v>
       </c>
-      <c r="H9" s="34">
+      <c r="H9" s="37">
         <f>G9*B9*100</f>
         <v>2800</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="2" t="s">
+      <c r="A10" t="s">
         <v>203</v>
       </c>
-      <c r="B10" s="35">
+      <c r="B10" s="4">
         <v>1</v>
       </c>
-      <c r="C10" s="35">
+      <c r="C10" s="4">
         <v>0.5</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="3">
         <f>C10*G10*100</f>
         <v>1400</v>
       </c>
-      <c r="E10" s="36">
-        <f>B10-C10</f>
+      <c r="E10" s="4">
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
-      <c r="F10" s="33">
+      <c r="F10" s="3">
         <f>E10*G10*100</f>
         <v>1400</v>
       </c>
       <c r="G10">
         <v>28</v>
       </c>
-      <c r="H10" s="34">
+      <c r="H10" s="37">
         <f>G10*B10*100</f>
         <v>2800</v>
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="2" t="s">
+      <c r="A11" t="s">
         <v>191</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="3">
         <v>100</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="3">
         <v>100</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="3">
         <f>C11*G11</f>
         <v>40000</v>
       </c>
-      <c r="E11" s="32">
-        <f>B11-C11</f>
+      <c r="E11" s="37">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F11" s="33">
-        <f>E11*G11</f>
+      <c r="F11" s="3">
+        <f t="shared" ref="F11:F17" si="1">E11*G11</f>
         <v>0</v>
       </c>
       <c r="G11">
         <v>400</v>
       </c>
-      <c r="H11" s="34">
+      <c r="H11" s="37">
         <f>G11*B11</f>
         <v>40000</v>
       </c>
@@ -5383,28 +5451,28 @@
       <c r="A12" t="s">
         <v>385</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="3">
         <v>4</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="3">
         <v>4</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="3">
         <f>C12*G12</f>
         <v>4500</v>
       </c>
-      <c r="E12" s="32">
-        <f>B12-C12</f>
+      <c r="E12" s="37">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F12" s="33">
-        <f>E12*G12</f>
+      <c r="F12" s="3">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G12">
         <v>1125</v>
       </c>
-      <c r="H12" s="34">
+      <c r="H12" s="37">
         <f>G12*B12</f>
         <v>4500</v>
       </c>
@@ -5413,28 +5481,28 @@
       <c r="A13" t="s">
         <v>386</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13" s="3">
         <v>1</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13" s="3">
         <v>0</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="3">
         <f>C13*G13</f>
         <v>0</v>
       </c>
-      <c r="E13" s="32">
-        <f>B13-C13</f>
+      <c r="E13" s="37">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F13" s="33">
-        <f>E13*G13</f>
+      <c r="F13" s="3">
+        <f t="shared" si="1"/>
         <v>4800</v>
       </c>
       <c r="G13">
         <v>4800</v>
       </c>
-      <c r="H13" s="34">
+      <c r="H13" s="37">
         <f>G13*B13</f>
         <v>4800</v>
       </c>
@@ -5443,133 +5511,133 @@
       <c r="A14" t="s">
         <v>387</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="3">
         <v>10</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="3">
         <v>10</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="3">
         <f>C14*G14</f>
         <v>23260</v>
       </c>
-      <c r="E14" s="32">
-        <f>B14-C14</f>
+      <c r="E14" s="37">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F14" s="33">
-        <f>E14*G14</f>
+      <c r="F14" s="3">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G14">
         <v>2326</v>
       </c>
-      <c r="H14" s="34">
+      <c r="H14" s="37">
         <f>G14*B14</f>
         <v>23260</v>
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="2" t="s">
+      <c r="A15" t="s">
         <v>211</v>
       </c>
-      <c r="B15" s="35">
+      <c r="B15" s="4">
         <v>1</v>
       </c>
-      <c r="C15" s="35">
+      <c r="C15" s="4">
         <v>1</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="3">
         <f>C15*G15*100</f>
         <v>16800</v>
       </c>
-      <c r="E15" s="32">
-        <f>B15-C15</f>
+      <c r="E15" s="37">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F15" s="33">
-        <f>E15*G15</f>
+      <c r="F15" s="3">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G15">
         <v>168</v>
       </c>
-      <c r="H15" s="34">
+      <c r="H15" s="37">
         <f>G15*B15*100</f>
         <v>16800</v>
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="2" t="s">
+      <c r="A16" t="s">
         <v>215</v>
       </c>
-      <c r="B16" s="35">
+      <c r="B16" s="4">
         <v>0</v>
       </c>
-      <c r="C16" s="35">
+      <c r="C16" s="4">
         <v>0</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="3">
         <f>C16*G16*100</f>
         <v>0</v>
       </c>
-      <c r="E16" s="32">
-        <f>B16-C16</f>
+      <c r="E16" s="37">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F16" s="33">
-        <f>E16*G16</f>
+      <c r="F16" s="3">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G16">
         <v>168</v>
       </c>
-      <c r="H16" s="34">
+      <c r="H16" s="37">
         <f>G16*B16</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="2" t="s">
+      <c r="A17" t="s">
         <v>219</v>
       </c>
-      <c r="B17" s="35">
+      <c r="B17" s="4">
         <v>0</v>
       </c>
-      <c r="C17" s="35"/>
-      <c r="D17" s="5">
+      <c r="C17" s="4"/>
+      <c r="D17" s="3">
         <f>C17*G17*100</f>
         <v>0</v>
       </c>
-      <c r="E17" s="32">
-        <f>B17-C17</f>
+      <c r="E17" s="37">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F17" s="33">
-        <f>E17*G17</f>
+      <c r="F17" s="3">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G17">
         <v>233</v>
       </c>
-      <c r="H17" s="34">
+      <c r="H17" s="37">
         <f>G17*B17</f>
         <v>0</v>
       </c>
     </row>
-    <row r="18" s="3" customFormat="1" spans="1:8">
-      <c r="A18" s="3" t="s">
+    <row r="18" s="2" customFormat="1" spans="1:8">
+      <c r="A18" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="D18" s="37">
+      <c r="D18" s="36">
         <f>SUM(D2:D17)</f>
         <v>156960</v>
       </c>
-      <c r="F18" s="37">
+      <c r="F18" s="36">
         <f>SUM(F2:F17)</f>
         <v>71600</v>
       </c>
-      <c r="H18" s="37">
+      <c r="H18" s="36">
         <f>SUM(H2:H17)</f>
         <v>228560</v>
       </c>
@@ -5578,7 +5646,7 @@
       <c r="A19" t="s">
         <v>389</v>
       </c>
-      <c r="F19" s="34">
+      <c r="F19" s="37">
         <f>F18/4</f>
         <v>17900</v>
       </c>
@@ -5588,219 +5656,183 @@
         <v>390</v>
       </c>
     </row>
-    <row r="24" ht="23.25" spans="1:1">
-      <c r="A24" s="38" t="s">
+    <row r="24" customFormat="1" ht="23.25" customHeight="1" spans="1:1">
+      <c r="A24" s="61" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="39"/>
-    </row>
-    <row r="26" ht="18.75" spans="1:1">
-      <c r="A26" s="40" t="s">
+    <row r="26" customFormat="1" ht="18.75" customHeight="1" spans="1:1">
+      <c r="A26" s="62" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="39"/>
-    </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="41" t="s">
+      <c r="A28" s="28" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="42" t="s">
+      <c r="A29" s="63" t="s">
         <v>394</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="42" t="s">
+      <c r="A30" s="63" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="42" t="s">
+      <c r="A31" s="63" t="s">
         <v>396</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="42" t="s">
+      <c r="A32" s="63" t="s">
         <v>397</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="42" t="s">
+      <c r="A33" s="63" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="42" t="s">
+      <c r="A34" s="63" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="42" t="s">
+      <c r="A35" s="63" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="42" t="s">
+      <c r="A36" s="63" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="42" t="s">
+      <c r="A37" s="63" t="s">
         <v>402</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="42" t="s">
+      <c r="A38" s="63" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="39"/>
-    </row>
-    <row r="40" ht="18.75" spans="1:1">
-      <c r="A40" s="40" t="s">
+    <row r="40" customFormat="1" ht="18.75" customHeight="1" spans="1:1">
+      <c r="A40" s="62" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="43" t="s">
+      <c r="A41" s="2" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="39" t="s">
+      <c r="A42" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="39"/>
-    </row>
     <row r="44" spans="1:1">
-      <c r="A44" s="43" t="s">
+      <c r="A44" s="2" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="39" t="s">
+      <c r="A45" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
-      <c r="A46" s="39"/>
-    </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="43" t="s">
+      <c r="A47" s="2" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" s="39" t="s">
+      <c r="A48" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="49" spans="1:1">
-      <c r="A49" s="39"/>
-    </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="43" t="s">
+      <c r="A50" s="2" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="39" t="s">
+      <c r="A51" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="52" spans="1:1">
-      <c r="A52" s="39"/>
-    </row>
     <row r="53" spans="1:1">
-      <c r="A53" s="43" t="s">
+      <c r="A53" s="2" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" s="39" t="s">
+      <c r="A54" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="55" spans="1:1">
-      <c r="A55" s="39"/>
-    </row>
     <row r="56" spans="1:1">
-      <c r="A56" s="43" t="s">
+      <c r="A56" s="2" t="s">
         <v>415</v>
       </c>
     </row>
     <row r="57" spans="1:1">
-      <c r="A57" s="39" t="s">
+      <c r="A57" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="58" spans="1:1">
-      <c r="A58" s="39"/>
-    </row>
     <row r="59" spans="1:1">
-      <c r="A59" s="39" t="s">
+      <c r="A59" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="60" spans="1:1">
-      <c r="A60" s="39"/>
-    </row>
-    <row r="61" ht="18.75" spans="1:1">
-      <c r="A61" s="40" t="s">
+    <row r="61" customFormat="1" ht="18.75" customHeight="1" spans="1:1">
+      <c r="A61" s="62" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="62" spans="1:1">
-      <c r="A62" s="39"/>
-    </row>
     <row r="63" spans="1:1">
-      <c r="A63" s="43" t="s">
+      <c r="A63" s="2" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="64" spans="1:1">
-      <c r="A64" s="39" t="s">
+      <c r="A64" t="s">
         <v>420</v>
       </c>
     </row>
     <row r="65" spans="1:1">
-      <c r="A65" s="39" t="s">
+      <c r="A65" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="66" spans="1:1">
-      <c r="A66" s="39"/>
-    </row>
     <row r="67" spans="1:1">
-      <c r="A67" s="43" t="s">
+      <c r="A67" s="2" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="68" spans="1:1">
-      <c r="A68" s="39" t="s">
+      <c r="A68" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="69" spans="1:1">
-      <c r="A69" s="39" t="s">
+      <c r="A69" t="s">
         <v>424</v>
       </c>
     </row>
     <row r="70" spans="1:1">
-      <c r="A70" s="39" t="s">
+      <c r="A70" t="s">
         <v>425</v>
       </c>
     </row>
     <row r="71" spans="1:1">
-      <c r="A71" s="39" t="s">
+      <c r="A71" t="s">
         <v>426</v>
       </c>
     </row>
@@ -5810,234 +5842,234 @@
       </c>
     </row>
     <row r="75" spans="1:3">
-      <c r="A75" s="44" t="s">
+      <c r="A75" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B75" s="44" t="s">
+      <c r="B75" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="C75" s="44" t="s">
+      <c r="C75" s="1" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="76" spans="1:3">
-      <c r="A76" s="43" t="s">
+      <c r="A76" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="B76" s="39" t="s">
+      <c r="B76" t="s">
         <v>430</v>
       </c>
-      <c r="C76" s="43" t="s">
+      <c r="C76" s="2" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="77" spans="1:3">
-      <c r="A77" s="43" t="s">
+      <c r="A77" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="B77" s="39" t="s">
+      <c r="B77" t="s">
         <v>432</v>
       </c>
-      <c r="C77" s="43" t="s">
+      <c r="C77" s="2" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="78" spans="1:3">
-      <c r="A78" s="43" t="s">
+      <c r="A78" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B78" s="39" t="s">
+      <c r="B78" t="s">
         <v>433</v>
       </c>
-      <c r="C78" s="43" t="s">
+      <c r="C78" s="2" t="s">
         <v>434</v>
       </c>
     </row>
     <row r="79" spans="1:3">
-      <c r="A79" s="43" t="s">
+      <c r="A79" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="B79" s="39" t="s">
+      <c r="B79" t="s">
         <v>435</v>
       </c>
-      <c r="C79" s="43" t="s">
+      <c r="C79" s="2" t="s">
         <v>436</v>
       </c>
     </row>
     <row r="80" spans="1:3">
-      <c r="A80" s="43" t="s">
+      <c r="A80" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="B80" s="39" t="s">
+      <c r="B80" t="s">
         <v>437</v>
       </c>
-      <c r="C80" s="43" t="s">
+      <c r="C80" s="2" t="s">
         <v>438</v>
       </c>
     </row>
     <row r="81" spans="1:3">
-      <c r="A81" s="43" t="s">
+      <c r="A81" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="B81" s="39" t="s">
+      <c r="B81" t="s">
         <v>439</v>
       </c>
-      <c r="C81" s="43" t="s">
+      <c r="C81" s="2" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="82" spans="1:3">
-      <c r="A82" s="43" t="s">
+      <c r="A82" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="B82" s="39" t="s">
+      <c r="B82" t="s">
         <v>441</v>
       </c>
-      <c r="C82" s="43" t="s">
+      <c r="C82" s="2" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="83" spans="1:3">
-      <c r="A83" s="43" t="s">
+      <c r="A83" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="B83" s="39" t="s">
+      <c r="B83" t="s">
         <v>442</v>
       </c>
-      <c r="C83" s="43" t="s">
+      <c r="C83" s="2" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="84" spans="1:3">
-      <c r="A84" s="43" t="s">
+      <c r="A84" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="B84" s="39" t="s">
+      <c r="B84" t="s">
         <v>443</v>
       </c>
-      <c r="C84" s="43" t="s">
+      <c r="C84" s="2" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="85" spans="1:3">
-      <c r="A85" s="43" t="s">
+      <c r="A85" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="B85" s="39" t="s">
+      <c r="B85" t="s">
         <v>445</v>
       </c>
-      <c r="C85" s="43" t="s">
+      <c r="C85" s="2" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="86" spans="1:3">
-      <c r="A86" s="43" t="s">
+      <c r="A86" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="B86" s="39" t="s">
+      <c r="B86" t="s">
         <v>447</v>
       </c>
-      <c r="C86" s="43" t="s">
+      <c r="C86" s="2" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="87" spans="1:3">
-      <c r="A87" s="43" t="s">
+      <c r="A87" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="B87" s="39" t="s">
+      <c r="B87" t="s">
         <v>450</v>
       </c>
-      <c r="C87" s="43" t="s">
+      <c r="C87" s="2" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="88" spans="1:3">
-      <c r="A88" s="43" t="s">
+      <c r="A88" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="B88" s="39" t="s">
+      <c r="B88" t="s">
         <v>452</v>
       </c>
-      <c r="C88" s="43" t="s">
+      <c r="C88" s="2" t="s">
         <v>453</v>
       </c>
     </row>
     <row r="89" spans="1:3">
-      <c r="A89" s="43" t="s">
+      <c r="A89" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="B89" s="39" t="s">
+      <c r="B89" t="s">
         <v>454</v>
       </c>
-      <c r="C89" s="43" t="s">
+      <c r="C89" s="2" t="s">
         <v>455</v>
       </c>
     </row>
     <row r="90" spans="1:3">
-      <c r="A90" s="43" t="s">
+      <c r="A90" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="B90" s="39" t="s">
+      <c r="B90" t="s">
         <v>456</v>
       </c>
-      <c r="C90" s="43" t="s">
+      <c r="C90" s="2" t="s">
         <v>455</v>
       </c>
     </row>
     <row r="91" spans="1:3">
-      <c r="A91" s="43" t="s">
+      <c r="A91" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="B91" s="39" t="s">
+      <c r="B91" t="s">
         <v>457</v>
       </c>
-      <c r="C91" s="43" t="s">
+      <c r="C91" s="2" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="93" ht="18.75" spans="1:1">
-      <c r="A93" s="45" t="s">
+    <row r="93" customFormat="1" ht="18.75" customHeight="1" spans="1:1">
+      <c r="A93" s="62" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="95" spans="1:1">
-      <c r="A95" s="46" t="s">
+      <c r="A95" s="2" t="s">
         <v>460</v>
       </c>
     </row>
     <row r="97" spans="1:1">
-      <c r="A97" s="47" t="s">
+      <c r="A97" s="63" t="s">
         <v>461</v>
       </c>
     </row>
     <row r="98" spans="1:1">
-      <c r="A98" s="47" t="s">
+      <c r="A98" s="63" t="s">
         <v>462</v>
       </c>
     </row>
     <row r="99" spans="1:1">
-      <c r="A99" s="47" t="s">
+      <c r="A99" s="63" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="100" spans="1:1">
-      <c r="A100" s="47" t="s">
+      <c r="A100" s="63" t="s">
         <v>464</v>
       </c>
     </row>
     <row r="101" spans="1:1">
-      <c r="A101" s="47" t="s">
+      <c r="A101" s="63" t="s">
         <v>465</v>
       </c>
     </row>
     <row r="102" spans="1:1">
-      <c r="A102" s="47" t="s">
+      <c r="A102" s="63" t="s">
         <v>466</v>
       </c>
     </row>
     <row r="104" spans="1:1">
-      <c r="A104" s="46" t="s">
+      <c r="A104" s="2" t="s">
         <v>191</v>
       </c>
     </row>
@@ -6047,7 +6079,7 @@
       </c>
     </row>
     <row r="107" spans="1:1">
-      <c r="A107" s="46" t="s">
+      <c r="A107" s="2" t="s">
         <v>219</v>
       </c>
     </row>
@@ -6056,8 +6088,8 @@
         <v>468</v>
       </c>
     </row>
-    <row r="110" ht="18.75" spans="1:1">
-      <c r="A110" s="45" t="s">
+    <row r="110" customFormat="1" ht="18.75" customHeight="1" spans="1:1">
+      <c r="A110" s="62" t="s">
         <v>469</v>
       </c>
     </row>
@@ -6107,997 +6139,2102 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
-  <ignoredErrors>
-    <ignoredError sqref="H15" formula="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20.7142857142857" style="5" customWidth="1"/>
-    <col min="2" max="2" width="13.5714285714286" style="5" customWidth="1"/>
-    <col min="3" max="3" width="14.1428571428571" style="5" customWidth="1"/>
-    <col min="4" max="4" width="34.4285714285714" style="6" customWidth="1"/>
-    <col min="5" max="5" width="28.4285714285714" style="5" customWidth="1"/>
-    <col min="6" max="6" width="9.57142857142857" style="5"/>
-    <col min="7" max="7" width="9.14285714285714" style="5"/>
-    <col min="8" max="8" width="18" style="7" customWidth="1"/>
-    <col min="9" max="9" width="11.7142857142857" style="5"/>
+    <col min="1" max="1" width="22.5714285714286" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="24.5714285714286" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="34.7142857142857" customWidth="1"/>
+    <col min="6" max="6" width="17.7142857142857" customWidth="1"/>
+    <col min="7" max="7" width="18.7142857142857" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="9" max="9" width="20.2857142857143" customWidth="1"/>
+    <col min="10" max="10" width="18.8571428571429" customWidth="1"/>
+    <col min="11" max="11" width="18.7142857142857" style="26" customWidth="1"/>
+    <col min="12" max="12" width="11.4285714285714" customWidth="1"/>
+    <col min="13" max="13" width="11.5714285714286" customWidth="1"/>
+    <col min="14" max="14" width="23.7142857142857" customWidth="1"/>
+    <col min="15" max="15" width="12.1428571428571" customWidth="1"/>
+    <col min="16" max="16" width="17.2857142857143" customWidth="1"/>
+    <col min="17" max="17" width="12.1428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="3" customFormat="1" spans="1:9">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
         <v>479</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" t="s">
         <v>480</v>
       </c>
-      <c r="C1" s="9" t="s">
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
         <v>481</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="B2" t="s">
         <v>482</v>
       </c>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8" t="s">
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>483</v>
+      </c>
+      <c r="B3" s="27" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>485</v>
+      </c>
+      <c r="B4" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>487</v>
+      </c>
+      <c r="B5" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>488</v>
+      </c>
+      <c r="B6" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="28" t="s">
+        <v>366</v>
+      </c>
+      <c r="B8" s="29" t="s">
+        <v>367</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>368</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>489</v>
+      </c>
+      <c r="E8" s="30" t="s">
+        <v>370</v>
+      </c>
+      <c r="F8" s="28" t="s">
+        <v>371</v>
+      </c>
+      <c r="G8" s="28" t="s">
+        <v>372</v>
+      </c>
+      <c r="H8" s="28" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>164</v>
+      </c>
+      <c r="B9" s="31">
+        <f>SUM(C9,E9)</f>
+        <v>51750</v>
+      </c>
+      <c r="C9" s="31">
+        <v>29500</v>
+      </c>
+      <c r="D9" s="31">
+        <f>C9*G9</f>
+        <v>29500</v>
+      </c>
+      <c r="E9" s="32">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A9)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A9)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A9)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A9)</f>
+        <v>22250</v>
+      </c>
+      <c r="F9" s="31">
+        <f>E9*G9</f>
+        <v>22250</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9" s="32">
+        <f>B9*G9</f>
+        <v>51750</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>169</v>
+      </c>
+      <c r="B10" s="31">
+        <f t="shared" ref="B9:B24" si="0">SUM(C10,E10)</f>
+        <v>19450</v>
+      </c>
+      <c r="C10" s="31">
+        <v>10500</v>
+      </c>
+      <c r="D10" s="31">
+        <f>C10*G10</f>
+        <v>10500</v>
+      </c>
+      <c r="E10" s="32">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A10)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A10)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A10)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A10)</f>
+        <v>8950</v>
+      </c>
+      <c r="F10" s="31">
+        <f>E10*G10</f>
+        <v>8950</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10" s="32">
+        <f>B10*G10</f>
+        <v>19450</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>172</v>
+      </c>
+      <c r="B11" s="31">
+        <f t="shared" si="0"/>
+        <v>5357.14285714286</v>
+      </c>
+      <c r="C11" s="31">
+        <f>D11/G11</f>
+        <v>1190.47619047619</v>
+      </c>
+      <c r="D11" s="31">
+        <v>10000</v>
+      </c>
+      <c r="E11" s="33">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A11)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A11)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A11)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A11)</f>
+        <v>4166.66666666667</v>
+      </c>
+      <c r="F11" s="31">
+        <f>E11*G11</f>
+        <v>35000</v>
+      </c>
+      <c r="G11">
+        <v>8.4</v>
+      </c>
+      <c r="H11" s="32">
+        <f>B11*G11</f>
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>176</v>
+      </c>
+      <c r="B12" s="31">
+        <f t="shared" si="0"/>
+        <v>1857.14285714286</v>
+      </c>
+      <c r="C12" s="31">
+        <f>D12/G12</f>
+        <v>821.428571428571</v>
+      </c>
+      <c r="D12" s="31">
+        <v>4600</v>
+      </c>
+      <c r="E12" s="33">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A12)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A12)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A12)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A12)</f>
+        <v>1035.71428571429</v>
+      </c>
+      <c r="F12" s="31">
+        <f>E12*G12</f>
+        <v>5800</v>
+      </c>
+      <c r="G12">
+        <v>5.6</v>
+      </c>
+      <c r="H12" s="32">
+        <f>B12*G12</f>
+        <v>10400</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>184</v>
+      </c>
+      <c r="B13" s="31">
+        <f t="shared" si="0"/>
+        <v>1086.20689655172</v>
+      </c>
+      <c r="C13" s="31">
+        <f>D13/G13</f>
+        <v>327.586206896552</v>
+      </c>
+      <c r="D13" s="31">
+        <v>3800</v>
+      </c>
+      <c r="E13" s="33">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A13)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A13)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A13)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A13)</f>
+        <v>758.620689655172</v>
+      </c>
+      <c r="F13" s="31">
+        <f>E13*G13</f>
+        <v>8800</v>
+      </c>
+      <c r="G13">
+        <v>11.6</v>
+      </c>
+      <c r="H13" s="32">
+        <f>B13*G13</f>
+        <v>12600</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>207</v>
+      </c>
+      <c r="B14" s="34">
+        <f>SUM(C14,E14)</f>
+        <v>1.2</v>
+      </c>
+      <c r="C14" s="34">
+        <v>1</v>
+      </c>
+      <c r="D14" s="31">
+        <f>C14*G14*100</f>
+        <v>14000</v>
+      </c>
+      <c r="E14" s="35">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A14)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A14)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A14)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A14)</f>
+        <v>0.2</v>
+      </c>
+      <c r="F14" s="31">
+        <f>E14*G14*100</f>
+        <v>2800</v>
+      </c>
+      <c r="G14">
+        <v>140</v>
+      </c>
+      <c r="H14" s="32">
+        <f>B14*G14*100</f>
+        <v>16800</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>384</v>
+      </c>
+      <c r="B15" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C15" s="34">
+        <v>0</v>
+      </c>
+      <c r="D15" s="31">
+        <f>C15*G15*100</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="35">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A15)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A15)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A15)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A15)</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="31">
+        <f>E15*G15*100</f>
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>140</v>
+      </c>
+      <c r="H15" s="32">
+        <f>B15*G15*100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>198</v>
+      </c>
+      <c r="B16" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C16" s="34">
+        <v>0</v>
+      </c>
+      <c r="D16" s="31">
+        <f>C16*G16*100</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="35">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A16)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A16)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A16)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A16)</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="31">
+        <f>E16*G16*100</f>
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>140</v>
+      </c>
+      <c r="H16" s="32">
+        <f>B16*G16*100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>203</v>
+      </c>
+      <c r="B17" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C17" s="34">
+        <v>0</v>
+      </c>
+      <c r="D17" s="31">
+        <f>C17*G17*100</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="35">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A17)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A17)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A17)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A17)</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="31">
+        <f>E17*G17*100</f>
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>28</v>
+      </c>
+      <c r="H17" s="32">
+        <f>B17*G17*100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>191</v>
+      </c>
+      <c r="B18" s="31">
+        <f>SUM(C18,E18)</f>
+        <v>70</v>
+      </c>
+      <c r="C18" s="31">
+        <v>100</v>
+      </c>
+      <c r="D18" s="31">
+        <f>C18*G18</f>
+        <v>40000</v>
+      </c>
+      <c r="E18" s="32">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A18)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A18)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A18)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A18)</f>
+        <v>-30</v>
+      </c>
+      <c r="F18" s="31">
+        <f>E18*G18</f>
+        <v>-12000</v>
+      </c>
+      <c r="G18">
+        <v>400</v>
+      </c>
+      <c r="H18" s="32">
+        <f>B18*G18</f>
+        <v>28000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
+        <v>361</v>
+      </c>
+      <c r="B19" s="31">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="C19" s="31">
+        <v>4</v>
+      </c>
+      <c r="D19" s="31">
+        <f>C19*G19</f>
+        <v>4500</v>
+      </c>
+      <c r="E19" s="32">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A19)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A19)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A19)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A19)</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="31">
+        <f>E19*G19</f>
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>1125</v>
+      </c>
+      <c r="H19" s="32">
+        <f>B19*G19</f>
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>386</v>
+      </c>
+      <c r="B20" s="31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C20" s="31">
+        <v>0</v>
+      </c>
+      <c r="D20" s="31">
+        <f>C20*G20</f>
+        <v>0</v>
+      </c>
+      <c r="E20" s="32">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A20)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A20)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A20)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A20)</f>
+        <v>0</v>
+      </c>
+      <c r="F20" s="31">
+        <f>E20*G20</f>
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>4800</v>
+      </c>
+      <c r="H20" s="32">
+        <f>B20*G20</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" t="s">
+        <v>387</v>
+      </c>
+      <c r="B21" s="31">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="C21" s="31">
+        <v>10</v>
+      </c>
+      <c r="D21" s="31">
+        <f>C21*G21</f>
+        <v>23260</v>
+      </c>
+      <c r="E21" s="32">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A21)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A21)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A21)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A21)</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="31">
+        <f>E21*G21</f>
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>2326</v>
+      </c>
+      <c r="H21" s="32">
+        <f>B21*G21</f>
+        <v>23260</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" t="s">
+        <v>211</v>
+      </c>
+      <c r="B22" s="34">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="C22" s="34">
+        <v>1</v>
+      </c>
+      <c r="D22" s="31">
+        <f>C22*G22*100</f>
+        <v>16800</v>
+      </c>
+      <c r="E22" s="35">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A22)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A22)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A22)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A22)</f>
+        <v>0</v>
+      </c>
+      <c r="F22" s="31">
+        <f>E22*G22*100</f>
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>168</v>
+      </c>
+      <c r="H22" s="32">
+        <f>B22*G22*100</f>
+        <v>16800</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>215</v>
+      </c>
+      <c r="B23" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C23" s="34">
+        <v>0</v>
+      </c>
+      <c r="D23" s="31">
+        <f>C23*G23*100</f>
+        <v>0</v>
+      </c>
+      <c r="E23" s="35">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A23)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A23)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A23)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A23)</f>
+        <v>0</v>
+      </c>
+      <c r="F23" s="31">
+        <f>E23*G23*100</f>
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>168</v>
+      </c>
+      <c r="H23" s="32">
+        <f>B23*G23*100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>219</v>
+      </c>
+      <c r="B24" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C24" s="34">
+        <v>0</v>
+      </c>
+      <c r="D24" s="31">
+        <f>C24*G24*100</f>
+        <v>0</v>
+      </c>
+      <c r="E24" s="35">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A24)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A24)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A24)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A24)</f>
+        <v>0</v>
+      </c>
+      <c r="F24" s="31">
+        <f>E24*G24*100</f>
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>233</v>
+      </c>
+      <c r="H24" s="32">
+        <f>B24*G24*100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="36">
+        <f>SUM(D9:D24)</f>
+        <v>156960</v>
+      </c>
+      <c r="E25" s="37"/>
+      <c r="F25" s="36">
+        <f>SUM(F9:F24)</f>
+        <v>71600</v>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="H25" s="36">
+        <f>SUM(H9:H24)</f>
+        <v>228560</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" t="s">
+        <v>490</v>
+      </c>
+      <c r="D26" s="37">
+        <f>'Balanced Dummy '!D18-D25</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="37"/>
+      <c r="F26" s="37"/>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="38" t="s">
+        <v>374</v>
+      </c>
+      <c r="B28" s="39" t="s">
+        <v>82</v>
+      </c>
+      <c r="C28" s="39" t="s">
+        <v>375</v>
+      </c>
+      <c r="D28" s="39" t="s">
+        <v>376</v>
+      </c>
+      <c r="E28" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="F28" s="38" t="s">
+        <v>491</v>
+      </c>
+      <c r="G28" s="38" t="s">
+        <v>492</v>
+      </c>
+      <c r="H28" s="38" t="s">
+        <v>111</v>
+      </c>
+      <c r="I28" s="39" t="s">
         <v>278</v>
       </c>
-      <c r="G1" s="8" t="s">
-        <v>483</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>484</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>485</v>
+      <c r="J28" s="38" t="s">
+        <v>493</v>
+      </c>
+      <c r="K28" s="56" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="38" t="s">
+        <v>495</v>
+      </c>
+      <c r="B29" s="40">
+        <v>150</v>
+      </c>
+      <c r="C29" s="41">
+        <f>B29*1000/50</f>
+        <v>3000</v>
+      </c>
+      <c r="D29" s="41">
+        <v>6</v>
+      </c>
+      <c r="E29" s="39" t="s">
+        <v>496</v>
+      </c>
+      <c r="F29" s="38" t="s">
+        <v>497</v>
+      </c>
+      <c r="G29" s="38" t="s">
+        <v>498</v>
+      </c>
+      <c r="H29" s="42">
+        <v>4</v>
+      </c>
+      <c r="I29" s="39" t="s">
+        <v>499</v>
+      </c>
+      <c r="J29" s="38" t="s">
+        <v>500</v>
+      </c>
+      <c r="K29" s="56">
+        <f>4.8*1000*2%*5</f>
+        <v>480</v>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1" spans="1:11">
+      <c r="A30" s="38"/>
+      <c r="B30" s="43"/>
+      <c r="C30" s="41"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="39"/>
+      <c r="F30" s="38"/>
+      <c r="G30" s="38"/>
+      <c r="H30" s="42"/>
+      <c r="I30" s="38" t="s">
+        <v>501</v>
+      </c>
+      <c r="J30" s="38" t="s">
+        <v>500</v>
+      </c>
+      <c r="K30" s="56">
+        <f>4.8*1000*2%*5</f>
+        <v>480</v>
+      </c>
+    </row>
+    <row r="31" ht="45" spans="1:11">
+      <c r="A31" s="44" t="s">
+        <v>502</v>
+      </c>
+      <c r="B31" s="44">
+        <v>300</v>
+      </c>
+      <c r="C31" s="45">
+        <f>B31*1000/50</f>
+        <v>6000</v>
+      </c>
+      <c r="D31" s="46">
+        <v>4</v>
+      </c>
+      <c r="E31" s="44" t="s">
+        <v>503</v>
+      </c>
+      <c r="F31" s="44" t="s">
+        <v>497</v>
+      </c>
+      <c r="G31" s="44" t="s">
+        <v>504</v>
+      </c>
+      <c r="H31" s="46"/>
+      <c r="I31" s="44" t="s">
+        <v>505</v>
+      </c>
+      <c r="J31" s="44" t="s">
+        <v>506</v>
+      </c>
+      <c r="K31" s="57">
+        <f>4.8*1000*70%*5</f>
+        <v>16800</v>
+      </c>
+    </row>
+    <row r="32" ht="30" spans="1:11">
+      <c r="A32" s="47" t="s">
+        <v>507</v>
+      </c>
+      <c r="B32" s="47" t="s">
+        <v>508</v>
+      </c>
+      <c r="C32" s="48">
+        <v>800</v>
+      </c>
+      <c r="D32" s="49">
+        <v>0</v>
+      </c>
+      <c r="E32" s="47" t="s">
+        <v>509</v>
+      </c>
+      <c r="F32" s="47" t="s">
+        <v>510</v>
+      </c>
+      <c r="G32" s="47" t="s">
+        <v>504</v>
+      </c>
+      <c r="H32" s="49">
+        <v>2</v>
+      </c>
+      <c r="I32" s="47" t="s">
+        <v>511</v>
+      </c>
+      <c r="J32" s="47" t="s">
+        <v>512</v>
+      </c>
+      <c r="K32" s="58">
+        <f>10%*5</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" s="47"/>
+      <c r="B33" s="47"/>
+      <c r="C33" s="48"/>
+      <c r="D33" s="49"/>
+      <c r="E33" s="47"/>
+      <c r="F33" s="47"/>
+      <c r="G33" s="47"/>
+      <c r="H33" s="49"/>
+      <c r="I33" s="47" t="s">
+        <v>513</v>
+      </c>
+      <c r="J33" s="47" t="s">
+        <v>514</v>
+      </c>
+      <c r="K33" s="59">
+        <f>6%*5</f>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="34" ht="43" customHeight="1" spans="1:11">
+      <c r="A34" s="47"/>
+      <c r="B34" s="47"/>
+      <c r="C34" s="48"/>
+      <c r="D34" s="49"/>
+      <c r="E34" s="47"/>
+      <c r="F34" s="47"/>
+      <c r="G34" s="47"/>
+      <c r="H34" s="49"/>
+      <c r="I34" s="47" t="s">
+        <v>515</v>
+      </c>
+      <c r="J34" s="47" t="s">
+        <v>516</v>
+      </c>
+      <c r="K34" s="59">
+        <f>3%*5</f>
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="36" ht="45" spans="1:8">
+      <c r="A36" s="50" t="s">
+        <v>517</v>
+      </c>
+      <c r="B36" s="50" t="s">
+        <v>518</v>
+      </c>
+      <c r="C36" s="50" t="s">
+        <v>519</v>
+      </c>
+      <c r="D36" s="50" t="s">
+        <v>520</v>
+      </c>
+      <c r="E36" s="51" t="s">
+        <v>521</v>
+      </c>
+      <c r="F36" s="51" t="s">
+        <v>522</v>
+      </c>
+      <c r="G36" s="51" t="s">
+        <v>523</v>
+      </c>
+      <c r="H36" s="51" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="37" ht="60" spans="1:8">
+      <c r="A37" s="50"/>
+      <c r="B37" s="50"/>
+      <c r="C37" s="50"/>
+      <c r="D37" s="50"/>
+      <c r="E37" s="51" t="s">
+        <v>525</v>
+      </c>
+      <c r="F37" s="51" t="s">
+        <v>526</v>
+      </c>
+      <c r="G37" s="51" t="s">
+        <v>527</v>
+      </c>
+      <c r="H37" s="51" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="52"/>
+      <c r="B38" s="52"/>
+      <c r="C38" s="52"/>
+      <c r="D38" s="52"/>
+      <c r="E38" s="53"/>
+      <c r="F38" s="53"/>
+      <c r="G38" s="53"/>
+      <c r="H38" s="53"/>
+    </row>
+    <row r="39" ht="60" spans="1:10">
+      <c r="A39" s="54" t="s">
+        <v>529</v>
+      </c>
+      <c r="B39" s="54" t="s">
+        <v>530</v>
+      </c>
+      <c r="C39" s="54" t="s">
+        <v>531</v>
+      </c>
+      <c r="D39" s="54" t="s">
+        <v>532</v>
+      </c>
+      <c r="E39" s="51" t="s">
+        <v>533</v>
+      </c>
+      <c r="F39" s="51" t="s">
+        <v>534</v>
+      </c>
+      <c r="G39" s="51" t="s">
+        <v>535</v>
+      </c>
+      <c r="H39" s="51" t="s">
+        <v>536</v>
+      </c>
+      <c r="I39" s="60"/>
+      <c r="J39" s="60"/>
+    </row>
+    <row r="40" ht="60" spans="1:10">
+      <c r="A40" s="55"/>
+      <c r="B40" s="55"/>
+      <c r="C40" s="55"/>
+      <c r="D40" s="55"/>
+      <c r="E40" s="51" t="s">
+        <v>537</v>
+      </c>
+      <c r="F40" s="51" t="s">
+        <v>538</v>
+      </c>
+      <c r="G40" s="50" t="s">
+        <v>539</v>
+      </c>
+      <c r="H40" s="51" t="s">
+        <v>540</v>
+      </c>
+      <c r="I40" s="60"/>
+      <c r="J40" s="60"/>
+    </row>
+  </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="B32:B34"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="D32:D34"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="E32:E34"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="F32:F34"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="G32:G34"/>
+    <mergeCell ref="H29:H30"/>
+    <mergeCell ref="H32:H34"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I52"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7142857142857" style="3" customWidth="1"/>
+    <col min="2" max="2" width="13.5714285714286" style="3" customWidth="1"/>
+    <col min="3" max="3" width="14.1428571428571" style="3" customWidth="1"/>
+    <col min="4" max="4" width="34.4285714285714" style="4" customWidth="1"/>
+    <col min="5" max="5" width="27" style="3" customWidth="1"/>
+    <col min="6" max="6" width="12.1428571428571" style="3" customWidth="1"/>
+    <col min="7" max="7" width="9.14285714285714" style="3" customWidth="1"/>
+    <col min="8" max="8" width="18" style="5" customWidth="1"/>
+    <col min="9" max="9" width="11.7142857142857" style="3" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="2" customFormat="1" spans="1:9">
+      <c r="A1" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>542</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>544</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>546</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>548</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="12" t="s">
-        <v>486</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>487</v>
-      </c>
-      <c r="C2" s="13" t="s">
-        <v>488</v>
-      </c>
-      <c r="D2" s="14">
+      <c r="A2" s="10" t="s">
+        <v>549</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>497</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>504</v>
+      </c>
+      <c r="D2" s="12">
         <v>0</v>
       </c>
-      <c r="E2" s="15" t="s">
-        <v>489</v>
-      </c>
-      <c r="F2" s="15">
-        <f>(17900-SUM(I3:I4))/H2</f>
+      <c r="E2" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="F2" s="13">
+        <f>I2/H2</f>
         <v>1975.71428571429</v>
       </c>
-      <c r="G2" s="16">
+      <c r="G2" s="14">
         <f>F2/1000</f>
         <v>1.97571428571429</v>
       </c>
-      <c r="H2" s="17">
+      <c r="H2" s="15">
         <v>8.4</v>
       </c>
-      <c r="I2" s="15">
-        <f t="shared" ref="I2:I6" si="0">F2*H2</f>
+      <c r="I2" s="13">
+        <f>17900-SUM(I3:I4)</f>
         <v>16596</v>
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="12"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="15" t="s">
-        <v>490</v>
-      </c>
-      <c r="F3" s="15">
+      <c r="A3" s="10" t="s">
+        <v>549</v>
+      </c>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="13" t="s">
+        <v>387</v>
+      </c>
+      <c r="F3" s="13">
         <v>4</v>
       </c>
-      <c r="G3" s="16"/>
-      <c r="H3" s="17">
+      <c r="G3" s="14"/>
+      <c r="H3" s="15">
         <v>2326</v>
       </c>
-      <c r="I3" s="15">
+      <c r="I3" s="13">
         <f>F3*H3</f>
         <v>9304</v>
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="12"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="15" t="s">
-        <v>491</v>
-      </c>
-      <c r="F4" s="15">
+      <c r="A4" s="10" t="s">
+        <v>549</v>
+      </c>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="F4" s="13">
         <v>-20</v>
       </c>
-      <c r="G4" s="16"/>
-      <c r="H4" s="17">
+      <c r="G4" s="14"/>
+      <c r="H4" s="15">
         <v>400</v>
       </c>
-      <c r="I4" s="15">
-        <f t="shared" si="0"/>
+      <c r="I4" s="13">
+        <f>F4*H4</f>
         <v>-8000</v>
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="12" t="s">
-        <v>492</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>487</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>493</v>
-      </c>
-      <c r="D5" s="14">
-        <v>-0.5</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>489</v>
-      </c>
-      <c r="F5" s="15">
+      <c r="A5" s="10" t="s">
+        <v>484</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>497</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>550</v>
+      </c>
+      <c r="D5" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="F5" s="13">
         <f>I5/H5</f>
         <v>3559.52380952381</v>
       </c>
-      <c r="G5" s="16">
+      <c r="G5" s="14">
         <f>F5/1000</f>
         <v>3.55952380952381</v>
       </c>
-      <c r="H5" s="17">
+      <c r="H5" s="15">
         <v>8.4</v>
       </c>
-      <c r="I5" s="15">
+      <c r="I5" s="13">
         <f>17900-I6</f>
         <v>29900</v>
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="12"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="15" t="s">
-        <v>491</v>
-      </c>
-      <c r="F6" s="15">
+      <c r="A6" s="10" t="s">
+        <v>484</v>
+      </c>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="F6" s="13">
         <v>-30</v>
       </c>
-      <c r="G6" s="16"/>
-      <c r="H6" s="17">
+      <c r="G6" s="14"/>
+      <c r="H6" s="15">
         <v>400</v>
       </c>
-      <c r="I6" s="15">
-        <f t="shared" si="0"/>
+      <c r="I6" s="13">
+        <f>F6*H6</f>
         <v>-12000</v>
       </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="12" t="s">
-        <v>494</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>487</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>495</v>
+      <c r="A7" s="10" t="s">
+        <v>551</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>497</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>552</v>
       </c>
       <c r="D7" s="18">
-        <v>-0.5</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>489</v>
-      </c>
-      <c r="F7" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="F7" s="13">
         <f>I7/H7</f>
         <v>2678.57142857143</v>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="14">
         <f>F7/1000</f>
         <v>2.67857142857143</v>
       </c>
-      <c r="H7" s="17">
+      <c r="H7" s="15">
         <v>8.4</v>
       </c>
-      <c r="I7" s="15">
+      <c r="I7" s="13">
         <f>17900-I8-I9</f>
         <v>22500</v>
       </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="12"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="15" t="s">
-        <v>496</v>
+      <c r="A8" s="10" t="s">
+        <v>551</v>
+      </c>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="13" t="s">
+        <v>198</v>
       </c>
       <c r="F8" s="19">
         <v>0.1</v>
       </c>
-      <c r="G8" s="16"/>
-      <c r="H8" s="17">
+      <c r="G8" s="14"/>
+      <c r="H8" s="15">
         <v>140</v>
       </c>
-      <c r="I8" s="15">
+      <c r="I8" s="13">
         <f>F8*H8*100</f>
         <v>1400</v>
       </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="12"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="15" t="s">
-        <v>497</v>
-      </c>
-      <c r="F9" s="15">
+      <c r="A9" s="10" t="s">
+        <v>551</v>
+      </c>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="F9" s="13">
         <v>-15</v>
       </c>
-      <c r="G9" s="16"/>
-      <c r="H9" s="17">
+      <c r="G9" s="14"/>
+      <c r="H9" s="15">
         <v>400</v>
       </c>
-      <c r="I9" s="15">
+      <c r="I9" s="13">
         <f>F9*H9</f>
         <v>-6000</v>
       </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="12" t="s">
-        <v>498</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>499</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>488</v>
-      </c>
-      <c r="D10" s="18">
+      <c r="A10" s="10" t="s">
+        <v>553</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>554</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>504</v>
+      </c>
+      <c r="D10" s="12">
         <v>0</v>
       </c>
-      <c r="E10" s="15" t="s">
-        <v>489</v>
-      </c>
-      <c r="F10" s="15">
+      <c r="E10" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="F10" s="13">
         <f>I10/H10</f>
         <v>1464.28571428571</v>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="14">
         <f>F10/1000</f>
         <v>1.46428571428571</v>
       </c>
-      <c r="H10" s="17">
+      <c r="H10" s="15">
         <v>8.4</v>
       </c>
-      <c r="I10" s="15">
+      <c r="I10" s="13">
         <f>17900-I11-I12</f>
         <v>12300</v>
       </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="12"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="15" t="s">
-        <v>496</v>
-      </c>
-      <c r="F11" s="20">
+      <c r="A11" s="10" t="s">
+        <v>553</v>
+      </c>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="F11" s="19">
         <v>0.1</v>
       </c>
-      <c r="G11" s="15"/>
-      <c r="H11" s="17">
+      <c r="G11" s="13"/>
+      <c r="H11" s="15">
         <v>140</v>
       </c>
-      <c r="I11" s="15">
+      <c r="I11" s="13">
         <f>F11*H11*100</f>
         <v>1400</v>
       </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="12"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="15" t="s">
-        <v>500</v>
+      <c r="A12" s="10" t="s">
+        <v>553</v>
+      </c>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="13" t="s">
+        <v>207</v>
       </c>
       <c r="F12" s="19">
         <v>0.3</v>
       </c>
-      <c r="G12" s="15"/>
-      <c r="H12" s="17">
+      <c r="G12" s="13"/>
+      <c r="H12" s="15">
         <v>140</v>
       </c>
-      <c r="I12" s="15">
+      <c r="I12" s="13">
         <f>F12*H12*100</f>
         <v>4200</v>
       </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="12" t="s">
-        <v>501</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>487</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>502</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>503</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>489</v>
-      </c>
-      <c r="F13" s="15">
+      <c r="A13" s="10" t="s">
+        <v>555</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>497</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>556</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>557</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="F13" s="13">
         <f>I13/H13</f>
         <v>1702.38095238095</v>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="14">
         <f>F13/1000</f>
         <v>1.70238095238095</v>
       </c>
-      <c r="H13" s="17">
+      <c r="H13" s="15">
         <v>8.4</v>
       </c>
-      <c r="I13" s="15">
+      <c r="I13" s="13">
         <f>17900-I14-I16-I15</f>
         <v>14300</v>
       </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="12"/>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="15" t="s">
-        <v>504</v>
-      </c>
-      <c r="F14" s="20">
+      <c r="A14" s="10" t="s">
+        <v>555</v>
+      </c>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="13" t="s">
+        <v>384</v>
+      </c>
+      <c r="F14" s="19">
         <v>0.2</v>
       </c>
-      <c r="G14" s="15"/>
-      <c r="H14" s="17">
+      <c r="G14" s="13"/>
+      <c r="H14" s="15">
         <v>140</v>
       </c>
-      <c r="I14" s="15">
+      <c r="I14" s="13">
         <f>F14*H14*100</f>
         <v>2800</v>
       </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="12"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="15" t="s">
-        <v>500</v>
+      <c r="A15" s="10" t="s">
+        <v>555</v>
+      </c>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="13" t="s">
+        <v>207</v>
       </c>
       <c r="F15" s="19">
         <v>0.2</v>
       </c>
-      <c r="G15" s="15"/>
-      <c r="H15" s="17">
+      <c r="G15" s="13"/>
+      <c r="H15" s="15">
         <v>140</v>
       </c>
-      <c r="I15" s="15">
+      <c r="I15" s="13">
         <f>F15*H15*100</f>
         <v>2800</v>
       </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="12"/>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="15" t="s">
-        <v>491</v>
-      </c>
-      <c r="F16" s="15">
+      <c r="A16" s="10" t="s">
+        <v>555</v>
+      </c>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="F16" s="13">
         <v>-5</v>
       </c>
-      <c r="G16" s="15"/>
-      <c r="H16" s="17">
+      <c r="G16" s="13"/>
+      <c r="H16" s="15">
         <v>400</v>
       </c>
-      <c r="I16" s="15">
+      <c r="I16" s="13">
         <f>F16*H16</f>
         <v>-2000</v>
       </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="12" t="s">
-        <v>505</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>499</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>506</v>
+      <c r="A17" s="10" t="s">
+        <v>558</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>554</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>559</v>
       </c>
       <c r="D17" s="18">
-        <v>-0.5</v>
-      </c>
-      <c r="E17" s="15" t="s">
-        <v>489</v>
-      </c>
-      <c r="F17" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="F17" s="13">
         <f>I17/H17</f>
         <v>2750</v>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="14">
         <f>F17/1000</f>
         <v>2.75</v>
       </c>
-      <c r="H17" s="17">
+      <c r="H17" s="15">
         <v>8.4</v>
       </c>
-      <c r="I17" s="15">
+      <c r="I17" s="13">
         <f>17900-I18-I19</f>
         <v>23100</v>
       </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="12"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="15" t="s">
-        <v>507</v>
-      </c>
-      <c r="F18" s="15">
+      <c r="A18" s="10" t="s">
+        <v>558</v>
+      </c>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="13" t="s">
+        <v>386</v>
+      </c>
+      <c r="F18" s="13">
         <v>1</v>
       </c>
-      <c r="G18" s="15"/>
-      <c r="H18" s="17">
+      <c r="G18" s="13"/>
+      <c r="H18" s="15">
         <v>4800</v>
       </c>
-      <c r="I18" s="15">
-        <f t="shared" ref="I18:I20" si="1">F18*H18</f>
+      <c r="I18" s="13">
+        <f>F18*H18</f>
         <v>4800</v>
       </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="12"/>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="15" t="s">
-        <v>491</v>
-      </c>
-      <c r="F19" s="15">
+      <c r="A19" s="10" t="s">
+        <v>558</v>
+      </c>
+      <c r="B19" s="17"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="F19" s="13">
         <v>-25</v>
       </c>
-      <c r="G19" s="15"/>
-      <c r="H19" s="17">
+      <c r="G19" s="13"/>
+      <c r="H19" s="15">
         <v>400</v>
       </c>
-      <c r="I19" s="15">
-        <f t="shared" si="1"/>
+      <c r="I19" s="13">
+        <f>F19*H19</f>
         <v>-10000</v>
       </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="12" t="s">
-        <v>508</v>
-      </c>
-      <c r="B20" s="13" t="s">
-        <v>487</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>488</v>
-      </c>
-      <c r="D20" s="19"/>
-      <c r="E20" s="15" t="s">
-        <v>489</v>
-      </c>
-      <c r="F20" s="15">
-        <f>17900/H20</f>
+      <c r="A20" s="20" t="s">
+        <v>560</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>497</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>504</v>
+      </c>
+      <c r="D20" s="21"/>
+      <c r="E20" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="F20" s="13">
+        <f>I20/H20</f>
         <v>2130.95238095238</v>
       </c>
-      <c r="G20" s="16">
+      <c r="G20" s="14">
         <f>F20/1000</f>
         <v>2.13095238095238</v>
       </c>
-      <c r="H20" s="17">
+      <c r="H20" s="15">
         <v>8.4</v>
       </c>
-      <c r="I20" s="15">
-        <f>F20*H20</f>
+      <c r="I20" s="13">
         <v>17900</v>
       </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="21" t="s">
-        <v>509</v>
+      <c r="A21" s="10" t="s">
+        <v>487</v>
       </c>
       <c r="B21" s="22"/>
       <c r="C21" s="22"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="24" t="s">
-        <v>510</v>
-      </c>
-      <c r="F21" s="24">
+      <c r="D21" s="12"/>
+      <c r="E21" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="F21" s="13">
         <v>500</v>
       </c>
-      <c r="G21" s="16">
-        <f>F21/1000</f>
+      <c r="G21" s="14">
+        <f t="shared" ref="G20:G27" si="0">F21/1000</f>
         <v>0.5</v>
       </c>
-      <c r="H21" s="25">
+      <c r="H21" s="23">
         <v>5.6</v>
       </c>
-      <c r="I21" s="24">
+      <c r="I21" s="13">
         <f>F21*H21</f>
         <v>2800</v>
       </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="21"/>
-      <c r="B22" s="26"/>
-      <c r="C22" s="26"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="15" t="s">
+      <c r="A22" s="10" t="s">
+        <v>487</v>
+      </c>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="F22" s="24">
+      <c r="F22" s="13">
         <v>500</v>
       </c>
-      <c r="G22" s="16">
-        <f>F22/1000</f>
+      <c r="G22" s="14">
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
-      <c r="H22" s="25">
+      <c r="H22" s="23">
         <v>11.6</v>
       </c>
-      <c r="I22" s="24">
+      <c r="I22" s="13">
         <f>F22*H22</f>
         <v>5800</v>
       </c>
     </row>
-    <row r="23" s="4" customFormat="1" spans="1:9">
-      <c r="A23" s="21"/>
-      <c r="B23" s="27"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="15" t="s">
-        <v>511</v>
-      </c>
-      <c r="F23" s="15">
+    <row r="23" customFormat="1" spans="1:9">
+      <c r="A23" s="10" t="s">
+        <v>487</v>
+      </c>
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="F23" s="13">
+        <f>I23/H23</f>
         <v>9300</v>
       </c>
-      <c r="G23" s="16">
-        <f>F23/1000</f>
+      <c r="G23" s="14">
+        <f t="shared" si="0"/>
         <v>9.3</v>
       </c>
-      <c r="H23" s="17">
+      <c r="H23" s="15">
         <v>1</v>
       </c>
-      <c r="I23" s="15">
+      <c r="I23" s="13">
         <f>17900-I21-I22</f>
         <v>9300</v>
       </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="12" t="s">
-        <v>512</v>
-      </c>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="15" t="s">
-        <v>511</v>
-      </c>
-      <c r="F24" s="15">
-        <v>9300</v>
-      </c>
-      <c r="G24" s="16">
-        <f>F24/1000</f>
-        <v>9.3</v>
-      </c>
-      <c r="H24" s="17">
+      <c r="A24" s="10" t="s">
+        <v>488</v>
+      </c>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="F24" s="13">
+        <f>I24/H24</f>
+        <v>8950</v>
+      </c>
+      <c r="G24" s="14">
+        <f t="shared" si="0"/>
+        <v>8.95</v>
+      </c>
+      <c r="H24" s="15">
         <v>1</v>
       </c>
-      <c r="I24" s="15">
-        <f>F24*H24</f>
-        <v>9300</v>
+      <c r="I24" s="13">
+        <f>17900-I25</f>
+        <v>8950</v>
       </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="12"/>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="15" t="s">
-        <v>513</v>
-      </c>
-      <c r="F25" s="15">
-        <f>I25*H25</f>
-        <v>8600</v>
-      </c>
-      <c r="G25" s="16">
-        <f>F25/1000</f>
-        <v>8.6</v>
-      </c>
-      <c r="H25" s="17">
+      <c r="A25" s="10" t="s">
+        <v>488</v>
+      </c>
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="F25" s="13">
+        <f>I25/H25</f>
+        <v>8950</v>
+      </c>
+      <c r="G25" s="14">
+        <f t="shared" si="0"/>
+        <v>8.95</v>
+      </c>
+      <c r="H25" s="15">
         <v>1</v>
       </c>
-      <c r="I25" s="15">
-        <f>17900-I24</f>
-        <v>8600</v>
+      <c r="I25" s="13">
+        <v>8950</v>
       </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="12" t="s">
-        <v>514</v>
-      </c>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="15" t="s">
-        <v>511</v>
-      </c>
-      <c r="F26" s="28">
+      <c r="A26" s="10" t="s">
+        <v>561</v>
+      </c>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="F26" s="24">
         <f>I26/H26</f>
-        <v>4100</v>
-      </c>
-      <c r="G26" s="16">
-        <f>F26/1000</f>
-        <v>4.1</v>
-      </c>
-      <c r="H26" s="17">
+        <v>4000</v>
+      </c>
+      <c r="G26" s="14">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="H26" s="15">
         <v>1</v>
       </c>
-      <c r="I26" s="15">
-        <f>17900-SUM(I27:I29)</f>
-        <v>4100</v>
+      <c r="I26" s="13">
+        <v>4000</v>
       </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="12"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="15" t="s">
-        <v>500</v>
-      </c>
-      <c r="F27" s="29">
+      <c r="A27" s="10" t="s">
+        <v>561</v>
+      </c>
+      <c r="B27" s="16"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="F27" s="24">
+        <f>I27/H27</f>
+        <v>607.142857142857</v>
+      </c>
+      <c r="G27" s="14">
+        <f t="shared" si="0"/>
+        <v>0.607142857142857</v>
+      </c>
+      <c r="H27" s="15">
+        <v>8.4</v>
+      </c>
+      <c r="I27" s="13">
+        <f>17900-SUM(I26,I28:I30)</f>
+        <v>5100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="10" t="s">
+        <v>561</v>
+      </c>
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="F28" s="25">
         <v>0.2</v>
       </c>
-      <c r="G27" s="16"/>
-      <c r="H27" s="17">
+      <c r="G28" s="14"/>
+      <c r="H28" s="15">
         <v>140</v>
       </c>
-      <c r="I27" s="15">
-        <f>F27*H27*100</f>
+      <c r="I28" s="13">
+        <f>F28*H28*100</f>
         <v>2800</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
-      <c r="A28" s="12"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="15" t="s">
-        <v>510</v>
-      </c>
-      <c r="F28" s="28">
-        <f>I28/H28</f>
-        <v>982.142857142857</v>
-      </c>
-      <c r="G28" s="16">
-        <f>F28/1000</f>
-        <v>0.982142857142857</v>
-      </c>
-      <c r="H28" s="25">
+    <row r="29" spans="1:9">
+      <c r="A29" s="10" t="s">
+        <v>561</v>
+      </c>
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="F29" s="24">
+        <f t="shared" ref="F29:F35" si="1">I29/H29</f>
+        <v>535.714285714286</v>
+      </c>
+      <c r="G29" s="14">
+        <f>F29/1000</f>
+        <v>0.535714285714286</v>
+      </c>
+      <c r="H29" s="23">
         <v>5.6</v>
       </c>
-      <c r="I28" s="15">
-        <f>(17900-1400)/3</f>
-        <v>5500</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9">
-      <c r="A29" s="12"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="15" t="s">
-        <v>515</v>
-      </c>
-      <c r="F29" s="28">
-        <f>I29/H29</f>
-        <v>474.137931034483</v>
-      </c>
-      <c r="G29" s="16">
-        <f>F29/1000</f>
-        <v>0.474137931034483</v>
-      </c>
-      <c r="H29" s="25">
+      <c r="I29" s="13">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="10" t="s">
+        <v>561</v>
+      </c>
+      <c r="B30" s="17"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="F30" s="24">
+        <f t="shared" si="1"/>
+        <v>258.620689655172</v>
+      </c>
+      <c r="G30" s="14">
+        <f>F30/1000</f>
+        <v>0.258620689655172</v>
+      </c>
+      <c r="H30" s="23">
         <v>11.6</v>
       </c>
-      <c r="I29" s="15">
-        <f>(17900-1400)/3</f>
-        <v>5500</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9">
-      <c r="A30" s="12" t="s">
-        <v>516</v>
-      </c>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="15" t="s">
-        <v>511</v>
-      </c>
-      <c r="F30" s="28">
-        <f>I30/H30</f>
+      <c r="I30" s="13">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="10" t="s">
+        <v>562</v>
+      </c>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="F31" s="24">
+        <f t="shared" si="1"/>
         <v>5900</v>
       </c>
-      <c r="G30" s="15"/>
-      <c r="H30" s="17">
+      <c r="G31" s="14">
+        <f>F31/1000</f>
+        <v>5.9</v>
+      </c>
+      <c r="H31" s="15">
         <v>1</v>
       </c>
-      <c r="I30" s="15">
+      <c r="I31" s="13">
         <v>5900</v>
       </c>
     </row>
-    <row r="31" spans="1:9">
-      <c r="A31" s="12"/>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="15" t="s">
-        <v>510</v>
-      </c>
-      <c r="F31" s="28">
-        <f>I31/H31</f>
+    <row r="32" spans="1:9">
+      <c r="A32" s="10" t="s">
+        <v>562</v>
+      </c>
+      <c r="B32" s="16"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="F32" s="24">
+        <f t="shared" si="1"/>
         <v>1071.42857142857</v>
       </c>
-      <c r="G31" s="15"/>
-      <c r="H31" s="25">
+      <c r="G32" s="14">
+        <f>F32/1000</f>
+        <v>1.07142857142857</v>
+      </c>
+      <c r="H32" s="23">
         <v>5.6</v>
       </c>
-      <c r="I31" s="15">
+      <c r="I32" s="13">
         <v>6000</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
-      <c r="A32" s="12"/>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="15" t="s">
-        <v>515</v>
-      </c>
-      <c r="F32" s="28">
-        <f>I32/H32</f>
+    <row r="33" spans="1:9">
+      <c r="A33" s="10" t="s">
+        <v>562</v>
+      </c>
+      <c r="B33" s="17"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="F33" s="24">
+        <f t="shared" si="1"/>
         <v>517.241379310345</v>
       </c>
-      <c r="G32" s="15"/>
-      <c r="H32" s="25">
+      <c r="G33" s="14">
+        <f>F33/1000</f>
+        <v>0.517241379310345</v>
+      </c>
+      <c r="H33" s="23">
         <v>11.6</v>
       </c>
-      <c r="I32" s="15">
+      <c r="I33" s="13">
         <v>6000</v>
       </c>
     </row>
-    <row r="33" spans="1:9">
-      <c r="A33" s="12" t="s">
-        <v>517</v>
-      </c>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="15" t="s">
-        <v>513</v>
-      </c>
-      <c r="F33" s="28">
-        <f>I33/H33</f>
-        <v>6748</v>
-      </c>
-      <c r="G33" s="15"/>
-      <c r="H33" s="17">
+    <row r="34" spans="1:9">
+      <c r="A34" s="10" t="s">
+        <v>563</v>
+      </c>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="F34" s="24">
+        <f t="shared" si="1"/>
+        <v>6000</v>
+      </c>
+      <c r="G34" s="13"/>
+      <c r="H34" s="15">
         <v>1</v>
       </c>
-      <c r="I33" s="15">
-        <f>17900-(I34+I35)</f>
-        <v>6748</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9">
-      <c r="A34" s="12"/>
-      <c r="B34" s="13"/>
-      <c r="C34" s="13"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="15" t="s">
-        <v>515</v>
-      </c>
-      <c r="F34" s="28">
-        <f>I34/H34</f>
-        <v>560.344827586207</v>
-      </c>
-      <c r="G34" s="15"/>
-      <c r="H34" s="25">
+      <c r="I34" s="13">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="10" t="s">
+        <v>563</v>
+      </c>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="F35" s="24">
+        <f t="shared" si="1"/>
+        <v>624.827586206897</v>
+      </c>
+      <c r="G35" s="13"/>
+      <c r="H35" s="23">
         <v>11.6</v>
       </c>
-      <c r="I34" s="15">
-        <v>6500</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9">
-      <c r="A35" s="12"/>
-      <c r="B35" s="13"/>
-      <c r="C35" s="13"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="15" t="s">
-        <v>490</v>
-      </c>
-      <c r="F35" s="15">
+      <c r="I35" s="13">
+        <f>17900-I34-I36</f>
+        <v>7248</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="10" t="s">
+        <v>563</v>
+      </c>
+      <c r="B36" s="17"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="13" t="s">
+        <v>387</v>
+      </c>
+      <c r="F36" s="13">
         <v>2</v>
       </c>
-      <c r="G35" s="15"/>
-      <c r="H35" s="17">
+      <c r="G36" s="13"/>
+      <c r="H36" s="15">
         <v>2326</v>
       </c>
-      <c r="I35" s="15">
-        <f>H35*F35</f>
+      <c r="I36" s="13">
+        <f>H36*F36</f>
         <v>4652</v>
       </c>
     </row>
-    <row r="36" spans="1:9">
-      <c r="A36" s="12" t="s">
-        <v>518</v>
-      </c>
-      <c r="B36" s="13"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="15" t="s">
-        <v>489</v>
-      </c>
-      <c r="F36" s="15">
-        <f>I36/H36</f>
-        <v>702.380952380952</v>
-      </c>
-      <c r="G36" s="15"/>
-      <c r="H36" s="17">
+    <row r="37" spans="1:9">
+      <c r="A37" s="10" t="s">
+        <v>564</v>
+      </c>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="F37" s="13">
+        <f>I37/H37</f>
+        <v>1464.28571428571</v>
+      </c>
+      <c r="G37" s="14">
+        <f>F37/1000</f>
+        <v>1.46428571428571</v>
+      </c>
+      <c r="H37" s="15">
         <v>8.4</v>
       </c>
-      <c r="I36" s="15">
-        <v>5900</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9">
-      <c r="A37" s="12"/>
-      <c r="B37" s="13"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="15" t="s">
-        <v>496</v>
-      </c>
-      <c r="F37" s="19">
-        <f>I37/H37/100</f>
-        <v>0.214285714285714</v>
-      </c>
-      <c r="G37" s="15"/>
-      <c r="H37" s="17">
+      <c r="I37" s="13">
+        <f>17900-SUM(I38:I39)</f>
+        <v>12300</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="10" t="s">
+        <v>564</v>
+      </c>
+      <c r="B38" s="16"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="F38" s="19">
+        <v>0.2</v>
+      </c>
+      <c r="G38" s="13"/>
+      <c r="H38" s="15">
         <v>140</v>
       </c>
-      <c r="I37" s="15">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9">
-      <c r="A38" s="12"/>
-      <c r="B38" s="13"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="15" t="s">
-        <v>519</v>
-      </c>
-      <c r="F38" s="19">
-        <f>I38/H38/100</f>
-        <v>1.07142857142857</v>
-      </c>
-      <c r="G38" s="15"/>
-      <c r="H38" s="17">
+      <c r="I38" s="13">
+        <f>F38*H38*100</f>
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="10" t="s">
+        <v>564</v>
+      </c>
+      <c r="B39" s="17"/>
+      <c r="C39" s="17"/>
+      <c r="D39" s="17"/>
+      <c r="E39" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="F39" s="19">
+        <v>0.2</v>
+      </c>
+      <c r="G39" s="13"/>
+      <c r="H39" s="15">
+        <v>140</v>
+      </c>
+      <c r="I39" s="13">
+        <f>F39*H39*100</f>
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="10" t="s">
+        <v>565</v>
+      </c>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="F40" s="13">
+        <f>I40/H40</f>
+        <v>630.952380952381</v>
+      </c>
+      <c r="G40" s="14">
+        <f>F40/1000</f>
+        <v>0.630952380952381</v>
+      </c>
+      <c r="H40" s="15">
+        <v>8.4</v>
+      </c>
+      <c r="I40" s="13">
+        <f>17900-SUM(I41:I43)</f>
+        <v>5300</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" s="10" t="s">
+        <v>565</v>
+      </c>
+      <c r="B41" s="16"/>
+      <c r="C41" s="16"/>
+      <c r="D41" s="16"/>
+      <c r="E41" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="F41" s="19">
+        <v>0.3</v>
+      </c>
+      <c r="G41" s="13"/>
+      <c r="H41" s="15">
+        <v>140</v>
+      </c>
+      <c r="I41" s="13">
+        <f>F41*H41*100</f>
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" s="10" t="s">
+        <v>565</v>
+      </c>
+      <c r="B42" s="16"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="16"/>
+      <c r="E42" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="F42" s="19">
+        <v>1</v>
+      </c>
+      <c r="G42" s="13"/>
+      <c r="H42" s="15">
         <v>28</v>
       </c>
-      <c r="I38" s="15">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9">
-      <c r="A39" s="12"/>
-      <c r="B39" s="13"/>
-      <c r="C39" s="13"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="15" t="s">
-        <v>500</v>
-      </c>
-      <c r="F39" s="19">
-        <f>I39/H39/100</f>
-        <v>0.428571428571429</v>
-      </c>
-      <c r="G39" s="15"/>
-      <c r="H39" s="17">
+      <c r="I42" s="13">
+        <f>F42*H42*100</f>
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" s="10" t="s">
+        <v>565</v>
+      </c>
+      <c r="B43" s="17"/>
+      <c r="C43" s="17"/>
+      <c r="D43" s="17"/>
+      <c r="E43" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="F43" s="19">
+        <v>0.4</v>
+      </c>
+      <c r="G43" s="13"/>
+      <c r="H43" s="15">
         <v>140</v>
       </c>
-      <c r="I39" s="15">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="4" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" s="5" t="s">
-        <v>522</v>
+      <c r="I43" s="13">
+        <f>F43*H43*100</f>
+        <v>5600</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="5" t="s">
-        <v>523</v>
+      <c r="A45" t="s">
+        <v>566</v>
       </c>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="5" t="s">
-        <v>524</v>
+      <c r="A46" t="s">
+        <v>567</v>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="5" t="s">
-        <v>525</v>
+      <c r="A47" s="3" t="s">
+        <v>568</v>
       </c>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" s="5" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Weapon Attack Target, Area of Attack, and secondary-target Attack modifiers apply only to normal attacks. Each skill defines its own target selection and area of effect and does not inherit these weapon targeting rules or secondary-target Attack modifiers.</t>
-        </is>
+      <c r="A48" s="3" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="3" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="3" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="3" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>573</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="48">
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A13:A16"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="A30:A32"/>
-    <mergeCell ref="A33:A35"/>
-    <mergeCell ref="A36:A39"/>
+  <mergeCells count="39">
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="B7:B9"/>
@@ -7106,10 +8243,11 @@
     <mergeCell ref="B17:B19"/>
     <mergeCell ref="B21:B23"/>
     <mergeCell ref="B24:B25"/>
-    <mergeCell ref="B26:B29"/>
-    <mergeCell ref="B30:B32"/>
-    <mergeCell ref="B33:B35"/>
-    <mergeCell ref="B36:B39"/>
+    <mergeCell ref="B26:B30"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="B37:B39"/>
+    <mergeCell ref="B40:B43"/>
     <mergeCell ref="C2:C4"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="C7:C9"/>
@@ -7118,10 +8256,11 @@
     <mergeCell ref="C17:C19"/>
     <mergeCell ref="C21:C23"/>
     <mergeCell ref="C24:C25"/>
-    <mergeCell ref="C26:C29"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="C33:C35"/>
-    <mergeCell ref="C36:C39"/>
+    <mergeCell ref="C26:C30"/>
+    <mergeCell ref="C31:C33"/>
+    <mergeCell ref="C34:C36"/>
+    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="C40:C43"/>
     <mergeCell ref="D2:D4"/>
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="D7:D9"/>
@@ -7130,26 +8269,13 @@
     <mergeCell ref="D17:D19"/>
     <mergeCell ref="D21:D23"/>
     <mergeCell ref="D24:D25"/>
-    <mergeCell ref="D26:D29"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="D36:D39"/>
+    <mergeCell ref="D26:D30"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="D34:D36"/>
+    <mergeCell ref="D37:D39"/>
+    <mergeCell ref="D40:D43"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-  <ignoredErrors>
-    <ignoredError sqref="I8" formula="1"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -7167,284 +8293,242 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>527</v>
+        <v>574</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>528</v>
+        <v>575</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>529</v>
+        <v>576</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2" t="s">
-        <v>531</v>
+      <c r="A2" t="s">
+        <v>577</v>
+      </c>
+      <c r="C2" t="s">
+        <v>578</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2" t="s">
-        <v>533</v>
+      <c r="A3" t="s">
+        <v>579</v>
+      </c>
+      <c r="C3" t="s">
+        <v>580</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2" t="s">
-        <v>535</v>
+      <c r="A4" t="s">
+        <v>513</v>
+      </c>
+      <c r="C4" t="s">
+        <v>581</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2" t="s">
-        <v>537</v>
+      <c r="A5" t="s">
+        <v>515</v>
+      </c>
+      <c r="C5" t="s">
+        <v>582</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2" t="s">
-        <v>539</v>
+      <c r="A6" t="s">
+        <v>583</v>
+      </c>
+      <c r="C6" t="s">
+        <v>584</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2" t="s">
-        <v>541</v>
+      <c r="A7" t="s">
+        <v>585</v>
+      </c>
+      <c r="C7" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2" t="s">
-        <v>543</v>
+      <c r="A8" t="s">
+        <v>587</v>
+      </c>
+      <c r="C8" t="s">
+        <v>588</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2" t="s">
-        <v>545</v>
+      <c r="A9" t="s">
+        <v>589</v>
+      </c>
+      <c r="C9" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2" t="s">
-        <v>547</v>
+      <c r="A10" t="s">
+        <v>591</v>
+      </c>
+      <c r="C10" t="s">
+        <v>592</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2" t="s">
-        <v>549</v>
+      <c r="A11" t="s">
+        <v>593</v>
+      </c>
+      <c r="C11" t="s">
+        <v>594</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2" t="s">
-        <v>551</v>
+      <c r="A12" t="s">
+        <v>595</v>
+      </c>
+      <c r="C12" t="s">
+        <v>596</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2" t="s">
-        <v>553</v>
+      <c r="A13" t="s">
+        <v>597</v>
+      </c>
+      <c r="C13" t="s">
+        <v>598</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2" t="s">
-        <v>555</v>
+      <c r="A14" t="s">
+        <v>599</v>
+      </c>
+      <c r="C14" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="B15" s="2">
+      <c r="A15" t="s">
+        <v>562</v>
+      </c>
+      <c r="B15">
         <v>5</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>556</v>
+      <c r="C15" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
+      <c r="A16" t="s">
+        <v>602</v>
+      </c>
+      <c r="C16" t="s">
+        <v>603</v>
+      </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="2" t="s">
+      <c r="A18" t="s">
         <v>460</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18">
         <v>3</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>559</v>
+      <c r="C18" t="s">
+        <v>604</v>
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="B19" s="2">
+      <c r="A19" t="s">
+        <v>605</v>
+      </c>
+      <c r="B19">
         <v>3</v>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Has no direct effect. Each target can gain at most 1 Stun Count stack per global turn, regardless of the number of hits or sources. All stacks share a 3-global-turn duration; gaining a stack refreshes the shared duration to 3 global turns. When the duration expires, all stacks reset to 0. Reaching Stun Threshold triggers Stun. Stun Count resets to 0 and cannot increase while stunned.</t>
-        </is>
+      <c r="C19" t="s">
+        <v>606</v>
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="2" t="s">
+      <c r="A20" t="s">
         <v>361</v>
       </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2" t="s">
-        <v>562</v>
+      <c r="C20" t="s">
+        <v>607</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2" t="s">
-        <v>564</v>
+      <c r="A21" t="s">
+        <v>608</v>
+      </c>
+      <c r="C21" t="s">
+        <v>609</v>
       </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2" t="s">
-        <v>566</v>
+      <c r="A22" t="s">
+        <v>610</v>
+      </c>
+      <c r="C22" t="s">
+        <v>611</v>
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2" t="s">
-        <v>568</v>
+      <c r="A23" t="s">
+        <v>612</v>
+      </c>
+      <c r="C23" t="s">
+        <v>613</v>
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2" t="s">
-        <v>570</v>
+      <c r="A24" t="s">
+        <v>614</v>
+      </c>
+      <c r="C24" t="s">
+        <v>615</v>
       </c>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2" t="s">
-        <v>572</v>
+      <c r="A25" t="s">
+        <v>616</v>
+      </c>
+      <c r="C25" t="s">
+        <v>617</v>
       </c>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2" t="s">
-        <v>574</v>
+      <c r="A26" t="s">
+        <v>618</v>
+      </c>
+      <c r="C26" t="s">
+        <v>619</v>
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="2" t="s">
-        <v>575</v>
-      </c>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2" t="s">
-        <v>576</v>
+      <c r="A27" t="s">
+        <v>620</v>
+      </c>
+      <c r="C27" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2" t="s">
-        <v>578</v>
+      <c r="A28" t="s">
+        <v>622</v>
+      </c>
+      <c r="C28" t="s">
+        <v>623</v>
       </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2" t="s">
-        <v>580</v>
+      <c r="A29" t="s">
+        <v>624</v>
+      </c>
+      <c r="C29" t="s">
+        <v>625</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/data/excel/Thiết kế game.xlsx
+++ b/data/excel/Thiết kế game.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12180" activeTab="5"/>
+    <workbookView windowWidth="27945" windowHeight="11460" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Ý tưởng chung" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="626">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="627">
   <si>
     <t>Tên game</t>
   </si>
@@ -1620,7 +1620,7 @@
   </si>
   <si>
     <t>S1.2.2 
-Base MHR +25%</t>
+Deadly strike doesnt require condititon</t>
   </si>
   <si>
     <t>S1.2.3 
@@ -1628,9 +1628,9 @@
   </si>
   <si>
     <t>S1.2.4 
-Base MHR + 15%
+Base MHR + 20%
 Base CHC + 25%
-Base CDB + 70%</t>
+Base CDB + 50%</t>
   </si>
   <si>
     <t>Specialization 2</t>
@@ -1651,15 +1651,15 @@
   </si>
   <si>
     <t>S2.1.2 
-Base SDEF + 350</t>
+Frozen Axe applied Chill, AP recovery -10%, MHR -10%</t>
   </si>
   <si>
     <t>S2.1.3
-Frozen Axe DOT effectiveness +100%</t>
+Frozen Axe DOT effectiveness +200%</t>
   </si>
   <si>
     <t>S2.1.4
-Skill Bluetooth connection effectiveness +20%</t>
+Bluetooth connection effectiveness +20%</t>
   </si>
   <si>
     <t>S2.2.1
@@ -1888,7 +1888,10 @@
     <t>Chill</t>
   </si>
   <si>
-    <t>Reduces AP Recovery and Multi-Hit Rate.</t>
+    <t>Infinity</t>
+  </si>
+  <si>
+    <t>Reduces AP Recovery and Multi-Hit Rate. Stackable. Maximum 5 stacks</t>
   </si>
   <si>
     <t>Break</t>
@@ -2610,7 +2613,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2702,18 +2705,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2727,12 +2718,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -2751,9 +2736,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -3440,7 +3422,7 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="1" ht="61" customHeight="1" spans="1:1">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="58" t="s">
         <v>25</v>
       </c>
     </row>
@@ -4039,79 +4021,79 @@
       </c>
     </row>
     <row r="57" spans="1:3">
-      <c r="A57" s="65" t="s">
+      <c r="A57" s="54" t="s">
         <v>143</v>
       </c>
-      <c r="B57" s="65" t="s">
+      <c r="B57" s="54" t="s">
         <v>144</v>
       </c>
-      <c r="C57" s="65" t="s">
+      <c r="C57" s="54" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="58" customFormat="1" ht="30" customHeight="1" spans="1:3">
-      <c r="A58" s="65" t="s">
+      <c r="A58" s="54" t="s">
         <v>143</v>
       </c>
-      <c r="B58" s="65" t="s">
+      <c r="B58" s="54" t="s">
         <v>146</v>
       </c>
-      <c r="C58" s="65" t="s">
+      <c r="C58" s="54" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="59" customFormat="1" ht="30" customHeight="1" spans="1:3">
-      <c r="A59" s="65" t="s">
+      <c r="A59" s="54" t="s">
         <v>143</v>
       </c>
-      <c r="B59" s="65" t="s">
+      <c r="B59" s="54" t="s">
         <v>148</v>
       </c>
-      <c r="C59" s="65" t="s">
+      <c r="C59" s="54" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="60" customFormat="1" ht="30" customHeight="1" spans="1:3">
-      <c r="A60" s="65" t="s">
+      <c r="A60" s="54" t="s">
         <v>150</v>
       </c>
-      <c r="B60" s="65" t="s">
+      <c r="B60" s="54" t="s">
         <v>151</v>
       </c>
-      <c r="C60" s="65" t="s">
+      <c r="C60" s="54" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="61" customFormat="1" ht="30" customHeight="1" spans="1:3">
-      <c r="A61" s="65" t="s">
+      <c r="A61" s="54" t="s">
         <v>150</v>
       </c>
-      <c r="B61" s="65" t="s">
+      <c r="B61" s="54" t="s">
         <v>153</v>
       </c>
-      <c r="C61" s="65" t="s">
+      <c r="C61" s="54" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="62" customFormat="1" ht="30" customHeight="1" spans="1:3">
-      <c r="A62" s="65" t="s">
+      <c r="A62" s="54" t="s">
         <v>150</v>
       </c>
-      <c r="B62" s="65" t="s">
+      <c r="B62" s="54" t="s">
         <v>155</v>
       </c>
-      <c r="C62" s="65" t="s">
+      <c r="C62" s="54" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="63" customFormat="1" ht="30" customHeight="1" spans="1:3">
-      <c r="A63" s="65" t="s">
+      <c r="A63" s="54" t="s">
         <v>150</v>
       </c>
-      <c r="B63" s="65" t="s">
+      <c r="B63" s="54" t="s">
         <v>157</v>
       </c>
-      <c r="C63" s="65" t="s">
+      <c r="C63" s="54" t="s">
         <v>158</v>
       </c>
     </row>
@@ -5657,12 +5639,12 @@
       </c>
     </row>
     <row r="24" customFormat="1" ht="23.25" customHeight="1" spans="1:1">
-      <c r="A24" s="61" t="s">
+      <c r="A24" s="55" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="26" customFormat="1" ht="18.75" customHeight="1" spans="1:1">
-      <c r="A26" s="62" t="s">
+      <c r="A26" s="56" t="s">
         <v>392</v>
       </c>
     </row>
@@ -5672,57 +5654,57 @@
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="63" t="s">
+      <c r="A29" s="57" t="s">
         <v>394</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="63" t="s">
+      <c r="A30" s="57" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="63" t="s">
+      <c r="A31" s="57" t="s">
         <v>396</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="63" t="s">
+      <c r="A32" s="57" t="s">
         <v>397</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="63" t="s">
+      <c r="A33" s="57" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="63" t="s">
+      <c r="A34" s="57" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="63" t="s">
+      <c r="A35" s="57" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="63" t="s">
+      <c r="A36" s="57" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="63" t="s">
+      <c r="A37" s="57" t="s">
         <v>402</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="63" t="s">
+      <c r="A38" s="57" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="40" customFormat="1" ht="18.75" customHeight="1" spans="1:1">
-      <c r="A40" s="62" t="s">
+      <c r="A40" s="56" t="s">
         <v>404</v>
       </c>
     </row>
@@ -5792,7 +5774,7 @@
       </c>
     </row>
     <row r="61" customFormat="1" ht="18.75" customHeight="1" spans="1:1">
-      <c r="A61" s="62" t="s">
+      <c r="A61" s="56" t="s">
         <v>418</v>
       </c>
     </row>
@@ -6029,7 +6011,7 @@
       </c>
     </row>
     <row r="93" customFormat="1" ht="18.75" customHeight="1" spans="1:1">
-      <c r="A93" s="62" t="s">
+      <c r="A93" s="56" t="s">
         <v>459</v>
       </c>
     </row>
@@ -6039,32 +6021,32 @@
       </c>
     </row>
     <row r="97" spans="1:1">
-      <c r="A97" s="63" t="s">
+      <c r="A97" s="57" t="s">
         <v>461</v>
       </c>
     </row>
     <row r="98" spans="1:1">
-      <c r="A98" s="63" t="s">
+      <c r="A98" s="57" t="s">
         <v>462</v>
       </c>
     </row>
     <row r="99" spans="1:1">
-      <c r="A99" s="63" t="s">
+      <c r="A99" s="57" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="100" spans="1:1">
-      <c r="A100" s="63" t="s">
+      <c r="A100" s="57" t="s">
         <v>464</v>
       </c>
     </row>
     <row r="101" spans="1:1">
-      <c r="A101" s="63" t="s">
+      <c r="A101" s="57" t="s">
         <v>465</v>
       </c>
     </row>
     <row r="102" spans="1:1">
-      <c r="A102" s="63" t="s">
+      <c r="A102" s="57" t="s">
         <v>466</v>
       </c>
     </row>
@@ -6089,7 +6071,7 @@
       </c>
     </row>
     <row r="110" customFormat="1" ht="18.75" customHeight="1" spans="1:1">
-      <c r="A110" s="62" t="s">
+      <c r="A110" s="56" t="s">
         <v>469</v>
       </c>
     </row>
@@ -6403,7 +6385,7 @@
         <v>207</v>
       </c>
       <c r="B14" s="34">
-        <f>SUM(C14,E14)</f>
+        <f t="shared" si="0"/>
         <v>1.2</v>
       </c>
       <c r="C14" s="34">
@@ -6527,7 +6509,7 @@
         <v>191</v>
       </c>
       <c r="B18" s="31">
-        <f>SUM(C18,E18)</f>
+        <f t="shared" si="0"/>
         <v>70</v>
       </c>
       <c r="C18" s="31">
@@ -6802,7 +6784,7 @@
       <c r="J28" s="38" t="s">
         <v>493</v>
       </c>
-      <c r="K28" s="56" t="s">
+      <c r="K28" s="39" t="s">
         <v>494</v>
       </c>
     </row>
@@ -6838,7 +6820,7 @@
       <c r="J29" s="38" t="s">
         <v>500</v>
       </c>
-      <c r="K29" s="56">
+      <c r="K29" s="39">
         <f>4.8*1000*2%*5</f>
         <v>480</v>
       </c>
@@ -6858,7 +6840,7 @@
       <c r="J30" s="38" t="s">
         <v>500</v>
       </c>
-      <c r="K30" s="56">
+      <c r="K30" s="39">
         <f>4.8*1000*2%*5</f>
         <v>480</v>
       </c>
@@ -6893,188 +6875,188 @@
       <c r="J31" s="44" t="s">
         <v>506</v>
       </c>
-      <c r="K31" s="57">
+      <c r="K31" s="40">
         <f>4.8*1000*70%*5</f>
         <v>16800</v>
       </c>
     </row>
     <row r="32" ht="30" spans="1:11">
-      <c r="A32" s="47" t="s">
+      <c r="A32" s="38" t="s">
         <v>507</v>
       </c>
-      <c r="B32" s="47" t="s">
+      <c r="B32" s="38" t="s">
         <v>508</v>
       </c>
-      <c r="C32" s="48">
+      <c r="C32" s="41">
         <v>800</v>
       </c>
-      <c r="D32" s="49">
+      <c r="D32" s="42">
         <v>0</v>
       </c>
-      <c r="E32" s="47" t="s">
+      <c r="E32" s="38" t="s">
         <v>509</v>
       </c>
-      <c r="F32" s="47" t="s">
+      <c r="F32" s="38" t="s">
         <v>510</v>
       </c>
-      <c r="G32" s="47" t="s">
+      <c r="G32" s="38" t="s">
         <v>504</v>
       </c>
-      <c r="H32" s="49">
+      <c r="H32" s="42">
         <v>2</v>
       </c>
-      <c r="I32" s="47" t="s">
+      <c r="I32" s="38" t="s">
         <v>511</v>
       </c>
-      <c r="J32" s="47" t="s">
+      <c r="J32" s="38" t="s">
         <v>512</v>
       </c>
-      <c r="K32" s="58">
+      <c r="K32" s="52">
         <f>10%*5</f>
         <v>0.5</v>
       </c>
     </row>
     <row r="33" spans="1:11">
-      <c r="A33" s="47"/>
-      <c r="B33" s="47"/>
-      <c r="C33" s="48"/>
-      <c r="D33" s="49"/>
-      <c r="E33" s="47"/>
-      <c r="F33" s="47"/>
-      <c r="G33" s="47"/>
-      <c r="H33" s="49"/>
-      <c r="I33" s="47" t="s">
+      <c r="A33" s="38"/>
+      <c r="B33" s="38"/>
+      <c r="C33" s="41"/>
+      <c r="D33" s="42"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="38"/>
+      <c r="H33" s="42"/>
+      <c r="I33" s="38" t="s">
         <v>513</v>
       </c>
-      <c r="J33" s="47" t="s">
+      <c r="J33" s="38" t="s">
         <v>514</v>
       </c>
-      <c r="K33" s="59">
+      <c r="K33" s="53">
         <f>6%*5</f>
         <v>0.3</v>
       </c>
     </row>
     <row r="34" ht="43" customHeight="1" spans="1:11">
-      <c r="A34" s="47"/>
-      <c r="B34" s="47"/>
-      <c r="C34" s="48"/>
-      <c r="D34" s="49"/>
-      <c r="E34" s="47"/>
-      <c r="F34" s="47"/>
-      <c r="G34" s="47"/>
-      <c r="H34" s="49"/>
-      <c r="I34" s="47" t="s">
+      <c r="A34" s="38"/>
+      <c r="B34" s="38"/>
+      <c r="C34" s="41"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="38"/>
+      <c r="F34" s="38"/>
+      <c r="G34" s="38"/>
+      <c r="H34" s="42"/>
+      <c r="I34" s="38" t="s">
         <v>515</v>
       </c>
-      <c r="J34" s="47" t="s">
+      <c r="J34" s="38" t="s">
         <v>516</v>
       </c>
-      <c r="K34" s="59">
+      <c r="K34" s="53">
         <f>3%*5</f>
         <v>0.15</v>
       </c>
     </row>
     <row r="36" ht="45" spans="1:8">
-      <c r="A36" s="50" t="s">
+      <c r="A36" s="47" t="s">
         <v>517</v>
       </c>
-      <c r="B36" s="50" t="s">
+      <c r="B36" s="47" t="s">
         <v>518</v>
       </c>
-      <c r="C36" s="50" t="s">
+      <c r="C36" s="47" t="s">
         <v>519</v>
       </c>
-      <c r="D36" s="50" t="s">
+      <c r="D36" s="47" t="s">
         <v>520</v>
       </c>
-      <c r="E36" s="51" t="s">
+      <c r="E36" s="47" t="s">
         <v>521</v>
       </c>
-      <c r="F36" s="51" t="s">
+      <c r="F36" s="47" t="s">
         <v>522</v>
       </c>
-      <c r="G36" s="51" t="s">
+      <c r="G36" s="47" t="s">
         <v>523</v>
       </c>
-      <c r="H36" s="51" t="s">
+      <c r="H36" s="47" t="s">
         <v>524</v>
       </c>
     </row>
     <row r="37" ht="60" spans="1:8">
-      <c r="A37" s="50"/>
-      <c r="B37" s="50"/>
-      <c r="C37" s="50"/>
-      <c r="D37" s="50"/>
-      <c r="E37" s="51" t="s">
+      <c r="A37" s="47"/>
+      <c r="B37" s="47"/>
+      <c r="C37" s="47"/>
+      <c r="D37" s="47"/>
+      <c r="E37" s="47" t="s">
         <v>525</v>
       </c>
-      <c r="F37" s="51" t="s">
+      <c r="F37" s="47" t="s">
         <v>526</v>
       </c>
-      <c r="G37" s="51" t="s">
+      <c r="G37" s="47" t="s">
         <v>527</v>
       </c>
-      <c r="H37" s="51" t="s">
+      <c r="H37" s="47" t="s">
         <v>528</v>
       </c>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="52"/>
-      <c r="B38" s="52"/>
-      <c r="C38" s="52"/>
-      <c r="D38" s="52"/>
-      <c r="E38" s="53"/>
-      <c r="F38" s="53"/>
-      <c r="G38" s="53"/>
-      <c r="H38" s="53"/>
+      <c r="A38" s="48"/>
+      <c r="B38" s="48"/>
+      <c r="C38" s="48"/>
+      <c r="D38" s="48"/>
+      <c r="E38" s="49"/>
+      <c r="F38" s="49"/>
+      <c r="G38" s="49"/>
+      <c r="H38" s="49"/>
     </row>
     <row r="39" ht="60" spans="1:10">
-      <c r="A39" s="54" t="s">
+      <c r="A39" s="50" t="s">
         <v>529</v>
       </c>
-      <c r="B39" s="54" t="s">
+      <c r="B39" s="50" t="s">
         <v>530</v>
       </c>
-      <c r="C39" s="54" t="s">
+      <c r="C39" s="50" t="s">
         <v>531</v>
       </c>
-      <c r="D39" s="54" t="s">
+      <c r="D39" s="50" t="s">
         <v>532</v>
       </c>
-      <c r="E39" s="51" t="s">
+      <c r="E39" s="47" t="s">
         <v>533</v>
       </c>
-      <c r="F39" s="51" t="s">
+      <c r="F39" s="47" t="s">
         <v>534</v>
       </c>
-      <c r="G39" s="51" t="s">
+      <c r="G39" s="47" t="s">
         <v>535</v>
       </c>
-      <c r="H39" s="51" t="s">
+      <c r="H39" s="47" t="s">
         <v>536</v>
       </c>
-      <c r="I39" s="60"/>
-      <c r="J39" s="60"/>
+      <c r="I39" s="54"/>
+      <c r="J39" s="54"/>
     </row>
     <row r="40" ht="60" spans="1:10">
-      <c r="A40" s="55"/>
-      <c r="B40" s="55"/>
-      <c r="C40" s="55"/>
-      <c r="D40" s="55"/>
-      <c r="E40" s="51" t="s">
+      <c r="A40" s="51"/>
+      <c r="B40" s="51"/>
+      <c r="C40" s="51"/>
+      <c r="D40" s="51"/>
+      <c r="E40" s="47" t="s">
         <v>537</v>
       </c>
-      <c r="F40" s="51" t="s">
+      <c r="F40" s="47" t="s">
         <v>538</v>
       </c>
-      <c r="G40" s="50" t="s">
+      <c r="G40" s="47" t="s">
         <v>539</v>
       </c>
-      <c r="H40" s="51" t="s">
+      <c r="H40" s="47" t="s">
         <v>540</v>
       </c>
-      <c r="I40" s="60"/>
-      <c r="J40" s="60"/>
+      <c r="I40" s="54"/>
+      <c r="J40" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="24">
@@ -8467,64 +8449,67 @@
       <c r="A22" t="s">
         <v>610</v>
       </c>
+      <c r="B22" t="s">
+        <v>611</v>
+      </c>
       <c r="C22" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C23" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C24" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C25" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C26" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C27" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C28" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C29" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
   </sheetData>

--- a/data/excel/Thiết kế game.xlsx
+++ b/data/excel/Thiết kế game.xlsx
@@ -6903,7 +6903,7 @@
         <v>504</v>
       </c>
       <c r="H32" s="42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I32" s="38" t="s">
         <v>511</v>

--- a/data/excel/Thiết kế game.xlsx
+++ b/data/excel/Thiết kế game.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11460" activeTab="4"/>
+    <workbookView windowWidth="27945" windowHeight="12180" firstSheet="1" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Ý tưởng chung" sheetId="1" r:id="rId1"/>
@@ -13,8 +13,9 @@
     <sheet name="Termynology" sheetId="4" r:id="rId4"/>
     <sheet name="Balanced Dummy " sheetId="5" r:id="rId5"/>
     <sheet name="Destroyer class" sheetId="6" r:id="rId6"/>
-    <sheet name="Item" sheetId="7" r:id="rId7"/>
-    <sheet name="status" sheetId="8" r:id="rId8"/>
+    <sheet name="Ranger class" sheetId="12" r:id="rId7"/>
+    <sheet name="Item" sheetId="7" r:id="rId8"/>
+    <sheet name="status" sheetId="8" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="627">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="738">
   <si>
     <t>Tên game</t>
   </si>
@@ -144,6 +145,15 @@
     <t>Action Points. AP may become negative through action costs or modifiers.</t>
   </si>
   <si>
+    <t>Global turn</t>
+  </si>
+  <si>
+    <t>One team's turn in the battle-wide sequence. Each team turn advances the global turn counter by 1.</t>
+  </si>
+  <si>
+    <t>One specific team's opportunity to act. One team turn equals one global turn; it does not include the opposing team's turn.</t>
+  </si>
+  <si>
     <t>I. Starting Team</t>
   </si>
   <si>
@@ -465,52 +475,121 @@
     <t>Defeat the opposing team's main character to win.</t>
   </si>
   <si>
-    <t>XI. Skill Cooldown</t>
+    <t>XI. Effect Duration</t>
+  </si>
+  <si>
+    <t>Default unit</t>
+  </si>
+  <si>
+    <t>Unless explicitly stated otherwise, duration is measured in global turns.</t>
+  </si>
+  <si>
+    <t>Application</t>
+  </si>
+  <si>
+    <t>An effect becomes active when applied. Its application turn counts as the first turn of its duration, regardless of when during that turn it is applied.</t>
+  </si>
+  <si>
+    <t>Expiration</t>
+  </si>
+  <si>
+    <t>An effect with duration D, applied on global turn T, remains active through global turn T + D − 1 and expires at the end of that turn.</t>
+  </si>
+  <si>
+    <t>Duration refresh</t>
+  </si>
+  <si>
+    <t>For effects that allow refreshing, reapplication on global turn R resets expiration to the end of global turn R + D − 1.</t>
+  </si>
+  <si>
+    <t>Trigger timing</t>
+  </si>
+  <si>
+    <t>An effect must already be active when its trigger occurs. Applying an effect after that trigger does not activate it retroactively.</t>
+  </si>
+  <si>
+    <t>Skill effect scope</t>
+  </si>
+  <si>
+    <t>A skill's duration applies to all timed effects it applies, unless an effect explicitly specifies a different duration.</t>
+  </si>
+  <si>
+    <t>XII. Skill Cooldown</t>
   </si>
   <si>
     <t>Definition</t>
   </si>
   <si>
-    <t>Each character tracks a separate remaining cooldown for each skill, measured in global turns. One team's turn counts as one global turn. Remaining cooldown cannot fall below 0.</t>
-  </si>
-  <si>
-    <t>Initialization and use</t>
-  </si>
-  <si>
-    <t>At battle initialization and whenever skill use is committed, set remaining cooldown to the applicable cooldown duration. On use, assign cooldown before resolving the skill's effects and effects triggered by that use.</t>
-  </si>
-  <si>
-    <t>Readiness and reuse</t>
-  </si>
-  <si>
-    <t>At 0 remaining cooldown, a skill is ready and may be used through a valid action slot, including again in the same owning-team turn. Normal usage conditions, AP costs, negative-AP rules and slot consumption still apply.</t>
-  </si>
-  <si>
-    <t>XII. Skill Cooldown Recovery</t>
+    <t>Each character tracks a separate remaining cooldown for each skill, measured in global turns and governed by the Effect Duration rules.</t>
+  </si>
+  <si>
+    <t>Initialization</t>
+  </si>
+  <si>
+    <t>At battle initialization, set each skill's remaining cooldown to its applicable cooldown duration. Each team's initial countdown begins on its first team turn.</t>
+  </si>
+  <si>
+    <t>On cast</t>
+  </si>
+  <si>
+    <t>When a skill cast is committed, set its remaining cooldown to the applicable cooldown duration before resolving its effects. The casting turn counts as the first cooldown turn.</t>
+  </si>
+  <si>
+    <t>Readiness</t>
+  </si>
+  <si>
+    <t>A skill is ready when its remaining cooldown reaches 0. Readiness does not bypass MP requirements, usage conditions, or action-slot requirements where applicable.</t>
+  </si>
+  <si>
+    <t>Reuse</t>
+  </si>
+  <si>
+    <t>If a skill becomes ready during a team turn through an explicit cooldown-reduction effect, it may be used again that turn, subject to its normal requirements. Each cast starts a new cooldown.</t>
+  </si>
+  <si>
+    <t>XIII. Cooldown Recovery</t>
   </si>
   <si>
     <t>Default timing</t>
   </si>
   <si>
-    <t>Each team's first default recovery occurs at the beginning of its first team turn. From then on, that team receives default recovery once at the beginning of every global turn, including the opponent's turns, before initial slot assignment.</t>
-  </si>
-  <si>
-    <t>Default amount and scope</t>
-  </si>
-  <si>
-    <t>Unless explicitly modified, each default recovery reduces remaining cooldown by 1 for all skills of living characters on the affected team, regardless of AP or action eligibility. Turns without actions still count; additional actions or slots do not trigger additional recovery.</t>
-  </si>
-  <si>
-    <t>Modifier application</t>
-  </si>
-  <si>
-    <t>Resolve modifiers in their defined effect order and specified scope. Changes to remaining cooldown apply immediately, including before a team's first turn; reductions stop at 0 and excess recovery is discarded. Changes to cooldown duration or default recovery affect subsequent uses or recovery events respectively, unless explicitly stated otherwise.</t>
+    <t>Each team's first default cooldown recovery occurs at the end of its first team turn. Thereafter, recovery occurs at the end of every global turn, including the opposing team's turns.</t>
+  </si>
+  <si>
+    <t>Default amount</t>
+  </si>
+  <si>
+    <t>Each default recovery reduces remaining cooldown by 1. Remaining cooldown cannot fall below 0; excess recovery is discarded.</t>
+  </si>
+  <si>
+    <t>Scope</t>
+  </si>
+  <si>
+    <t>Default recovery applies to all skills of living characters, regardless of AP or action eligibility. Turns without actions still count.</t>
   </si>
   <si>
     <t>Action independence</t>
   </si>
   <si>
-    <t>Recovery grants no action slot or AP and does not bypass slot-transfer restrictions. Each subsequent skill use assigns cooldown again; earlier recovery does not carry over to that new cooldown.</t>
+    <t>Additional actions, hits, or casts do not grant additional default recovery. Recovery grants no AP or action slots.</t>
+  </si>
+  <si>
+    <t>Remaining cooldown modifiers</t>
+  </si>
+  <si>
+    <t>Effects that directly change remaining cooldown apply immediately, according to their specified timing and scope.</t>
+  </si>
+  <si>
+    <t>Duration modifiers</t>
+  </si>
+  <si>
+    <t>Changes to cooldown duration affect subsequent cooldown assignments. They do not change an existing remaining cooldown unless explicitly stated.</t>
+  </si>
+  <si>
+    <t>Recovery modifiers</t>
+  </si>
+  <si>
+    <t>Changes to cooldown recovery affect subsequent recovery events according to their specified amount, timing, and scope.</t>
   </si>
   <si>
     <t>Term (stat)</t>
@@ -1134,6 +1213,135 @@
     <t>The number of Stun Count stacks required to stun the character.</t>
   </si>
   <si>
+    <t>Term (action)</t>
+  </si>
+  <si>
+    <t>Normal Attack</t>
+  </si>
+  <si>
+    <t>An offensive action that generates hits based on Multi-Hit Rate. Uses the weapon’s targeting and area rules.</t>
+  </si>
+  <si>
+    <t>Offensive Cast</t>
+  </si>
+  <si>
+    <t>A skill use that directly attacks enemies. Uses the skill’s own targeting, area, and damage rules. Does not generate hits or use Multi-Hit Rate.</t>
+  </si>
+  <si>
+    <t>Hit</t>
+  </si>
+  <si>
+    <t>An individual strike generated by a normal attack. Each affected recipient receives a separate hit check. A hit may land or miss.</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>A character explicitly selected as a primary recipient of an attack or skill. Characters affected only by its area are secondary recipients, not selected targets.</t>
+  </si>
+  <si>
+    <t>Cast</t>
+  </si>
+  <si>
+    <t>To commit a skill use after meeting its requirements, before resolving its effects. Applies to damaging, healing, buffing, and debuffing skills.</t>
+  </si>
+  <si>
+    <t>When Attacking</t>
+  </si>
+  <si>
+    <t>Triggers once per normal attack that lands at least one hit, regardless of the number of hits or recipients struck.</t>
+  </si>
+  <si>
+    <t>When Casting Offensively</t>
+  </si>
+  <si>
+    <t>Triggers once per offensive cast that directly strikes at least one enemy, regardless of the number of recipients struck.</t>
+  </si>
+  <si>
+    <t>When Hitting</t>
+  </si>
+  <si>
+    <t>Triggers each time a normal-attack hit lands on a recipient.</t>
+  </si>
+  <si>
+    <t>When Targeting</t>
+  </si>
+  <si>
+    <t>Triggers once when the character commits a normal attack or skill with one or more selected primary targets, regardless of the outcome.</t>
+  </si>
+  <si>
+    <t>When Casting</t>
+  </si>
+  <si>
+    <t>Triggers once when the character commits a valid skill use, before its effects resolve.</t>
+  </si>
+  <si>
+    <t>When Being Attacked</t>
+  </si>
+  <si>
+    <t>Triggers once per incoming normal attack that lands at least one hit on the character, regardless of the number of hits.</t>
+  </si>
+  <si>
+    <t>When Receiving an Offensive Cast</t>
+  </si>
+  <si>
+    <t>Triggers once per offensive cast that directly strikes the character.</t>
+  </si>
+  <si>
+    <t>When Being Hit</t>
+  </si>
+  <si>
+    <t>Triggers separately for each normal-attack hit that lands on the character.</t>
+  </si>
+  <si>
+    <t>When Being Targeted</t>
+  </si>
+  <si>
+    <t>Triggers once when the character is selected as a primary target of a committed normal attack or skill, regardless of the outcome.</t>
+  </si>
+  <si>
+    <t>When Affected by a Skill</t>
+  </si>
+  <si>
+    <t>Triggers once per skill use that successfully applies a direct effect to the character, including damage, healing, buffs, or debuffs. Includes primary and secondary recipients.</t>
+  </si>
+  <si>
+    <t>Hit Scope</t>
+  </si>
+  <si>
+    <t>Only normal attacks generate hits. Skills do not generate hits.</t>
+  </si>
+  <si>
+    <t>Target Selection</t>
+  </si>
+  <si>
+    <t>Targeting occurs when an action is committed. Previewing or hovering over a target does not count. Area effects do not count as selecting additional primary targets.</t>
+  </si>
+  <si>
+    <t>Passive Casting</t>
+  </si>
+  <si>
+    <t>A passive skill with an automatic casting mechanism can trigger When Casting. A passive stat bonus alone is not a cast.</t>
+  </si>
+  <si>
+    <t>Repeated Effects</t>
+  </si>
+  <si>
+    <t>Damage-over-time ticks and transferred damage do not create new attacks, hits, or casts, and do not trigger the receiving events listed above. Applying a damage-over-time effect initially can trigger When Affected by a Skill.</t>
+  </si>
+  <si>
+    <t>Multiple Recipients</t>
+  </si>
+  <si>
+    <t>Action-level triggers occur once per action. Recipient-level triggers are checked separately for each qualifying character.</t>
+  </si>
+  <si>
+    <t>Auto-Cast</t>
+  </si>
+  <si>
+    <t>Automatically commits a skill cast when its specified trigger occurs and all casting requirements are met. Requires no manual input or action slot. Applies the skill’s specified costs, cooldown, targeting, and effects, and triggers When Casting.</t>
+  </si>
+  <si>
     <t>Dummy Character</t>
   </si>
   <si>
@@ -1482,7 +1690,7 @@
     <t>Character</t>
   </si>
   <si>
-    <t>Bluetooth</t>
+    <t>Harald Bluetooth</t>
   </si>
   <si>
     <t>Weapon</t>
@@ -1509,9 +1717,6 @@
     <t>Spare</t>
   </si>
   <si>
-    <t>Target</t>
-  </si>
-  <si>
     <t>Area of Effect</t>
   </si>
   <si>
@@ -1524,7 +1729,7 @@
     <t>Frozen Axe</t>
   </si>
   <si>
-    <t>Deals initial skill damage, applies damage over time, and inflicts Freeze on enemies in the target row.</t>
+    <t>Deals initial skill damage, applies damage over time, and inflicts immobilized  on enemies in the target row.</t>
   </si>
   <si>
     <t>Front</t>
@@ -1560,7 +1765,7 @@
     <t>Bluetooth Connection</t>
   </si>
   <si>
-    <t>Passive</t>
+    <t>Passive, Auto-cast</t>
   </si>
   <si>
     <t>At the start of each team turn, links with the two allies with the lowest HP to share damage. Grants Fortify and Resistance based on Bluetooth’s current DEF and SDEF, respectively.</t>
@@ -1569,7 +1774,7 @@
     <t>2 Lowest health teamates</t>
   </si>
   <si>
-    <t>Shared damage before migation</t>
+    <t>Shared damage after migation</t>
   </si>
   <si>
     <t>10%*SL</t>
@@ -1578,19 +1783,19 @@
     <t>Fortify</t>
   </si>
   <si>
-    <t>6%*SL</t>
+    <t>3%*SL</t>
   </si>
   <si>
     <t>Resistance</t>
   </si>
   <si>
-    <t>3%*SL</t>
+    <t>1.5%*SL</t>
   </si>
   <si>
     <t>Specialization 1</t>
   </si>
   <si>
-    <t>The Viking Conqueror</t>
+    <t>Viking Striker</t>
   </si>
   <si>
     <t>Crushes enemy formations with brute force, sweeping attacks, and a devastating finishing strike.</t>
@@ -1605,7 +1810,7 @@
   </si>
   <si>
     <t>S1.1.2 
-Sub target damage penalty - 25%</t>
+Deadly strike doesnt require condititon</t>
   </si>
   <si>
     <t>S1.1.3 
@@ -1615,12 +1820,12 @@
     <t>S1.1.4 Increased AP recovery +20%</t>
   </si>
   <si>
-    <t>S1.2.1 1
+    <t>S1.2.1 
 Base AP recovery +10</t>
   </si>
   <si>
     <t>S1.2.2 
-Deadly strike doesnt require condititon</t>
+Sub target damage penalty - 25%</t>
   </si>
   <si>
     <t>S1.2.3 
@@ -1636,7 +1841,7 @@
     <t>Specialization 2</t>
   </si>
   <si>
-    <t>The Viking Unifier</t>
+    <t>Viking Unifier</t>
   </si>
   <si>
     <t>Links and protects allies, weakens enemies, and sustains the team through shared strength.</t>
@@ -1667,15 +1872,172 @@
   </si>
   <si>
     <t xml:space="preserve">S2.2.2
-Frozen Axe applied Sunder -20% </t>
+Frozen Axe applied Exposure -20% </t>
   </si>
   <si>
     <t>S2.2.3
-Each team turn, restores 5% Max HP</t>
+When being attacked, has 20% chance to restore 0.5%  Max HP</t>
   </si>
   <si>
     <t>S2.2.4
-When attacked, has 20% chance to restore 1%  Max HP</t>
+Each team turn, restores 2.5% Max HP</t>
+  </si>
+  <si>
+    <t>Ranger</t>
+  </si>
+  <si>
+    <t>Robin Hood</t>
+  </si>
+  <si>
+    <t>Ranger weapon</t>
+  </si>
+  <si>
+    <t>Arrow</t>
+  </si>
+  <si>
+    <t>Golden Arrow Shot</t>
+  </si>
+  <si>
+    <t>Fires an unavoidable arrow that deals  skill damage.</t>
+  </si>
+  <si>
+    <t>Any</t>
+  </si>
+  <si>
+    <t>Satk</t>
+  </si>
+  <si>
+    <t>4.8*K*30%*SL</t>
+  </si>
+  <si>
+    <t>Man Under the Hood</t>
+  </si>
+  <si>
+    <t>Grants Invisible and increased Critical Hit Chance. Immediately grants another action slot.</t>
+  </si>
+  <si>
+    <t>Self</t>
+  </si>
+  <si>
+    <t>increased CHC</t>
+  </si>
+  <si>
+    <t>Thief’s Mark</t>
+  </si>
+  <si>
+    <t>Passive, Auto-Cast</t>
+  </si>
+  <si>
+    <t>At the start of each team turn, marks the living enemy that has dealt the most total damage to your team during the battle. The marked enemy takes increased damage from Robin Hood.</t>
+  </si>
+  <si>
+    <t>Highest-damage living enemy</t>
+  </si>
+  <si>
+    <t>Damage received</t>
+  </si>
+  <si>
+    <t>4%*SL</t>
+  </si>
+  <si>
+    <t>Satk (upgrade)</t>
+  </si>
+  <si>
+    <t>4.8*K*20%*SL</t>
+  </si>
+  <si>
+    <t>Outlaw’s Mark</t>
+  </si>
+  <si>
+    <t>Marks the living enemy that has dealt the most total damage to your team during the battle, plus two other random living enemies. Marked enemies take increased damage.</t>
+  </si>
+  <si>
+    <t>Primary target and 2 other random enemies</t>
+  </si>
+  <si>
+    <t>Golden Arrow</t>
+  </si>
+  <si>
+    <t>An unrivaled archer who strikes with precision and escapes unharmed.</t>
+  </si>
+  <si>
+    <t>S1
+Unlocks Man Under the Hood.</t>
+  </si>
+  <si>
+    <t>S1.1.1
+Atk + 20%</t>
+  </si>
+  <si>
+    <t>S1.1.2 
+Base Acc +20%
+Multi-hit rate +10%</t>
+  </si>
+  <si>
+    <t>S1.1.3
+Man Under the Hood immediately restores 50 AP. Its cooldown is reduced by 2.</t>
+  </si>
+  <si>
+    <t>S1.1.4
+When hitting, has a 50% chance to trigger Golden Arrow Shot. Its cooldown and mana cost still applied</t>
+  </si>
+  <si>
+    <t>S1.2.1
+Golden Arrow Shot SATK +20%.</t>
+  </si>
+  <si>
+    <t>S1.2.2
+Golden Arrow Shot has a 20% chance to preserve the current action slot.</t>
+  </si>
+  <si>
+    <t>S1.2.3
+Golden Arrow Shot applies +1 Base Stun Count. Its SATK increases by 10%.</t>
+  </si>
+  <si>
+    <t>S1.2.4
+Golden Arrow Shot can critically strike using the character’s CHC and CDB.</t>
+  </si>
+  <si>
+    <t>People's Champion</t>
+  </si>
+  <si>
+    <t>Punishes enemies that have dealt the most damage to his team.</t>
+  </si>
+  <si>
+    <t>S2
+Unlocks Thief’s Mark.</t>
+  </si>
+  <si>
+    <t>S2.1.1
+Thief’s Mark Stat Effectiveness +20%.</t>
+  </si>
+  <si>
+    <t>S2.1.2
+Thief’s Mark costs no mana.</t>
+  </si>
+  <si>
+    <t>S2.1.3
+Thief’s Mark affects 1 additional targets follow its rules</t>
+  </si>
+  <si>
+    <t>S2.2.1
+Upgrades Thief’s Mark with Outlaw’s Mark, retaining all applicable passive upgrades to Thief’s Mark.</t>
+  </si>
+  <si>
+    <t>S2.2.2
+Outlaw’s Mark duration +1.</t>
+  </si>
+  <si>
+    <t>S2.3.1
+Base Eva +20%</t>
+  </si>
+  <si>
+    <t>S2.3.2
+Thief’s Mark also deals skill damage using its upgraded SATK.</t>
+  </si>
+  <si>
+    <t>S2.3.3
+Thief’s Mark also applies Silence for 2 global turns.</t>
   </si>
   <si>
     <t>Item</t>
@@ -1714,12 +2076,6 @@
     <t>Line adjection</t>
   </si>
   <si>
-    <t>Ranger weapon</t>
-  </si>
-  <si>
-    <t>Any</t>
-  </si>
-  <si>
     <t>Piercer weapon</t>
   </si>
   <si>
@@ -1750,9 +2106,6 @@
     <t>Ammunition</t>
   </si>
   <si>
-    <t>Arrow</t>
-  </si>
-  <si>
     <t>Each character has four equipment slots: one weapon slot, equipped with one of the available weapon types; one body armor slot; one accessory slot; and one off-hand slot, equipped with exactly one of the following: Rune Enhancement, Shield, Focus, or Ammunition. Only one item can occupy each slot.</t>
   </si>
   <si>
@@ -1864,7 +2217,7 @@
     <t>Damage over Time</t>
   </si>
   <si>
-    <t xml:space="preserve">Deals damage at the start of each global turn </t>
+    <t>Deals damage at the end of each global turn. multiple DOT source can stack with its own modifies</t>
   </si>
   <si>
     <t>Prevents receiving action slots and performing voluntary actions, including attacks, defending, swaps, and active skills. Sets Character Base AP Recovery to 0. Passive skills remain usable.</t>
@@ -2613,7 +2966,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2658,9 +3011,6 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2678,6 +3028,57 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2705,21 +3106,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2734,6 +3120,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -3413,7 +3805,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C63"/>
+  <dimension ref="A1:C76"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="29.2857142857143" customWidth="1"/>
@@ -3422,7 +3814,7 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="1" ht="61" customHeight="1" spans="1:1">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="73" t="s">
         <v>25</v>
       </c>
     </row>
@@ -3471,264 +3863,264 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="65" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="65" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="C7" s="65" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="23" t="s">
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="65" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="65" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="65" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="23" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="23" t="s">
         <v>41</v>
-      </c>
-      <c r="B9" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" s="23" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="23" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="23" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B11" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="23" t="s">
         <v>46</v>
-      </c>
-      <c r="C11" s="23" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="23" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B12" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="23" t="s">
         <v>48</v>
-      </c>
-      <c r="C12" s="23" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="23" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B13" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="23" t="s">
         <v>50</v>
-      </c>
-      <c r="C13" s="23" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="23" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B14" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" s="23" t="s">
         <v>52</v>
-      </c>
-      <c r="C14" s="23" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="23" t="s">
         <v>54</v>
-      </c>
-      <c r="B15" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="C15" s="23" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="23" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="23" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B17" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="23" t="s">
         <v>59</v>
-      </c>
-      <c r="C17" s="23" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="B18" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18" s="23" t="s">
         <v>61</v>
-      </c>
-      <c r="B18" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="C18" s="23" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="23" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="23" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B20" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" s="23" t="s">
         <v>66</v>
-      </c>
-      <c r="C20" s="23" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="23" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B21" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" s="23" t="s">
         <v>68</v>
-      </c>
-      <c r="C21" s="23" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="23" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B22" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="C22" s="23" t="s">
         <v>70</v>
-      </c>
-      <c r="C22" s="23" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="23" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B23" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="C23" s="23" t="s">
         <v>72</v>
-      </c>
-      <c r="C23" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="23" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B24" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" s="23" t="s">
         <v>74</v>
-      </c>
-      <c r="C24" s="23" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="B25" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="C25" t="s">
         <v>76</v>
-      </c>
-      <c r="B25" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="C25" s="23" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="23" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="B27" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="C27" s="23" t="s">
         <v>81</v>
-      </c>
-      <c r="B27" s="23" t="s">
-        <v>82</v>
-      </c>
-      <c r="C27" s="23" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="23" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="B29" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="C29" s="23" t="s">
         <v>86</v>
-      </c>
-      <c r="B29" s="23" t="s">
-        <v>82</v>
-      </c>
-      <c r="C29" s="23" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="23" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C30" s="23" t="s">
         <v>88</v>
@@ -3739,7 +4131,7 @@
         <v>89</v>
       </c>
       <c r="B31" s="23" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C31" s="23" t="s">
         <v>90</v>
@@ -3750,150 +4142,150 @@
         <v>89</v>
       </c>
       <c r="B32" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="C32" s="23" t="s">
         <v>91</v>
-      </c>
-      <c r="C32" s="23" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="23" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B33" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="C33" s="23" t="s">
         <v>93</v>
-      </c>
-      <c r="C33" s="23" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="23" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B34" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="C34" s="23" t="s">
         <v>95</v>
-      </c>
-      <c r="C34" s="23" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="23" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B35" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="C35" s="23" t="s">
         <v>97</v>
-      </c>
-      <c r="C35" s="23" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="B36" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="C36" s="23" t="s">
         <v>99</v>
-      </c>
-      <c r="B36" s="23" t="s">
-        <v>82</v>
-      </c>
-      <c r="C36" s="23" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="23" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="B37" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="C37" s="23" t="s">
         <v>101</v>
-      </c>
-      <c r="C37" s="23" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="23" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B38" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="C38" s="23" t="s">
         <v>103</v>
-      </c>
-      <c r="C38" s="23" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="23" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B39" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="C39" s="23" t="s">
         <v>105</v>
-      </c>
-      <c r="C39" s="23" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="23" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B40" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="C40" s="23" t="s">
         <v>107</v>
-      </c>
-      <c r="C40" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="23" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B41" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="C41" s="23" t="s">
         <v>109</v>
-      </c>
-      <c r="C41" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="23" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B42" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="C42" t="s">
         <v>111</v>
-      </c>
-      <c r="C42" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="B43" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="C43" t="s">
         <v>113</v>
-      </c>
-      <c r="B43" s="23" t="s">
-        <v>82</v>
-      </c>
-      <c r="C43" s="23" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="23" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="B44" s="23" t="s">
-        <v>84</v>
-      </c>
-      <c r="C44" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="C44" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="23" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B45" s="23" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="C45" s="23" t="s">
         <v>117</v>
@@ -3901,79 +4293,79 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="B46" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="C46" s="23" t="s">
         <v>118</v>
-      </c>
-      <c r="B46" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="C46" s="23" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="23" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B47" s="23" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C47" s="23" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="23" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B48" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="C48" s="23" t="s">
         <v>123</v>
-      </c>
-      <c r="C48" s="23" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="23" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B49" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="C49" s="23" t="s">
         <v>125</v>
-      </c>
-      <c r="C49" s="23" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="23" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B50" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="C50" s="23" t="s">
         <v>127</v>
-      </c>
-      <c r="C50" s="23" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="B51" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="C51" s="23" t="s">
         <v>129</v>
-      </c>
-      <c r="B51" s="23" t="s">
-        <v>130</v>
-      </c>
-      <c r="C51" s="23" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="23" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="B52" s="23" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C52" s="23" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -3981,120 +4373,263 @@
         <v>132</v>
       </c>
       <c r="B53" s="23" t="s">
-        <v>135</v>
-      </c>
-      <c r="C53" t="s">
-        <v>136</v>
+        <v>133</v>
+      </c>
+      <c r="C53" s="23" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="23" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B54" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="C54" s="23" t="s">
         <v>137</v>
-      </c>
-      <c r="C54" s="23" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="B55" s="23" t="s">
+        <v>138</v>
+      </c>
+      <c r="C55" t="s">
         <v>139</v>
       </c>
-      <c r="B55" s="23" t="s">
-        <v>64</v>
-      </c>
-      <c r="C55" s="23" t="s">
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="B56" s="23" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="A56" t="s">
-        <v>139</v>
-      </c>
-      <c r="B56" t="s">
+      <c r="C56" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="C56" t="s">
+    </row>
+    <row r="57" customFormat="1" spans="1:3">
+      <c r="A57" s="23" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="54" t="s">
+      <c r="B57" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="C57" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="B57" s="54" t="s">
+    </row>
+    <row r="58" customFormat="1" spans="1:3">
+      <c r="A58" t="s">
+        <v>142</v>
+      </c>
+      <c r="B58" t="s">
         <v>144</v>
       </c>
-      <c r="C57" s="54" t="s">
+      <c r="C58" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="58" customFormat="1" ht="30" customHeight="1" spans="1:3">
-      <c r="A58" s="54" t="s">
-        <v>143</v>
-      </c>
-      <c r="B58" s="54" t="s">
+    <row r="59" customFormat="1" spans="1:3">
+      <c r="A59" s="65" t="s">
         <v>146</v>
       </c>
-      <c r="C58" s="54" t="s">
+      <c r="B59" s="65" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="59" customFormat="1" ht="30" customHeight="1" spans="1:3">
-      <c r="A59" s="54" t="s">
-        <v>143</v>
-      </c>
-      <c r="B59" s="54" t="s">
+      <c r="C59" s="65" t="s">
         <v>148</v>
       </c>
-      <c r="C59" s="54" t="s">
+    </row>
+    <row r="60" customFormat="1" spans="1:3">
+      <c r="A60" s="65" t="s">
+        <v>146</v>
+      </c>
+      <c r="B60" s="65" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="60" customFormat="1" ht="30" customHeight="1" spans="1:3">
-      <c r="A60" s="54" t="s">
+      <c r="C60" s="65" t="s">
         <v>150</v>
       </c>
-      <c r="B60" s="54" t="s">
+    </row>
+    <row r="61" customFormat="1" spans="1:3">
+      <c r="A61" s="65" t="s">
+        <v>146</v>
+      </c>
+      <c r="B61" s="65" t="s">
         <v>151</v>
       </c>
-      <c r="C60" s="54" t="s">
+      <c r="C61" s="65" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="61" customFormat="1" ht="30" customHeight="1" spans="1:3">
-      <c r="A61" s="54" t="s">
-        <v>150</v>
-      </c>
-      <c r="B61" s="54" t="s">
+    <row r="62" customFormat="1" spans="1:3">
+      <c r="A62" s="65" t="s">
+        <v>146</v>
+      </c>
+      <c r="B62" s="65" t="s">
         <v>153</v>
       </c>
-      <c r="C61" s="54" t="s">
+      <c r="C62" s="65" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="62" customFormat="1" ht="30" customHeight="1" spans="1:3">
-      <c r="A62" s="54" t="s">
-        <v>150</v>
-      </c>
-      <c r="B62" s="54" t="s">
+    <row r="63" spans="1:3">
+      <c r="A63" s="65" t="s">
+        <v>146</v>
+      </c>
+      <c r="B63" s="65" t="s">
         <v>155</v>
       </c>
-      <c r="C62" s="54" t="s">
+      <c r="C63" s="65" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="63" customFormat="1" ht="30" customHeight="1" spans="1:3">
-      <c r="A63" s="54" t="s">
-        <v>150</v>
-      </c>
-      <c r="B63" s="54" t="s">
+    <row r="64" spans="1:3">
+      <c r="A64" s="65" t="s">
+        <v>146</v>
+      </c>
+      <c r="B64" s="65" t="s">
         <v>157</v>
       </c>
-      <c r="C63" s="54" t="s">
+      <c r="C64" s="65" t="s">
         <v>158</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" s="65" t="s">
+        <v>159</v>
+      </c>
+      <c r="B65" s="65" t="s">
+        <v>160</v>
+      </c>
+      <c r="C65" s="65" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" s="65" t="s">
+        <v>159</v>
+      </c>
+      <c r="B66" s="65" t="s">
+        <v>162</v>
+      </c>
+      <c r="C66" s="65" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" s="65" t="s">
+        <v>159</v>
+      </c>
+      <c r="B67" s="65" t="s">
+        <v>164</v>
+      </c>
+      <c r="C67" s="65" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" s="65" t="s">
+        <v>159</v>
+      </c>
+      <c r="B68" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="C68" s="65" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="69" ht="30" spans="1:3">
+      <c r="A69" s="65" t="s">
+        <v>159</v>
+      </c>
+      <c r="B69" s="65" t="s">
+        <v>168</v>
+      </c>
+      <c r="C69" s="65" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" s="65" t="s">
+        <v>170</v>
+      </c>
+      <c r="B70" s="65" t="s">
+        <v>171</v>
+      </c>
+      <c r="C70" s="65" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" s="65" t="s">
+        <v>170</v>
+      </c>
+      <c r="B71" s="65" t="s">
+        <v>173</v>
+      </c>
+      <c r="C71" s="65" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" s="65" t="s">
+        <v>170</v>
+      </c>
+      <c r="B72" s="65" t="s">
+        <v>175</v>
+      </c>
+      <c r="C72" s="65" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" s="65" t="s">
+        <v>170</v>
+      </c>
+      <c r="B73" s="65" t="s">
+        <v>177</v>
+      </c>
+      <c r="C73" s="65" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" s="65" t="s">
+        <v>170</v>
+      </c>
+      <c r="B74" s="65" t="s">
+        <v>179</v>
+      </c>
+      <c r="C74" s="65" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" s="65" t="s">
+        <v>170</v>
+      </c>
+      <c r="B75" s="65" t="s">
+        <v>181</v>
+      </c>
+      <c r="C75" s="65" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" s="65" t="s">
+        <v>170</v>
+      </c>
+      <c r="B76" s="65" t="s">
+        <v>183</v>
+      </c>
+      <c r="C76" s="65" t="s">
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -4109,7 +4644,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E82"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="22.5714285714286" customWidth="1"/>
@@ -4120,898 +4655,1102 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="B1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E1" t="s">
         <v>160</v>
-      </c>
-      <c r="C1" t="s">
-        <v>161</v>
-      </c>
-      <c r="D1" t="s">
-        <v>162</v>
-      </c>
-      <c r="E1" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="B2" t="s">
-        <v>164</v>
+        <v>190</v>
       </c>
       <c r="C2" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="D2" t="s">
-        <v>166</v>
+        <v>192</v>
       </c>
       <c r="E2" t="s">
-        <v>167</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>168</v>
+        <v>194</v>
       </c>
       <c r="B3" t="s">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="C3" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="D3" t="s">
-        <v>170</v>
+        <v>196</v>
       </c>
       <c r="E3" t="s">
-        <v>171</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="B4" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
       <c r="C4" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="D4" t="s">
-        <v>174</v>
+        <v>200</v>
       </c>
       <c r="E4" t="s">
-        <v>175</v>
+        <v>201</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>176</v>
+        <v>202</v>
       </c>
       <c r="B5" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="C5" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="D5" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="E5" t="s">
-        <v>179</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>180</v>
+        <v>206</v>
       </c>
       <c r="B6" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
       <c r="C6" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="D6" t="s">
-        <v>182</v>
+        <v>208</v>
       </c>
       <c r="E6" t="s">
-        <v>183</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>184</v>
+        <v>210</v>
       </c>
       <c r="B7" t="s">
-        <v>185</v>
+        <v>211</v>
       </c>
       <c r="C7" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="D7" t="s">
-        <v>186</v>
+        <v>212</v>
       </c>
       <c r="E7" t="s">
-        <v>187</v>
+        <v>213</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>188</v>
+        <v>214</v>
       </c>
       <c r="B8" t="s">
         <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="D8" t="s">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="E8" t="s">
-        <v>190</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
+        <v>217</v>
+      </c>
+      <c r="B9" t="s">
+        <v>218</v>
+      </c>
+      <c r="C9" t="s">
         <v>191</v>
       </c>
-      <c r="B9" t="s">
-        <v>192</v>
-      </c>
-      <c r="C9" t="s">
-        <v>165</v>
-      </c>
       <c r="D9" t="s">
-        <v>193</v>
+        <v>219</v>
       </c>
       <c r="E9" t="s">
-        <v>194</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>195</v>
+        <v>221</v>
       </c>
       <c r="B10" t="s">
-        <v>196</v>
+        <v>222</v>
       </c>
       <c r="C10" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="E10" t="s">
-        <v>197</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>198</v>
+        <v>224</v>
       </c>
       <c r="B11" t="s">
-        <v>199</v>
+        <v>225</v>
       </c>
       <c r="C11" t="s">
-        <v>200</v>
+        <v>226</v>
       </c>
       <c r="D11" t="s">
-        <v>201</v>
+        <v>227</v>
       </c>
       <c r="E11" t="s">
-        <v>202</v>
+        <v>228</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>203</v>
+        <v>229</v>
       </c>
       <c r="B12" t="s">
-        <v>204</v>
+        <v>230</v>
       </c>
       <c r="C12" t="s">
-        <v>200</v>
+        <v>226</v>
       </c>
       <c r="D12" t="s">
-        <v>205</v>
+        <v>231</v>
       </c>
       <c r="E12" t="s">
-        <v>206</v>
+        <v>232</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>207</v>
+        <v>233</v>
       </c>
       <c r="B13" t="s">
-        <v>208</v>
+        <v>234</v>
       </c>
       <c r="C13" t="s">
-        <v>200</v>
+        <v>226</v>
       </c>
       <c r="D13" t="s">
-        <v>209</v>
+        <v>235</v>
       </c>
       <c r="E13" t="s">
-        <v>210</v>
+        <v>236</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>211</v>
+        <v>237</v>
       </c>
       <c r="B14" t="s">
-        <v>212</v>
+        <v>238</v>
       </c>
       <c r="C14" t="s">
-        <v>200</v>
+        <v>226</v>
       </c>
       <c r="D14" t="s">
-        <v>213</v>
+        <v>239</v>
       </c>
       <c r="E14" t="s">
-        <v>214</v>
+        <v>240</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>215</v>
+        <v>241</v>
       </c>
       <c r="B15" t="s">
-        <v>216</v>
+        <v>242</v>
       </c>
       <c r="C15" t="s">
-        <v>200</v>
+        <v>226</v>
       </c>
       <c r="D15" t="s">
-        <v>217</v>
+        <v>243</v>
       </c>
       <c r="E15" t="s">
-        <v>218</v>
+        <v>244</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>219</v>
+        <v>245</v>
       </c>
       <c r="B16" t="s">
-        <v>220</v>
+        <v>246</v>
       </c>
       <c r="C16" t="s">
-        <v>200</v>
+        <v>226</v>
       </c>
       <c r="D16" t="s">
-        <v>221</v>
+        <v>247</v>
       </c>
       <c r="E16" t="s">
-        <v>222</v>
+        <v>248</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>223</v>
+        <v>249</v>
       </c>
       <c r="B17" t="s">
-        <v>224</v>
+        <v>250</v>
       </c>
       <c r="C17" t="s">
-        <v>200</v>
+        <v>226</v>
       </c>
       <c r="D17" t="s">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="E17" t="s">
-        <v>226</v>
+        <v>252</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>227</v>
+        <v>253</v>
       </c>
       <c r="B18" t="s">
-        <v>228</v>
+        <v>254</v>
       </c>
       <c r="C18" t="s">
-        <v>200</v>
+        <v>226</v>
       </c>
       <c r="D18" t="s">
-        <v>229</v>
+        <v>255</v>
       </c>
       <c r="E18" t="s">
-        <v>230</v>
+        <v>256</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>231</v>
+        <v>257</v>
       </c>
       <c r="B20" t="s">
+        <v>186</v>
+      </c>
+      <c r="C20" t="s">
+        <v>187</v>
+      </c>
+      <c r="D20" t="s">
+        <v>188</v>
+      </c>
+      <c r="E20" t="s">
         <v>160</v>
-      </c>
-      <c r="C20" t="s">
-        <v>161</v>
-      </c>
-      <c r="D20" t="s">
-        <v>162</v>
-      </c>
-      <c r="E20" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>232</v>
+        <v>258</v>
       </c>
       <c r="B21" t="s">
-        <v>233</v>
+        <v>259</v>
       </c>
       <c r="C21" t="s">
-        <v>200</v>
+        <v>226</v>
       </c>
       <c r="D21" t="s">
-        <v>234</v>
+        <v>260</v>
       </c>
       <c r="E21" t="s">
-        <v>235</v>
+        <v>261</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>236</v>
+        <v>262</v>
       </c>
       <c r="B22" t="s">
-        <v>237</v>
+        <v>263</v>
       </c>
       <c r="C22" t="s">
-        <v>238</v>
+        <v>264</v>
       </c>
       <c r="D22" t="s">
-        <v>239</v>
+        <v>265</v>
       </c>
       <c r="E22" t="s">
-        <v>240</v>
+        <v>266</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>241</v>
+        <v>267</v>
       </c>
       <c r="B23" t="s">
-        <v>242</v>
+        <v>268</v>
       </c>
       <c r="C23" t="s">
-        <v>238</v>
+        <v>264</v>
       </c>
       <c r="D23" t="s">
-        <v>243</v>
+        <v>269</v>
       </c>
       <c r="E23" t="s">
-        <v>244</v>
+        <v>270</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>245</v>
+        <v>271</v>
       </c>
       <c r="B24" t="s">
-        <v>246</v>
+        <v>272</v>
       </c>
       <c r="C24" t="s">
-        <v>238</v>
+        <v>264</v>
       </c>
       <c r="D24" t="s">
-        <v>247</v>
+        <v>273</v>
       </c>
       <c r="E24" t="s">
-        <v>248</v>
+        <v>274</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>249</v>
+        <v>275</v>
       </c>
       <c r="B25" t="s">
-        <v>250</v>
+        <v>276</v>
       </c>
       <c r="C25" t="s">
-        <v>251</v>
+        <v>277</v>
       </c>
       <c r="D25" t="s">
-        <v>252</v>
+        <v>278</v>
       </c>
       <c r="E25" t="s">
-        <v>253</v>
+        <v>279</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>254</v>
+        <v>280</v>
       </c>
       <c r="B26" t="s">
-        <v>255</v>
+        <v>281</v>
       </c>
       <c r="C26" t="s">
-        <v>200</v>
+        <v>226</v>
       </c>
       <c r="D26" t="s">
-        <v>256</v>
+        <v>282</v>
       </c>
       <c r="E26" t="s">
-        <v>257</v>
+        <v>283</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>258</v>
+        <v>284</v>
       </c>
       <c r="B27" t="s">
-        <v>259</v>
+        <v>285</v>
       </c>
       <c r="C27" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="D27" t="s">
-        <v>260</v>
+        <v>286</v>
       </c>
       <c r="E27" t="s">
-        <v>261</v>
+        <v>287</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>262</v>
+        <v>288</v>
       </c>
       <c r="B28" t="s">
-        <v>263</v>
+        <v>289</v>
       </c>
       <c r="C28" t="s">
-        <v>200</v>
+        <v>226</v>
       </c>
       <c r="D28" t="s">
-        <v>264</v>
+        <v>290</v>
       </c>
       <c r="E28" t="s">
-        <v>265</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>266</v>
+        <v>292</v>
       </c>
       <c r="B29" t="s">
-        <v>267</v>
+        <v>293</v>
       </c>
       <c r="C29" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="D29" t="s">
-        <v>268</v>
+        <v>294</v>
       </c>
       <c r="E29" t="s">
-        <v>269</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>270</v>
+        <v>296</v>
       </c>
       <c r="B30" t="s">
-        <v>271</v>
+        <v>297</v>
       </c>
       <c r="C30" t="s">
-        <v>200</v>
+        <v>226</v>
       </c>
       <c r="D30" t="s">
-        <v>272</v>
+        <v>298</v>
       </c>
       <c r="E30" t="s">
-        <v>273</v>
+        <v>299</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>274</v>
+        <v>300</v>
       </c>
       <c r="B31" t="s">
-        <v>275</v>
+        <v>301</v>
       </c>
       <c r="C31" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="E31" t="s">
-        <v>276</v>
+        <v>302</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>277</v>
+        <v>303</v>
       </c>
       <c r="B35" t="s">
+        <v>186</v>
+      </c>
+      <c r="C35" t="s">
+        <v>187</v>
+      </c>
+      <c r="D35" t="s">
+        <v>188</v>
+      </c>
+      <c r="E35" t="s">
         <v>160</v>
-      </c>
-      <c r="C35" t="s">
-        <v>161</v>
-      </c>
-      <c r="D35" t="s">
-        <v>162</v>
-      </c>
-      <c r="E35" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>278</v>
+        <v>304</v>
       </c>
       <c r="B36" t="s">
-        <v>279</v>
+        <v>305</v>
       </c>
       <c r="C36" t="s">
-        <v>280</v>
+        <v>306</v>
       </c>
       <c r="E36" t="s">
-        <v>281</v>
+        <v>307</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>282</v>
+        <v>308</v>
       </c>
       <c r="B37" t="s">
-        <v>283</v>
+        <v>309</v>
       </c>
       <c r="C37" t="s">
-        <v>284</v>
+        <v>310</v>
       </c>
       <c r="E37" t="s">
-        <v>285</v>
+        <v>311</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>286</v>
+        <v>312</v>
       </c>
       <c r="B38" t="s">
-        <v>287</v>
+        <v>313</v>
       </c>
       <c r="C38" t="s">
-        <v>284</v>
+        <v>310</v>
       </c>
       <c r="E38" t="s">
-        <v>288</v>
+        <v>314</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>289</v>
+        <v>315</v>
       </c>
       <c r="B39" t="s">
-        <v>290</v>
+        <v>316</v>
       </c>
       <c r="C39" t="s">
-        <v>284</v>
+        <v>310</v>
       </c>
       <c r="E39" t="s">
-        <v>291</v>
+        <v>317</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>292</v>
+        <v>318</v>
       </c>
       <c r="B40" t="s">
-        <v>293</v>
+        <v>319</v>
       </c>
       <c r="C40" t="s">
-        <v>284</v>
+        <v>310</v>
       </c>
       <c r="D40" t="s">
-        <v>294</v>
+        <v>320</v>
       </c>
       <c r="E40" t="s">
-        <v>295</v>
+        <v>321</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>296</v>
+        <v>322</v>
       </c>
       <c r="B41" t="s">
-        <v>297</v>
+        <v>323</v>
       </c>
       <c r="C41" t="s">
-        <v>284</v>
+        <v>310</v>
       </c>
       <c r="D41" t="s">
-        <v>298</v>
+        <v>324</v>
       </c>
       <c r="E41" t="s">
-        <v>299</v>
+        <v>325</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>300</v>
+        <v>326</v>
       </c>
       <c r="B42" t="s">
-        <v>301</v>
+        <v>327</v>
       </c>
       <c r="C42" t="s">
-        <v>284</v>
+        <v>310</v>
       </c>
       <c r="D42" t="s">
-        <v>302</v>
+        <v>328</v>
       </c>
       <c r="E42" t="s">
-        <v>303</v>
+        <v>329</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>304</v>
+        <v>330</v>
       </c>
       <c r="B43" t="s">
-        <v>305</v>
+        <v>331</v>
       </c>
       <c r="C43" t="s">
-        <v>284</v>
+        <v>310</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>332</v>
       </c>
       <c r="E43" t="s">
-        <v>307</v>
+        <v>333</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>308</v>
+        <v>334</v>
       </c>
       <c r="B44" t="s">
-        <v>309</v>
+        <v>335</v>
       </c>
       <c r="C44" t="s">
-        <v>284</v>
+        <v>310</v>
       </c>
       <c r="D44" t="s">
-        <v>310</v>
+        <v>336</v>
       </c>
       <c r="E44" t="s">
-        <v>311</v>
+        <v>337</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>312</v>
+        <v>338</v>
       </c>
       <c r="B45" t="s">
-        <v>313</v>
+        <v>339</v>
       </c>
       <c r="C45" t="s">
-        <v>284</v>
+        <v>310</v>
       </c>
       <c r="D45" t="s">
-        <v>314</v>
+        <v>340</v>
       </c>
       <c r="E45" t="s">
-        <v>315</v>
+        <v>341</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" t="s">
-        <v>316</v>
+        <v>342</v>
       </c>
       <c r="B46" t="s">
-        <v>317</v>
+        <v>343</v>
       </c>
       <c r="C46" t="s">
-        <v>284</v>
+        <v>310</v>
       </c>
       <c r="D46" t="s">
-        <v>318</v>
+        <v>344</v>
       </c>
       <c r="E46" t="s">
-        <v>319</v>
+        <v>345</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>320</v>
+        <v>346</v>
       </c>
       <c r="B47" t="s">
-        <v>321</v>
+        <v>347</v>
       </c>
       <c r="C47" t="s">
-        <v>284</v>
+        <v>310</v>
       </c>
       <c r="D47" t="s">
-        <v>322</v>
+        <v>348</v>
       </c>
       <c r="E47" t="s">
-        <v>323</v>
+        <v>349</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" t="s">
-        <v>324</v>
+        <v>350</v>
       </c>
       <c r="B48" t="s">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="C48" t="s">
-        <v>200</v>
+        <v>226</v>
       </c>
       <c r="E48" t="s">
-        <v>326</v>
+        <v>352</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>327</v>
+        <v>353</v>
       </c>
       <c r="B49" t="s">
-        <v>328</v>
+        <v>354</v>
       </c>
       <c r="C49" t="s">
-        <v>200</v>
+        <v>226</v>
       </c>
       <c r="E49" t="s">
-        <v>329</v>
+        <v>355</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>330</v>
+        <v>356</v>
       </c>
       <c r="B50" t="s">
-        <v>331</v>
+        <v>357</v>
       </c>
       <c r="C50" t="s">
-        <v>200</v>
+        <v>226</v>
       </c>
       <c r="E50" t="s">
-        <v>332</v>
+        <v>358</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>333</v>
+        <v>359</v>
       </c>
       <c r="B51" t="s">
-        <v>334</v>
+        <v>360</v>
       </c>
       <c r="C51" t="s">
-        <v>200</v>
+        <v>226</v>
       </c>
       <c r="E51" t="s">
-        <v>335</v>
+        <v>361</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>336</v>
+        <v>362</v>
       </c>
       <c r="B52" t="s">
-        <v>337</v>
+        <v>363</v>
       </c>
       <c r="C52" t="s">
-        <v>200</v>
+        <v>226</v>
       </c>
       <c r="E52" t="s">
-        <v>338</v>
+        <v>364</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>339</v>
+        <v>365</v>
       </c>
       <c r="B53" t="s">
-        <v>340</v>
+        <v>366</v>
       </c>
       <c r="C53" t="s">
-        <v>200</v>
+        <v>226</v>
       </c>
       <c r="D53" t="s">
-        <v>341</v>
+        <v>367</v>
       </c>
       <c r="E53" t="s">
-        <v>342</v>
+        <v>368</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>343</v>
+        <v>369</v>
       </c>
       <c r="B54" t="s">
-        <v>344</v>
+        <v>370</v>
       </c>
       <c r="C54" t="s">
-        <v>345</v>
+        <v>371</v>
       </c>
       <c r="E54" t="s">
-        <v>346</v>
+        <v>372</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>347</v>
+        <v>373</v>
       </c>
       <c r="B55" t="s">
-        <v>348</v>
+        <v>374</v>
       </c>
       <c r="C55" t="s">
-        <v>200</v>
+        <v>226</v>
       </c>
       <c r="E55" t="s">
-        <v>349</v>
+        <v>375</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" t="s">
-        <v>195</v>
+        <v>221</v>
       </c>
       <c r="B56" t="s">
-        <v>196</v>
+        <v>222</v>
       </c>
       <c r="C56" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="D56" t="s">
-        <v>350</v>
+        <v>376</v>
       </c>
       <c r="E56" t="s">
-        <v>351</v>
+        <v>377</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" t="s">
-        <v>352</v>
+        <v>378</v>
       </c>
       <c r="B57" t="s">
-        <v>353</v>
+        <v>379</v>
       </c>
       <c r="C57" t="s">
-        <v>354</v>
+        <v>380</v>
       </c>
       <c r="D57" t="s">
-        <v>355</v>
+        <v>381</v>
       </c>
       <c r="E57" t="s">
-        <v>356</v>
+        <v>382</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" t="s">
-        <v>357</v>
+        <v>383</v>
       </c>
       <c r="B58" t="s">
-        <v>358</v>
+        <v>384</v>
       </c>
       <c r="C58" t="s">
-        <v>354</v>
+        <v>380</v>
       </c>
       <c r="D58" t="s">
-        <v>359</v>
+        <v>385</v>
       </c>
       <c r="E58" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" t="s">
-        <v>361</v>
+        <v>387</v>
       </c>
       <c r="B59" t="s">
-        <v>362</v>
+        <v>388</v>
       </c>
       <c r="C59" t="s">
-        <v>363</v>
+        <v>389</v>
       </c>
       <c r="D59" t="s">
-        <v>364</v>
+        <v>390</v>
       </c>
       <c r="E59" t="s">
-        <v>365</v>
+        <v>391</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="69" t="s">
+        <v>392</v>
+      </c>
+      <c r="B61" s="69"/>
+      <c r="C61" s="69"/>
+      <c r="D61" s="69"/>
+      <c r="E61" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="70" t="s">
+        <v>393</v>
+      </c>
+      <c r="C62" s="69"/>
+      <c r="D62" s="69"/>
+      <c r="E62" s="70" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="70" t="s">
+        <v>395</v>
+      </c>
+      <c r="C63" s="69"/>
+      <c r="D63" s="69"/>
+      <c r="E63" s="70" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="70" t="s">
+        <v>397</v>
+      </c>
+      <c r="C64" s="71"/>
+      <c r="E64" s="70" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="70" t="s">
+        <v>399</v>
+      </c>
+      <c r="C65" s="71"/>
+      <c r="E65" s="70" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="70" t="s">
+        <v>401</v>
+      </c>
+      <c r="C66" s="71"/>
+      <c r="E66" s="70" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="70" t="s">
+        <v>403</v>
+      </c>
+      <c r="C67" s="71"/>
+      <c r="E67" s="70" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="70" t="s">
+        <v>405</v>
+      </c>
+      <c r="C68" s="71"/>
+      <c r="E68" s="70" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="70" t="s">
+        <v>407</v>
+      </c>
+      <c r="C69" s="71"/>
+      <c r="E69" s="70" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="70" t="s">
+        <v>409</v>
+      </c>
+      <c r="C70" s="71"/>
+      <c r="E70" s="70" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="70" t="s">
+        <v>411</v>
+      </c>
+      <c r="C71" s="71"/>
+      <c r="E71" s="70" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="70" t="s">
+        <v>413</v>
+      </c>
+      <c r="C72" s="71"/>
+      <c r="E72" s="70" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="70" t="s">
+        <v>415</v>
+      </c>
+      <c r="C73" s="71"/>
+      <c r="E73" s="70" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="70" t="s">
+        <v>417</v>
+      </c>
+      <c r="C74" s="71"/>
+      <c r="E74" s="70" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="70" t="s">
+        <v>419</v>
+      </c>
+      <c r="C75" s="71"/>
+      <c r="E75" s="70" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="70" t="s">
+        <v>421</v>
+      </c>
+      <c r="C76" s="71"/>
+      <c r="E76" s="70" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="70" t="s">
+        <v>423</v>
+      </c>
+      <c r="C77" s="71"/>
+      <c r="E77" s="70" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="70" t="s">
+        <v>425</v>
+      </c>
+      <c r="C78" s="71"/>
+      <c r="E78" s="70" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="70" t="s">
+        <v>427</v>
+      </c>
+      <c r="C79" s="71"/>
+      <c r="E79" s="70" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="70" t="s">
+        <v>429</v>
+      </c>
+      <c r="C80" s="71"/>
+      <c r="E80" s="70" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="70" t="s">
+        <v>431</v>
+      </c>
+      <c r="C81" s="71"/>
+      <c r="E81" s="70" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="72" t="s">
+        <v>433</v>
+      </c>
+      <c r="B82" s="72"/>
+      <c r="C82" s="72"/>
+      <c r="D82" s="72"/>
+      <c r="E82" s="72" t="s">
+        <v>434</v>
       </c>
     </row>
   </sheetData>
@@ -5045,59 +5784,59 @@
     <col min="17" max="17" width="12.1428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="28" customFormat="1" spans="1:17">
-      <c r="A1" s="28" t="s">
-        <v>366</v>
-      </c>
-      <c r="B1" s="29" t="s">
-        <v>367</v>
-      </c>
-      <c r="C1" s="29" t="s">
-        <v>368</v>
-      </c>
-      <c r="D1" s="29" t="s">
-        <v>369</v>
-      </c>
-      <c r="E1" s="29" t="s">
-        <v>370</v>
-      </c>
-      <c r="F1" s="28" t="s">
-        <v>371</v>
-      </c>
-      <c r="G1" s="28" t="s">
-        <v>372</v>
-      </c>
-      <c r="H1" s="28" t="s">
-        <v>373</v>
+    <row r="1" s="27" customFormat="1" spans="1:17">
+      <c r="A1" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="B1" s="28" t="s">
+        <v>436</v>
+      </c>
+      <c r="C1" s="28" t="s">
+        <v>437</v>
+      </c>
+      <c r="D1" s="28" t="s">
+        <v>438</v>
+      </c>
+      <c r="E1" s="28" t="s">
+        <v>439</v>
+      </c>
+      <c r="F1" s="27" t="s">
+        <v>440</v>
+      </c>
+      <c r="G1" s="27" t="s">
+        <v>441</v>
+      </c>
+      <c r="H1" s="27" t="s">
+        <v>442</v>
       </c>
       <c r="J1" t="s">
-        <v>374</v>
+        <v>443</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>375</v>
+        <v>444</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>376</v>
+        <v>445</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>28</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>278</v>
+        <v>304</v>
       </c>
       <c r="P1" t="s">
-        <v>162</v>
+        <v>188</v>
       </c>
       <c r="Q1" t="s">
-        <v>377</v>
+        <v>446</v>
       </c>
     </row>
     <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>164</v>
+        <v>190</v>
       </c>
       <c r="B2" s="3">
         <v>40000</v>
@@ -5109,7 +5848,7 @@
         <f>C2*G2</f>
         <v>20000</v>
       </c>
-      <c r="E2" s="37">
+      <c r="E2" s="36">
         <f t="shared" ref="E2:E17" si="0">B2-C2</f>
         <v>20000</v>
       </c>
@@ -5120,30 +5859,30 @@
       <c r="G2">
         <v>1</v>
       </c>
-      <c r="H2" s="37">
+      <c r="H2" s="36">
         <f>G2*B2</f>
         <v>40000</v>
       </c>
       <c r="J2" t="s">
-        <v>378</v>
+        <v>447</v>
       </c>
       <c r="K2" s="3">
         <v>100</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>275</v>
+        <v>301</v>
       </c>
       <c r="M2" s="3">
         <v>4</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>379</v>
+        <v>448</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>380</v>
+        <v>449</v>
       </c>
       <c r="P2" t="s">
-        <v>381</v>
+        <v>450</v>
       </c>
       <c r="Q2">
         <f>1000*10*0.48</f>
@@ -5152,7 +5891,7 @@
     </row>
     <row r="3" spans="1:17">
       <c r="A3" t="s">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="B3" s="3">
         <v>40000</v>
@@ -5164,7 +5903,7 @@
         <f>C3*G3</f>
         <v>20000</v>
       </c>
-      <c r="E3" s="37">
+      <c r="E3" s="36">
         <f t="shared" si="0"/>
         <v>20000</v>
       </c>
@@ -5175,15 +5914,15 @@
       <c r="G3">
         <v>1</v>
       </c>
-      <c r="H3" s="37">
+      <c r="H3" s="36">
         <f>G3*B3</f>
         <v>40000</v>
       </c>
       <c r="O3" t="s">
-        <v>382</v>
+        <v>451</v>
       </c>
       <c r="P3" t="s">
-        <v>383</v>
+        <v>452</v>
       </c>
       <c r="Q3">
         <v>1</v>
@@ -5191,7 +5930,7 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="B4" s="3">
         <v>2000</v>
@@ -5203,7 +5942,7 @@
         <f>C4*G4</f>
         <v>8400</v>
       </c>
-      <c r="E4" s="37">
+      <c r="E4" s="36">
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
@@ -5214,14 +5953,14 @@
       <c r="G4">
         <v>8.4</v>
       </c>
-      <c r="H4" s="37">
+      <c r="H4" s="36">
         <f>G4*B4</f>
         <v>16800</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>176</v>
+        <v>202</v>
       </c>
       <c r="B5" s="3">
         <v>1000</v>
@@ -5233,7 +5972,7 @@
         <f>C5*G5</f>
         <v>2800</v>
       </c>
-      <c r="E5" s="37">
+      <c r="E5" s="36">
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
@@ -5244,14 +5983,14 @@
       <c r="G5">
         <v>5.6</v>
       </c>
-      <c r="H5" s="37">
+      <c r="H5" s="36">
         <f>G5*B5</f>
         <v>5600</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>184</v>
+        <v>210</v>
       </c>
       <c r="B6" s="3">
         <v>1000</v>
@@ -5263,7 +6002,7 @@
         <f>C6*G6</f>
         <v>5800</v>
       </c>
-      <c r="E6" s="37">
+      <c r="E6" s="36">
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
@@ -5274,14 +6013,14 @@
       <c r="G6">
         <v>11.6</v>
       </c>
-      <c r="H6" s="37">
+      <c r="H6" s="36">
         <f>G6*B6</f>
         <v>11600</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>207</v>
+        <v>233</v>
       </c>
       <c r="B7" s="4">
         <v>1.2</v>
@@ -5304,14 +6043,14 @@
       <c r="G7">
         <v>140</v>
       </c>
-      <c r="H7" s="37">
+      <c r="H7" s="36">
         <f>G7*B7*100</f>
         <v>16800</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>384</v>
+        <v>453</v>
       </c>
       <c r="B8" s="4">
         <v>0.2</v>
@@ -5334,14 +6073,14 @@
       <c r="G8">
         <v>140</v>
       </c>
-      <c r="H8" s="37">
+      <c r="H8" s="36">
         <f>G8*B8*100</f>
         <v>2800</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>198</v>
+        <v>224</v>
       </c>
       <c r="B9" s="4">
         <v>0.2</v>
@@ -5364,14 +6103,14 @@
       <c r="G9">
         <v>140</v>
       </c>
-      <c r="H9" s="37">
+      <c r="H9" s="36">
         <f>G9*B9*100</f>
         <v>2800</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>203</v>
+        <v>229</v>
       </c>
       <c r="B10" s="4">
         <v>1</v>
@@ -5394,14 +6133,14 @@
       <c r="G10">
         <v>28</v>
       </c>
-      <c r="H10" s="37">
+      <c r="H10" s="36">
         <f>G10*B10*100</f>
         <v>2800</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>191</v>
+        <v>217</v>
       </c>
       <c r="B11" s="3">
         <v>100</v>
@@ -5413,7 +6152,7 @@
         <f>C11*G11</f>
         <v>40000</v>
       </c>
-      <c r="E11" s="37">
+      <c r="E11" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5424,14 +6163,14 @@
       <c r="G11">
         <v>400</v>
       </c>
-      <c r="H11" s="37">
+      <c r="H11" s="36">
         <f>G11*B11</f>
         <v>40000</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>385</v>
+        <v>454</v>
       </c>
       <c r="B12" s="3">
         <v>4</v>
@@ -5443,7 +6182,7 @@
         <f>C12*G12</f>
         <v>4500</v>
       </c>
-      <c r="E12" s="37">
+      <c r="E12" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5454,14 +6193,14 @@
       <c r="G12">
         <v>1125</v>
       </c>
-      <c r="H12" s="37">
+      <c r="H12" s="36">
         <f>G12*B12</f>
         <v>4500</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>386</v>
+        <v>455</v>
       </c>
       <c r="B13" s="3">
         <v>1</v>
@@ -5473,7 +6212,7 @@
         <f>C13*G13</f>
         <v>0</v>
       </c>
-      <c r="E13" s="37">
+      <c r="E13" s="36">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -5484,14 +6223,14 @@
       <c r="G13">
         <v>4800</v>
       </c>
-      <c r="H13" s="37">
+      <c r="H13" s="36">
         <f>G13*B13</f>
         <v>4800</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>387</v>
+        <v>456</v>
       </c>
       <c r="B14" s="3">
         <v>10</v>
@@ -5503,7 +6242,7 @@
         <f>C14*G14</f>
         <v>23260</v>
       </c>
-      <c r="E14" s="37">
+      <c r="E14" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5514,14 +6253,14 @@
       <c r="G14">
         <v>2326</v>
       </c>
-      <c r="H14" s="37">
+      <c r="H14" s="36">
         <f>G14*B14</f>
         <v>23260</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>211</v>
+        <v>237</v>
       </c>
       <c r="B15" s="4">
         <v>1</v>
@@ -5533,7 +6272,7 @@
         <f>C15*G15*100</f>
         <v>16800</v>
       </c>
-      <c r="E15" s="37">
+      <c r="E15" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5544,14 +6283,14 @@
       <c r="G15">
         <v>168</v>
       </c>
-      <c r="H15" s="37">
+      <c r="H15" s="36">
         <f>G15*B15*100</f>
         <v>16800</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>215</v>
+        <v>241</v>
       </c>
       <c r="B16" s="4">
         <v>0</v>
@@ -5563,7 +6302,7 @@
         <f>C16*G16*100</f>
         <v>0</v>
       </c>
-      <c r="E16" s="37">
+      <c r="E16" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5574,14 +6313,14 @@
       <c r="G16">
         <v>168</v>
       </c>
-      <c r="H16" s="37">
+      <c r="H16" s="36">
         <f>G16*B16</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>219</v>
+        <v>245</v>
       </c>
       <c r="B17" s="4">
         <v>0</v>
@@ -5591,7 +6330,7 @@
         <f>C17*G17*100</f>
         <v>0</v>
       </c>
-      <c r="E17" s="37">
+      <c r="E17" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5602,522 +6341,522 @@
       <c r="G17">
         <v>233</v>
       </c>
-      <c r="H17" s="37">
+      <c r="H17" s="36">
         <f>G17*B17</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" spans="1:8">
       <c r="A18" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="D18" s="36">
+        <v>457</v>
+      </c>
+      <c r="D18" s="35">
         <f>SUM(D2:D17)</f>
         <v>156960</v>
       </c>
-      <c r="F18" s="36">
+      <c r="F18" s="35">
         <f>SUM(F2:F17)</f>
         <v>71600</v>
       </c>
-      <c r="H18" s="36">
+      <c r="H18" s="35">
         <f>SUM(H2:H17)</f>
         <v>228560</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>389</v>
-      </c>
-      <c r="F19" s="37">
+        <v>458</v>
+      </c>
+      <c r="F19" s="36">
         <f>F18/4</f>
         <v>17900</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>390</v>
+        <v>459</v>
       </c>
     </row>
     <row r="24" customFormat="1" ht="23.25" customHeight="1" spans="1:1">
-      <c r="A24" s="55" t="s">
-        <v>391</v>
+      <c r="A24" s="66" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="26" customFormat="1" ht="18.75" customHeight="1" spans="1:1">
-      <c r="A26" s="56" t="s">
-        <v>392</v>
+      <c r="A26" s="67" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="28" t="s">
-        <v>393</v>
+      <c r="A28" s="27" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="57" t="s">
-        <v>394</v>
+      <c r="A29" s="68" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="57" t="s">
-        <v>395</v>
+      <c r="A30" s="68" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="57" t="s">
-        <v>396</v>
+      <c r="A31" s="68" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="57" t="s">
-        <v>397</v>
+      <c r="A32" s="68" t="s">
+        <v>466</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="57" t="s">
-        <v>398</v>
+      <c r="A33" s="68" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="57" t="s">
-        <v>399</v>
+      <c r="A34" s="68" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="57" t="s">
-        <v>400</v>
+      <c r="A35" s="68" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="57" t="s">
-        <v>401</v>
+      <c r="A36" s="68" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="57" t="s">
-        <v>402</v>
+      <c r="A37" s="68" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="57" t="s">
-        <v>403</v>
+      <c r="A38" s="68" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="40" customFormat="1" ht="18.75" customHeight="1" spans="1:1">
-      <c r="A40" s="56" t="s">
-        <v>404</v>
+      <c r="A40" s="67" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="2" t="s">
-        <v>405</v>
+        <v>474</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>406</v>
+        <v>475</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="2" t="s">
-        <v>407</v>
+        <v>476</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>408</v>
+        <v>477</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="2" t="s">
-        <v>409</v>
+        <v>478</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>410</v>
+        <v>479</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="2" t="s">
-        <v>411</v>
+        <v>480</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>412</v>
+        <v>481</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="2" t="s">
-        <v>413</v>
+        <v>482</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>414</v>
+        <v>483</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="2" t="s">
-        <v>415</v>
+        <v>484</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>416</v>
+        <v>485</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>417</v>
+        <v>486</v>
       </c>
     </row>
     <row r="61" customFormat="1" ht="18.75" customHeight="1" spans="1:1">
-      <c r="A61" s="56" t="s">
-        <v>418</v>
+      <c r="A61" s="67" t="s">
+        <v>487</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="2" t="s">
-        <v>419</v>
+        <v>488</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>420</v>
+        <v>489</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>421</v>
+        <v>490</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="2" t="s">
-        <v>422</v>
+        <v>491</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>423</v>
+        <v>492</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>424</v>
+        <v>493</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" t="s">
-        <v>425</v>
+        <v>494</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" t="s">
-        <v>426</v>
+        <v>495</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>427</v>
+        <v>496</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" s="1" t="s">
-        <v>278</v>
+        <v>304</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>428</v>
+        <v>497</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>429</v>
+        <v>498</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" s="2" t="s">
-        <v>164</v>
+        <v>190</v>
       </c>
       <c r="B76" t="s">
-        <v>430</v>
+        <v>499</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>431</v>
+        <v>500</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="2" t="s">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="B77" t="s">
-        <v>432</v>
+        <v>501</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>431</v>
+        <v>500</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" s="2" t="s">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="B78" t="s">
-        <v>433</v>
+        <v>502</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>434</v>
+        <v>503</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" s="2" t="s">
-        <v>176</v>
+        <v>202</v>
       </c>
       <c r="B79" t="s">
-        <v>435</v>
+        <v>504</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>436</v>
+        <v>505</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" s="2" t="s">
-        <v>184</v>
+        <v>210</v>
       </c>
       <c r="B80" t="s">
-        <v>437</v>
+        <v>506</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>438</v>
+        <v>507</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" s="2" t="s">
-        <v>207</v>
+        <v>233</v>
       </c>
       <c r="B81" t="s">
-        <v>439</v>
+        <v>508</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>440</v>
+        <v>509</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" s="2" t="s">
-        <v>227</v>
+        <v>253</v>
       </c>
       <c r="B82" t="s">
-        <v>441</v>
+        <v>510</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>440</v>
+        <v>509</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" s="2" t="s">
-        <v>198</v>
+        <v>224</v>
       </c>
       <c r="B83" t="s">
-        <v>442</v>
+        <v>511</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>440</v>
+        <v>509</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" s="2" t="s">
-        <v>203</v>
+        <v>229</v>
       </c>
       <c r="B84" t="s">
-        <v>443</v>
+        <v>512</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>444</v>
+        <v>513</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" s="2" t="s">
-        <v>191</v>
+        <v>217</v>
       </c>
       <c r="B85" t="s">
-        <v>445</v>
+        <v>514</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>446</v>
+        <v>515</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" s="2" t="s">
-        <v>361</v>
+        <v>387</v>
       </c>
       <c r="B86" t="s">
-        <v>447</v>
+        <v>516</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>448</v>
+        <v>517</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" s="2" t="s">
-        <v>449</v>
+        <v>518</v>
       </c>
       <c r="B87" t="s">
-        <v>450</v>
+        <v>519</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>451</v>
+        <v>520</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" s="2" t="s">
-        <v>387</v>
+        <v>456</v>
       </c>
       <c r="B88" t="s">
-        <v>452</v>
+        <v>521</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>453</v>
+        <v>522</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" s="2" t="s">
-        <v>211</v>
+        <v>237</v>
       </c>
       <c r="B89" t="s">
-        <v>454</v>
+        <v>523</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>455</v>
+        <v>524</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" s="2" t="s">
-        <v>215</v>
+        <v>241</v>
       </c>
       <c r="B90" t="s">
-        <v>456</v>
+        <v>525</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>455</v>
+        <v>524</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" s="2" t="s">
-        <v>219</v>
+        <v>245</v>
       </c>
       <c r="B91" t="s">
-        <v>457</v>
+        <v>526</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>458</v>
+        <v>527</v>
       </c>
     </row>
     <row r="93" customFormat="1" ht="18.75" customHeight="1" spans="1:1">
-      <c r="A93" s="56" t="s">
-        <v>459</v>
+      <c r="A93" s="67" t="s">
+        <v>528</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="2" t="s">
-        <v>460</v>
+        <v>529</v>
       </c>
     </row>
     <row r="97" spans="1:1">
-      <c r="A97" s="57" t="s">
-        <v>461</v>
+      <c r="A97" s="68" t="s">
+        <v>530</v>
       </c>
     </row>
     <row r="98" spans="1:1">
-      <c r="A98" s="57" t="s">
-        <v>462</v>
+      <c r="A98" s="68" t="s">
+        <v>531</v>
       </c>
     </row>
     <row r="99" spans="1:1">
-      <c r="A99" s="57" t="s">
-        <v>463</v>
+      <c r="A99" s="68" t="s">
+        <v>532</v>
       </c>
     </row>
     <row r="100" spans="1:1">
-      <c r="A100" s="57" t="s">
-        <v>464</v>
+      <c r="A100" s="68" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="101" spans="1:1">
-      <c r="A101" s="57" t="s">
-        <v>465</v>
+      <c r="A101" s="68" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="102" spans="1:1">
-      <c r="A102" s="57" t="s">
-        <v>466</v>
+      <c r="A102" s="68" t="s">
+        <v>535</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" s="2" t="s">
-        <v>191</v>
+        <v>217</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" t="s">
-        <v>467</v>
+        <v>536</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" s="2" t="s">
-        <v>219</v>
+        <v>245</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" t="s">
-        <v>468</v>
+        <v>537</v>
       </c>
     </row>
     <row r="110" customFormat="1" ht="18.75" customHeight="1" spans="1:1">
-      <c r="A110" s="56" t="s">
-        <v>469</v>
+      <c r="A110" s="67" t="s">
+        <v>538</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112" t="s">
-        <v>470</v>
+        <v>539</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" t="s">
-        <v>471</v>
+        <v>540</v>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114" t="s">
-        <v>472</v>
+        <v>541</v>
       </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115" t="s">
-        <v>473</v>
+        <v>542</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" t="s">
-        <v>474</v>
+        <v>543</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" t="s">
-        <v>475</v>
+        <v>544</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" t="s">
-        <v>476</v>
+        <v>545</v>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120" t="s">
-        <v>477</v>
+        <v>546</v>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121" t="s">
-        <v>478</v>
+        <v>547</v>
       </c>
     </row>
   </sheetData>
@@ -6129,7 +6868,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.5714285714286" customWidth="1"/>
@@ -6138,11 +6877,11 @@
     <col min="4" max="4" width="20" customWidth="1"/>
     <col min="5" max="5" width="34.7142857142857" customWidth="1"/>
     <col min="6" max="6" width="17.7142857142857" customWidth="1"/>
-    <col min="7" max="7" width="18.7142857142857" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="7" max="7" width="21.8571428571429" customWidth="1"/>
+    <col min="8" max="8" width="19.8571428571429" customWidth="1"/>
     <col min="9" max="9" width="20.2857142857143" customWidth="1"/>
     <col min="10" max="10" width="18.8571428571429" customWidth="1"/>
-    <col min="11" max="11" width="18.7142857142857" style="26" customWidth="1"/>
+    <col min="11" max="11" width="18.7142857142857" style="50" customWidth="1"/>
     <col min="12" max="12" width="11.4285714285714" customWidth="1"/>
     <col min="13" max="13" width="11.5714285714286" customWidth="1"/>
     <col min="14" max="14" width="23.7142857142857" customWidth="1"/>
@@ -6153,929 +6892,918 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>479</v>
+        <v>548</v>
       </c>
       <c r="B1" t="s">
-        <v>480</v>
+        <v>549</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>481</v>
+        <v>550</v>
       </c>
       <c r="B2" t="s">
-        <v>482</v>
+        <v>551</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>483</v>
-      </c>
-      <c r="B3" s="27" t="s">
-        <v>484</v>
+        <v>552</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>553</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>485</v>
+        <v>554</v>
       </c>
       <c r="B4" t="s">
-        <v>486</v>
+        <v>555</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>487</v>
+        <v>556</v>
       </c>
       <c r="B5" t="s">
-        <v>487</v>
+        <v>556</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>488</v>
+        <v>557</v>
       </c>
       <c r="B6" t="s">
-        <v>488</v>
+        <v>557</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="28" t="s">
-        <v>366</v>
-      </c>
-      <c r="B8" s="29" t="s">
-        <v>367</v>
-      </c>
-      <c r="C8" s="29" t="s">
-        <v>368</v>
-      </c>
-      <c r="D8" s="29" t="s">
-        <v>489</v>
-      </c>
-      <c r="E8" s="30" t="s">
-        <v>370</v>
-      </c>
-      <c r="F8" s="28" t="s">
-        <v>371</v>
-      </c>
-      <c r="G8" s="28" t="s">
-        <v>372</v>
-      </c>
-      <c r="H8" s="28" t="s">
-        <v>373</v>
+      <c r="A8" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>436</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>437</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>558</v>
+      </c>
+      <c r="E8" s="29" t="s">
+        <v>439</v>
+      </c>
+      <c r="F8" s="27" t="s">
+        <v>440</v>
+      </c>
+      <c r="G8" s="27" t="s">
+        <v>441</v>
+      </c>
+      <c r="H8" s="27" t="s">
+        <v>442</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>164</v>
-      </c>
-      <c r="B9" s="31">
+        <v>190</v>
+      </c>
+      <c r="B9" s="30">
         <f>SUM(C9,E9)</f>
         <v>51750</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="30">
         <v>29500</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="30">
         <f>C9*G9</f>
         <v>29500</v>
       </c>
-      <c r="E9" s="32">
+      <c r="E9" s="31">
         <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A9)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A9)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A9)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A9)</f>
         <v>22250</v>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="30">
         <f>E9*G9</f>
         <v>22250</v>
       </c>
       <c r="G9">
         <v>1</v>
       </c>
-      <c r="H9" s="32">
+      <c r="H9" s="31">
         <f>B9*G9</f>
         <v>51750</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>169</v>
-      </c>
-      <c r="B10" s="31">
+        <v>195</v>
+      </c>
+      <c r="B10" s="30">
         <f t="shared" ref="B9:B24" si="0">SUM(C10,E10)</f>
         <v>19450</v>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="30">
         <v>10500</v>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="30">
         <f>C10*G10</f>
         <v>10500</v>
       </c>
-      <c r="E10" s="32">
+      <c r="E10" s="31">
         <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A10)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A10)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A10)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A10)</f>
         <v>8950</v>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="30">
         <f>E10*G10</f>
         <v>8950</v>
       </c>
       <c r="G10">
         <v>1</v>
       </c>
-      <c r="H10" s="32">
+      <c r="H10" s="31">
         <f>B10*G10</f>
         <v>19450</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>172</v>
-      </c>
-      <c r="B11" s="31">
+        <v>198</v>
+      </c>
+      <c r="B11" s="30">
         <f t="shared" si="0"/>
         <v>5357.14285714286</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="30">
         <f>D11/G11</f>
         <v>1190.47619047619</v>
       </c>
-      <c r="D11" s="31">
+      <c r="D11" s="30">
         <v>10000</v>
       </c>
-      <c r="E11" s="33">
+      <c r="E11" s="32">
         <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A11)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A11)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A11)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A11)</f>
         <v>4166.66666666667</v>
       </c>
-      <c r="F11" s="31">
+      <c r="F11" s="30">
         <f>E11*G11</f>
         <v>35000</v>
       </c>
       <c r="G11">
         <v>8.4</v>
       </c>
-      <c r="H11" s="32">
+      <c r="H11" s="31">
         <f>B11*G11</f>
         <v>45000</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>176</v>
-      </c>
-      <c r="B12" s="31">
+        <v>202</v>
+      </c>
+      <c r="B12" s="30">
         <f t="shared" si="0"/>
         <v>1857.14285714286</v>
       </c>
-      <c r="C12" s="31">
+      <c r="C12" s="30">
         <f>D12/G12</f>
         <v>821.428571428571</v>
       </c>
-      <c r="D12" s="31">
+      <c r="D12" s="30">
         <v>4600</v>
       </c>
-      <c r="E12" s="33">
+      <c r="E12" s="32">
         <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A12)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A12)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A12)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A12)</f>
         <v>1035.71428571429</v>
       </c>
-      <c r="F12" s="31">
+      <c r="F12" s="30">
         <f>E12*G12</f>
         <v>5800</v>
       </c>
       <c r="G12">
         <v>5.6</v>
       </c>
-      <c r="H12" s="32">
+      <c r="H12" s="31">
         <f>B12*G12</f>
         <v>10400</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>184</v>
-      </c>
-      <c r="B13" s="31">
+        <v>210</v>
+      </c>
+      <c r="B13" s="30">
         <f t="shared" si="0"/>
         <v>1086.20689655172</v>
       </c>
-      <c r="C13" s="31">
+      <c r="C13" s="30">
         <f>D13/G13</f>
         <v>327.586206896552</v>
       </c>
-      <c r="D13" s="31">
+      <c r="D13" s="30">
         <v>3800</v>
       </c>
-      <c r="E13" s="33">
+      <c r="E13" s="32">
         <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A13)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A13)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A13)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A13)</f>
         <v>758.620689655172</v>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="30">
         <f>E13*G13</f>
         <v>8800</v>
       </c>
       <c r="G13">
         <v>11.6</v>
       </c>
-      <c r="H13" s="32">
+      <c r="H13" s="31">
         <f>B13*G13</f>
         <v>12600</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>207</v>
-      </c>
-      <c r="B14" s="34">
+        <v>233</v>
+      </c>
+      <c r="B14" s="33">
         <f t="shared" si="0"/>
         <v>1.2</v>
       </c>
-      <c r="C14" s="34">
+      <c r="C14" s="33">
         <v>1</v>
       </c>
-      <c r="D14" s="31">
+      <c r="D14" s="30">
         <f>C14*G14*100</f>
         <v>14000</v>
       </c>
-      <c r="E14" s="35">
+      <c r="E14" s="34">
         <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A14)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A14)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A14)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A14)</f>
         <v>0.2</v>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="30">
         <f>E14*G14*100</f>
         <v>2800</v>
       </c>
       <c r="G14">
         <v>140</v>
       </c>
-      <c r="H14" s="32">
+      <c r="H14" s="31">
         <f>B14*G14*100</f>
         <v>16800</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>384</v>
-      </c>
-      <c r="B15" s="34">
+        <v>453</v>
+      </c>
+      <c r="B15" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C15" s="34">
+      <c r="C15" s="33">
         <v>0</v>
       </c>
-      <c r="D15" s="31">
+      <c r="D15" s="30">
         <f>C15*G15*100</f>
         <v>0</v>
       </c>
-      <c r="E15" s="35">
+      <c r="E15" s="34">
         <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A15)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A15)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A15)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A15)</f>
         <v>0</v>
       </c>
-      <c r="F15" s="31">
+      <c r="F15" s="30">
         <f>E15*G15*100</f>
         <v>0</v>
       </c>
       <c r="G15">
         <v>140</v>
       </c>
-      <c r="H15" s="32">
+      <c r="H15" s="31">
         <f>B15*G15*100</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>198</v>
-      </c>
-      <c r="B16" s="34">
+        <v>224</v>
+      </c>
+      <c r="B16" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C16" s="34">
+      <c r="C16" s="33">
         <v>0</v>
       </c>
-      <c r="D16" s="31">
+      <c r="D16" s="30">
         <f>C16*G16*100</f>
         <v>0</v>
       </c>
-      <c r="E16" s="35">
+      <c r="E16" s="34">
         <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A16)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A16)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A16)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A16)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="31">
+      <c r="F16" s="30">
         <f>E16*G16*100</f>
         <v>0</v>
       </c>
       <c r="G16">
         <v>140</v>
       </c>
-      <c r="H16" s="32">
+      <c r="H16" s="31">
         <f>B16*G16*100</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>203</v>
-      </c>
-      <c r="B17" s="34">
+        <v>229</v>
+      </c>
+      <c r="B17" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C17" s="34">
+      <c r="C17" s="33">
         <v>0</v>
       </c>
-      <c r="D17" s="31">
+      <c r="D17" s="30">
         <f>C17*G17*100</f>
         <v>0</v>
       </c>
-      <c r="E17" s="35">
+      <c r="E17" s="34">
         <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A17)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A17)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A17)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A17)</f>
         <v>0</v>
       </c>
-      <c r="F17" s="31">
+      <c r="F17" s="30">
         <f>E17*G17*100</f>
         <v>0</v>
       </c>
       <c r="G17">
         <v>28</v>
       </c>
-      <c r="H17" s="32">
+      <c r="H17" s="31">
         <f>B17*G17*100</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>191</v>
-      </c>
-      <c r="B18" s="31">
+        <v>217</v>
+      </c>
+      <c r="B18" s="30">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="C18" s="31">
+      <c r="C18" s="30">
         <v>100</v>
       </c>
-      <c r="D18" s="31">
+      <c r="D18" s="30">
         <f>C18*G18</f>
         <v>40000</v>
       </c>
-      <c r="E18" s="32">
+      <c r="E18" s="31">
         <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A18)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A18)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A18)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A18)</f>
         <v>-30</v>
       </c>
-      <c r="F18" s="31">
+      <c r="F18" s="30">
         <f>E18*G18</f>
         <v>-12000</v>
       </c>
       <c r="G18">
         <v>400</v>
       </c>
-      <c r="H18" s="32">
+      <c r="H18" s="31">
         <f>B18*G18</f>
         <v>28000</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>361</v>
-      </c>
-      <c r="B19" s="31">
+        <v>387</v>
+      </c>
+      <c r="B19" s="30">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C19" s="31">
+      <c r="C19" s="30">
         <v>4</v>
       </c>
-      <c r="D19" s="31">
+      <c r="D19" s="30">
         <f>C19*G19</f>
         <v>4500</v>
       </c>
-      <c r="E19" s="32">
+      <c r="E19" s="31">
         <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A19)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A19)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A19)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A19)</f>
         <v>0</v>
       </c>
-      <c r="F19" s="31">
+      <c r="F19" s="30">
         <f>E19*G19</f>
         <v>0</v>
       </c>
       <c r="G19">
         <v>1125</v>
       </c>
-      <c r="H19" s="32">
+      <c r="H19" s="31">
         <f>B19*G19</f>
         <v>4500</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>386</v>
-      </c>
-      <c r="B20" s="31">
+        <v>455</v>
+      </c>
+      <c r="B20" s="30">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C20" s="31">
+      <c r="C20" s="30">
         <v>0</v>
       </c>
-      <c r="D20" s="31">
+      <c r="D20" s="30">
         <f>C20*G20</f>
         <v>0</v>
       </c>
-      <c r="E20" s="32">
+      <c r="E20" s="31">
         <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A20)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A20)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A20)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A20)</f>
         <v>0</v>
       </c>
-      <c r="F20" s="31">
+      <c r="F20" s="30">
         <f>E20*G20</f>
         <v>0</v>
       </c>
       <c r="G20">
         <v>4800</v>
       </c>
-      <c r="H20" s="32">
+      <c r="H20" s="31">
         <f>B20*G20</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>387</v>
-      </c>
-      <c r="B21" s="31">
+        <v>456</v>
+      </c>
+      <c r="B21" s="30">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C21" s="31">
+      <c r="C21" s="30">
         <v>10</v>
       </c>
-      <c r="D21" s="31">
+      <c r="D21" s="30">
         <f>C21*G21</f>
         <v>23260</v>
       </c>
-      <c r="E21" s="32">
+      <c r="E21" s="31">
         <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A21)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A21)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A21)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A21)</f>
         <v>0</v>
       </c>
-      <c r="F21" s="31">
+      <c r="F21" s="30">
         <f>E21*G21</f>
         <v>0</v>
       </c>
       <c r="G21">
         <v>2326</v>
       </c>
-      <c r="H21" s="32">
+      <c r="H21" s="31">
         <f>B21*G21</f>
         <v>23260</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>211</v>
-      </c>
-      <c r="B22" s="34">
+        <v>237</v>
+      </c>
+      <c r="B22" s="33">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="C22" s="34">
+      <c r="C22" s="33">
         <v>1</v>
       </c>
-      <c r="D22" s="31">
+      <c r="D22" s="30">
         <f>C22*G22*100</f>
         <v>16800</v>
       </c>
-      <c r="E22" s="35">
+      <c r="E22" s="34">
         <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A22)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A22)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A22)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A22)</f>
         <v>0</v>
       </c>
-      <c r="F22" s="31">
+      <c r="F22" s="30">
         <f>E22*G22*100</f>
         <v>0</v>
       </c>
       <c r="G22">
         <v>168</v>
       </c>
-      <c r="H22" s="32">
+      <c r="H22" s="31">
         <f>B22*G22*100</f>
         <v>16800</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>215</v>
-      </c>
-      <c r="B23" s="34">
+        <v>241</v>
+      </c>
+      <c r="B23" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C23" s="34">
+      <c r="C23" s="33">
         <v>0</v>
       </c>
-      <c r="D23" s="31">
+      <c r="D23" s="30">
         <f>C23*G23*100</f>
         <v>0</v>
       </c>
-      <c r="E23" s="35">
+      <c r="E23" s="34">
         <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A23)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A23)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A23)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A23)</f>
         <v>0</v>
       </c>
-      <c r="F23" s="31">
+      <c r="F23" s="30">
         <f>E23*G23*100</f>
         <v>0</v>
       </c>
       <c r="G23">
         <v>168</v>
       </c>
-      <c r="H23" s="32">
+      <c r="H23" s="31">
         <f>B23*G23*100</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" t="s">
-        <v>219</v>
-      </c>
-      <c r="B24" s="34">
+        <v>245</v>
+      </c>
+      <c r="B24" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C24" s="34">
+      <c r="C24" s="33">
         <v>0</v>
       </c>
-      <c r="D24" s="31">
+      <c r="D24" s="30">
         <f>C24*G24*100</f>
         <v>0</v>
       </c>
-      <c r="E24" s="35">
+      <c r="E24" s="34">
         <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A24)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A24)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A24)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A24)</f>
         <v>0</v>
       </c>
-      <c r="F24" s="31">
+      <c r="F24" s="30">
         <f>E24*G24*100</f>
         <v>0</v>
       </c>
       <c r="G24">
         <v>233</v>
       </c>
-      <c r="H24" s="32">
+      <c r="H24" s="31">
         <f>B24*G24*100</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="2" t="s">
-        <v>388</v>
+        <v>457</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
-      <c r="D25" s="36">
+      <c r="D25" s="35">
         <f>SUM(D9:D24)</f>
         <v>156960</v>
       </c>
-      <c r="E25" s="37"/>
-      <c r="F25" s="36">
+      <c r="E25" s="36"/>
+      <c r="F25" s="35">
         <f>SUM(F9:F24)</f>
         <v>71600</v>
       </c>
       <c r="G25" s="2"/>
-      <c r="H25" s="36">
+      <c r="H25" s="35">
         <f>SUM(H9:H24)</f>
         <v>228560</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>490</v>
-      </c>
-      <c r="D26" s="37">
+        <v>559</v>
+      </c>
+      <c r="D26" s="36">
         <f>'Balanced Dummy '!D18-D25</f>
         <v>0</v>
       </c>
-      <c r="E26" s="37"/>
-      <c r="F26" s="37"/>
+      <c r="E26" s="36"/>
+      <c r="F26" s="36"/>
     </row>
     <row r="28" spans="1:11">
-      <c r="A28" s="38" t="s">
-        <v>374</v>
-      </c>
-      <c r="B28" s="39" t="s">
-        <v>82</v>
-      </c>
-      <c r="C28" s="39" t="s">
-        <v>375</v>
-      </c>
-      <c r="D28" s="39" t="s">
-        <v>376</v>
-      </c>
-      <c r="E28" s="39" t="s">
+      <c r="A28" s="54" t="s">
+        <v>443</v>
+      </c>
+      <c r="B28" s="55" t="s">
+        <v>85</v>
+      </c>
+      <c r="C28" s="55" t="s">
+        <v>444</v>
+      </c>
+      <c r="D28" s="55" t="s">
+        <v>445</v>
+      </c>
+      <c r="E28" s="55" t="s">
         <v>28</v>
       </c>
-      <c r="F28" s="38" t="s">
-        <v>491</v>
-      </c>
-      <c r="G28" s="38" t="s">
-        <v>492</v>
-      </c>
-      <c r="H28" s="38" t="s">
-        <v>111</v>
-      </c>
-      <c r="I28" s="39" t="s">
-        <v>278</v>
-      </c>
-      <c r="J28" s="38" t="s">
-        <v>493</v>
-      </c>
-      <c r="K28" s="39" t="s">
-        <v>494</v>
+      <c r="F28" s="54" t="s">
+        <v>399</v>
+      </c>
+      <c r="G28" s="54" t="s">
+        <v>560</v>
+      </c>
+      <c r="H28" s="54" t="s">
+        <v>114</v>
+      </c>
+      <c r="I28" s="55" t="s">
+        <v>304</v>
+      </c>
+      <c r="J28" s="54" t="s">
+        <v>561</v>
+      </c>
+      <c r="K28" s="55" t="s">
+        <v>562</v>
       </c>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="38" t="s">
-        <v>495</v>
-      </c>
-      <c r="B29" s="40">
+      <c r="A29" s="54" t="s">
+        <v>563</v>
+      </c>
+      <c r="B29" s="56">
         <v>150</v>
       </c>
-      <c r="C29" s="41">
+      <c r="C29" s="57">
         <f>B29*1000/50</f>
         <v>3000</v>
       </c>
-      <c r="D29" s="41">
+      <c r="D29" s="57">
         <v>6</v>
       </c>
-      <c r="E29" s="39" t="s">
-        <v>496</v>
-      </c>
-      <c r="F29" s="38" t="s">
-        <v>497</v>
-      </c>
-      <c r="G29" s="38" t="s">
-        <v>498</v>
-      </c>
-      <c r="H29" s="42">
-        <v>4</v>
-      </c>
-      <c r="I29" s="39" t="s">
-        <v>499</v>
-      </c>
-      <c r="J29" s="38" t="s">
-        <v>500</v>
-      </c>
-      <c r="K29" s="39">
+      <c r="E29" s="55" t="s">
+        <v>564</v>
+      </c>
+      <c r="F29" s="54" t="s">
+        <v>565</v>
+      </c>
+      <c r="G29" s="54" t="s">
+        <v>566</v>
+      </c>
+      <c r="H29" s="58">
+        <v>3</v>
+      </c>
+      <c r="I29" s="55" t="s">
+        <v>567</v>
+      </c>
+      <c r="J29" s="54" t="s">
+        <v>568</v>
+      </c>
+      <c r="K29" s="55">
         <f>4.8*1000*2%*5</f>
         <v>480</v>
       </c>
     </row>
-    <row r="30" ht="36" customHeight="1" spans="1:11">
-      <c r="A30" s="38"/>
-      <c r="B30" s="43"/>
-      <c r="C30" s="41"/>
-      <c r="D30" s="41"/>
-      <c r="E30" s="39"/>
-      <c r="F30" s="38"/>
-      <c r="G30" s="38"/>
-      <c r="H30" s="42"/>
-      <c r="I30" s="38" t="s">
-        <v>501</v>
-      </c>
-      <c r="J30" s="38" t="s">
-        <v>500</v>
-      </c>
-      <c r="K30" s="39">
+    <row r="30" ht="49" customHeight="1" spans="1:11">
+      <c r="A30" s="54"/>
+      <c r="B30" s="59"/>
+      <c r="C30" s="57"/>
+      <c r="D30" s="57"/>
+      <c r="E30" s="55"/>
+      <c r="F30" s="54"/>
+      <c r="G30" s="54"/>
+      <c r="H30" s="58"/>
+      <c r="I30" s="54" t="s">
+        <v>569</v>
+      </c>
+      <c r="J30" s="54" t="s">
+        <v>568</v>
+      </c>
+      <c r="K30" s="55">
         <f>4.8*1000*2%*5</f>
         <v>480</v>
       </c>
     </row>
     <row r="31" ht="45" spans="1:11">
-      <c r="A31" s="44" t="s">
-        <v>502</v>
-      </c>
-      <c r="B31" s="44">
+      <c r="A31" s="60" t="s">
+        <v>570</v>
+      </c>
+      <c r="B31" s="60">
         <v>300</v>
       </c>
-      <c r="C31" s="45">
+      <c r="C31" s="61">
         <f>B31*1000/50</f>
         <v>6000</v>
       </c>
-      <c r="D31" s="46">
+      <c r="D31" s="62">
         <v>4</v>
       </c>
-      <c r="E31" s="44" t="s">
-        <v>503</v>
-      </c>
-      <c r="F31" s="44" t="s">
-        <v>497</v>
-      </c>
-      <c r="G31" s="44" t="s">
-        <v>504</v>
-      </c>
-      <c r="H31" s="46"/>
-      <c r="I31" s="44" t="s">
-        <v>505</v>
-      </c>
-      <c r="J31" s="44" t="s">
-        <v>506</v>
-      </c>
-      <c r="K31" s="40">
+      <c r="E31" s="60" t="s">
+        <v>571</v>
+      </c>
+      <c r="F31" s="60" t="s">
+        <v>565</v>
+      </c>
+      <c r="G31" s="60" t="s">
+        <v>572</v>
+      </c>
+      <c r="H31" s="62"/>
+      <c r="I31" s="60" t="s">
+        <v>573</v>
+      </c>
+      <c r="J31" s="60" t="s">
+        <v>574</v>
+      </c>
+      <c r="K31" s="56">
         <f>4.8*1000*70%*5</f>
         <v>16800</v>
       </c>
     </row>
     <row r="32" ht="30" spans="1:11">
-      <c r="A32" s="38" t="s">
-        <v>507</v>
-      </c>
-      <c r="B32" s="38" t="s">
-        <v>508</v>
-      </c>
-      <c r="C32" s="41">
+      <c r="A32" s="54" t="s">
+        <v>575</v>
+      </c>
+      <c r="B32" s="54" t="s">
+        <v>576</v>
+      </c>
+      <c r="C32" s="57">
         <v>800</v>
       </c>
-      <c r="D32" s="42">
-        <v>0</v>
-      </c>
-      <c r="E32" s="38" t="s">
-        <v>509</v>
-      </c>
-      <c r="F32" s="38" t="s">
-        <v>510</v>
-      </c>
-      <c r="G32" s="38" t="s">
-        <v>504</v>
-      </c>
-      <c r="H32" s="42">
-        <v>3</v>
-      </c>
-      <c r="I32" s="38" t="s">
-        <v>511</v>
-      </c>
-      <c r="J32" s="38" t="s">
-        <v>512</v>
-      </c>
-      <c r="K32" s="52">
+      <c r="D32" s="58">
+        <v>2</v>
+      </c>
+      <c r="E32" s="54" t="s">
+        <v>577</v>
+      </c>
+      <c r="F32" s="54" t="s">
+        <v>578</v>
+      </c>
+      <c r="G32" s="54" t="s">
+        <v>572</v>
+      </c>
+      <c r="H32" s="58">
+        <v>2</v>
+      </c>
+      <c r="I32" s="54" t="s">
+        <v>579</v>
+      </c>
+      <c r="J32" s="54" t="s">
+        <v>580</v>
+      </c>
+      <c r="K32" s="63">
         <f>10%*5</f>
         <v>0.5</v>
       </c>
     </row>
     <row r="33" spans="1:11">
-      <c r="A33" s="38"/>
-      <c r="B33" s="38"/>
-      <c r="C33" s="41"/>
-      <c r="D33" s="42"/>
-      <c r="E33" s="38"/>
-      <c r="F33" s="38"/>
-      <c r="G33" s="38"/>
-      <c r="H33" s="42"/>
-      <c r="I33" s="38" t="s">
-        <v>513</v>
-      </c>
-      <c r="J33" s="38" t="s">
-        <v>514</v>
-      </c>
-      <c r="K33" s="53">
-        <f>6%*5</f>
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="34" ht="43" customHeight="1" spans="1:11">
-      <c r="A34" s="38"/>
-      <c r="B34" s="38"/>
-      <c r="C34" s="41"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="38"/>
-      <c r="F34" s="38"/>
-      <c r="G34" s="38"/>
-      <c r="H34" s="42"/>
-      <c r="I34" s="38" t="s">
-        <v>515</v>
-      </c>
-      <c r="J34" s="38" t="s">
-        <v>516</v>
-      </c>
-      <c r="K34" s="53">
+      <c r="A33" s="54"/>
+      <c r="B33" s="54"/>
+      <c r="C33" s="57"/>
+      <c r="D33" s="58"/>
+      <c r="E33" s="54"/>
+      <c r="F33" s="54"/>
+      <c r="G33" s="54"/>
+      <c r="H33" s="58"/>
+      <c r="I33" s="54" t="s">
+        <v>581</v>
+      </c>
+      <c r="J33" s="54" t="s">
+        <v>582</v>
+      </c>
+      <c r="K33" s="64">
         <f>3%*5</f>
         <v>0.15</v>
       </c>
     </row>
-    <row r="36" ht="45" spans="1:8">
-      <c r="A36" s="47" t="s">
-        <v>517</v>
-      </c>
-      <c r="B36" s="47" t="s">
-        <v>518</v>
-      </c>
-      <c r="C36" s="47" t="s">
-        <v>519</v>
-      </c>
-      <c r="D36" s="47" t="s">
-        <v>520</v>
-      </c>
-      <c r="E36" s="47" t="s">
-        <v>521</v>
-      </c>
-      <c r="F36" s="47" t="s">
-        <v>522</v>
-      </c>
-      <c r="G36" s="47" t="s">
-        <v>523</v>
-      </c>
-      <c r="H36" s="47" t="s">
-        <v>524</v>
+    <row r="34" ht="43" customHeight="1" spans="1:11">
+      <c r="A34" s="54"/>
+      <c r="B34" s="54"/>
+      <c r="C34" s="57"/>
+      <c r="D34" s="58"/>
+      <c r="E34" s="54"/>
+      <c r="F34" s="54"/>
+      <c r="G34" s="54"/>
+      <c r="H34" s="58"/>
+      <c r="I34" s="54" t="s">
+        <v>583</v>
+      </c>
+      <c r="J34" s="54" t="s">
+        <v>584</v>
+      </c>
+      <c r="K34" s="64">
+        <f>3%*5</f>
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="36" ht="60" spans="1:8">
+      <c r="A36" s="42" t="s">
+        <v>585</v>
+      </c>
+      <c r="B36" s="42" t="s">
+        <v>586</v>
+      </c>
+      <c r="C36" s="42" t="s">
+        <v>587</v>
+      </c>
+      <c r="D36" s="42" t="s">
+        <v>588</v>
+      </c>
+      <c r="E36" s="42" t="s">
+        <v>589</v>
+      </c>
+      <c r="F36" s="42" t="s">
+        <v>590</v>
+      </c>
+      <c r="G36" s="42" t="s">
+        <v>591</v>
+      </c>
+      <c r="H36" s="42" t="s">
+        <v>592</v>
       </c>
     </row>
     <row r="37" ht="60" spans="1:8">
-      <c r="A37" s="47"/>
-      <c r="B37" s="47"/>
-      <c r="C37" s="47"/>
-      <c r="D37" s="47"/>
-      <c r="E37" s="47" t="s">
-        <v>525</v>
-      </c>
-      <c r="F37" s="47" t="s">
-        <v>526</v>
-      </c>
-      <c r="G37" s="47" t="s">
-        <v>527</v>
-      </c>
-      <c r="H37" s="47" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="48"/>
-      <c r="B38" s="48"/>
-      <c r="C38" s="48"/>
-      <c r="D38" s="48"/>
-      <c r="E38" s="49"/>
-      <c r="F38" s="49"/>
-      <c r="G38" s="49"/>
-      <c r="H38" s="49"/>
+      <c r="A37" s="42"/>
+      <c r="B37" s="42"/>
+      <c r="C37" s="42"/>
+      <c r="D37" s="42"/>
+      <c r="E37" s="42" t="s">
+        <v>593</v>
+      </c>
+      <c r="F37" s="42" t="s">
+        <v>594</v>
+      </c>
+      <c r="G37" s="42" t="s">
+        <v>595</v>
+      </c>
+      <c r="H37" s="42" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="38" ht="60" spans="1:10">
+      <c r="A38" s="41" t="s">
+        <v>597</v>
+      </c>
+      <c r="B38" s="41" t="s">
+        <v>598</v>
+      </c>
+      <c r="C38" s="41" t="s">
+        <v>599</v>
+      </c>
+      <c r="D38" s="41" t="s">
+        <v>600</v>
+      </c>
+      <c r="E38" s="42" t="s">
+        <v>601</v>
+      </c>
+      <c r="F38" s="42" t="s">
+        <v>602</v>
+      </c>
+      <c r="G38" s="42" t="s">
+        <v>603</v>
+      </c>
+      <c r="H38" s="42" t="s">
+        <v>604</v>
+      </c>
+      <c r="I38" s="65"/>
+      <c r="J38" s="65"/>
     </row>
     <row r="39" ht="60" spans="1:10">
-      <c r="A39" s="50" t="s">
-        <v>529</v>
-      </c>
-      <c r="B39" s="50" t="s">
-        <v>530</v>
-      </c>
-      <c r="C39" s="50" t="s">
-        <v>531</v>
-      </c>
-      <c r="D39" s="50" t="s">
-        <v>532</v>
-      </c>
-      <c r="E39" s="47" t="s">
-        <v>533</v>
-      </c>
-      <c r="F39" s="47" t="s">
-        <v>534</v>
-      </c>
-      <c r="G39" s="47" t="s">
-        <v>535</v>
-      </c>
-      <c r="H39" s="47" t="s">
-        <v>536</v>
-      </c>
-      <c r="I39" s="54"/>
-      <c r="J39" s="54"/>
-    </row>
-    <row r="40" ht="60" spans="1:10">
-      <c r="A40" s="51"/>
-      <c r="B40" s="51"/>
-      <c r="C40" s="51"/>
-      <c r="D40" s="51"/>
-      <c r="E40" s="47" t="s">
-        <v>537</v>
-      </c>
-      <c r="F40" s="47" t="s">
-        <v>538</v>
-      </c>
-      <c r="G40" s="47" t="s">
-        <v>539</v>
-      </c>
-      <c r="H40" s="47" t="s">
-        <v>540</v>
-      </c>
-      <c r="I40" s="54"/>
-      <c r="J40" s="54"/>
+      <c r="A39" s="43"/>
+      <c r="B39" s="43"/>
+      <c r="C39" s="43"/>
+      <c r="D39" s="43"/>
+      <c r="E39" s="42" t="s">
+        <v>605</v>
+      </c>
+      <c r="F39" s="42" t="s">
+        <v>606</v>
+      </c>
+      <c r="G39" s="42" t="s">
+        <v>607</v>
+      </c>
+      <c r="H39" s="42" t="s">
+        <v>608</v>
+      </c>
+      <c r="J39" s="65"/>
     </row>
   </sheetData>
   <mergeCells count="24">
     <mergeCell ref="A29:A30"/>
     <mergeCell ref="A32:A34"/>
     <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="A38:A39"/>
     <mergeCell ref="B29:B30"/>
     <mergeCell ref="B32:B34"/>
     <mergeCell ref="B36:B37"/>
-    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="B38:B39"/>
     <mergeCell ref="C29:C30"/>
     <mergeCell ref="C32:C34"/>
     <mergeCell ref="C36:C37"/>
-    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="C38:C39"/>
     <mergeCell ref="D29:D30"/>
     <mergeCell ref="D32:D34"/>
     <mergeCell ref="D36:D37"/>
-    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="D38:D39"/>
     <mergeCell ref="E29:E30"/>
     <mergeCell ref="E32:E34"/>
     <mergeCell ref="F29:F30"/>
@@ -7091,6 +7819,995 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:K41"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="22.5714285714286" customWidth="1"/>
+    <col min="2" max="2" width="19.5714285714286" customWidth="1"/>
+    <col min="3" max="3" width="26.4285714285714" customWidth="1"/>
+    <col min="4" max="4" width="18.8571428571429" customWidth="1"/>
+    <col min="5" max="5" width="34.8571428571429" customWidth="1"/>
+    <col min="6" max="6" width="23.4285714285714" customWidth="1"/>
+    <col min="7" max="7" width="27" customWidth="1"/>
+    <col min="8" max="8" width="34" customWidth="1"/>
+    <col min="9" max="9" width="14.7142857142857" customWidth="1"/>
+    <col min="10" max="10" width="15.4285714285714" customWidth="1"/>
+    <col min="11" max="11" width="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>548</v>
+      </c>
+      <c r="B1" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>550</v>
+      </c>
+      <c r="B2" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>552</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>554</v>
+      </c>
+      <c r="B4" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>556</v>
+      </c>
+      <c r="B5" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>557</v>
+      </c>
+      <c r="B6" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="27" t="s">
+        <v>435</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>436</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>437</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>558</v>
+      </c>
+      <c r="E8" s="29" t="s">
+        <v>439</v>
+      </c>
+      <c r="F8" s="27" t="s">
+        <v>440</v>
+      </c>
+      <c r="G8" s="27" t="s">
+        <v>441</v>
+      </c>
+      <c r="H8" s="27" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>190</v>
+      </c>
+      <c r="B9" s="30">
+        <f t="shared" ref="B9:B24" si="0">SUM(C9,E9)</f>
+        <v>36250</v>
+      </c>
+      <c r="C9" s="30">
+        <v>18000</v>
+      </c>
+      <c r="D9" s="30">
+        <f>C9*G9</f>
+        <v>18000</v>
+      </c>
+      <c r="E9" s="31">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A9)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A9)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A9)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A9)</f>
+        <v>18250</v>
+      </c>
+      <c r="F9" s="30">
+        <f t="shared" ref="F9:F13" si="1">E9*G9</f>
+        <v>18250</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9" s="31">
+        <f t="shared" ref="H9:H13" si="2">B9*G9</f>
+        <v>36250</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>195</v>
+      </c>
+      <c r="B10" s="30">
+        <f t="shared" si="0"/>
+        <v>27350</v>
+      </c>
+      <c r="C10" s="30">
+        <v>18400</v>
+      </c>
+      <c r="D10" s="30">
+        <f>C10*G10</f>
+        <v>18400</v>
+      </c>
+      <c r="E10" s="31">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A10)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A10)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A10)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A10)</f>
+        <v>8950</v>
+      </c>
+      <c r="F10" s="30">
+        <f t="shared" si="1"/>
+        <v>8950</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10" s="31">
+        <f t="shared" si="2"/>
+        <v>27350</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>198</v>
+      </c>
+      <c r="B11" s="30">
+        <f t="shared" si="0"/>
+        <v>2909.52380952381</v>
+      </c>
+      <c r="C11" s="30">
+        <f>6840/G11</f>
+        <v>814.285714285714</v>
+      </c>
+      <c r="D11" s="30">
+        <f>C11*G11</f>
+        <v>6840</v>
+      </c>
+      <c r="E11" s="32">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A11)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A11)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A11)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A11)</f>
+        <v>2095.23809523809</v>
+      </c>
+      <c r="F11" s="30">
+        <f t="shared" si="1"/>
+        <v>17600</v>
+      </c>
+      <c r="G11">
+        <v>8.4</v>
+      </c>
+      <c r="H11" s="31">
+        <f t="shared" si="2"/>
+        <v>24440</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>202</v>
+      </c>
+      <c r="B12" s="30">
+        <f t="shared" si="0"/>
+        <v>870</v>
+      </c>
+      <c r="C12" s="30">
+        <v>370</v>
+      </c>
+      <c r="D12" s="30">
+        <f>C12*G12</f>
+        <v>2072</v>
+      </c>
+      <c r="E12" s="32">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A12)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A12)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A12)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A12)</f>
+        <v>500</v>
+      </c>
+      <c r="F12" s="30">
+        <f t="shared" si="1"/>
+        <v>2800</v>
+      </c>
+      <c r="G12">
+        <v>5.6</v>
+      </c>
+      <c r="H12" s="31">
+        <f t="shared" si="2"/>
+        <v>4872</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>210</v>
+      </c>
+      <c r="B13" s="30">
+        <f t="shared" si="0"/>
+        <v>880</v>
+      </c>
+      <c r="C13" s="30">
+        <v>380</v>
+      </c>
+      <c r="D13" s="30">
+        <f>C13*G13</f>
+        <v>4408</v>
+      </c>
+      <c r="E13" s="32">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A13)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A13)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A13)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A13)</f>
+        <v>500</v>
+      </c>
+      <c r="F13" s="30">
+        <f t="shared" si="1"/>
+        <v>5800</v>
+      </c>
+      <c r="G13">
+        <v>11.6</v>
+      </c>
+      <c r="H13" s="31">
+        <f t="shared" si="2"/>
+        <v>10208</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>233</v>
+      </c>
+      <c r="B14" s="33">
+        <f t="shared" si="0"/>
+        <v>1.9</v>
+      </c>
+      <c r="C14" s="33">
+        <v>1.2</v>
+      </c>
+      <c r="D14" s="30">
+        <f t="shared" ref="D14:D17" si="3">C14*G14*100</f>
+        <v>16800</v>
+      </c>
+      <c r="E14" s="34">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A14)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A14)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A14)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A14)</f>
+        <v>0.7</v>
+      </c>
+      <c r="F14" s="30">
+        <f t="shared" ref="F14:F17" si="4">E14*G14*100</f>
+        <v>9800</v>
+      </c>
+      <c r="G14">
+        <v>140</v>
+      </c>
+      <c r="H14" s="31">
+        <f t="shared" ref="H14:H17" si="5">B14*G14*100</f>
+        <v>26600</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>453</v>
+      </c>
+      <c r="B15" s="33">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C15" s="33">
+        <v>0</v>
+      </c>
+      <c r="D15" s="30">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E15" s="34">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A15)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A15)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A15)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A15)</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="30">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>140</v>
+      </c>
+      <c r="H15" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>224</v>
+      </c>
+      <c r="B16" s="33">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+      <c r="C16" s="33">
+        <v>0.2</v>
+      </c>
+      <c r="D16" s="30">
+        <f t="shared" si="3"/>
+        <v>2800</v>
+      </c>
+      <c r="E16" s="34">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A16)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A16)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A16)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A16)</f>
+        <v>0.4</v>
+      </c>
+      <c r="F16" s="30">
+        <f t="shared" si="4"/>
+        <v>5600</v>
+      </c>
+      <c r="G16">
+        <v>140</v>
+      </c>
+      <c r="H16" s="31">
+        <f t="shared" si="5"/>
+        <v>8400</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>229</v>
+      </c>
+      <c r="B17" s="33">
+        <f t="shared" si="0"/>
+        <v>1.5</v>
+      </c>
+      <c r="C17" s="33">
+        <v>0.5</v>
+      </c>
+      <c r="D17" s="30">
+        <f t="shared" si="3"/>
+        <v>1400</v>
+      </c>
+      <c r="E17" s="34">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A17)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A17)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A17)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A17)</f>
+        <v>1</v>
+      </c>
+      <c r="F17" s="30">
+        <f t="shared" si="4"/>
+        <v>2800</v>
+      </c>
+      <c r="G17">
+        <v>28</v>
+      </c>
+      <c r="H17" s="31">
+        <f t="shared" si="5"/>
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>217</v>
+      </c>
+      <c r="B18" s="30">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="C18" s="30">
+        <v>100</v>
+      </c>
+      <c r="D18" s="30">
+        <f t="shared" ref="D18:D21" si="6">C18*G18</f>
+        <v>40000</v>
+      </c>
+      <c r="E18" s="31">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A18)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A18)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A18)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A18)</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="30">
+        <f t="shared" ref="F18:F21" si="7">E18*G18</f>
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>400</v>
+      </c>
+      <c r="H18" s="31">
+        <f t="shared" ref="H18:H21" si="8">B18*G18</f>
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
+        <v>387</v>
+      </c>
+      <c r="B19" s="30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="C19" s="30">
+        <v>4</v>
+      </c>
+      <c r="D19" s="30">
+        <f t="shared" si="6"/>
+        <v>4500</v>
+      </c>
+      <c r="E19" s="31">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A19)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A19)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A19)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A19)</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="30">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>1125</v>
+      </c>
+      <c r="H19" s="31">
+        <f t="shared" si="8"/>
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>455</v>
+      </c>
+      <c r="B20" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C20" s="30">
+        <v>0</v>
+      </c>
+      <c r="D20" s="30">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="E20" s="31">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A20)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A20)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A20)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A20)</f>
+        <v>0</v>
+      </c>
+      <c r="F20" s="30">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>4800</v>
+      </c>
+      <c r="H20" s="31">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" t="s">
+        <v>456</v>
+      </c>
+      <c r="B21" s="30">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="C21" s="30">
+        <v>10</v>
+      </c>
+      <c r="D21" s="30">
+        <f t="shared" si="6"/>
+        <v>23260</v>
+      </c>
+      <c r="E21" s="31">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A21)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A21)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A21)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A21)</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="30">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>2326</v>
+      </c>
+      <c r="H21" s="31">
+        <f t="shared" si="8"/>
+        <v>23260</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" t="s">
+        <v>237</v>
+      </c>
+      <c r="B22" s="33">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="C22" s="33">
+        <v>1</v>
+      </c>
+      <c r="D22" s="30">
+        <f t="shared" ref="D22:D24" si="9">C22*G22*100</f>
+        <v>16800</v>
+      </c>
+      <c r="E22" s="34">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A22)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A22)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A22)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A22)</f>
+        <v>0</v>
+      </c>
+      <c r="F22" s="30">
+        <f t="shared" ref="F22:F24" si="10">E22*G22*100</f>
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>168</v>
+      </c>
+      <c r="H22" s="31">
+        <f t="shared" ref="H22:H24" si="11">B22*G22*100</f>
+        <v>16800</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>241</v>
+      </c>
+      <c r="B23" s="33">
+        <f t="shared" si="0"/>
+        <v>0.1</v>
+      </c>
+      <c r="C23" s="33">
+        <v>0.1</v>
+      </c>
+      <c r="D23" s="30">
+        <f t="shared" si="9"/>
+        <v>1680</v>
+      </c>
+      <c r="E23" s="34">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A23)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A23)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A23)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A23)</f>
+        <v>0</v>
+      </c>
+      <c r="F23" s="30">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>168</v>
+      </c>
+      <c r="H23" s="31">
+        <f t="shared" si="11"/>
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>245</v>
+      </c>
+      <c r="B24" s="33">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C24" s="33">
+        <v>0</v>
+      </c>
+      <c r="D24" s="30">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="E24" s="34">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A24)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A24)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A24)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A24)</f>
+        <v>0</v>
+      </c>
+      <c r="F24" s="30">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>233</v>
+      </c>
+      <c r="H24" s="31">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="35">
+        <f t="shared" ref="D25:H25" si="12">SUM(D9:D24)</f>
+        <v>156960</v>
+      </c>
+      <c r="E25" s="36"/>
+      <c r="F25" s="35">
+        <f t="shared" si="12"/>
+        <v>71600</v>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="H25" s="35">
+        <f t="shared" si="12"/>
+        <v>228560</v>
+      </c>
+    </row>
+    <row r="26" customFormat="1" spans="1:11">
+      <c r="A26" t="s">
+        <v>559</v>
+      </c>
+      <c r="D26" s="36">
+        <f>'Balanced Dummy '!D18-D25</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="36"/>
+      <c r="F26" s="36"/>
+      <c r="K26" s="50"/>
+    </row>
+    <row r="27" customFormat="1" spans="4:11">
+      <c r="D27" s="36"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="36"/>
+      <c r="K27" s="50"/>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="37" t="s">
+        <v>443</v>
+      </c>
+      <c r="B28" s="38" t="s">
+        <v>85</v>
+      </c>
+      <c r="C28" s="38" t="s">
+        <v>444</v>
+      </c>
+      <c r="D28" s="38" t="s">
+        <v>445</v>
+      </c>
+      <c r="E28" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="F28" s="37" t="s">
+        <v>399</v>
+      </c>
+      <c r="G28" s="37" t="s">
+        <v>560</v>
+      </c>
+      <c r="H28" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="I28" s="38" t="s">
+        <v>304</v>
+      </c>
+      <c r="J28" s="37" t="s">
+        <v>561</v>
+      </c>
+      <c r="K28" s="38" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="29" ht="30" spans="1:11">
+      <c r="A29" s="37" t="s">
+        <v>613</v>
+      </c>
+      <c r="B29" s="37">
+        <v>100</v>
+      </c>
+      <c r="C29" s="37">
+        <f>2*1000*1.5</f>
+        <v>3000</v>
+      </c>
+      <c r="D29" s="37">
+        <v>1</v>
+      </c>
+      <c r="E29" s="37" t="s">
+        <v>614</v>
+      </c>
+      <c r="F29" s="37" t="s">
+        <v>615</v>
+      </c>
+      <c r="G29" s="37" t="s">
+        <v>572</v>
+      </c>
+      <c r="H29" s="37"/>
+      <c r="I29" s="37" t="s">
+        <v>616</v>
+      </c>
+      <c r="J29" s="37" t="s">
+        <v>617</v>
+      </c>
+      <c r="K29" s="37">
+        <f>4.8*1000*30%*5</f>
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="30" ht="45" spans="1:11">
+      <c r="A30" s="37" t="s">
+        <v>618</v>
+      </c>
+      <c r="B30" s="37">
+        <v>100</v>
+      </c>
+      <c r="C30" s="37">
+        <f>2*1000*2</f>
+        <v>4000</v>
+      </c>
+      <c r="D30" s="37">
+        <v>10</v>
+      </c>
+      <c r="E30" s="37" t="s">
+        <v>619</v>
+      </c>
+      <c r="F30" s="37" t="s">
+        <v>620</v>
+      </c>
+      <c r="G30" s="37" t="s">
+        <v>620</v>
+      </c>
+      <c r="H30" s="37">
+        <v>6</v>
+      </c>
+      <c r="I30" s="37" t="s">
+        <v>621</v>
+      </c>
+      <c r="J30" s="37" t="s">
+        <v>582</v>
+      </c>
+      <c r="K30" s="51">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="31" ht="30" spans="1:11">
+      <c r="A31" s="39" t="s">
+        <v>622</v>
+      </c>
+      <c r="B31" s="39" t="s">
+        <v>623</v>
+      </c>
+      <c r="C31" s="39">
+        <f>2*1000*0.4</f>
+        <v>800</v>
+      </c>
+      <c r="D31" s="39">
+        <v>1</v>
+      </c>
+      <c r="E31" s="39" t="s">
+        <v>624</v>
+      </c>
+      <c r="F31" s="40" t="s">
+        <v>625</v>
+      </c>
+      <c r="G31" s="39" t="s">
+        <v>572</v>
+      </c>
+      <c r="H31" s="39">
+        <v>1</v>
+      </c>
+      <c r="I31" s="52" t="s">
+        <v>626</v>
+      </c>
+      <c r="J31" s="52" t="s">
+        <v>627</v>
+      </c>
+      <c r="K31" s="53">
+        <f>4%*5</f>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="32" ht="66" customHeight="1" spans="1:11">
+      <c r="A32" s="39"/>
+      <c r="B32" s="39"/>
+      <c r="C32" s="39"/>
+      <c r="D32" s="39"/>
+      <c r="E32" s="39"/>
+      <c r="F32" s="40"/>
+      <c r="G32" s="39"/>
+      <c r="H32" s="39"/>
+      <c r="I32" s="40" t="s">
+        <v>628</v>
+      </c>
+      <c r="J32" s="40" t="s">
+        <v>629</v>
+      </c>
+      <c r="K32" s="40">
+        <f>4.8*1000*20%*5</f>
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="33" ht="30" spans="1:11">
+      <c r="A33" s="40" t="s">
+        <v>630</v>
+      </c>
+      <c r="B33" s="40">
+        <v>150</v>
+      </c>
+      <c r="C33" s="40">
+        <f>2*1000*1.5</f>
+        <v>3000</v>
+      </c>
+      <c r="D33" s="40">
+        <v>5</v>
+      </c>
+      <c r="E33" s="40" t="s">
+        <v>631</v>
+      </c>
+      <c r="F33" s="40" t="s">
+        <v>625</v>
+      </c>
+      <c r="G33" s="40" t="s">
+        <v>632</v>
+      </c>
+      <c r="H33" s="40">
+        <v>3</v>
+      </c>
+      <c r="I33" s="52" t="s">
+        <v>626</v>
+      </c>
+      <c r="J33" s="52" t="s">
+        <v>627</v>
+      </c>
+      <c r="K33" s="53">
+        <f>4%*5</f>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="34" ht="54" customHeight="1" spans="1:11">
+      <c r="A34" s="40"/>
+      <c r="B34" s="40"/>
+      <c r="C34" s="40"/>
+      <c r="D34" s="40"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="40"/>
+      <c r="H34" s="40"/>
+      <c r="I34" s="40" t="s">
+        <v>628</v>
+      </c>
+      <c r="J34" s="40" t="s">
+        <v>629</v>
+      </c>
+      <c r="K34" s="40">
+        <f>4.8*1000*20%*5</f>
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="36" ht="60" spans="1:8">
+      <c r="A36" s="41" t="s">
+        <v>585</v>
+      </c>
+      <c r="B36" s="41" t="s">
+        <v>633</v>
+      </c>
+      <c r="C36" s="41" t="s">
+        <v>634</v>
+      </c>
+      <c r="D36" s="42" t="s">
+        <v>635</v>
+      </c>
+      <c r="E36" s="42" t="s">
+        <v>636</v>
+      </c>
+      <c r="F36" s="42" t="s">
+        <v>637</v>
+      </c>
+      <c r="G36" s="42" t="s">
+        <v>638</v>
+      </c>
+      <c r="H36" s="42" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="37" ht="60" spans="1:8">
+      <c r="A37" s="43"/>
+      <c r="B37" s="43"/>
+      <c r="C37" s="43"/>
+      <c r="D37" s="42"/>
+      <c r="E37" s="42" t="s">
+        <v>640</v>
+      </c>
+      <c r="F37" s="42" t="s">
+        <v>641</v>
+      </c>
+      <c r="G37" s="42" t="s">
+        <v>642</v>
+      </c>
+      <c r="H37" s="42" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="44"/>
+      <c r="B38" s="44"/>
+      <c r="C38" s="44"/>
+      <c r="D38" s="44"/>
+      <c r="E38" s="44"/>
+      <c r="F38" s="44"/>
+      <c r="G38" s="44"/>
+      <c r="H38" s="44"/>
+    </row>
+    <row r="39" ht="60" spans="1:8">
+      <c r="A39" s="45" t="s">
+        <v>597</v>
+      </c>
+      <c r="B39" s="45" t="s">
+        <v>644</v>
+      </c>
+      <c r="C39" s="45" t="s">
+        <v>645</v>
+      </c>
+      <c r="D39" s="45" t="s">
+        <v>646</v>
+      </c>
+      <c r="E39" s="46" t="s">
+        <v>647</v>
+      </c>
+      <c r="F39" s="46" t="s">
+        <v>648</v>
+      </c>
+      <c r="G39" s="46" t="s">
+        <v>649</v>
+      </c>
+      <c r="H39" s="47"/>
+    </row>
+    <row r="40" ht="60" spans="1:8">
+      <c r="A40" s="48"/>
+      <c r="B40" s="48"/>
+      <c r="C40" s="48"/>
+      <c r="D40" s="48"/>
+      <c r="E40" s="46" t="s">
+        <v>650</v>
+      </c>
+      <c r="F40" s="46" t="s">
+        <v>651</v>
+      </c>
+      <c r="G40" s="46"/>
+      <c r="H40" s="47"/>
+    </row>
+    <row r="41" ht="60" spans="1:8">
+      <c r="A41" s="49"/>
+      <c r="B41" s="49"/>
+      <c r="C41" s="49"/>
+      <c r="D41" s="49"/>
+      <c r="E41" s="46" t="s">
+        <v>652</v>
+      </c>
+      <c r="F41" s="46" t="s">
+        <v>653</v>
+      </c>
+      <c r="G41" s="46" t="s">
+        <v>654</v>
+      </c>
+      <c r="H41" s="47"/>
+    </row>
+  </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A39:A41"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="B39:B41"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="C39:C41"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="F33:F34"/>
+    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="G33:G34"/>
+    <mergeCell ref="H31:H32"/>
+    <mergeCell ref="H33:H34"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I52"/>
@@ -7109,48 +8826,48 @@
   <sheetData>
     <row r="1" s="2" customFormat="1" spans="1:9">
       <c r="A1" s="6" t="s">
-        <v>541</v>
+        <v>655</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>542</v>
+        <v>656</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>543</v>
+        <v>657</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>544</v>
+        <v>658</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>278</v>
+        <v>304</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>545</v>
+        <v>659</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>546</v>
+        <v>660</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>547</v>
+        <v>661</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>548</v>
+        <v>662</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="10" t="s">
-        <v>549</v>
+        <v>663</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>497</v>
+        <v>565</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>504</v>
+        <v>572</v>
       </c>
       <c r="D2" s="12">
         <v>0</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="F2" s="13">
         <f>I2/H2</f>
@@ -7170,13 +8887,13 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="10" t="s">
-        <v>549</v>
+        <v>663</v>
       </c>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
       <c r="D3" s="16"/>
       <c r="E3" s="13" t="s">
-        <v>387</v>
+        <v>456</v>
       </c>
       <c r="F3" s="13">
         <v>4</v>
@@ -7192,13 +8909,13 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="10" t="s">
-        <v>549</v>
+        <v>663</v>
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
       <c r="D4" s="17"/>
       <c r="E4" s="13" t="s">
-        <v>191</v>
+        <v>217</v>
       </c>
       <c r="F4" s="13">
         <v>-20</v>
@@ -7214,19 +8931,19 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="10" t="s">
-        <v>484</v>
+        <v>553</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>497</v>
+        <v>565</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>550</v>
+        <v>664</v>
       </c>
       <c r="D5" s="18">
         <v>0.5</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="F5" s="13">
         <f>I5/H5</f>
@@ -7246,13 +8963,13 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="10" t="s">
-        <v>484</v>
+        <v>553</v>
       </c>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
       <c r="D6" s="17"/>
       <c r="E6" s="13" t="s">
-        <v>191</v>
+        <v>217</v>
       </c>
       <c r="F6" s="13">
         <v>-30</v>
@@ -7268,19 +8985,19 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="10" t="s">
-        <v>551</v>
+        <v>665</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>497</v>
+        <v>565</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>552</v>
+        <v>666</v>
       </c>
       <c r="D7" s="18">
         <v>0.5</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="F7" s="13">
         <f>I7/H7</f>
@@ -7300,13 +9017,13 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="10" t="s">
-        <v>551</v>
+        <v>665</v>
       </c>
       <c r="B8" s="16"/>
       <c r="C8" s="16"/>
       <c r="D8" s="16"/>
       <c r="E8" s="13" t="s">
-        <v>198</v>
+        <v>224</v>
       </c>
       <c r="F8" s="19">
         <v>0.1</v>
@@ -7322,13 +9039,13 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="10" t="s">
-        <v>551</v>
+        <v>665</v>
       </c>
       <c r="B9" s="17"/>
       <c r="C9" s="17"/>
       <c r="D9" s="17"/>
       <c r="E9" s="13" t="s">
-        <v>191</v>
+        <v>217</v>
       </c>
       <c r="F9" s="13">
         <v>-15</v>
@@ -7344,19 +9061,19 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="10" t="s">
-        <v>553</v>
+        <v>611</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>554</v>
+        <v>615</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>504</v>
+        <v>572</v>
       </c>
       <c r="D10" s="12">
         <v>0</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="F10" s="13">
         <f>I10/H10</f>
@@ -7376,13 +9093,13 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="10" t="s">
-        <v>553</v>
+        <v>611</v>
       </c>
       <c r="B11" s="16"/>
       <c r="C11" s="16"/>
       <c r="D11" s="16"/>
       <c r="E11" s="13" t="s">
-        <v>198</v>
+        <v>224</v>
       </c>
       <c r="F11" s="19">
         <v>0.1</v>
@@ -7398,13 +9115,13 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="10" t="s">
-        <v>553</v>
+        <v>611</v>
       </c>
       <c r="B12" s="17"/>
       <c r="C12" s="17"/>
       <c r="D12" s="17"/>
       <c r="E12" s="13" t="s">
-        <v>207</v>
+        <v>233</v>
       </c>
       <c r="F12" s="19">
         <v>0.3</v>
@@ -7420,19 +9137,19 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="10" t="s">
-        <v>555</v>
+        <v>667</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>497</v>
+        <v>565</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>556</v>
+        <v>668</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>557</v>
+        <v>669</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="F13" s="13">
         <f>I13/H13</f>
@@ -7452,13 +9169,13 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="10" t="s">
-        <v>555</v>
+        <v>667</v>
       </c>
       <c r="B14" s="16"/>
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="13" t="s">
-        <v>384</v>
+        <v>453</v>
       </c>
       <c r="F14" s="19">
         <v>0.2</v>
@@ -7474,13 +9191,13 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="10" t="s">
-        <v>555</v>
+        <v>667</v>
       </c>
       <c r="B15" s="16"/>
       <c r="C15" s="16"/>
       <c r="D15" s="16"/>
       <c r="E15" s="13" t="s">
-        <v>207</v>
+        <v>233</v>
       </c>
       <c r="F15" s="19">
         <v>0.2</v>
@@ -7496,13 +9213,13 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="10" t="s">
-        <v>555</v>
+        <v>667</v>
       </c>
       <c r="B16" s="17"/>
       <c r="C16" s="17"/>
       <c r="D16" s="17"/>
       <c r="E16" s="13" t="s">
-        <v>191</v>
+        <v>217</v>
       </c>
       <c r="F16" s="13">
         <v>-5</v>
@@ -7518,19 +9235,19 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="10" t="s">
-        <v>558</v>
+        <v>670</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>554</v>
+        <v>615</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>559</v>
+        <v>671</v>
       </c>
       <c r="D17" s="18">
         <v>0.5</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="F17" s="13">
         <f>I17/H17</f>
@@ -7550,13 +9267,13 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="10" t="s">
-        <v>558</v>
+        <v>670</v>
       </c>
       <c r="B18" s="16"/>
       <c r="C18" s="16"/>
       <c r="D18" s="16"/>
       <c r="E18" s="13" t="s">
-        <v>386</v>
+        <v>455</v>
       </c>
       <c r="F18" s="13">
         <v>1</v>
@@ -7572,13 +9289,13 @@
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="10" t="s">
-        <v>558</v>
+        <v>670</v>
       </c>
       <c r="B19" s="17"/>
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
       <c r="E19" s="13" t="s">
-        <v>191</v>
+        <v>217</v>
       </c>
       <c r="F19" s="13">
         <v>-25</v>
@@ -7594,17 +9311,17 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="20" t="s">
-        <v>560</v>
+        <v>672</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>497</v>
+        <v>565</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>504</v>
+        <v>572</v>
       </c>
       <c r="D20" s="21"/>
       <c r="E20" s="13" t="s">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="F20" s="13">
         <f>I20/H20</f>
@@ -7623,13 +9340,13 @@
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="10" t="s">
-        <v>487</v>
+        <v>556</v>
       </c>
       <c r="B21" s="22"/>
       <c r="C21" s="22"/>
       <c r="D21" s="12"/>
       <c r="E21" s="13" t="s">
-        <v>176</v>
+        <v>202</v>
       </c>
       <c r="F21" s="13">
         <v>500</v>
@@ -7648,13 +9365,13 @@
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="10" t="s">
-        <v>487</v>
+        <v>556</v>
       </c>
       <c r="B22" s="16"/>
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="13" t="s">
-        <v>184</v>
+        <v>210</v>
       </c>
       <c r="F22" s="13">
         <v>500</v>
@@ -7673,13 +9390,13 @@
     </row>
     <row r="23" customFormat="1" spans="1:9">
       <c r="A23" s="10" t="s">
-        <v>487</v>
+        <v>556</v>
       </c>
       <c r="B23" s="17"/>
       <c r="C23" s="17"/>
       <c r="D23" s="17"/>
       <c r="E23" s="13" t="s">
-        <v>164</v>
+        <v>190</v>
       </c>
       <c r="F23" s="13">
         <f>I23/H23</f>
@@ -7699,13 +9416,13 @@
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="10" t="s">
-        <v>488</v>
+        <v>557</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
       <c r="D24" s="12"/>
       <c r="E24" s="13" t="s">
-        <v>164</v>
+        <v>190</v>
       </c>
       <c r="F24" s="13">
         <f>I24/H24</f>
@@ -7725,13 +9442,13 @@
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="10" t="s">
-        <v>488</v>
+        <v>557</v>
       </c>
       <c r="B25" s="17"/>
       <c r="C25" s="17"/>
       <c r="D25" s="17"/>
       <c r="E25" s="13" t="s">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="F25" s="13">
         <f>I25/H25</f>
@@ -7750,13 +9467,13 @@
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="10" t="s">
-        <v>561</v>
+        <v>673</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
       <c r="D26" s="12"/>
       <c r="E26" s="13" t="s">
-        <v>164</v>
+        <v>190</v>
       </c>
       <c r="F26" s="24">
         <f>I26/H26</f>
@@ -7775,13 +9492,13 @@
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="10" t="s">
-        <v>561</v>
+        <v>673</v>
       </c>
       <c r="B27" s="16"/>
       <c r="C27" s="16"/>
       <c r="D27" s="16"/>
       <c r="E27" s="13" t="s">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="F27" s="24">
         <f>I27/H27</f>
@@ -7801,13 +9518,13 @@
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="10" t="s">
-        <v>561</v>
+        <v>673</v>
       </c>
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
       <c r="D28" s="16"/>
       <c r="E28" s="13" t="s">
-        <v>207</v>
+        <v>233</v>
       </c>
       <c r="F28" s="25">
         <v>0.2</v>
@@ -7823,13 +9540,13 @@
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="10" t="s">
-        <v>561</v>
+        <v>673</v>
       </c>
       <c r="B29" s="16"/>
       <c r="C29" s="16"/>
       <c r="D29" s="16"/>
       <c r="E29" s="13" t="s">
-        <v>176</v>
+        <v>202</v>
       </c>
       <c r="F29" s="24">
         <f t="shared" ref="F29:F35" si="1">I29/H29</f>
@@ -7848,13 +9565,13 @@
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="10" t="s">
-        <v>561</v>
+        <v>673</v>
       </c>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
       <c r="E30" s="13" t="s">
-        <v>184</v>
+        <v>210</v>
       </c>
       <c r="F30" s="24">
         <f t="shared" si="1"/>
@@ -7873,13 +9590,13 @@
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="10" t="s">
-        <v>562</v>
+        <v>674</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
       <c r="D31" s="12"/>
       <c r="E31" s="13" t="s">
-        <v>164</v>
+        <v>190</v>
       </c>
       <c r="F31" s="24">
         <f t="shared" si="1"/>
@@ -7898,13 +9615,13 @@
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="10" t="s">
-        <v>562</v>
+        <v>674</v>
       </c>
       <c r="B32" s="16"/>
       <c r="C32" s="16"/>
       <c r="D32" s="16"/>
       <c r="E32" s="13" t="s">
-        <v>176</v>
+        <v>202</v>
       </c>
       <c r="F32" s="24">
         <f t="shared" si="1"/>
@@ -7923,13 +9640,13 @@
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="10" t="s">
-        <v>562</v>
+        <v>674</v>
       </c>
       <c r="B33" s="17"/>
       <c r="C33" s="17"/>
       <c r="D33" s="17"/>
       <c r="E33" s="13" t="s">
-        <v>184</v>
+        <v>210</v>
       </c>
       <c r="F33" s="24">
         <f t="shared" si="1"/>
@@ -7948,13 +9665,13 @@
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="10" t="s">
-        <v>563</v>
+        <v>675</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
       <c r="D34" s="12"/>
       <c r="E34" s="13" t="s">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="F34" s="24">
         <f t="shared" si="1"/>
@@ -7970,13 +9687,13 @@
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="10" t="s">
-        <v>563</v>
+        <v>675</v>
       </c>
       <c r="B35" s="16"/>
       <c r="C35" s="16"/>
       <c r="D35" s="16"/>
       <c r="E35" s="13" t="s">
-        <v>184</v>
+        <v>210</v>
       </c>
       <c r="F35" s="24">
         <f t="shared" si="1"/>
@@ -7993,13 +9710,13 @@
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="10" t="s">
-        <v>563</v>
+        <v>675</v>
       </c>
       <c r="B36" s="17"/>
       <c r="C36" s="17"/>
       <c r="D36" s="17"/>
       <c r="E36" s="13" t="s">
-        <v>387</v>
+        <v>456</v>
       </c>
       <c r="F36" s="13">
         <v>2</v>
@@ -8015,13 +9732,13 @@
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="10" t="s">
-        <v>564</v>
+        <v>676</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
       <c r="D37" s="12"/>
       <c r="E37" s="13" t="s">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="F37" s="13">
         <f>I37/H37</f>
@@ -8041,13 +9758,13 @@
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="10" t="s">
-        <v>564</v>
+        <v>676</v>
       </c>
       <c r="B38" s="16"/>
       <c r="C38" s="16"/>
       <c r="D38" s="16"/>
       <c r="E38" s="13" t="s">
-        <v>198</v>
+        <v>224</v>
       </c>
       <c r="F38" s="19">
         <v>0.2</v>
@@ -8063,13 +9780,13 @@
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="10" t="s">
-        <v>564</v>
+        <v>676</v>
       </c>
       <c r="B39" s="17"/>
       <c r="C39" s="17"/>
       <c r="D39" s="17"/>
       <c r="E39" s="13" t="s">
-        <v>207</v>
+        <v>233</v>
       </c>
       <c r="F39" s="19">
         <v>0.2</v>
@@ -8085,13 +9802,13 @@
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="10" t="s">
-        <v>565</v>
+        <v>612</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
       <c r="D40" s="12"/>
       <c r="E40" s="13" t="s">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="F40" s="13">
         <f>I40/H40</f>
@@ -8111,13 +9828,13 @@
     </row>
     <row r="41" spans="1:9">
       <c r="A41" s="10" t="s">
-        <v>565</v>
+        <v>612</v>
       </c>
       <c r="B41" s="16"/>
       <c r="C41" s="16"/>
       <c r="D41" s="16"/>
       <c r="E41" s="13" t="s">
-        <v>198</v>
+        <v>224</v>
       </c>
       <c r="F41" s="19">
         <v>0.3</v>
@@ -8133,13 +9850,13 @@
     </row>
     <row r="42" spans="1:9">
       <c r="A42" s="10" t="s">
-        <v>565</v>
+        <v>612</v>
       </c>
       <c r="B42" s="16"/>
       <c r="C42" s="16"/>
       <c r="D42" s="16"/>
       <c r="E42" s="13" t="s">
-        <v>203</v>
+        <v>229</v>
       </c>
       <c r="F42" s="19">
         <v>1</v>
@@ -8155,13 +9872,13 @@
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="10" t="s">
-        <v>565</v>
+        <v>612</v>
       </c>
       <c r="B43" s="17"/>
       <c r="C43" s="17"/>
       <c r="D43" s="17"/>
       <c r="E43" s="13" t="s">
-        <v>207</v>
+        <v>233</v>
       </c>
       <c r="F43" s="19">
         <v>0.4</v>
@@ -8177,42 +9894,42 @@
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>566</v>
+        <v>677</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>567</v>
+        <v>678</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="3" t="s">
-        <v>568</v>
+        <v>679</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="3" t="s">
-        <v>569</v>
+        <v>680</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="3" t="s">
-        <v>570</v>
+        <v>681</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="3" t="s">
-        <v>571</v>
+        <v>682</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="3" t="s">
-        <v>572</v>
+        <v>683</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>573</v>
+        <v>684</v>
       </c>
     </row>
   </sheetData>
@@ -8262,7 +9979,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C29"/>
@@ -8275,241 +9992,241 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>574</v>
+        <v>685</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>575</v>
+        <v>686</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>576</v>
+        <v>687</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>577</v>
+        <v>688</v>
       </c>
       <c r="C2" t="s">
-        <v>578</v>
+        <v>689</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>579</v>
+        <v>690</v>
       </c>
       <c r="C3" t="s">
-        <v>580</v>
+        <v>691</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>513</v>
+        <v>581</v>
       </c>
       <c r="C4" t="s">
-        <v>581</v>
+        <v>692</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>515</v>
+        <v>583</v>
       </c>
       <c r="C5" t="s">
-        <v>582</v>
+        <v>693</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>583</v>
+        <v>694</v>
       </c>
       <c r="C6" t="s">
-        <v>584</v>
+        <v>695</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>585</v>
+        <v>696</v>
       </c>
       <c r="C7" t="s">
-        <v>586</v>
+        <v>697</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>587</v>
+        <v>698</v>
       </c>
       <c r="C8" t="s">
-        <v>588</v>
+        <v>699</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>589</v>
+        <v>700</v>
       </c>
       <c r="C9" t="s">
-        <v>590</v>
+        <v>701</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>591</v>
+        <v>702</v>
       </c>
       <c r="C10" t="s">
-        <v>592</v>
+        <v>703</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>593</v>
+        <v>704</v>
       </c>
       <c r="C11" t="s">
-        <v>594</v>
+        <v>705</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>595</v>
+        <v>706</v>
       </c>
       <c r="C12" t="s">
-        <v>596</v>
+        <v>707</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>597</v>
+        <v>708</v>
       </c>
       <c r="C13" t="s">
-        <v>598</v>
+        <v>709</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>599</v>
+        <v>710</v>
       </c>
       <c r="C14" t="s">
-        <v>600</v>
+        <v>711</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>562</v>
+        <v>674</v>
       </c>
       <c r="B15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C15" t="s">
-        <v>601</v>
+        <v>712</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>602</v>
+        <v>713</v>
       </c>
       <c r="C16" t="s">
-        <v>603</v>
+        <v>714</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>460</v>
+        <v>529</v>
       </c>
       <c r="B18">
         <v>3</v>
       </c>
       <c r="C18" t="s">
-        <v>604</v>
+        <v>715</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>605</v>
+        <v>716</v>
       </c>
       <c r="B19">
         <v>3</v>
       </c>
       <c r="C19" t="s">
-        <v>606</v>
+        <v>717</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>361</v>
+        <v>387</v>
       </c>
       <c r="C20" t="s">
-        <v>607</v>
+        <v>718</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>608</v>
+        <v>719</v>
       </c>
       <c r="C21" t="s">
-        <v>609</v>
+        <v>720</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>610</v>
+        <v>721</v>
       </c>
       <c r="B22" t="s">
-        <v>611</v>
+        <v>722</v>
       </c>
       <c r="C22" t="s">
-        <v>612</v>
+        <v>723</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>613</v>
+        <v>724</v>
       </c>
       <c r="C23" t="s">
-        <v>614</v>
+        <v>725</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>615</v>
+        <v>726</v>
       </c>
       <c r="C24" t="s">
-        <v>616</v>
+        <v>727</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>617</v>
+        <v>728</v>
       </c>
       <c r="C25" t="s">
-        <v>618</v>
+        <v>729</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>619</v>
+        <v>730</v>
       </c>
       <c r="C26" t="s">
-        <v>620</v>
+        <v>731</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>621</v>
+        <v>732</v>
       </c>
       <c r="C27" t="s">
-        <v>622</v>
+        <v>733</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>623</v>
+        <v>734</v>
       </c>
       <c r="C28" t="s">
-        <v>624</v>
+        <v>735</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>625</v>
+        <v>736</v>
       </c>
       <c r="C29" t="s">
-        <v>626</v>
+        <v>737</v>
       </c>
     </row>
   </sheetData>

--- a/data/excel/Thiết kế game.xlsx
+++ b/data/excel/Thiết kế game.xlsx
@@ -1966,12 +1966,13 @@
   </si>
   <si>
     <t>S1.1.1
-Atk + 20%</t>
+Atk + 10%
+Base MHR +10%</t>
   </si>
   <si>
     <t>S1.1.2 
 Base Acc +20%
-Multi-hit rate +10%</t>
+Base MHR +10%</t>
   </si>
   <si>
     <t>S1.1.3
@@ -7979,7 +7980,7 @@
       </c>
       <c r="B11" s="30">
         <f t="shared" si="0"/>
-        <v>2909.52380952381</v>
+        <v>2909.5238095238</v>
       </c>
       <c r="C11" s="30">
         <f>6840/G11</f>
@@ -8522,11 +8523,11 @@
         <v>618</v>
       </c>
       <c r="B30" s="37">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="C30" s="37">
-        <f>2*1000*2</f>
-        <v>4000</v>
+        <f>2*1000*2*1.3</f>
+        <v>5200</v>
       </c>
       <c r="D30" s="37">
         <v>10</v>
@@ -8565,7 +8566,7 @@
         <v>800</v>
       </c>
       <c r="D31" s="39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31" s="39" t="s">
         <v>624</v>

--- a/data/excel/Thiết kế game.xlsx
+++ b/data/excel/Thiết kế game.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12180" firstSheet="1" activeTab="6"/>
+    <workbookView windowWidth="27945" windowHeight="12180" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Ý tưởng chung" sheetId="1" r:id="rId1"/>
@@ -13,9 +13,10 @@
     <sheet name="Termynology" sheetId="4" r:id="rId4"/>
     <sheet name="Balanced Dummy " sheetId="5" r:id="rId5"/>
     <sheet name="Destroyer class" sheetId="6" r:id="rId6"/>
-    <sheet name="Ranger class" sheetId="12" r:id="rId7"/>
-    <sheet name="Item" sheetId="7" r:id="rId8"/>
-    <sheet name="status" sheetId="8" r:id="rId9"/>
+    <sheet name="Warrior class" sheetId="13" r:id="rId7"/>
+    <sheet name="Ranger class" sheetId="12" r:id="rId8"/>
+    <sheet name="Item" sheetId="7" r:id="rId9"/>
+    <sheet name="status" sheetId="8" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="738">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="796">
   <si>
     <t>Tên game</t>
   </si>
@@ -946,6 +947,18 @@
     <t>A fixed reference value used to express and compare the numerical scale of stats. Stat values may be defined as multiples of K; their actual gameplay effectiveness depends on the applicable formulas.</t>
   </si>
   <si>
+    <t>Heal</t>
+  </si>
+  <si>
+    <t>HEAL</t>
+  </si>
+  <si>
+    <t>MIN(Target’s Missing HP, Base Heal × (1 + Healing Amplification))</t>
+  </si>
+  <si>
+    <t>The amount of HP restored to a target. Cannot exceed the target’s missing HP.</t>
+  </si>
+  <si>
     <t>Term (general)</t>
   </si>
   <si>
@@ -1714,9 +1727,15 @@
     <t>Base character CP</t>
   </si>
   <si>
+    <t>Skill mitigation</t>
+  </si>
+  <si>
     <t>Spare</t>
   </si>
   <si>
+    <t>Skill - max level</t>
+  </si>
+  <si>
     <t>Area of Effect</t>
   </si>
   <si>
@@ -1726,7 +1745,7 @@
     <t>Stat at SL 5</t>
   </si>
   <si>
-    <t>Frozen Axe</t>
+    <t>Frozen Axe - 5</t>
   </si>
   <si>
     <t>Deals initial skill damage, applies damage over time, and inflicts immobilized  on enemies in the target row.</t>
@@ -1747,7 +1766,7 @@
     <t>DOT Satk</t>
   </si>
   <si>
-    <t>Deadly Strike</t>
+    <t>Deadly Strike - 5</t>
   </si>
   <si>
     <t>Deals heavy skill damage to one Front target. Usable only while the caster’s current HP is below 50% of Max HP.</t>
@@ -1762,7 +1781,7 @@
     <t>4.8*K*70%*SL</t>
   </si>
   <si>
-    <t>Bluetooth Connection</t>
+    <t>Bluetooth Connection - 5</t>
   </si>
   <si>
     <t>Passive, Auto-cast</t>
@@ -1852,7 +1871,7 @@
   </si>
   <si>
     <t>S2.1.1 
-Base DEF +700</t>
+Base DEF +476</t>
   </si>
   <si>
     <t>S2.1.2 
@@ -1883,6 +1902,194 @@
 Each team turn, restores 2.5% Max HP</t>
   </si>
   <si>
+    <t>Warrior</t>
+  </si>
+  <si>
+    <t>Joan of Arc</t>
+  </si>
+  <si>
+    <t>Warrior weapon</t>
+  </si>
+  <si>
+    <t>Rune Enhancement</t>
+  </si>
+  <si>
+    <t>Light Saber - 5</t>
+  </si>
+  <si>
+    <t>tần công bằng ánh sáng thần thánh.</t>
+  </si>
+  <si>
+    <t>line adjecent</t>
+  </si>
+  <si>
+    <t>Satk</t>
+  </si>
+  <si>
+    <t>4.8*K*25%*SL</t>
+  </si>
+  <si>
+    <t>Sub target Damage penalty</t>
+  </si>
+  <si>
+    <t>Holy Guard - 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bảo vệ đồng minh bằng ánh sáng thần thành. trao immunity cho đồng minh. </t>
+  </si>
+  <si>
+    <t>Any</t>
+  </si>
+  <si>
+    <t>4.8*K*8%*SL</t>
+  </si>
+  <si>
+    <t>Maid care - 5</t>
+  </si>
+  <si>
+    <t>Passive - Auto cast</t>
+  </si>
+  <si>
+    <t>Hộ vệ nhân vật chính, hồi máu và áp resistance dựa vào current SDEF của Jean</t>
+  </si>
+  <si>
+    <t>Main character</t>
+  </si>
+  <si>
+    <t>2%*SL</t>
+  </si>
+  <si>
+    <t>Follow the God's path - 5</t>
+  </si>
+  <si>
+    <t>Passive</t>
+  </si>
+  <si>
+    <t>Chuyển đổi Final Atk sang Final Def và Final Sdef theo tỉ lệ nhất định</t>
+  </si>
+  <si>
+    <t>Maximum FAtk to FDef</t>
+  </si>
+  <si>
+    <t>8%*SL</t>
+  </si>
+  <si>
+    <t>FAtk to FDef rate</t>
+  </si>
+  <si>
+    <t>Maximum FAtk to Sdef</t>
+  </si>
+  <si>
+    <t>FAtk to SDef rate</t>
+  </si>
+  <si>
+    <t>The Martyr Saint - 5</t>
+  </si>
+  <si>
+    <t>Infinitive</t>
+  </si>
+  <si>
+    <t>ở đầu turn sau khi chết, ngay lập tức hồi sinh trong trạng thái spirit, trở invincible và tiếp tục hoạt động cho đến khi hết duration. trong trạng thái này, convert DEF và SDEF sang light saber Stak theo tỉ lệ nhất định</t>
+  </si>
+  <si>
+    <t>Self</t>
+  </si>
+  <si>
+    <t>Maximum FDEF to FSTAK</t>
+  </si>
+  <si>
+    <t>FDef to FStak rate</t>
+  </si>
+  <si>
+    <t>Maximum FSDEF to FStak</t>
+  </si>
+  <si>
+    <t>FSDEF to FSTAK rate</t>
+  </si>
+  <si>
+    <t>Holy Knight</t>
+  </si>
+  <si>
+    <t>Hiệp sĩ được chúa chúc phúc, mang sứ mệnh giải phóng và dẫn dắt quốc gia</t>
+  </si>
+  <si>
+    <t>S1
+Unlock Maid care</t>
+  </si>
+  <si>
+    <t>S1.1.1
+Base AP recovery +10</t>
+  </si>
+  <si>
+    <t>S1.1.2
+DEF + 71%</t>
+  </si>
+  <si>
+    <t>S1.1.3
+Holy Guard applied Fortify 71%</t>
+  </si>
+  <si>
+    <t>S1.1.4
+Holy Guard also applied to main character when cast</t>
+  </si>
+  <si>
+    <t>S1.2.1
+Base HP + 4000</t>
+  </si>
+  <si>
+    <t>S1.2.2
+SDEF +34%</t>
+  </si>
+  <si>
+    <t>S1.2.3
+Maid care mana cost - 50%</t>
+  </si>
+  <si>
+    <t>S1.2.4
+Maid Care stat effectiveness + 40%</t>
+  </si>
+  <si>
+    <t>Undying Flame</t>
+  </si>
+  <si>
+    <t>Ý chí mạnh mẽ không thể bị tiêu diệt, dù cho thân xác có biến thành tro bụi</t>
+  </si>
+  <si>
+    <t>Unlock Follow the God's path</t>
+  </si>
+  <si>
+    <t>S2.1.1
+Immune to DOT effect</t>
+  </si>
+  <si>
+    <t>S2.1.2
+Base HA + 20%</t>
+  </si>
+  <si>
+    <t>S2.1.3
+Holly guard also applied to self when cast</t>
+  </si>
+  <si>
+    <t>S2.1.4
+Unlock The Martyr Saint</t>
+  </si>
+  <si>
+    <t>S2.1.5
+Update The Martyr Saint to level 5</t>
+  </si>
+  <si>
+    <t>S2.2.1
+Base AP recovery +10</t>
+  </si>
+  <si>
+    <t>S2.2.2
+Holy Guard intial cooldown = 0</t>
+  </si>
+  <si>
+    <t>S2.2.3
+Base AP recovery +10</t>
+  </si>
+  <si>
     <t>Ranger</t>
   </si>
   <si>
@@ -1895,34 +2102,25 @@
     <t>Arrow</t>
   </si>
   <si>
-    <t>Golden Arrow Shot</t>
+    <t>Golden Arrow Shot - 5</t>
   </si>
   <si>
     <t>Fires an unavoidable arrow that deals  skill damage.</t>
   </si>
   <si>
-    <t>Any</t>
-  </si>
-  <si>
-    <t>Satk</t>
-  </si>
-  <si>
     <t>4.8*K*30%*SL</t>
   </si>
   <si>
-    <t>Man Under the Hood</t>
+    <t>Man Under the Hood - 5</t>
   </si>
   <si>
     <t>Grants Invisible and increased Critical Hit Chance. Immediately grants another action slot.</t>
   </si>
   <si>
-    <t>Self</t>
-  </si>
-  <si>
     <t>increased CHC</t>
   </si>
   <si>
-    <t>Thief’s Mark</t>
+    <t>Thief’s Mark - 5</t>
   </si>
   <si>
     <t>Passive, Auto-Cast</t>
@@ -1943,10 +2141,10 @@
     <t>Satk (upgrade)</t>
   </si>
   <si>
-    <t>4.8*K*20%*SL</t>
-  </si>
-  <si>
-    <t>Outlaw’s Mark</t>
+    <t>4.8*K*5%*SL</t>
+  </si>
+  <si>
+    <t>Outlaw’s Mark - 5</t>
   </si>
   <si>
     <t>Marks the living enemy that has dealt the most total damage to your team during the battle, plus two other random living enemies. Marked enemies take increased damage.</t>
@@ -1992,7 +2190,7 @@
   </si>
   <si>
     <t>S1.2.3
-Golden Arrow Shot applies +1 Base Stun Count. Its SATK increases by 10%.</t>
+Golden Arrow Shot applies +2 Base Stun Count. Its SATK increases by 10%.</t>
   </si>
   <si>
     <t>S1.2.4
@@ -2065,9 +2263,6 @@
     <t>CP</t>
   </si>
   <si>
-    <t>Warrior weapon</t>
-  </si>
-  <si>
     <t>Row adjection</t>
   </si>
   <si>
@@ -2093,9 +2288,6 @@
   </si>
   <si>
     <t>Caster weapon</t>
-  </si>
-  <si>
-    <t>Rune Enhancement</t>
   </si>
   <si>
     <t>Shield</t>
@@ -2294,7 +2486,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="9">
+  <numFmts count="8">
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
@@ -2303,7 +2495,6 @@
     <numFmt numFmtId="179" formatCode="_ * #,##0.0_ ;_ * \-#,##0.0_ ;_ * &quot;-&quot;??.0_ ;_ @_ "/>
     <numFmt numFmtId="180" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??.00_ ;_ @_ "/>
     <numFmt numFmtId="181" formatCode="#,##0;[Red]\-#,##0;&quot;-&quot;"/>
-    <numFmt numFmtId="182" formatCode="#,##0.00;[Red]\-#,##0.00;&quot;-&quot;"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -2967,7 +3158,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3024,7 +3215,9 @@
     </xf>
     <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -3033,9 +3226,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3053,19 +3243,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1">
@@ -3074,16 +3255,44 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="3" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -3121,12 +3330,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -3739,6 +3952,262 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C29"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="1" width="18.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="15.1428571428571" customWidth="1"/>
+    <col min="3" max="3" width="11.8571428571429" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>746</v>
+      </c>
+      <c r="C2" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>748</v>
+      </c>
+      <c r="C3" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>587</v>
+      </c>
+      <c r="C4" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>589</v>
+      </c>
+      <c r="C5" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>752</v>
+      </c>
+      <c r="C6" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>754</v>
+      </c>
+      <c r="C7" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>756</v>
+      </c>
+      <c r="C8" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>758</v>
+      </c>
+      <c r="C9" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>760</v>
+      </c>
+      <c r="C10" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>762</v>
+      </c>
+      <c r="C11" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>764</v>
+      </c>
+      <c r="C12" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>766</v>
+      </c>
+      <c r="C13" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>768</v>
+      </c>
+      <c r="C14" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>732</v>
+      </c>
+      <c r="B15">
+        <v>4</v>
+      </c>
+      <c r="C15" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>771</v>
+      </c>
+      <c r="C16" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>533</v>
+      </c>
+      <c r="B18">
+        <v>3</v>
+      </c>
+      <c r="C18" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>774</v>
+      </c>
+      <c r="B19">
+        <v>3</v>
+      </c>
+      <c r="C19" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>391</v>
+      </c>
+      <c r="C20" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>777</v>
+      </c>
+      <c r="C21" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>779</v>
+      </c>
+      <c r="B22" t="s">
+        <v>780</v>
+      </c>
+      <c r="C22" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>782</v>
+      </c>
+      <c r="C23" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>784</v>
+      </c>
+      <c r="C24" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>786</v>
+      </c>
+      <c r="C25" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>788</v>
+      </c>
+      <c r="C26" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>790</v>
+      </c>
+      <c r="C27" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>792</v>
+      </c>
+      <c r="C28" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>794</v>
+      </c>
+      <c r="C29" t="s">
+        <v>795</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
@@ -3815,7 +4284,7 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="1" ht="61" customHeight="1" spans="1:1">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="81" t="s">
         <v>25</v>
       </c>
     </row>
@@ -3864,24 +4333,24 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="65" t="s">
+      <c r="A7" s="71" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="65" t="s">
+      <c r="B7" s="71" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="65" t="s">
+      <c r="C7" s="71" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="65" t="s">
+      <c r="A8" s="71" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="65" t="s">
+      <c r="B8" s="71" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="65" t="s">
+      <c r="C8" s="71" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4436,200 +4905,200 @@
       </c>
     </row>
     <row r="59" customFormat="1" spans="1:3">
-      <c r="A59" s="65" t="s">
+      <c r="A59" s="71" t="s">
         <v>146</v>
       </c>
-      <c r="B59" s="65" t="s">
+      <c r="B59" s="71" t="s">
         <v>147</v>
       </c>
-      <c r="C59" s="65" t="s">
+      <c r="C59" s="71" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="60" customFormat="1" spans="1:3">
-      <c r="A60" s="65" t="s">
+      <c r="A60" s="71" t="s">
         <v>146</v>
       </c>
-      <c r="B60" s="65" t="s">
+      <c r="B60" s="71" t="s">
         <v>149</v>
       </c>
-      <c r="C60" s="65" t="s">
+      <c r="C60" s="71" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="61" customFormat="1" spans="1:3">
-      <c r="A61" s="65" t="s">
+      <c r="A61" s="71" t="s">
         <v>146</v>
       </c>
-      <c r="B61" s="65" t="s">
+      <c r="B61" s="71" t="s">
         <v>151</v>
       </c>
-      <c r="C61" s="65" t="s">
+      <c r="C61" s="71" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="62" customFormat="1" spans="1:3">
-      <c r="A62" s="65" t="s">
+      <c r="A62" s="71" t="s">
         <v>146</v>
       </c>
-      <c r="B62" s="65" t="s">
+      <c r="B62" s="71" t="s">
         <v>153</v>
       </c>
-      <c r="C62" s="65" t="s">
+      <c r="C62" s="71" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="63" spans="1:3">
-      <c r="A63" s="65" t="s">
+      <c r="A63" s="71" t="s">
         <v>146</v>
       </c>
-      <c r="B63" s="65" t="s">
+      <c r="B63" s="71" t="s">
         <v>155</v>
       </c>
-      <c r="C63" s="65" t="s">
+      <c r="C63" s="71" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="64" spans="1:3">
-      <c r="A64" s="65" t="s">
+      <c r="A64" s="71" t="s">
         <v>146</v>
       </c>
-      <c r="B64" s="65" t="s">
+      <c r="B64" s="71" t="s">
         <v>157</v>
       </c>
-      <c r="C64" s="65" t="s">
+      <c r="C64" s="71" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="65" spans="1:3">
-      <c r="A65" s="65" t="s">
+      <c r="A65" s="71" t="s">
         <v>159</v>
       </c>
-      <c r="B65" s="65" t="s">
+      <c r="B65" s="71" t="s">
         <v>160</v>
       </c>
-      <c r="C65" s="65" t="s">
+      <c r="C65" s="71" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="66" spans="1:3">
-      <c r="A66" s="65" t="s">
+      <c r="A66" s="71" t="s">
         <v>159</v>
       </c>
-      <c r="B66" s="65" t="s">
+      <c r="B66" s="71" t="s">
         <v>162</v>
       </c>
-      <c r="C66" s="65" t="s">
+      <c r="C66" s="71" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="67" spans="1:3">
-      <c r="A67" s="65" t="s">
+      <c r="A67" s="71" t="s">
         <v>159</v>
       </c>
-      <c r="B67" s="65" t="s">
+      <c r="B67" s="71" t="s">
         <v>164</v>
       </c>
-      <c r="C67" s="65" t="s">
+      <c r="C67" s="71" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="68" spans="1:3">
-      <c r="A68" s="65" t="s">
+      <c r="A68" s="71" t="s">
         <v>159</v>
       </c>
-      <c r="B68" s="65" t="s">
+      <c r="B68" s="71" t="s">
         <v>166</v>
       </c>
-      <c r="C68" s="65" t="s">
+      <c r="C68" s="71" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="69" ht="30" spans="1:3">
-      <c r="A69" s="65" t="s">
+      <c r="A69" s="71" t="s">
         <v>159</v>
       </c>
-      <c r="B69" s="65" t="s">
+      <c r="B69" s="71" t="s">
         <v>168</v>
       </c>
-      <c r="C69" s="65" t="s">
+      <c r="C69" s="71" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="70" spans="1:3">
-      <c r="A70" s="65" t="s">
+      <c r="A70" s="71" t="s">
         <v>170</v>
       </c>
-      <c r="B70" s="65" t="s">
+      <c r="B70" s="71" t="s">
         <v>171</v>
       </c>
-      <c r="C70" s="65" t="s">
+      <c r="C70" s="71" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="71" spans="1:3">
-      <c r="A71" s="65" t="s">
+      <c r="A71" s="71" t="s">
         <v>170</v>
       </c>
-      <c r="B71" s="65" t="s">
+      <c r="B71" s="71" t="s">
         <v>173</v>
       </c>
-      <c r="C71" s="65" t="s">
+      <c r="C71" s="71" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="72" spans="1:3">
-      <c r="A72" s="65" t="s">
+      <c r="A72" s="71" t="s">
         <v>170</v>
       </c>
-      <c r="B72" s="65" t="s">
+      <c r="B72" s="71" t="s">
         <v>175</v>
       </c>
-      <c r="C72" s="65" t="s">
+      <c r="C72" s="71" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="73" spans="1:3">
-      <c r="A73" s="65" t="s">
+      <c r="A73" s="71" t="s">
         <v>170</v>
       </c>
-      <c r="B73" s="65" t="s">
+      <c r="B73" s="71" t="s">
         <v>177</v>
       </c>
-      <c r="C73" s="65" t="s">
+      <c r="C73" s="71" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="74" spans="1:3">
-      <c r="A74" s="65" t="s">
+      <c r="A74" s="71" t="s">
         <v>170</v>
       </c>
-      <c r="B74" s="65" t="s">
+      <c r="B74" s="71" t="s">
         <v>179</v>
       </c>
-      <c r="C74" s="65" t="s">
+      <c r="C74" s="71" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="75" spans="1:3">
-      <c r="A75" s="65" t="s">
+      <c r="A75" s="71" t="s">
         <v>170</v>
       </c>
-      <c r="B75" s="65" t="s">
+      <c r="B75" s="71" t="s">
         <v>181</v>
       </c>
-      <c r="C75" s="65" t="s">
+      <c r="C75" s="71" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="76" spans="1:3">
-      <c r="A76" s="65" t="s">
+      <c r="A76" s="71" t="s">
         <v>170</v>
       </c>
-      <c r="B76" s="65" t="s">
+      <c r="B76" s="71" t="s">
         <v>183</v>
       </c>
-      <c r="C76" s="65" t="s">
+      <c r="C76" s="71" t="s">
         <v>184</v>
       </c>
     </row>
@@ -4645,7 +5114,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E82"/>
+  <dimension ref="A1:E84"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="22.5714285714286" customWidth="1"/>
@@ -5158,9 +5627,26 @@
         <v>302</v>
       </c>
     </row>
+    <row r="32" s="75" customFormat="1" spans="1:5">
+      <c r="A32" s="75" t="s">
+        <v>303</v>
+      </c>
+      <c r="B32" s="75" t="s">
+        <v>304</v>
+      </c>
+      <c r="C32" s="75" t="s">
+        <v>190</v>
+      </c>
+      <c r="D32" s="75" t="s">
+        <v>305</v>
+      </c>
+      <c r="E32" s="75" t="s">
+        <v>306</v>
+      </c>
+    </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B35" t="s">
         <v>186</v>
@@ -5177,309 +5663,309 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B36" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="C36" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="E36" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B37" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C37" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="E37" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B38" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C38" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="E38" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B39" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="C39" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="E39" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B40" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="C40" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="D40" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="E40" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B41" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="C41" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="D41" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="E41" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B42" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="C42" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="D42" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="E42" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B43" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C43" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="D43" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="E43" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B44" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="C44" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="D44" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="E44" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B45" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="C45" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="D45" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="E45" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="B46" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="C46" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="D46" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="E46" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B47" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="C47" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="D47" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="E47" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B48" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C48" t="s">
         <v>226</v>
       </c>
       <c r="E48" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B49" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="C49" t="s">
         <v>226</v>
       </c>
       <c r="E49" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B50" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="C50" t="s">
         <v>226</v>
       </c>
       <c r="E50" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B51" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C51" t="s">
         <v>226</v>
       </c>
       <c r="E51" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B52" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C52" t="s">
         <v>226</v>
       </c>
       <c r="E52" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B53" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C53" t="s">
         <v>226</v>
       </c>
       <c r="D53" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="E53" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B54" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="C54" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="E54" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B55" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C55" t="s">
         <v>226</v>
       </c>
       <c r="E55" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -5493,265 +5979,282 @@
         <v>191</v>
       </c>
       <c r="D56" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="E56" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="B57" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C57" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D57" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="E57" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B58" t="s">
+        <v>388</v>
+      </c>
+      <c r="C58" t="s">
         <v>384</v>
       </c>
-      <c r="C58" t="s">
-        <v>380</v>
-      </c>
       <c r="D58" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="E58" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B59" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C59" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="D59" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="E59" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="61" spans="1:5">
-      <c r="A61" s="69" t="s">
-        <v>392</v>
-      </c>
-      <c r="B61" s="69"/>
-      <c r="C61" s="69"/>
-      <c r="D61" s="69"/>
+      <c r="A61" s="76" t="s">
+        <v>396</v>
+      </c>
+      <c r="B61" s="76"/>
+      <c r="C61" s="76"/>
+      <c r="D61" s="76"/>
       <c r="E61" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="62" spans="1:5">
-      <c r="A62" s="70" t="s">
-        <v>393</v>
-      </c>
-      <c r="C62" s="69"/>
-      <c r="D62" s="69"/>
-      <c r="E62" s="70" t="s">
-        <v>394</v>
+      <c r="A62" s="77" t="s">
+        <v>397</v>
+      </c>
+      <c r="C62" s="76"/>
+      <c r="D62" s="76"/>
+      <c r="E62" s="77" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="63" spans="1:5">
-      <c r="A63" s="70" t="s">
-        <v>395</v>
-      </c>
-      <c r="C63" s="69"/>
-      <c r="D63" s="69"/>
-      <c r="E63" s="70" t="s">
-        <v>396</v>
+      <c r="A63" s="77" t="s">
+        <v>399</v>
+      </c>
+      <c r="C63" s="76"/>
+      <c r="D63" s="76"/>
+      <c r="E63" s="77" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="64" spans="1:5">
-      <c r="A64" s="70" t="s">
-        <v>397</v>
-      </c>
-      <c r="C64" s="71"/>
-      <c r="E64" s="70" t="s">
-        <v>398</v>
+      <c r="A64" s="77" t="s">
+        <v>401</v>
+      </c>
+      <c r="C64" s="78"/>
+      <c r="E64" s="77" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="65" spans="1:5">
-      <c r="A65" s="70" t="s">
-        <v>399</v>
-      </c>
-      <c r="C65" s="71"/>
-      <c r="E65" s="70" t="s">
-        <v>400</v>
+      <c r="A65" s="77" t="s">
+        <v>403</v>
+      </c>
+      <c r="C65" s="78"/>
+      <c r="E65" s="77" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="66" spans="1:5">
-      <c r="A66" s="70" t="s">
-        <v>401</v>
-      </c>
-      <c r="C66" s="71"/>
-      <c r="E66" s="70" t="s">
-        <v>402</v>
+      <c r="A66" s="77" t="s">
+        <v>405</v>
+      </c>
+      <c r="C66" s="78"/>
+      <c r="E66" s="77" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="67" spans="1:5">
-      <c r="A67" s="70" t="s">
-        <v>403</v>
-      </c>
-      <c r="C67" s="71"/>
-      <c r="E67" s="70" t="s">
-        <v>404</v>
+      <c r="A67" s="77" t="s">
+        <v>407</v>
+      </c>
+      <c r="C67" s="78"/>
+      <c r="E67" s="77" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="68" spans="1:5">
-      <c r="A68" s="70" t="s">
-        <v>405</v>
-      </c>
-      <c r="C68" s="71"/>
-      <c r="E68" s="70" t="s">
-        <v>406</v>
+      <c r="A68" s="77" t="s">
+        <v>409</v>
+      </c>
+      <c r="C68" s="78"/>
+      <c r="E68" s="77" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="69" spans="1:5">
-      <c r="A69" s="70" t="s">
-        <v>407</v>
-      </c>
-      <c r="C69" s="71"/>
-      <c r="E69" s="70" t="s">
-        <v>408</v>
+      <c r="A69" s="77" t="s">
+        <v>411</v>
+      </c>
+      <c r="C69" s="78"/>
+      <c r="E69" s="77" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="70" spans="1:5">
-      <c r="A70" s="70" t="s">
-        <v>409</v>
-      </c>
-      <c r="C70" s="71"/>
-      <c r="E70" s="70" t="s">
-        <v>410</v>
+      <c r="A70" s="77" t="s">
+        <v>413</v>
+      </c>
+      <c r="C70" s="78"/>
+      <c r="E70" s="77" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="71" spans="1:5">
-      <c r="A71" s="70" t="s">
-        <v>411</v>
-      </c>
-      <c r="C71" s="71"/>
-      <c r="E71" s="70" t="s">
-        <v>412</v>
+      <c r="A71" s="77" t="s">
+        <v>415</v>
+      </c>
+      <c r="C71" s="78"/>
+      <c r="E71" s="77" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="72" spans="1:5">
-      <c r="A72" s="70" t="s">
-        <v>413</v>
-      </c>
-      <c r="C72" s="71"/>
-      <c r="E72" s="70" t="s">
-        <v>414</v>
+      <c r="A72" s="77" t="s">
+        <v>417</v>
+      </c>
+      <c r="C72" s="78"/>
+      <c r="E72" s="77" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="73" spans="1:5">
-      <c r="A73" s="70" t="s">
-        <v>415</v>
-      </c>
-      <c r="C73" s="71"/>
-      <c r="E73" s="70" t="s">
-        <v>416</v>
+      <c r="A73" s="77" t="s">
+        <v>419</v>
+      </c>
+      <c r="C73" s="78"/>
+      <c r="E73" s="77" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="74" spans="1:5">
-      <c r="A74" s="70" t="s">
-        <v>417</v>
-      </c>
-      <c r="C74" s="71"/>
-      <c r="E74" s="70" t="s">
-        <v>418</v>
+      <c r="A74" s="77" t="s">
+        <v>421</v>
+      </c>
+      <c r="C74" s="78"/>
+      <c r="E74" s="77" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="75" spans="1:5">
-      <c r="A75" s="70" t="s">
-        <v>419</v>
-      </c>
-      <c r="C75" s="71"/>
-      <c r="E75" s="70" t="s">
-        <v>420</v>
+      <c r="A75" s="77" t="s">
+        <v>423</v>
+      </c>
+      <c r="C75" s="78"/>
+      <c r="E75" s="77" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="76" spans="1:5">
-      <c r="A76" s="70" t="s">
-        <v>421</v>
-      </c>
-      <c r="C76" s="71"/>
-      <c r="E76" s="70" t="s">
-        <v>422</v>
+      <c r="A76" s="77" t="s">
+        <v>425</v>
+      </c>
+      <c r="C76" s="78"/>
+      <c r="E76" s="77" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="77" spans="1:5">
-      <c r="A77" s="70" t="s">
-        <v>423</v>
-      </c>
-      <c r="C77" s="71"/>
-      <c r="E77" s="70" t="s">
-        <v>424</v>
+      <c r="A77" s="77" t="s">
+        <v>427</v>
+      </c>
+      <c r="C77" s="78"/>
+      <c r="E77" s="77" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="78" spans="1:5">
-      <c r="A78" s="70" t="s">
-        <v>425</v>
-      </c>
-      <c r="C78" s="71"/>
-      <c r="E78" s="70" t="s">
-        <v>426</v>
+      <c r="A78" s="77" t="s">
+        <v>429</v>
+      </c>
+      <c r="C78" s="78"/>
+      <c r="E78" s="77" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="79" spans="1:5">
-      <c r="A79" s="70" t="s">
-        <v>427</v>
-      </c>
-      <c r="C79" s="71"/>
-      <c r="E79" s="70" t="s">
-        <v>428</v>
+      <c r="A79" s="77" t="s">
+        <v>431</v>
+      </c>
+      <c r="C79" s="78"/>
+      <c r="E79" s="77" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="80" spans="1:5">
-      <c r="A80" s="70" t="s">
-        <v>429</v>
-      </c>
-      <c r="C80" s="71"/>
-      <c r="E80" s="70" t="s">
-        <v>430</v>
+      <c r="A80" s="77" t="s">
+        <v>433</v>
+      </c>
+      <c r="C80" s="78"/>
+      <c r="E80" s="77" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="81" spans="1:5">
-      <c r="A81" s="70" t="s">
-        <v>431</v>
-      </c>
-      <c r="C81" s="71"/>
-      <c r="E81" s="70" t="s">
-        <v>432</v>
+      <c r="A81" s="77" t="s">
+        <v>435</v>
+      </c>
+      <c r="C81" s="78"/>
+      <c r="E81" s="77" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="82" spans="1:5">
-      <c r="A82" s="72" t="s">
-        <v>433</v>
-      </c>
-      <c r="B82" s="72"/>
-      <c r="C82" s="72"/>
-      <c r="D82" s="72"/>
-      <c r="E82" s="72" t="s">
-        <v>434</v>
+      <c r="A82" s="79" t="s">
+        <v>437</v>
+      </c>
+      <c r="B82" s="79"/>
+      <c r="C82" s="79"/>
+      <c r="D82" s="79"/>
+      <c r="E82" s="79" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="84" ht="30" spans="1:5">
+      <c r="A84" s="80" t="s">
+        <v>185</v>
+      </c>
+      <c r="B84" s="80" t="s">
+        <v>186</v>
+      </c>
+      <c r="C84" s="80" t="s">
+        <v>187</v>
+      </c>
+      <c r="D84" s="80" t="s">
+        <v>188</v>
+      </c>
+      <c r="E84" s="80" t="s">
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -5787,52 +6290,52 @@
   <sheetData>
     <row r="1" s="27" customFormat="1" spans="1:17">
       <c r="A1" s="27" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="F1" s="27" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="G1" s="27" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="H1" s="27" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="J1" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>85</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>28</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="P1" t="s">
         <v>188</v>
       </c>
       <c r="Q1" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -5865,7 +6368,7 @@
         <v>40000</v>
       </c>
       <c r="J2" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="K2" s="3">
         <v>100</v>
@@ -5877,13 +6380,13 @@
         <v>4</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="P2" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="Q2">
         <f>1000*10*0.48</f>
@@ -5920,10 +6423,10 @@
         <v>40000</v>
       </c>
       <c r="O3" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="P3" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="Q3">
         <v>1</v>
@@ -6051,7 +6554,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B8" s="4">
         <v>0.2</v>
@@ -6139,7 +6642,7 @@
         <v>2800</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:12">
       <c r="A11" t="s">
         <v>217</v>
       </c>
@@ -6168,10 +6671,11 @@
         <f>G11*B11</f>
         <v>40000</v>
       </c>
+      <c r="L11" s="32"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="B12" s="3">
         <v>4</v>
@@ -6201,7 +6705,7 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="B13" s="3">
         <v>1</v>
@@ -6231,7 +6735,7 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="B14" s="3">
         <v>10</v>
@@ -6349,7 +6853,7 @@
     </row>
     <row r="18" s="2" customFormat="1" spans="1:8">
       <c r="A18" s="2" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="D18" s="35">
         <f>SUM(D2:D17)</f>
@@ -6366,7 +6870,7 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="F19" s="36">
         <f>F18/4</f>
@@ -6375,203 +6879,206 @@
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>459</v>
-      </c>
+        <v>463</v>
+      </c>
+    </row>
+    <row r="22" spans="12:12">
+      <c r="L22" s="32"/>
     </row>
     <row r="24" customFormat="1" ht="23.25" customHeight="1" spans="1:1">
-      <c r="A24" s="66" t="s">
-        <v>460</v>
+      <c r="A24" s="72" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="26" customFormat="1" ht="18.75" customHeight="1" spans="1:1">
-      <c r="A26" s="67" t="s">
-        <v>461</v>
+      <c r="A26" s="73" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="27" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="68" t="s">
-        <v>463</v>
+      <c r="A29" s="74" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="68" t="s">
-        <v>464</v>
+      <c r="A30" s="74" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="68" t="s">
-        <v>465</v>
+      <c r="A31" s="74" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="68" t="s">
-        <v>466</v>
+      <c r="A32" s="74" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="68" t="s">
-        <v>467</v>
+      <c r="A33" s="74" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="68" t="s">
-        <v>468</v>
+      <c r="A34" s="74" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="68" t="s">
-        <v>469</v>
+      <c r="A35" s="74" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="68" t="s">
-        <v>470</v>
+      <c r="A36" s="74" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="68" t="s">
-        <v>471</v>
+      <c r="A37" s="74" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="68" t="s">
-        <v>472</v>
+      <c r="A38" s="74" t="s">
+        <v>476</v>
       </c>
     </row>
     <row r="40" customFormat="1" ht="18.75" customHeight="1" spans="1:1">
-      <c r="A40" s="67" t="s">
-        <v>473</v>
+      <c r="A40" s="73" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="2" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="2" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="2" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="2" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="2" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="2" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="61" customFormat="1" ht="18.75" customHeight="1" spans="1:1">
-      <c r="A61" s="67" t="s">
-        <v>487</v>
+      <c r="A61" s="73" t="s">
+        <v>491</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" s="2" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="2" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" s="1" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -6579,10 +7086,10 @@
         <v>190</v>
       </c>
       <c r="B76" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -6590,10 +7097,10 @@
         <v>195</v>
       </c>
       <c r="B77" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="78" spans="1:3">
@@ -6601,10 +7108,10 @@
         <v>198</v>
       </c>
       <c r="B78" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -6612,10 +7119,10 @@
         <v>202</v>
       </c>
       <c r="B79" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -6623,10 +7130,10 @@
         <v>210</v>
       </c>
       <c r="B80" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -6634,10 +7141,10 @@
         <v>233</v>
       </c>
       <c r="B81" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -6645,10 +7152,10 @@
         <v>253</v>
       </c>
       <c r="B82" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -6656,10 +7163,10 @@
         <v>224</v>
       </c>
       <c r="B83" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -6667,10 +7174,10 @@
         <v>229</v>
       </c>
       <c r="B84" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -6678,43 +7185,43 @@
         <v>217</v>
       </c>
       <c r="B85" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" s="2" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B86" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" s="2" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="B87" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" s="2" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="B88" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -6722,10 +7229,10 @@
         <v>237</v>
       </c>
       <c r="B89" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -6733,10 +7240,10 @@
         <v>241</v>
       </c>
       <c r="B90" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -6744,50 +7251,50 @@
         <v>245</v>
       </c>
       <c r="B91" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
     </row>
     <row r="93" customFormat="1" ht="18.75" customHeight="1" spans="1:1">
-      <c r="A93" s="67" t="s">
-        <v>528</v>
+      <c r="A93" s="73" t="s">
+        <v>532</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="2" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
     </row>
     <row r="97" spans="1:1">
-      <c r="A97" s="68" t="s">
-        <v>530</v>
+      <c r="A97" s="74" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="98" spans="1:1">
-      <c r="A98" s="68" t="s">
-        <v>531</v>
+      <c r="A98" s="74" t="s">
+        <v>535</v>
       </c>
     </row>
     <row r="99" spans="1:1">
-      <c r="A99" s="68" t="s">
-        <v>532</v>
+      <c r="A99" s="74" t="s">
+        <v>536</v>
       </c>
     </row>
     <row r="100" spans="1:1">
-      <c r="A100" s="68" t="s">
-        <v>533</v>
+      <c r="A100" s="74" t="s">
+        <v>537</v>
       </c>
     </row>
     <row r="101" spans="1:1">
-      <c r="A101" s="68" t="s">
-        <v>534</v>
+      <c r="A101" s="74" t="s">
+        <v>538</v>
       </c>
     </row>
     <row r="102" spans="1:1">
-      <c r="A102" s="68" t="s">
-        <v>535</v>
+      <c r="A102" s="74" t="s">
+        <v>539</v>
       </c>
     </row>
     <row r="104" spans="1:1">
@@ -6797,7 +7304,7 @@
     </row>
     <row r="105" spans="1:1">
       <c r="A105" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
     </row>
     <row r="107" spans="1:1">
@@ -6807,57 +7314,57 @@
     </row>
     <row r="108" spans="1:1">
       <c r="A108" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
     </row>
     <row r="110" customFormat="1" ht="18.75" customHeight="1" spans="1:1">
-      <c r="A110" s="67" t="s">
-        <v>538</v>
+      <c r="A110" s="73" t="s">
+        <v>542</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
     </row>
   </sheetData>
@@ -6869,7 +7376,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.5714285714286" customWidth="1"/>
@@ -6882,7 +7389,7 @@
     <col min="8" max="8" width="19.8571428571429" customWidth="1"/>
     <col min="9" max="9" width="20.2857142857143" customWidth="1"/>
     <col min="10" max="10" width="18.8571428571429" customWidth="1"/>
-    <col min="11" max="11" width="18.7142857142857" style="50" customWidth="1"/>
+    <col min="11" max="11" width="18.7142857142857" style="46" customWidth="1"/>
     <col min="12" max="12" width="11.4285714285714" customWidth="1"/>
     <col min="13" max="13" width="11.5714285714286" customWidth="1"/>
     <col min="14" max="14" width="23.7142857142857" customWidth="1"/>
@@ -6893,76 +7400,76 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="B1" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="B2" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="B4" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="B5" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="B6" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="27" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="E8" s="29" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="F8" s="27" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="G8" s="27" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="H8" s="27" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -7001,7 +7508,7 @@
         <v>195</v>
       </c>
       <c r="B10" s="30">
-        <f t="shared" ref="B9:B24" si="0">SUM(C10,E10)</f>
+        <f>SUM(C10,E10)</f>
         <v>19450</v>
       </c>
       <c r="C10" s="30">
@@ -7032,7 +7539,7 @@
         <v>198</v>
       </c>
       <c r="B11" s="30">
-        <f t="shared" si="0"/>
+        <f>SUM(C11,E11)</f>
         <v>5357.14285714286</v>
       </c>
       <c r="C11" s="30">
@@ -7042,7 +7549,7 @@
       <c r="D11" s="30">
         <v>10000</v>
       </c>
-      <c r="E11" s="32">
+      <c r="E11" s="31">
         <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A11)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A11)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A11)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A11)</f>
         <v>4166.66666666667</v>
       </c>
@@ -7063,7 +7570,7 @@
         <v>202</v>
       </c>
       <c r="B12" s="30">
-        <f t="shared" si="0"/>
+        <f>SUM(C12,E12)</f>
         <v>1857.14285714286</v>
       </c>
       <c r="C12" s="30">
@@ -7073,7 +7580,7 @@
       <c r="D12" s="30">
         <v>4600</v>
       </c>
-      <c r="E12" s="32">
+      <c r="E12" s="31">
         <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A12)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A12)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A12)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A12)</f>
         <v>1035.71428571429</v>
       </c>
@@ -7094,7 +7601,7 @@
         <v>210</v>
       </c>
       <c r="B13" s="30">
-        <f t="shared" si="0"/>
+        <f>SUM(C13,E13)</f>
         <v>1086.20689655172</v>
       </c>
       <c r="C13" s="30">
@@ -7104,7 +7611,7 @@
       <c r="D13" s="30">
         <v>3800</v>
       </c>
-      <c r="E13" s="32">
+      <c r="E13" s="31">
         <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A13)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A13)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A13)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A13)</f>
         <v>758.620689655172</v>
       </c>
@@ -7120,102 +7627,70 @@
         <v>12600</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" customFormat="1" spans="1:10">
       <c r="A14" t="s">
-        <v>233</v>
-      </c>
-      <c r="B14" s="33">
-        <f t="shared" si="0"/>
-        <v>1.2</v>
-      </c>
-      <c r="C14" s="33">
-        <v>1</v>
-      </c>
-      <c r="D14" s="30">
-        <f>C14*G14*100</f>
-        <v>14000</v>
-      </c>
-      <c r="E14" s="34">
-        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A14)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A14)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A14)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A14)</f>
-        <v>0.2</v>
-      </c>
-      <c r="F14" s="30">
-        <f>E14*G14*100</f>
-        <v>2800</v>
-      </c>
-      <c r="G14">
-        <v>140</v>
-      </c>
-      <c r="H14" s="31">
-        <f>B14*G14*100</f>
-        <v>16800</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
+        <v>288</v>
+      </c>
+      <c r="B14" s="32">
+        <f>B12/(B12+1000)</f>
+        <v>0.65</v>
+      </c>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="30"/>
+      <c r="H14" s="31"/>
+      <c r="J14" s="32"/>
+    </row>
+    <row r="15" customFormat="1" spans="1:10">
       <c r="A15" t="s">
-        <v>453</v>
-      </c>
-      <c r="B15" s="33">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C15" s="33">
-        <v>0</v>
-      </c>
-      <c r="D15" s="30">
-        <f>C15*G15*100</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="34">
-        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A15)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A15)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A15)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A15)</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="30">
-        <f>E15*G15*100</f>
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>140</v>
-      </c>
-      <c r="H15" s="31">
-        <f>B15*G15*100</f>
-        <v>0</v>
-      </c>
+        <v>563</v>
+      </c>
+      <c r="B15" s="32">
+        <f>B13/(B13+1000)</f>
+        <v>0.520661157024793</v>
+      </c>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="30"/>
+      <c r="H15" s="31"/>
+      <c r="J15" s="32"/>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="B16" s="33">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" ref="B16:B26" si="0">SUM(C16,E16)</f>
+        <v>1.2</v>
       </c>
       <c r="C16" s="33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" s="30">
         <f>C16*G16*100</f>
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="E16" s="34">
         <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A16)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A16)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A16)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A16)</f>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F16" s="30">
         <f>E16*G16*100</f>
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="G16">
         <v>140</v>
       </c>
       <c r="H16" s="31">
         <f>B16*G16*100</f>
-        <v>0</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>229</v>
+        <v>457</v>
       </c>
       <c r="B17" s="33">
         <f t="shared" si="0"/>
@@ -7237,7 +7712,7 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>28</v>
+        <v>140</v>
       </c>
       <c r="H17" s="31">
         <f>B17*G17*100</f>
@@ -7246,204 +7721,204 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
+        <v>224</v>
+      </c>
+      <c r="B18" s="33">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C18" s="33">
+        <v>0</v>
+      </c>
+      <c r="D18" s="30">
+        <f>C18*G18*100</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="34">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A18)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A18)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A18)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A18)</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="30">
+        <f>E18*G18*100</f>
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>140</v>
+      </c>
+      <c r="H18" s="31">
+        <f>B18*G18*100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
+        <v>229</v>
+      </c>
+      <c r="B19" s="33">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C19" s="33">
+        <v>0</v>
+      </c>
+      <c r="D19" s="30">
+        <f>C19*G19*100</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="34">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A19)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A19)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A19)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A19)</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="30">
+        <f>E19*G19*100</f>
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>28</v>
+      </c>
+      <c r="H19" s="31">
+        <f>B19*G19*100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
         <v>217</v>
       </c>
-      <c r="B18" s="30">
+      <c r="B20" s="30">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="C18" s="30">
+      <c r="C20" s="30">
         <v>100</v>
       </c>
-      <c r="D18" s="30">
-        <f>C18*G18</f>
+      <c r="D20" s="30">
+        <f>C20*G20</f>
         <v>40000</v>
       </c>
-      <c r="E18" s="31">
-        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A18)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A18)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A18)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A18)</f>
+      <c r="E20" s="31">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A20)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A20)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A20)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A20)</f>
         <v>-30</v>
       </c>
-      <c r="F18" s="30">
-        <f>E18*G18</f>
+      <c r="F20" s="30">
+        <f>E20*G20</f>
         <v>-12000</v>
       </c>
-      <c r="G18">
+      <c r="G20">
         <v>400</v>
       </c>
-      <c r="H18" s="31">
-        <f>B18*G18</f>
+      <c r="H20" s="31">
+        <f>B20*G20</f>
         <v>28000</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
-      <c r="A19" t="s">
-        <v>387</v>
-      </c>
-      <c r="B19" s="30">
+    <row r="21" spans="1:8">
+      <c r="A21" t="s">
+        <v>391</v>
+      </c>
+      <c r="B21" s="30">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C19" s="30">
+      <c r="C21" s="30">
         <v>4</v>
       </c>
-      <c r="D19" s="30">
-        <f>C19*G19</f>
+      <c r="D21" s="30">
+        <f>C21*G21</f>
         <v>4500</v>
       </c>
-      <c r="E19" s="31">
-        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A19)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A19)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A19)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A19)</f>
-        <v>0</v>
-      </c>
-      <c r="F19" s="30">
-        <f>E19*G19</f>
-        <v>0</v>
-      </c>
-      <c r="G19">
+      <c r="E21" s="31">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A21)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A21)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A21)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A21)</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="30">
+        <f>E21*G21</f>
+        <v>0</v>
+      </c>
+      <c r="G21">
         <v>1125</v>
       </c>
-      <c r="H19" s="31">
-        <f>B19*G19</f>
+      <c r="H21" s="31">
+        <f>B21*G21</f>
         <v>4500</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
-      <c r="A20" t="s">
-        <v>455</v>
-      </c>
-      <c r="B20" s="30">
+    <row r="22" spans="1:8">
+      <c r="A22" t="s">
+        <v>459</v>
+      </c>
+      <c r="B22" s="30">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C20" s="30">
-        <v>0</v>
-      </c>
-      <c r="D20" s="30">
-        <f>C20*G20</f>
-        <v>0</v>
-      </c>
-      <c r="E20" s="31">
-        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A20)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A20)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A20)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A20)</f>
-        <v>0</v>
-      </c>
-      <c r="F20" s="30">
-        <f>E20*G20</f>
-        <v>0</v>
-      </c>
-      <c r="G20">
+      <c r="C22" s="30">
+        <v>0</v>
+      </c>
+      <c r="D22" s="30">
+        <f>C22*G22</f>
+        <v>0</v>
+      </c>
+      <c r="E22" s="31">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A22)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A22)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A22)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A22)</f>
+        <v>0</v>
+      </c>
+      <c r="F22" s="30">
+        <f>E22*G22</f>
+        <v>0</v>
+      </c>
+      <c r="G22">
         <v>4800</v>
       </c>
-      <c r="H20" s="31">
-        <f>B20*G20</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" t="s">
-        <v>456</v>
-      </c>
-      <c r="B21" s="30">
+      <c r="H22" s="31">
+        <f>B22*G22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>460</v>
+      </c>
+      <c r="B23" s="30">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C21" s="30">
+      <c r="C23" s="30">
         <v>10</v>
       </c>
-      <c r="D21" s="30">
-        <f>C21*G21</f>
+      <c r="D23" s="30">
+        <f>C23*G23</f>
         <v>23260</v>
       </c>
-      <c r="E21" s="31">
-        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A21)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A21)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A21)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A21)</f>
-        <v>0</v>
-      </c>
-      <c r="F21" s="30">
-        <f>E21*G21</f>
-        <v>0</v>
-      </c>
-      <c r="G21">
+      <c r="E23" s="31">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A23)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A23)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A23)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A23)</f>
+        <v>0</v>
+      </c>
+      <c r="F23" s="30">
+        <f>E23*G23</f>
+        <v>0</v>
+      </c>
+      <c r="G23">
         <v>2326</v>
       </c>
-      <c r="H21" s="31">
-        <f>B21*G21</f>
+      <c r="H23" s="31">
+        <f>B23*G23</f>
         <v>23260</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
-      <c r="A22" t="s">
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
         <v>237</v>
       </c>
-      <c r="B22" s="33">
+      <c r="B24" s="33">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="C22" s="33">
+      <c r="C24" s="33">
         <v>1</v>
-      </c>
-      <c r="D22" s="30">
-        <f>C22*G22*100</f>
-        <v>16800</v>
-      </c>
-      <c r="E22" s="34">
-        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A22)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A22)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A22)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A22)</f>
-        <v>0</v>
-      </c>
-      <c r="F22" s="30">
-        <f>E22*G22*100</f>
-        <v>0</v>
-      </c>
-      <c r="G22">
-        <v>168</v>
-      </c>
-      <c r="H22" s="31">
-        <f>B22*G22*100</f>
-        <v>16800</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" t="s">
-        <v>241</v>
-      </c>
-      <c r="B23" s="33">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C23" s="33">
-        <v>0</v>
-      </c>
-      <c r="D23" s="30">
-        <f>C23*G23*100</f>
-        <v>0</v>
-      </c>
-      <c r="E23" s="34">
-        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A23)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A23)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A23)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A23)</f>
-        <v>0</v>
-      </c>
-      <c r="F23" s="30">
-        <f>E23*G23*100</f>
-        <v>0</v>
-      </c>
-      <c r="G23">
-        <v>168</v>
-      </c>
-      <c r="H23" s="31">
-        <f>B23*G23*100</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" t="s">
-        <v>245</v>
-      </c>
-      <c r="B24" s="33">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C24" s="33">
-        <v>0</v>
       </c>
       <c r="D24" s="30">
         <f>C24*G24*100</f>
-        <v>0</v>
+        <v>16800</v>
       </c>
       <c r="E24" s="34">
         <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A24)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A24)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A24)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A24)</f>
@@ -7454,365 +7929,427 @@
         <v>0</v>
       </c>
       <c r="G24">
-        <v>233</v>
+        <v>168</v>
       </c>
       <c r="H24" s="31">
         <f>B24*G24*100</f>
-        <v>0</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="35">
-        <f>SUM(D9:D24)</f>
+      <c r="A25" t="s">
+        <v>241</v>
+      </c>
+      <c r="B25" s="33">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C25" s="33">
+        <v>0</v>
+      </c>
+      <c r="D25" s="30">
+        <f>C25*G25*100</f>
+        <v>0</v>
+      </c>
+      <c r="E25" s="34">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A25)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A25)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A25)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A25)</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="30">
+        <f>E25*G25*100</f>
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>168</v>
+      </c>
+      <c r="H25" s="31">
+        <f>B25*G25*100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>245</v>
+      </c>
+      <c r="B26" s="33">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C26" s="33">
+        <v>0</v>
+      </c>
+      <c r="D26" s="30">
+        <f>C26*G26*100</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="34">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A26)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A26)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A26)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A26)</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="30">
+        <f>E26*G26*100</f>
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>233</v>
+      </c>
+      <c r="H26" s="31">
+        <f>B26*G26*100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="35">
+        <f>SUM(D9:D26)</f>
         <v>156960</v>
       </c>
-      <c r="E25" s="36"/>
-      <c r="F25" s="35">
-        <f>SUM(F9:F24)</f>
+      <c r="E27" s="36"/>
+      <c r="F27" s="35">
+        <f>SUM(F9:F26)</f>
         <v>71600</v>
       </c>
-      <c r="G25" s="2"/>
-      <c r="H25" s="35">
-        <f>SUM(H9:H24)</f>
+      <c r="G27" s="2"/>
+      <c r="H27" s="35">
+        <f>SUM(H9:H26)</f>
         <v>228560</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
-      <c r="A26" t="s">
-        <v>559</v>
-      </c>
-      <c r="D26" s="36">
-        <f>'Balanced Dummy '!D18-D25</f>
-        <v>0</v>
-      </c>
-      <c r="E26" s="36"/>
-      <c r="F26" s="36"/>
-    </row>
-    <row r="28" spans="1:11">
-      <c r="A28" s="54" t="s">
-        <v>443</v>
-      </c>
-      <c r="B28" s="55" t="s">
+    <row r="28" spans="1:6">
+      <c r="A28" t="s">
+        <v>564</v>
+      </c>
+      <c r="D28" s="36">
+        <f>'Balanced Dummy '!D18-D27</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="36"/>
+      <c r="F28" s="36"/>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="37" t="s">
+        <v>565</v>
+      </c>
+      <c r="B30" s="60" t="s">
         <v>85</v>
       </c>
-      <c r="C28" s="55" t="s">
-        <v>444</v>
-      </c>
-      <c r="D28" s="55" t="s">
-        <v>445</v>
-      </c>
-      <c r="E28" s="55" t="s">
+      <c r="C30" s="60" t="s">
+        <v>448</v>
+      </c>
+      <c r="D30" s="60" t="s">
+        <v>449</v>
+      </c>
+      <c r="E30" s="60" t="s">
         <v>28</v>
       </c>
-      <c r="F28" s="54" t="s">
-        <v>399</v>
-      </c>
-      <c r="G28" s="54" t="s">
-        <v>560</v>
-      </c>
-      <c r="H28" s="54" t="s">
+      <c r="F30" s="61" t="s">
+        <v>403</v>
+      </c>
+      <c r="G30" s="61" t="s">
+        <v>566</v>
+      </c>
+      <c r="H30" s="61" t="s">
         <v>114</v>
       </c>
-      <c r="I28" s="55" t="s">
-        <v>304</v>
-      </c>
-      <c r="J28" s="54" t="s">
-        <v>561</v>
-      </c>
-      <c r="K28" s="55" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
-      <c r="A29" s="54" t="s">
-        <v>563</v>
-      </c>
-      <c r="B29" s="56">
+      <c r="I30" s="60" t="s">
+        <v>308</v>
+      </c>
+      <c r="J30" s="61" t="s">
+        <v>567</v>
+      </c>
+      <c r="K30" s="60" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="61" t="s">
+        <v>569</v>
+      </c>
+      <c r="B31" s="62">
         <v>150</v>
       </c>
-      <c r="C29" s="57">
-        <f>B29*1000/50</f>
+      <c r="C31" s="63">
+        <f>B31*1000/50</f>
         <v>3000</v>
       </c>
-      <c r="D29" s="57">
+      <c r="D31" s="63">
         <v>6</v>
       </c>
-      <c r="E29" s="55" t="s">
-        <v>564</v>
-      </c>
-      <c r="F29" s="54" t="s">
-        <v>565</v>
-      </c>
-      <c r="G29" s="54" t="s">
-        <v>566</v>
-      </c>
-      <c r="H29" s="58">
+      <c r="E31" s="60" t="s">
+        <v>570</v>
+      </c>
+      <c r="F31" s="61" t="s">
+        <v>571</v>
+      </c>
+      <c r="G31" s="61" t="s">
+        <v>572</v>
+      </c>
+      <c r="H31" s="64">
         <v>3</v>
       </c>
-      <c r="I29" s="55" t="s">
-        <v>567</v>
-      </c>
-      <c r="J29" s="54" t="s">
-        <v>568</v>
-      </c>
-      <c r="K29" s="55">
+      <c r="I31" s="60" t="s">
+        <v>573</v>
+      </c>
+      <c r="J31" s="61" t="s">
+        <v>574</v>
+      </c>
+      <c r="K31" s="60">
         <f>4.8*1000*2%*5</f>
         <v>480</v>
       </c>
     </row>
-    <row r="30" ht="49" customHeight="1" spans="1:11">
-      <c r="A30" s="54"/>
-      <c r="B30" s="59"/>
-      <c r="C30" s="57"/>
-      <c r="D30" s="57"/>
-      <c r="E30" s="55"/>
-      <c r="F30" s="54"/>
-      <c r="G30" s="54"/>
-      <c r="H30" s="58"/>
-      <c r="I30" s="54" t="s">
-        <v>569</v>
-      </c>
-      <c r="J30" s="54" t="s">
-        <v>568</v>
-      </c>
-      <c r="K30" s="55">
+    <row r="32" ht="49" customHeight="1" spans="1:11">
+      <c r="A32" s="61"/>
+      <c r="B32" s="65"/>
+      <c r="C32" s="63"/>
+      <c r="D32" s="63"/>
+      <c r="E32" s="60"/>
+      <c r="F32" s="61"/>
+      <c r="G32" s="61"/>
+      <c r="H32" s="64"/>
+      <c r="I32" s="61" t="s">
+        <v>575</v>
+      </c>
+      <c r="J32" s="61" t="s">
+        <v>574</v>
+      </c>
+      <c r="K32" s="60">
         <f>4.8*1000*2%*5</f>
         <v>480</v>
       </c>
     </row>
-    <row r="31" ht="45" spans="1:11">
-      <c r="A31" s="60" t="s">
-        <v>570</v>
-      </c>
-      <c r="B31" s="60">
+    <row r="33" ht="45" spans="1:11">
+      <c r="A33" s="66" t="s">
+        <v>576</v>
+      </c>
+      <c r="B33" s="66">
         <v>300</v>
       </c>
-      <c r="C31" s="61">
-        <f>B31*1000/50</f>
+      <c r="C33" s="67">
+        <f>B33*1000/50</f>
         <v>6000</v>
       </c>
-      <c r="D31" s="62">
+      <c r="D33" s="68">
         <v>4</v>
       </c>
-      <c r="E31" s="60" t="s">
+      <c r="E33" s="66" t="s">
+        <v>577</v>
+      </c>
+      <c r="F33" s="66" t="s">
         <v>571</v>
       </c>
-      <c r="F31" s="60" t="s">
-        <v>565</v>
-      </c>
-      <c r="G31" s="60" t="s">
-        <v>572</v>
-      </c>
-      <c r="H31" s="62"/>
-      <c r="I31" s="60" t="s">
-        <v>573</v>
-      </c>
-      <c r="J31" s="60" t="s">
-        <v>574</v>
-      </c>
-      <c r="K31" s="56">
+      <c r="G33" s="66" t="s">
+        <v>578</v>
+      </c>
+      <c r="H33" s="68"/>
+      <c r="I33" s="66" t="s">
+        <v>579</v>
+      </c>
+      <c r="J33" s="66" t="s">
+        <v>580</v>
+      </c>
+      <c r="K33" s="62">
         <f>4.8*1000*70%*5</f>
         <v>16800</v>
       </c>
     </row>
-    <row r="32" ht="30" spans="1:11">
-      <c r="A32" s="54" t="s">
-        <v>575</v>
-      </c>
-      <c r="B32" s="54" t="s">
-        <v>576</v>
-      </c>
-      <c r="C32" s="57">
+    <row r="34" ht="30" spans="1:11">
+      <c r="A34" s="61" t="s">
+        <v>581</v>
+      </c>
+      <c r="B34" s="61" t="s">
+        <v>582</v>
+      </c>
+      <c r="C34" s="63">
         <v>800</v>
       </c>
-      <c r="D32" s="58">
+      <c r="D34" s="64">
         <v>2</v>
       </c>
-      <c r="E32" s="54" t="s">
-        <v>577</v>
-      </c>
-      <c r="F32" s="54" t="s">
+      <c r="E34" s="61" t="s">
+        <v>583</v>
+      </c>
+      <c r="F34" s="61" t="s">
+        <v>584</v>
+      </c>
+      <c r="G34" s="61" t="s">
         <v>578</v>
       </c>
-      <c r="G32" s="54" t="s">
-        <v>572</v>
-      </c>
-      <c r="H32" s="58">
+      <c r="H34" s="64">
         <v>2</v>
       </c>
-      <c r="I32" s="54" t="s">
-        <v>579</v>
-      </c>
-      <c r="J32" s="54" t="s">
-        <v>580</v>
-      </c>
-      <c r="K32" s="63">
+      <c r="I34" s="61" t="s">
+        <v>585</v>
+      </c>
+      <c r="J34" s="61" t="s">
+        <v>586</v>
+      </c>
+      <c r="K34" s="69">
         <f>10%*5</f>
         <v>0.5</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
-      <c r="A33" s="54"/>
-      <c r="B33" s="54"/>
-      <c r="C33" s="57"/>
-      <c r="D33" s="58"/>
-      <c r="E33" s="54"/>
-      <c r="F33" s="54"/>
-      <c r="G33" s="54"/>
-      <c r="H33" s="58"/>
-      <c r="I33" s="54" t="s">
-        <v>581</v>
-      </c>
-      <c r="J33" s="54" t="s">
-        <v>582</v>
-      </c>
-      <c r="K33" s="64">
+    <row r="35" spans="1:11">
+      <c r="A35" s="61"/>
+      <c r="B35" s="61"/>
+      <c r="C35" s="63"/>
+      <c r="D35" s="64"/>
+      <c r="E35" s="61"/>
+      <c r="F35" s="61"/>
+      <c r="G35" s="61"/>
+      <c r="H35" s="64"/>
+      <c r="I35" s="61" t="s">
+        <v>587</v>
+      </c>
+      <c r="J35" s="61" t="s">
+        <v>588</v>
+      </c>
+      <c r="K35" s="70">
         <f>3%*5</f>
         <v>0.15</v>
       </c>
     </row>
-    <row r="34" ht="43" customHeight="1" spans="1:11">
-      <c r="A34" s="54"/>
-      <c r="B34" s="54"/>
-      <c r="C34" s="57"/>
-      <c r="D34" s="58"/>
-      <c r="E34" s="54"/>
-      <c r="F34" s="54"/>
-      <c r="G34" s="54"/>
-      <c r="H34" s="58"/>
-      <c r="I34" s="54" t="s">
-        <v>583</v>
-      </c>
-      <c r="J34" s="54" t="s">
-        <v>584</v>
-      </c>
-      <c r="K34" s="64">
+    <row r="36" ht="43" customHeight="1" spans="1:11">
+      <c r="A36" s="61"/>
+      <c r="B36" s="61"/>
+      <c r="C36" s="63"/>
+      <c r="D36" s="64"/>
+      <c r="E36" s="61"/>
+      <c r="F36" s="61"/>
+      <c r="G36" s="61"/>
+      <c r="H36" s="64"/>
+      <c r="I36" s="61" t="s">
+        <v>589</v>
+      </c>
+      <c r="J36" s="61" t="s">
+        <v>590</v>
+      </c>
+      <c r="K36" s="70">
         <f>3%*5</f>
         <v>0.15</v>
       </c>
     </row>
-    <row r="36" ht="60" spans="1:8">
-      <c r="A36" s="42" t="s">
-        <v>585</v>
-      </c>
-      <c r="B36" s="42" t="s">
-        <v>586</v>
-      </c>
-      <c r="C36" s="42" t="s">
-        <v>587</v>
-      </c>
-      <c r="D36" s="42" t="s">
-        <v>588</v>
-      </c>
-      <c r="E36" s="42" t="s">
-        <v>589</v>
-      </c>
-      <c r="F36" s="42" t="s">
-        <v>590</v>
-      </c>
-      <c r="G36" s="42" t="s">
+    <row r="38" ht="60" spans="1:8">
+      <c r="A38" s="41" t="s">
         <v>591</v>
       </c>
-      <c r="H36" s="42" t="s">
+      <c r="B38" s="41" t="s">
         <v>592</v>
       </c>
-    </row>
-    <row r="37" ht="60" spans="1:8">
-      <c r="A37" s="42"/>
-      <c r="B37" s="42"/>
-      <c r="C37" s="42"/>
-      <c r="D37" s="42"/>
-      <c r="E37" s="42" t="s">
+      <c r="C38" s="41" t="s">
         <v>593</v>
       </c>
-      <c r="F37" s="42" t="s">
+      <c r="D38" s="41" t="s">
         <v>594</v>
       </c>
-      <c r="G37" s="42" t="s">
+      <c r="E38" s="41" t="s">
         <v>595</v>
       </c>
-      <c r="H37" s="42" t="s">
+      <c r="F38" s="41" t="s">
         <v>596</v>
       </c>
-    </row>
-    <row r="38" ht="60" spans="1:10">
-      <c r="A38" s="41" t="s">
+      <c r="G38" s="41" t="s">
         <v>597</v>
       </c>
-      <c r="B38" s="41" t="s">
+      <c r="H38" s="41" t="s">
         <v>598</v>
       </c>
-      <c r="C38" s="41" t="s">
+    </row>
+    <row r="39" ht="60" spans="1:8">
+      <c r="A39" s="41"/>
+      <c r="B39" s="41"/>
+      <c r="C39" s="41"/>
+      <c r="D39" s="41"/>
+      <c r="E39" s="41" t="s">
         <v>599</v>
       </c>
-      <c r="D38" s="41" t="s">
+      <c r="F39" s="41" t="s">
         <v>600</v>
       </c>
-      <c r="E38" s="42" t="s">
+      <c r="G39" s="41" t="s">
         <v>601</v>
       </c>
-      <c r="F38" s="42" t="s">
+      <c r="H39" s="41" t="s">
         <v>602</v>
       </c>
-      <c r="G38" s="42" t="s">
+    </row>
+    <row r="40" ht="60" spans="1:10">
+      <c r="A40" s="40" t="s">
         <v>603</v>
       </c>
-      <c r="H38" s="42" t="s">
+      <c r="B40" s="40" t="s">
         <v>604</v>
       </c>
-      <c r="I38" s="65"/>
-      <c r="J38" s="65"/>
-    </row>
-    <row r="39" ht="60" spans="1:10">
-      <c r="A39" s="43"/>
-      <c r="B39" s="43"/>
-      <c r="C39" s="43"/>
-      <c r="D39" s="43"/>
-      <c r="E39" s="42" t="s">
+      <c r="C40" s="40" t="s">
         <v>605</v>
       </c>
-      <c r="F39" s="42" t="s">
+      <c r="D40" s="40" t="s">
         <v>606</v>
       </c>
-      <c r="G39" s="42" t="s">
+      <c r="E40" s="41" t="s">
         <v>607</v>
       </c>
-      <c r="H39" s="42" t="s">
+      <c r="F40" s="41" t="s">
         <v>608</v>
       </c>
-      <c r="J39" s="65"/>
+      <c r="G40" s="41" t="s">
+        <v>609</v>
+      </c>
+      <c r="H40" s="41" t="s">
+        <v>610</v>
+      </c>
+      <c r="I40" s="71"/>
+      <c r="J40" s="71"/>
+    </row>
+    <row r="41" ht="60" spans="1:10">
+      <c r="A41" s="42"/>
+      <c r="B41" s="42"/>
+      <c r="C41" s="42"/>
+      <c r="D41" s="42"/>
+      <c r="E41" s="41" t="s">
+        <v>611</v>
+      </c>
+      <c r="F41" s="41" t="s">
+        <v>612</v>
+      </c>
+      <c r="G41" s="41" t="s">
+        <v>613</v>
+      </c>
+      <c r="H41" s="41" t="s">
+        <v>614</v>
+      </c>
+      <c r="J41" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="A34:A36"/>
     <mergeCell ref="A38:A39"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="B32:B34"/>
-    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="B34:B36"/>
     <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="C34:C36"/>
     <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="D32:D34"/>
-    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="D34:D36"/>
     <mergeCell ref="D38:D39"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="E32:E34"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="F32:F34"/>
-    <mergeCell ref="G29:G30"/>
-    <mergeCell ref="G32:G34"/>
-    <mergeCell ref="H29:H30"/>
-    <mergeCell ref="H32:H34"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="E34:E36"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="F34:F36"/>
+    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="G34:G36"/>
+    <mergeCell ref="H31:H32"/>
+    <mergeCell ref="H34:H36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -7822,7 +8359,1193 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K50"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="22.5714285714286" customWidth="1"/>
+    <col min="2" max="2" width="19.5714285714286" customWidth="1"/>
+    <col min="3" max="3" width="26.4285714285714" customWidth="1"/>
+    <col min="4" max="4" width="18.8571428571429" customWidth="1"/>
+    <col min="5" max="5" width="34.8571428571429" customWidth="1"/>
+    <col min="6" max="6" width="23.4285714285714" customWidth="1"/>
+    <col min="7" max="7" width="27" customWidth="1"/>
+    <col min="8" max="8" width="34" customWidth="1"/>
+    <col min="9" max="9" width="34.1428571428571" customWidth="1"/>
+    <col min="10" max="10" width="15.4285714285714" customWidth="1"/>
+    <col min="11" max="11" width="10.8571428571429" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>552</v>
+      </c>
+      <c r="B1" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>554</v>
+      </c>
+      <c r="B2" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>558</v>
+      </c>
+      <c r="B4" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>560</v>
+      </c>
+      <c r="B5" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>561</v>
+      </c>
+      <c r="B6" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="27" t="s">
+        <v>439</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>440</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>441</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>562</v>
+      </c>
+      <c r="E8" s="29" t="s">
+        <v>443</v>
+      </c>
+      <c r="F8" s="27" t="s">
+        <v>444</v>
+      </c>
+      <c r="G8" s="27" t="s">
+        <v>445</v>
+      </c>
+      <c r="H8" s="27" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>190</v>
+      </c>
+      <c r="B9" s="30">
+        <f>SUM(C9,E9)</f>
+        <v>46650</v>
+      </c>
+      <c r="C9" s="30">
+        <v>24400</v>
+      </c>
+      <c r="D9" s="30">
+        <f t="shared" ref="D9:D13" si="0">C9*G9</f>
+        <v>24400</v>
+      </c>
+      <c r="E9" s="31">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A9)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A9)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A9)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A9)</f>
+        <v>22250</v>
+      </c>
+      <c r="F9" s="30">
+        <f t="shared" ref="F9:F13" si="1">E9*G9</f>
+        <v>22250</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9" s="31">
+        <f t="shared" ref="H9:H13" si="2">B9*G9</f>
+        <v>46650</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>195</v>
+      </c>
+      <c r="B10" s="30">
+        <f>SUM(C10,E10)</f>
+        <v>26950</v>
+      </c>
+      <c r="C10" s="30">
+        <v>18000</v>
+      </c>
+      <c r="D10" s="30">
+        <f t="shared" si="0"/>
+        <v>18000</v>
+      </c>
+      <c r="E10" s="31">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A10)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A10)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A10)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A10)</f>
+        <v>8950</v>
+      </c>
+      <c r="F10" s="30">
+        <f t="shared" si="1"/>
+        <v>8950</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10" s="31">
+        <f t="shared" si="2"/>
+        <v>26950</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>198</v>
+      </c>
+      <c r="B11" s="30">
+        <f>SUM(C11,E11)</f>
+        <v>2988.33333333334</v>
+      </c>
+      <c r="C11" s="30">
+        <f>3406/G11</f>
+        <v>405.47619047619</v>
+      </c>
+      <c r="D11" s="30">
+        <f t="shared" si="0"/>
+        <v>3406</v>
+      </c>
+      <c r="E11" s="31">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A11)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A11)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A11)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A11)</f>
+        <v>2582.85714285715</v>
+      </c>
+      <c r="F11" s="30">
+        <f t="shared" si="1"/>
+        <v>21696</v>
+      </c>
+      <c r="G11">
+        <v>8.4</v>
+      </c>
+      <c r="H11" s="31">
+        <f t="shared" si="2"/>
+        <v>25102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>202</v>
+      </c>
+      <c r="B12" s="30">
+        <f>SUM(C12,E12)</f>
+        <v>1749.71428571429</v>
+      </c>
+      <c r="C12" s="30">
+        <v>714</v>
+      </c>
+      <c r="D12" s="30">
+        <f t="shared" si="0"/>
+        <v>3998.4</v>
+      </c>
+      <c r="E12" s="31">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A12)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A12)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A12)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A12)</f>
+        <v>1035.71428571429</v>
+      </c>
+      <c r="F12" s="30">
+        <f t="shared" si="1"/>
+        <v>5800</v>
+      </c>
+      <c r="G12">
+        <v>5.6</v>
+      </c>
+      <c r="H12" s="31">
+        <f t="shared" si="2"/>
+        <v>9798.4</v>
+      </c>
+      <c r="I12" s="31"/>
+      <c r="J12" s="31"/>
+      <c r="K12" s="32"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" t="s">
+        <v>210</v>
+      </c>
+      <c r="B13" s="30">
+        <f>SUM(C13,E13)</f>
+        <v>1499.62068965517</v>
+      </c>
+      <c r="C13" s="30">
+        <v>741</v>
+      </c>
+      <c r="D13" s="30">
+        <f>C13*G13</f>
+        <v>8595.6</v>
+      </c>
+      <c r="E13" s="31">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A13)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A13)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A13)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A13)</f>
+        <v>758.620689655172</v>
+      </c>
+      <c r="F13" s="30">
+        <f t="shared" si="1"/>
+        <v>8799.99999999999</v>
+      </c>
+      <c r="G13">
+        <v>11.6</v>
+      </c>
+      <c r="H13" s="31">
+        <f t="shared" si="2"/>
+        <v>17395.6</v>
+      </c>
+      <c r="I13" s="31"/>
+      <c r="J13" s="32"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" t="s">
+        <v>288</v>
+      </c>
+      <c r="B14" s="32">
+        <f>B12/(B12+1000)</f>
+        <v>0.636325852036575</v>
+      </c>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="30"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="32"/>
+      <c r="J14" s="32"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" t="s">
+        <v>563</v>
+      </c>
+      <c r="B15" s="32">
+        <f>B13/(B13+1000)</f>
+        <v>0.599939301135345</v>
+      </c>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="30"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>233</v>
+      </c>
+      <c r="B16" s="33">
+        <f t="shared" ref="B16:B26" si="3">SUM(C16,E16)</f>
+        <v>1.2</v>
+      </c>
+      <c r="C16" s="33">
+        <v>1</v>
+      </c>
+      <c r="D16" s="30">
+        <f t="shared" ref="D16:D19" si="4">C16*G16*100</f>
+        <v>14000</v>
+      </c>
+      <c r="E16" s="34">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A16)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A16)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A16)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A16)</f>
+        <v>0.2</v>
+      </c>
+      <c r="F16" s="30">
+        <f t="shared" ref="F16:F19" si="5">E16*G16*100</f>
+        <v>2800</v>
+      </c>
+      <c r="G16">
+        <v>140</v>
+      </c>
+      <c r="H16" s="31">
+        <f t="shared" ref="H16:H19" si="6">B16*G16*100</f>
+        <v>16800</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>457</v>
+      </c>
+      <c r="B17" s="33">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="C17" s="33">
+        <v>0</v>
+      </c>
+      <c r="D17" s="30">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E17" s="34">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A17)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A17)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A17)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A17)</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>140</v>
+      </c>
+      <c r="H17" s="31">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>224</v>
+      </c>
+      <c r="B18" s="33">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="C18" s="33">
+        <v>0</v>
+      </c>
+      <c r="D18" s="30">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E18" s="34">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A18)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A18)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A18)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A18)</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>140</v>
+      </c>
+      <c r="H18" s="31">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
+        <v>229</v>
+      </c>
+      <c r="B19" s="33">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="C19" s="33">
+        <v>0</v>
+      </c>
+      <c r="D19" s="30">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="E19" s="34">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A19)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A19)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A19)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A19)</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="30">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>28</v>
+      </c>
+      <c r="H19" s="31">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>217</v>
+      </c>
+      <c r="B20" s="30">
+        <f t="shared" si="3"/>
+        <v>80</v>
+      </c>
+      <c r="C20" s="30">
+        <v>100</v>
+      </c>
+      <c r="D20" s="30">
+        <f t="shared" ref="D20:D23" si="7">C20*G20</f>
+        <v>40000</v>
+      </c>
+      <c r="E20" s="31">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A20)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A20)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A20)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A20)</f>
+        <v>-20</v>
+      </c>
+      <c r="F20" s="30">
+        <f t="shared" ref="F20:F23" si="8">E20*G20</f>
+        <v>-8000</v>
+      </c>
+      <c r="G20">
+        <v>400</v>
+      </c>
+      <c r="H20" s="31">
+        <f t="shared" ref="H20:H23" si="9">B20*G20</f>
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" t="s">
+        <v>391</v>
+      </c>
+      <c r="B21" s="30">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="C21" s="30">
+        <v>4</v>
+      </c>
+      <c r="D21" s="30">
+        <f t="shared" si="7"/>
+        <v>4500</v>
+      </c>
+      <c r="E21" s="31">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A21)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A21)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A21)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A21)</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="30">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>1125</v>
+      </c>
+      <c r="H21" s="31">
+        <f t="shared" si="9"/>
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" t="s">
+        <v>459</v>
+      </c>
+      <c r="B22" s="30">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="C22" s="30">
+        <v>0</v>
+      </c>
+      <c r="D22" s="30">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="E22" s="31">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A22)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A22)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A22)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A22)</f>
+        <v>0</v>
+      </c>
+      <c r="F22" s="30">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>4800</v>
+      </c>
+      <c r="H22" s="31">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>460</v>
+      </c>
+      <c r="B23" s="30">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="C23" s="30">
+        <v>10</v>
+      </c>
+      <c r="D23" s="30">
+        <f t="shared" si="7"/>
+        <v>23260</v>
+      </c>
+      <c r="E23" s="31">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A23)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A23)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A23)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A23)</f>
+        <v>4</v>
+      </c>
+      <c r="F23" s="30">
+        <f t="shared" si="8"/>
+        <v>9304</v>
+      </c>
+      <c r="G23">
+        <v>2326</v>
+      </c>
+      <c r="H23" s="31">
+        <f t="shared" si="9"/>
+        <v>32564</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>237</v>
+      </c>
+      <c r="B24" s="33">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="C24" s="33">
+        <v>1</v>
+      </c>
+      <c r="D24" s="30">
+        <f t="shared" ref="D24:D26" si="10">C24*G24*100</f>
+        <v>16800</v>
+      </c>
+      <c r="E24" s="34">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A24)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A24)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A24)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A24)</f>
+        <v>0</v>
+      </c>
+      <c r="F24" s="30">
+        <f t="shared" ref="F24:F26" si="11">E24*G24*100</f>
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>168</v>
+      </c>
+      <c r="H24" s="31">
+        <f t="shared" ref="H24:H26" si="12">B24*G24*100</f>
+        <v>16800</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>241</v>
+      </c>
+      <c r="B25" s="33">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="C25" s="33">
+        <v>0</v>
+      </c>
+      <c r="D25" s="30">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="E25" s="34">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A25)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A25)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A25)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A25)</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="30">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>168</v>
+      </c>
+      <c r="H25" s="31">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>245</v>
+      </c>
+      <c r="B26" s="33">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="C26" s="33">
+        <v>0</v>
+      </c>
+      <c r="D26" s="30">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="E26" s="34">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A26)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A26)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A26)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A26)</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="30">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>233</v>
+      </c>
+      <c r="H26" s="31">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="35">
+        <f>SUM(D9:D26)</f>
+        <v>156960</v>
+      </c>
+      <c r="E27" s="36"/>
+      <c r="F27" s="35">
+        <f>SUM(F9:F26)</f>
+        <v>71600</v>
+      </c>
+      <c r="G27" s="2"/>
+      <c r="H27" s="35">
+        <f>SUM(H9:H26)</f>
+        <v>228560</v>
+      </c>
+    </row>
+    <row r="28" customFormat="1" spans="1:11">
+      <c r="A28" t="s">
+        <v>564</v>
+      </c>
+      <c r="D28" s="36">
+        <f>'Balanced Dummy '!D18-D27</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="36"/>
+      <c r="F28" s="36"/>
+      <c r="K28" s="46"/>
+    </row>
+    <row r="29" customFormat="1" spans="4:11">
+      <c r="D29" s="36"/>
+      <c r="E29" s="36"/>
+      <c r="F29" s="36"/>
+      <c r="K29" s="46"/>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="37" t="s">
+        <v>565</v>
+      </c>
+      <c r="B30" s="38" t="s">
+        <v>85</v>
+      </c>
+      <c r="C30" s="38" t="s">
+        <v>448</v>
+      </c>
+      <c r="D30" s="38" t="s">
+        <v>449</v>
+      </c>
+      <c r="E30" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="F30" s="37" t="s">
+        <v>403</v>
+      </c>
+      <c r="G30" s="37" t="s">
+        <v>566</v>
+      </c>
+      <c r="H30" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="I30" s="38" t="s">
+        <v>308</v>
+      </c>
+      <c r="J30" s="37" t="s">
+        <v>567</v>
+      </c>
+      <c r="K30" s="38" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="49" t="s">
+        <v>619</v>
+      </c>
+      <c r="B31" s="49">
+        <v>100</v>
+      </c>
+      <c r="C31" s="49">
+        <f>2*1000*1.25</f>
+        <v>2500</v>
+      </c>
+      <c r="D31" s="49">
+        <v>3</v>
+      </c>
+      <c r="E31" s="49" t="s">
+        <v>620</v>
+      </c>
+      <c r="F31" s="49" t="s">
+        <v>571</v>
+      </c>
+      <c r="G31" s="49" t="s">
+        <v>621</v>
+      </c>
+      <c r="H31" s="49"/>
+      <c r="I31" s="37" t="s">
+        <v>622</v>
+      </c>
+      <c r="J31" s="37" t="s">
+        <v>623</v>
+      </c>
+      <c r="K31" s="37">
+        <f>4.8*1000*25%*5</f>
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" s="50"/>
+      <c r="B32" s="50"/>
+      <c r="C32" s="50"/>
+      <c r="D32" s="50"/>
+      <c r="E32" s="50"/>
+      <c r="F32" s="50"/>
+      <c r="G32" s="50"/>
+      <c r="H32" s="50"/>
+      <c r="I32" s="37" t="s">
+        <v>455</v>
+      </c>
+      <c r="J32" s="37">
+        <v>1</v>
+      </c>
+      <c r="K32" s="47"/>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" s="51"/>
+      <c r="B33" s="51"/>
+      <c r="C33" s="51"/>
+      <c r="D33" s="51"/>
+      <c r="E33" s="51"/>
+      <c r="F33" s="51"/>
+      <c r="G33" s="51"/>
+      <c r="H33" s="51"/>
+      <c r="I33" s="39" t="s">
+        <v>624</v>
+      </c>
+      <c r="J33" s="56">
+        <v>0.5</v>
+      </c>
+      <c r="K33" s="48"/>
+    </row>
+    <row r="34" ht="66" customHeight="1" spans="1:11">
+      <c r="A34" s="39" t="s">
+        <v>625</v>
+      </c>
+      <c r="B34" s="39">
+        <v>150</v>
+      </c>
+      <c r="C34" s="39">
+        <f>2*1000*1.9</f>
+        <v>3800</v>
+      </c>
+      <c r="D34" s="39">
+        <v>8</v>
+      </c>
+      <c r="E34" s="39" t="s">
+        <v>626</v>
+      </c>
+      <c r="F34" s="39" t="s">
+        <v>627</v>
+      </c>
+      <c r="G34" s="39" t="s">
+        <v>578</v>
+      </c>
+      <c r="H34" s="39">
+        <v>4</v>
+      </c>
+      <c r="I34" s="39" t="s">
+        <v>303</v>
+      </c>
+      <c r="J34" s="39" t="s">
+        <v>628</v>
+      </c>
+      <c r="K34" s="39">
+        <f>4.8*1000*8%*5</f>
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="35" ht="45" spans="1:11">
+      <c r="A35" s="52" t="s">
+        <v>629</v>
+      </c>
+      <c r="B35" s="52" t="s">
+        <v>630</v>
+      </c>
+      <c r="C35" s="52">
+        <f>2*1000*0.4</f>
+        <v>800</v>
+      </c>
+      <c r="D35" s="52">
+        <v>2</v>
+      </c>
+      <c r="E35" s="52" t="s">
+        <v>631</v>
+      </c>
+      <c r="F35" s="52" t="s">
+        <v>632</v>
+      </c>
+      <c r="G35" s="52" t="s">
+        <v>632</v>
+      </c>
+      <c r="H35" s="52">
+        <v>2</v>
+      </c>
+      <c r="I35" s="39" t="s">
+        <v>303</v>
+      </c>
+      <c r="J35" s="39" t="s">
+        <v>628</v>
+      </c>
+      <c r="K35" s="39">
+        <f>4.8*1000*8%*5</f>
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" s="53"/>
+      <c r="B36" s="53"/>
+      <c r="C36" s="53"/>
+      <c r="D36" s="53"/>
+      <c r="E36" s="53"/>
+      <c r="F36" s="53"/>
+      <c r="G36" s="53"/>
+      <c r="H36" s="53"/>
+      <c r="I36" s="39" t="s">
+        <v>589</v>
+      </c>
+      <c r="J36" s="39" t="s">
+        <v>633</v>
+      </c>
+      <c r="K36" s="57">
+        <f>2%*5</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="37" ht="30" spans="1:11">
+      <c r="A37" s="52" t="s">
+        <v>634</v>
+      </c>
+      <c r="B37" s="52" t="s">
+        <v>635</v>
+      </c>
+      <c r="C37" s="52"/>
+      <c r="D37" s="52"/>
+      <c r="E37" s="52" t="s">
+        <v>636</v>
+      </c>
+      <c r="F37" s="52"/>
+      <c r="G37" s="52"/>
+      <c r="H37" s="52"/>
+      <c r="I37" s="39" t="s">
+        <v>637</v>
+      </c>
+      <c r="J37" s="39" t="s">
+        <v>638</v>
+      </c>
+      <c r="K37" s="57">
+        <f t="shared" ref="K37:K41" si="13">8%*5</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" s="54"/>
+      <c r="B38" s="54"/>
+      <c r="C38" s="54"/>
+      <c r="D38" s="54"/>
+      <c r="E38" s="54"/>
+      <c r="F38" s="54"/>
+      <c r="G38" s="54"/>
+      <c r="H38" s="54"/>
+      <c r="I38" s="39" t="s">
+        <v>639</v>
+      </c>
+      <c r="J38" s="56">
+        <v>1.5</v>
+      </c>
+      <c r="K38" s="58">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" s="54"/>
+      <c r="B39" s="54"/>
+      <c r="C39" s="54"/>
+      <c r="D39" s="54"/>
+      <c r="E39" s="54"/>
+      <c r="F39" s="54"/>
+      <c r="G39" s="54"/>
+      <c r="H39" s="54"/>
+      <c r="I39" s="39" t="s">
+        <v>640</v>
+      </c>
+      <c r="J39" s="39" t="s">
+        <v>638</v>
+      </c>
+      <c r="K39" s="57">
+        <f t="shared" si="13"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" s="53"/>
+      <c r="B40" s="53"/>
+      <c r="C40" s="53"/>
+      <c r="D40" s="53"/>
+      <c r="E40" s="53"/>
+      <c r="F40" s="53"/>
+      <c r="G40" s="53"/>
+      <c r="H40" s="53"/>
+      <c r="I40" s="39" t="s">
+        <v>641</v>
+      </c>
+      <c r="J40" s="56">
+        <v>0.72</v>
+      </c>
+      <c r="K40" s="58">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="41" ht="90" spans="1:11">
+      <c r="A41" s="52" t="s">
+        <v>642</v>
+      </c>
+      <c r="B41" s="52" t="s">
+        <v>635</v>
+      </c>
+      <c r="C41" s="52">
+        <v>0</v>
+      </c>
+      <c r="D41" s="52" t="s">
+        <v>643</v>
+      </c>
+      <c r="E41" s="52" t="s">
+        <v>644</v>
+      </c>
+      <c r="F41" s="52" t="s">
+        <v>645</v>
+      </c>
+      <c r="G41" s="52" t="s">
+        <v>645</v>
+      </c>
+      <c r="H41" s="52">
+        <v>4</v>
+      </c>
+      <c r="I41" s="39" t="s">
+        <v>646</v>
+      </c>
+      <c r="J41" s="39" t="s">
+        <v>586</v>
+      </c>
+      <c r="K41" s="57">
+        <f t="shared" si="13"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" s="54"/>
+      <c r="B42" s="54"/>
+      <c r="C42" s="54"/>
+      <c r="D42" s="54"/>
+      <c r="E42" s="54"/>
+      <c r="F42" s="54"/>
+      <c r="G42" s="54"/>
+      <c r="H42" s="54"/>
+      <c r="I42" s="39" t="s">
+        <v>647</v>
+      </c>
+      <c r="J42" s="56">
+        <v>2.3</v>
+      </c>
+      <c r="K42" s="56">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43" s="54"/>
+      <c r="B43" s="54"/>
+      <c r="C43" s="54"/>
+      <c r="D43" s="54"/>
+      <c r="E43" s="54"/>
+      <c r="F43" s="54"/>
+      <c r="G43" s="54"/>
+      <c r="H43" s="54"/>
+      <c r="I43" s="39" t="s">
+        <v>648</v>
+      </c>
+      <c r="J43" s="39" t="s">
+        <v>586</v>
+      </c>
+      <c r="K43" s="57">
+        <f>8%*5</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" s="53"/>
+      <c r="B44" s="53"/>
+      <c r="C44" s="53"/>
+      <c r="D44" s="53"/>
+      <c r="E44" s="53"/>
+      <c r="F44" s="53"/>
+      <c r="G44" s="53"/>
+      <c r="H44" s="53"/>
+      <c r="I44" s="39" t="s">
+        <v>649</v>
+      </c>
+      <c r="J44" s="56">
+        <v>4.78</v>
+      </c>
+      <c r="K44" s="56">
+        <v>4.78</v>
+      </c>
+    </row>
+    <row r="46" ht="45" spans="1:8">
+      <c r="A46" s="40" t="s">
+        <v>591</v>
+      </c>
+      <c r="B46" s="40" t="s">
+        <v>650</v>
+      </c>
+      <c r="C46" s="40" t="s">
+        <v>651</v>
+      </c>
+      <c r="D46" s="41" t="s">
+        <v>652</v>
+      </c>
+      <c r="E46" s="41" t="s">
+        <v>653</v>
+      </c>
+      <c r="F46" s="41" t="s">
+        <v>654</v>
+      </c>
+      <c r="G46" s="41" t="s">
+        <v>655</v>
+      </c>
+      <c r="H46" s="41" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="47" ht="30" spans="1:8">
+      <c r="A47" s="42"/>
+      <c r="B47" s="42"/>
+      <c r="C47" s="42"/>
+      <c r="D47" s="41"/>
+      <c r="E47" s="41" t="s">
+        <v>657</v>
+      </c>
+      <c r="F47" s="41" t="s">
+        <v>658</v>
+      </c>
+      <c r="G47" s="41" t="s">
+        <v>659</v>
+      </c>
+      <c r="H47" s="41" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="43"/>
+      <c r="B48" s="43"/>
+      <c r="C48" s="43"/>
+      <c r="D48" s="43"/>
+      <c r="E48" s="43"/>
+      <c r="F48" s="43"/>
+      <c r="G48" s="43"/>
+      <c r="H48" s="43"/>
+    </row>
+    <row r="49" ht="45" spans="1:9">
+      <c r="A49" s="39" t="s">
+        <v>603</v>
+      </c>
+      <c r="B49" s="39" t="s">
+        <v>661</v>
+      </c>
+      <c r="C49" s="39" t="s">
+        <v>662</v>
+      </c>
+      <c r="D49" s="39" t="s">
+        <v>663</v>
+      </c>
+      <c r="E49" s="39" t="s">
+        <v>664</v>
+      </c>
+      <c r="F49" s="39" t="s">
+        <v>665</v>
+      </c>
+      <c r="G49" s="39" t="s">
+        <v>666</v>
+      </c>
+      <c r="H49" s="39" t="s">
+        <v>667</v>
+      </c>
+      <c r="I49" s="55" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="50" ht="45" spans="1:9">
+      <c r="A50" s="39"/>
+      <c r="B50" s="39"/>
+      <c r="C50" s="39"/>
+      <c r="D50" s="39"/>
+      <c r="E50" s="55" t="s">
+        <v>669</v>
+      </c>
+      <c r="F50" s="39" t="s">
+        <v>670</v>
+      </c>
+      <c r="G50" s="55" t="s">
+        <v>671</v>
+      </c>
+      <c r="H50" s="39"/>
+      <c r="I50" s="59"/>
+    </row>
+  </sheetData>
+  <mergeCells count="36">
+    <mergeCell ref="A31:A33"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A37:A40"/>
+    <mergeCell ref="A41:A44"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="B37:B40"/>
+    <mergeCell ref="B41:B44"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="C31:C33"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="C37:C40"/>
+    <mergeCell ref="C41:C44"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="D37:D40"/>
+    <mergeCell ref="D41:D44"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="E31:E33"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="E37:E40"/>
+    <mergeCell ref="E41:E44"/>
+    <mergeCell ref="F31:F33"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="F37:F40"/>
+    <mergeCell ref="F41:F44"/>
+    <mergeCell ref="G31:G33"/>
+    <mergeCell ref="G35:G36"/>
+    <mergeCell ref="G37:G40"/>
+    <mergeCell ref="G41:G44"/>
+    <mergeCell ref="H31:H33"/>
+    <mergeCell ref="H35:H36"/>
+    <mergeCell ref="H37:H40"/>
+    <mergeCell ref="H41:H44"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.5714285714286" customWidth="1"/>
@@ -7840,76 +9563,76 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="B1" t="s">
-        <v>609</v>
+        <v>672</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="B2" t="s">
-        <v>610</v>
+        <v>673</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>611</v>
+        <v>674</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="B4" t="s">
-        <v>612</v>
+        <v>675</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="B5" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="B6" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="27" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="E8" s="29" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="F8" s="27" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="G8" s="27" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="H8" s="27" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -7917,7 +9640,7 @@
         <v>190</v>
       </c>
       <c r="B9" s="30">
-        <f t="shared" ref="B9:B24" si="0">SUM(C9,E9)</f>
+        <f>SUM(C9,E9)</f>
         <v>36250</v>
       </c>
       <c r="C9" s="30">
@@ -7932,14 +9655,14 @@
         <v>18250</v>
       </c>
       <c r="F9" s="30">
-        <f t="shared" ref="F9:F13" si="1">E9*G9</f>
+        <f t="shared" ref="F9:F13" si="0">E9*G9</f>
         <v>18250</v>
       </c>
       <c r="G9">
         <v>1</v>
       </c>
       <c r="H9" s="31">
-        <f t="shared" ref="H9:H13" si="2">B9*G9</f>
+        <f t="shared" ref="H9:H13" si="1">B9*G9</f>
         <v>36250</v>
       </c>
     </row>
@@ -7948,7 +9671,7 @@
         <v>195</v>
       </c>
       <c r="B10" s="30">
-        <f t="shared" si="0"/>
+        <f>SUM(C10,E10)</f>
         <v>27350</v>
       </c>
       <c r="C10" s="30">
@@ -7963,14 +9686,14 @@
         <v>8950</v>
       </c>
       <c r="F10" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>8950</v>
       </c>
       <c r="G10">
         <v>1</v>
       </c>
       <c r="H10" s="31">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>27350</v>
       </c>
     </row>
@@ -7979,7 +9702,7 @@
         <v>198</v>
       </c>
       <c r="B11" s="30">
-        <f t="shared" si="0"/>
+        <f>SUM(C11,E11)</f>
         <v>2909.5238095238</v>
       </c>
       <c r="C11" s="30">
@@ -7990,28 +9713,28 @@
         <f>C11*G11</f>
         <v>6840</v>
       </c>
-      <c r="E11" s="32">
+      <c r="E11" s="31">
         <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A11)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A11)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A11)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A11)</f>
         <v>2095.23809523809</v>
       </c>
       <c r="F11" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>17600</v>
       </c>
       <c r="G11">
         <v>8.4</v>
       </c>
       <c r="H11" s="31">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>24440</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:11">
       <c r="A12" t="s">
         <v>202</v>
       </c>
       <c r="B12" s="30">
-        <f t="shared" si="0"/>
+        <f>SUM(C12,E12)</f>
         <v>870</v>
       </c>
       <c r="C12" s="30">
@@ -8021,28 +9744,29 @@
         <f>C12*G12</f>
         <v>2072</v>
       </c>
-      <c r="E12" s="32">
+      <c r="E12" s="31">
         <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A12)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A12)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A12)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A12)</f>
         <v>500</v>
       </c>
       <c r="F12" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2800</v>
       </c>
       <c r="G12">
         <v>5.6</v>
       </c>
       <c r="H12" s="31">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>4872</v>
       </c>
+      <c r="K12" s="32"/>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>210</v>
       </c>
       <c r="B13" s="30">
-        <f t="shared" si="0"/>
+        <f>SUM(C13,E13)</f>
         <v>880</v>
       </c>
       <c r="C13" s="30">
@@ -8052,763 +9776,793 @@
         <f>C13*G13</f>
         <v>4408</v>
       </c>
-      <c r="E13" s="32">
+      <c r="E13" s="31">
         <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A13)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A13)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A13)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A13)</f>
         <v>500</v>
       </c>
       <c r="F13" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>5800</v>
       </c>
       <c r="G13">
         <v>11.6</v>
       </c>
       <c r="H13" s="31">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>10208</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" customFormat="1" spans="1:10">
       <c r="A14" t="s">
-        <v>233</v>
-      </c>
-      <c r="B14" s="33">
-        <f t="shared" si="0"/>
-        <v>1.9</v>
-      </c>
-      <c r="C14" s="33">
-        <v>1.2</v>
-      </c>
-      <c r="D14" s="30">
-        <f t="shared" ref="D14:D17" si="3">C14*G14*100</f>
-        <v>16800</v>
-      </c>
-      <c r="E14" s="34">
-        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A14)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A14)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A14)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A14)</f>
-        <v>0.7</v>
-      </c>
-      <c r="F14" s="30">
-        <f t="shared" ref="F14:F17" si="4">E14*G14*100</f>
-        <v>9800</v>
-      </c>
-      <c r="G14">
-        <v>140</v>
-      </c>
-      <c r="H14" s="31">
-        <f t="shared" ref="H14:H17" si="5">B14*G14*100</f>
-        <v>26600</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
+        <v>288</v>
+      </c>
+      <c r="B14" s="32">
+        <f>B12/(B12+1000)</f>
+        <v>0.46524064171123</v>
+      </c>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="30"/>
+      <c r="H14" s="31"/>
+      <c r="J14" s="32"/>
+    </row>
+    <row r="15" customFormat="1" spans="1:10">
       <c r="A15" t="s">
-        <v>453</v>
-      </c>
-      <c r="B15" s="33">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C15" s="33">
-        <v>0</v>
-      </c>
-      <c r="D15" s="30">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E15" s="34">
-        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A15)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A15)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A15)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A15)</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="30">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>140</v>
-      </c>
-      <c r="H15" s="31">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+        <v>563</v>
+      </c>
+      <c r="B15" s="32">
+        <f>B13/(B13+1000)</f>
+        <v>0.468085106382979</v>
+      </c>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="30"/>
+      <c r="H15" s="31"/>
+      <c r="J15" s="32"/>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
+        <v>233</v>
+      </c>
+      <c r="B16" s="33">
+        <f t="shared" ref="B16:B26" si="2">SUM(C16,E16)</f>
+        <v>1.9</v>
+      </c>
+      <c r="C16" s="33">
+        <v>1.2</v>
+      </c>
+      <c r="D16" s="30">
+        <f t="shared" ref="D16:D19" si="3">C16*G16*100</f>
+        <v>16800</v>
+      </c>
+      <c r="E16" s="34">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A16)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A16)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A16)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A16)</f>
+        <v>0.7</v>
+      </c>
+      <c r="F16" s="30">
+        <f t="shared" ref="F16:F19" si="4">E16*G16*100</f>
+        <v>9800</v>
+      </c>
+      <c r="G16">
+        <v>140</v>
+      </c>
+      <c r="H16" s="31">
+        <f t="shared" ref="H16:H19" si="5">B16*G16*100</f>
+        <v>26600</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>457</v>
+      </c>
+      <c r="B17" s="33">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C17" s="33">
+        <v>0</v>
+      </c>
+      <c r="D17" s="30">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E17" s="34">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A17)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A17)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A17)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A17)</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="30">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>140</v>
+      </c>
+      <c r="H17" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
         <v>224</v>
       </c>
-      <c r="B16" s="33">
-        <f t="shared" si="0"/>
+      <c r="B18" s="33">
+        <f t="shared" si="2"/>
         <v>0.6</v>
       </c>
-      <c r="C16" s="33">
+      <c r="C18" s="33">
         <v>0.2</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D18" s="30">
         <f t="shared" si="3"/>
         <v>2800</v>
       </c>
-      <c r="E16" s="34">
-        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A16)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A16)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A16)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A16)</f>
+      <c r="E18" s="34">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A18)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A18)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A18)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A18)</f>
         <v>0.4</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F18" s="30">
         <f t="shared" si="4"/>
         <v>5600</v>
       </c>
-      <c r="G16">
+      <c r="G18">
         <v>140</v>
       </c>
-      <c r="H16" s="31">
+      <c r="H18" s="31">
         <f t="shared" si="5"/>
         <v>8400</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
-      <c r="A17" t="s">
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
         <v>229</v>
       </c>
-      <c r="B17" s="33">
-        <f t="shared" si="0"/>
+      <c r="B19" s="33">
+        <f t="shared" si="2"/>
         <v>1.5</v>
       </c>
-      <c r="C17" s="33">
+      <c r="C19" s="33">
         <v>0.5</v>
       </c>
-      <c r="D17" s="30">
+      <c r="D19" s="30">
         <f t="shared" si="3"/>
         <v>1400</v>
       </c>
-      <c r="E17" s="34">
-        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A17)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A17)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A17)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A17)</f>
+      <c r="E19" s="34">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A19)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A19)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A19)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A19)</f>
         <v>1</v>
       </c>
-      <c r="F17" s="30">
+      <c r="F19" s="30">
         <f t="shared" si="4"/>
         <v>2800</v>
       </c>
-      <c r="G17">
+      <c r="G19">
         <v>28</v>
       </c>
-      <c r="H17" s="31">
+      <c r="H19" s="31">
         <f t="shared" si="5"/>
         <v>4200</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
-      <c r="A18" t="s">
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
         <v>217</v>
       </c>
-      <c r="B18" s="30">
-        <f t="shared" si="0"/>
+      <c r="B20" s="30">
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="C18" s="30">
+      <c r="C20" s="30">
         <v>100</v>
       </c>
-      <c r="D18" s="30">
-        <f t="shared" ref="D18:D21" si="6">C18*G18</f>
+      <c r="D20" s="30">
+        <f t="shared" ref="D20:D23" si="6">C20*G20</f>
         <v>40000</v>
       </c>
-      <c r="E18" s="31">
-        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A18)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A18)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A18)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A18)</f>
-        <v>0</v>
-      </c>
-      <c r="F18" s="30">
-        <f t="shared" ref="F18:F21" si="7">E18*G18</f>
-        <v>0</v>
-      </c>
-      <c r="G18">
+      <c r="E20" s="31">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A20)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A20)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A20)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A20)</f>
+        <v>0</v>
+      </c>
+      <c r="F20" s="30">
+        <f t="shared" ref="F20:F23" si="7">E20*G20</f>
+        <v>0</v>
+      </c>
+      <c r="G20">
         <v>400</v>
       </c>
-      <c r="H18" s="31">
-        <f t="shared" ref="H18:H21" si="8">B18*G18</f>
+      <c r="H20" s="31">
+        <f t="shared" ref="H20:H23" si="8">B20*G20</f>
         <v>40000</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
-      <c r="A19" t="s">
-        <v>387</v>
-      </c>
-      <c r="B19" s="30">
-        <f t="shared" si="0"/>
+    <row r="21" spans="1:8">
+      <c r="A21" t="s">
+        <v>391</v>
+      </c>
+      <c r="B21" s="30">
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="C19" s="30">
+      <c r="C21" s="30">
         <v>4</v>
       </c>
-      <c r="D19" s="30">
+      <c r="D21" s="30">
         <f t="shared" si="6"/>
         <v>4500</v>
       </c>
-      <c r="E19" s="31">
-        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A19)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A19)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A19)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A19)</f>
-        <v>0</v>
-      </c>
-      <c r="F19" s="30">
+      <c r="E21" s="31">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A21)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A21)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A21)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A21)</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="30">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="G19">
+      <c r="G21">
         <v>1125</v>
       </c>
-      <c r="H19" s="31">
+      <c r="H21" s="31">
         <f t="shared" si="8"/>
         <v>4500</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
-      <c r="A20" t="s">
-        <v>455</v>
-      </c>
-      <c r="B20" s="30">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C20" s="30">
-        <v>0</v>
-      </c>
-      <c r="D20" s="30">
+    <row r="22" spans="1:8">
+      <c r="A22" t="s">
+        <v>459</v>
+      </c>
+      <c r="B22" s="30">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C22" s="30">
+        <v>0</v>
+      </c>
+      <c r="D22" s="30">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="E20" s="31">
-        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A20)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A20)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A20)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A20)</f>
-        <v>0</v>
-      </c>
-      <c r="F20" s="30">
+      <c r="E22" s="31">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A22)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A22)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A22)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A22)</f>
+        <v>0</v>
+      </c>
+      <c r="F22" s="30">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="G20">
+      <c r="G22">
         <v>4800</v>
       </c>
-      <c r="H20" s="31">
+      <c r="H22" s="31">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
-      <c r="A21" t="s">
-        <v>456</v>
-      </c>
-      <c r="B21" s="30">
-        <f t="shared" si="0"/>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>460</v>
+      </c>
+      <c r="B23" s="30">
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="C21" s="30">
+      <c r="C23" s="30">
         <v>10</v>
       </c>
-      <c r="D21" s="30">
+      <c r="D23" s="30">
         <f t="shared" si="6"/>
         <v>23260</v>
       </c>
-      <c r="E21" s="31">
-        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A21)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A21)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A21)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A21)</f>
-        <v>0</v>
-      </c>
-      <c r="F21" s="30">
+      <c r="E23" s="31">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A23)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A23)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A23)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A23)</f>
+        <v>0</v>
+      </c>
+      <c r="F23" s="30">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="G21">
+      <c r="G23">
         <v>2326</v>
       </c>
-      <c r="H21" s="31">
+      <c r="H23" s="31">
         <f t="shared" si="8"/>
         <v>23260</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
-      <c r="A22" t="s">
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
         <v>237</v>
       </c>
-      <c r="B22" s="33">
-        <f t="shared" si="0"/>
+      <c r="B24" s="33">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="C22" s="33">
+      <c r="C24" s="33">
         <v>1</v>
       </c>
-      <c r="D22" s="30">
-        <f t="shared" ref="D22:D24" si="9">C22*G22*100</f>
+      <c r="D24" s="30">
+        <f t="shared" ref="D24:D26" si="9">C24*G24*100</f>
         <v>16800</v>
       </c>
-      <c r="E22" s="34">
-        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A22)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A22)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A22)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A22)</f>
-        <v>0</v>
-      </c>
-      <c r="F22" s="30">
-        <f t="shared" ref="F22:F24" si="10">E22*G22*100</f>
-        <v>0</v>
-      </c>
-      <c r="G22">
+      <c r="E24" s="34">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A24)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A24)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A24)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A24)</f>
+        <v>0</v>
+      </c>
+      <c r="F24" s="30">
+        <f t="shared" ref="F24:F26" si="10">E24*G24*100</f>
+        <v>0</v>
+      </c>
+      <c r="G24">
         <v>168</v>
       </c>
-      <c r="H22" s="31">
-        <f t="shared" ref="H22:H24" si="11">B22*G22*100</f>
+      <c r="H24" s="31">
+        <f t="shared" ref="H24:H26" si="11">B24*G24*100</f>
         <v>16800</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
-      <c r="A23" t="s">
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
         <v>241</v>
       </c>
-      <c r="B23" s="33">
-        <f t="shared" si="0"/>
+      <c r="B25" s="33">
+        <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
-      <c r="C23" s="33">
+      <c r="C25" s="33">
         <v>0.1</v>
       </c>
-      <c r="D23" s="30">
+      <c r="D25" s="30">
         <f t="shared" si="9"/>
         <v>1680</v>
       </c>
-      <c r="E23" s="34">
-        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A23)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A23)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A23)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A23)</f>
-        <v>0</v>
-      </c>
-      <c r="F23" s="30">
+      <c r="E25" s="34">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A25)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A25)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A25)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A25)</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="30">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G23">
+      <c r="G25">
         <v>168</v>
       </c>
-      <c r="H23" s="31">
+      <c r="H25" s="31">
         <f t="shared" si="11"/>
         <v>1680</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
-      <c r="A24" t="s">
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
         <v>245</v>
       </c>
-      <c r="B24" s="33">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C24" s="33">
-        <v>0</v>
-      </c>
-      <c r="D24" s="30">
+      <c r="B26" s="33">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="C26" s="33">
+        <v>0</v>
+      </c>
+      <c r="D26" s="30">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="E24" s="34">
-        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A24)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A24)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A24)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A24)</f>
-        <v>0</v>
-      </c>
-      <c r="F24" s="30">
+      <c r="E26" s="34">
+        <f>SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$3,Item!$E$2:$E$1000,$A26)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$4,Item!$E$2:$E$1000,$A26)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$5,Item!$E$2:$E$1000,$A26)+SUMIFS(Item!$F$2:$F$1000,Item!$A$2:$A$1000,$B$6,Item!$E$2:$E$1000,$A26)</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="30">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G24">
+      <c r="G26">
         <v>233</v>
       </c>
-      <c r="H24" s="31">
+      <c r="H26" s="31">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="35">
-        <f t="shared" ref="D25:H25" si="12">SUM(D9:D24)</f>
+    <row r="27" spans="1:8">
+      <c r="A27" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="35">
+        <f>SUM(D9:D26)</f>
         <v>156960</v>
       </c>
-      <c r="E25" s="36"/>
-      <c r="F25" s="35">
-        <f t="shared" si="12"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="35">
+        <f>SUM(F9:F26)</f>
         <v>71600</v>
       </c>
-      <c r="G25" s="2"/>
-      <c r="H25" s="35">
-        <f t="shared" si="12"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="35">
+        <f>SUM(H9:H26)</f>
         <v>228560</v>
       </c>
     </row>
-    <row r="26" customFormat="1" spans="1:11">
-      <c r="A26" t="s">
-        <v>559</v>
-      </c>
-      <c r="D26" s="36">
-        <f>'Balanced Dummy '!D18-D25</f>
-        <v>0</v>
-      </c>
-      <c r="E26" s="36"/>
-      <c r="F26" s="36"/>
-      <c r="K26" s="50"/>
-    </row>
-    <row r="27" customFormat="1" spans="4:11">
-      <c r="D27" s="36"/>
-      <c r="E27" s="36"/>
-      <c r="F27" s="36"/>
-      <c r="K27" s="50"/>
-    </row>
-    <row r="28" spans="1:11">
-      <c r="A28" s="37" t="s">
-        <v>443</v>
-      </c>
-      <c r="B28" s="38" t="s">
+    <row r="28" customFormat="1" spans="1:11">
+      <c r="A28" t="s">
+        <v>564</v>
+      </c>
+      <c r="D28" s="36">
+        <f>'Balanced Dummy '!D18-D27</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="36"/>
+      <c r="F28" s="36"/>
+      <c r="K28" s="46"/>
+    </row>
+    <row r="29" customFormat="1" spans="4:11">
+      <c r="D29" s="36"/>
+      <c r="E29" s="36"/>
+      <c r="F29" s="36"/>
+      <c r="K29" s="46"/>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="37" t="s">
+        <v>565</v>
+      </c>
+      <c r="B30" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="C28" s="38" t="s">
-        <v>444</v>
-      </c>
-      <c r="D28" s="38" t="s">
-        <v>445</v>
-      </c>
-      <c r="E28" s="38" t="s">
+      <c r="C30" s="38" t="s">
+        <v>448</v>
+      </c>
+      <c r="D30" s="38" t="s">
+        <v>449</v>
+      </c>
+      <c r="E30" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="F28" s="37" t="s">
-        <v>399</v>
-      </c>
-      <c r="G28" s="37" t="s">
-        <v>560</v>
-      </c>
-      <c r="H28" s="37" t="s">
+      <c r="F30" s="37" t="s">
+        <v>403</v>
+      </c>
+      <c r="G30" s="37" t="s">
+        <v>566</v>
+      </c>
+      <c r="H30" s="37" t="s">
         <v>114</v>
       </c>
-      <c r="I28" s="38" t="s">
-        <v>304</v>
-      </c>
-      <c r="J28" s="37" t="s">
-        <v>561</v>
-      </c>
-      <c r="K28" s="38" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="29" ht="30" spans="1:11">
-      <c r="A29" s="37" t="s">
-        <v>613</v>
-      </c>
-      <c r="B29" s="37">
+      <c r="I30" s="38" t="s">
+        <v>308</v>
+      </c>
+      <c r="J30" s="37" t="s">
+        <v>567</v>
+      </c>
+      <c r="K30" s="38" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="31" ht="30" spans="1:11">
+      <c r="A31" s="37" t="s">
+        <v>676</v>
+      </c>
+      <c r="B31" s="37">
         <v>100</v>
       </c>
-      <c r="C29" s="37">
+      <c r="C31" s="37">
         <f>2*1000*1.5</f>
         <v>3000</v>
       </c>
-      <c r="D29" s="37">
+      <c r="D31" s="37">
         <v>1</v>
       </c>
-      <c r="E29" s="37" t="s">
-        <v>614</v>
-      </c>
-      <c r="F29" s="37" t="s">
-        <v>615</v>
-      </c>
-      <c r="G29" s="37" t="s">
-        <v>572</v>
-      </c>
-      <c r="H29" s="37"/>
-      <c r="I29" s="37" t="s">
-        <v>616</v>
-      </c>
-      <c r="J29" s="37" t="s">
-        <v>617</v>
-      </c>
-      <c r="K29" s="37">
+      <c r="E31" s="37" t="s">
+        <v>677</v>
+      </c>
+      <c r="F31" s="37" t="s">
+        <v>627</v>
+      </c>
+      <c r="G31" s="37" t="s">
+        <v>578</v>
+      </c>
+      <c r="H31" s="37"/>
+      <c r="I31" s="37" t="s">
+        <v>622</v>
+      </c>
+      <c r="J31" s="37" t="s">
+        <v>678</v>
+      </c>
+      <c r="K31" s="37">
         <f>4.8*1000*30%*5</f>
         <v>7200</v>
       </c>
     </row>
-    <row r="30" ht="45" spans="1:11">
-      <c r="A30" s="37" t="s">
-        <v>618</v>
-      </c>
-      <c r="B30" s="37">
+    <row r="32" ht="45" spans="1:11">
+      <c r="A32" s="37" t="s">
+        <v>679</v>
+      </c>
+      <c r="B32" s="37">
         <v>75</v>
       </c>
-      <c r="C30" s="37">
+      <c r="C32" s="37">
         <f>2*1000*2*1.3</f>
         <v>5200</v>
       </c>
-      <c r="D30" s="37">
+      <c r="D32" s="37">
         <v>10</v>
       </c>
-      <c r="E30" s="37" t="s">
-        <v>619</v>
-      </c>
-      <c r="F30" s="37" t="s">
-        <v>620</v>
-      </c>
-      <c r="G30" s="37" t="s">
-        <v>620</v>
-      </c>
-      <c r="H30" s="37">
+      <c r="E32" s="37" t="s">
+        <v>680</v>
+      </c>
+      <c r="F32" s="37" t="s">
+        <v>645</v>
+      </c>
+      <c r="G32" s="37" t="s">
+        <v>645</v>
+      </c>
+      <c r="H32" s="37">
         <v>6</v>
       </c>
-      <c r="I30" s="37" t="s">
-        <v>621</v>
-      </c>
-      <c r="J30" s="37" t="s">
-        <v>582</v>
-      </c>
-      <c r="K30" s="51">
+      <c r="I32" s="37" t="s">
+        <v>681</v>
+      </c>
+      <c r="J32" s="37" t="s">
+        <v>588</v>
+      </c>
+      <c r="K32" s="47">
         <v>0.15</v>
       </c>
     </row>
-    <row r="31" ht="30" spans="1:11">
-      <c r="A31" s="39" t="s">
-        <v>622</v>
-      </c>
-      <c r="B31" s="39" t="s">
-        <v>623</v>
-      </c>
-      <c r="C31" s="39">
+    <row r="33" ht="30" spans="1:11">
+      <c r="A33" s="39" t="s">
+        <v>682</v>
+      </c>
+      <c r="B33" s="39" t="s">
+        <v>683</v>
+      </c>
+      <c r="C33" s="39">
         <f>2*1000*0.4</f>
         <v>800</v>
       </c>
-      <c r="D31" s="39">
+      <c r="D33" s="39">
         <v>2</v>
       </c>
-      <c r="E31" s="39" t="s">
-        <v>624</v>
-      </c>
-      <c r="F31" s="40" t="s">
-        <v>625</v>
-      </c>
-      <c r="G31" s="39" t="s">
-        <v>572</v>
-      </c>
-      <c r="H31" s="39">
+      <c r="E33" s="39" t="s">
+        <v>684</v>
+      </c>
+      <c r="F33" s="39" t="s">
+        <v>685</v>
+      </c>
+      <c r="G33" s="39" t="s">
+        <v>578</v>
+      </c>
+      <c r="H33" s="39">
         <v>1</v>
       </c>
-      <c r="I31" s="52" t="s">
-        <v>626</v>
-      </c>
-      <c r="J31" s="52" t="s">
-        <v>627</v>
-      </c>
-      <c r="K31" s="53">
+      <c r="I33" s="39" t="s">
+        <v>686</v>
+      </c>
+      <c r="J33" s="39" t="s">
+        <v>687</v>
+      </c>
+      <c r="K33" s="48">
         <f>4%*5</f>
         <v>0.2</v>
       </c>
     </row>
-    <row r="32" ht="66" customHeight="1" spans="1:11">
-      <c r="A32" s="39"/>
-      <c r="B32" s="39"/>
-      <c r="C32" s="39"/>
-      <c r="D32" s="39"/>
-      <c r="E32" s="39"/>
-      <c r="F32" s="40"/>
-      <c r="G32" s="39"/>
-      <c r="H32" s="39"/>
-      <c r="I32" s="40" t="s">
-        <v>628</v>
-      </c>
-      <c r="J32" s="40" t="s">
-        <v>629</v>
-      </c>
-      <c r="K32" s="40">
-        <f>4.8*1000*20%*5</f>
-        <v>4800</v>
-      </c>
-    </row>
-    <row r="33" ht="30" spans="1:11">
-      <c r="A33" s="40" t="s">
-        <v>630</v>
-      </c>
-      <c r="B33" s="40">
+    <row r="34" ht="66" customHeight="1" spans="1:11">
+      <c r="A34" s="39"/>
+      <c r="B34" s="39"/>
+      <c r="C34" s="39"/>
+      <c r="D34" s="39"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="39"/>
+      <c r="G34" s="39"/>
+      <c r="H34" s="39"/>
+      <c r="I34" s="39" t="s">
+        <v>688</v>
+      </c>
+      <c r="J34" s="39" t="s">
+        <v>689</v>
+      </c>
+      <c r="K34" s="39">
+        <f>4.8*1000*5%*5</f>
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="35" ht="30" spans="1:11">
+      <c r="A35" s="39" t="s">
+        <v>690</v>
+      </c>
+      <c r="B35" s="39">
         <v>150</v>
       </c>
-      <c r="C33" s="40">
+      <c r="C35" s="39">
         <f>2*1000*1.5</f>
         <v>3000</v>
       </c>
-      <c r="D33" s="40">
+      <c r="D35" s="39">
         <v>5</v>
       </c>
-      <c r="E33" s="40" t="s">
-        <v>631</v>
-      </c>
-      <c r="F33" s="40" t="s">
-        <v>625</v>
-      </c>
-      <c r="G33" s="40" t="s">
-        <v>632</v>
-      </c>
-      <c r="H33" s="40">
+      <c r="E35" s="39" t="s">
+        <v>691</v>
+      </c>
+      <c r="F35" s="39" t="s">
+        <v>685</v>
+      </c>
+      <c r="G35" s="39" t="s">
+        <v>692</v>
+      </c>
+      <c r="H35" s="39">
         <v>3</v>
       </c>
-      <c r="I33" s="52" t="s">
-        <v>626</v>
-      </c>
-      <c r="J33" s="52" t="s">
-        <v>627</v>
-      </c>
-      <c r="K33" s="53">
+      <c r="I35" s="39" t="s">
+        <v>686</v>
+      </c>
+      <c r="J35" s="39" t="s">
+        <v>687</v>
+      </c>
+      <c r="K35" s="48">
         <f>4%*5</f>
         <v>0.2</v>
       </c>
     </row>
-    <row r="34" ht="54" customHeight="1" spans="1:11">
-      <c r="A34" s="40"/>
-      <c r="B34" s="40"/>
-      <c r="C34" s="40"/>
-      <c r="D34" s="40"/>
-      <c r="E34" s="40"/>
-      <c r="F34" s="40"/>
-      <c r="G34" s="40"/>
-      <c r="H34" s="40"/>
-      <c r="I34" s="40" t="s">
-        <v>628</v>
-      </c>
-      <c r="J34" s="40" t="s">
-        <v>629</v>
-      </c>
-      <c r="K34" s="40">
-        <f>4.8*1000*20%*5</f>
-        <v>4800</v>
-      </c>
-    </row>
-    <row r="36" ht="60" spans="1:8">
-      <c r="A36" s="41" t="s">
-        <v>585</v>
-      </c>
-      <c r="B36" s="41" t="s">
-        <v>633</v>
-      </c>
-      <c r="C36" s="41" t="s">
-        <v>634</v>
-      </c>
-      <c r="D36" s="42" t="s">
-        <v>635</v>
-      </c>
-      <c r="E36" s="42" t="s">
-        <v>636</v>
-      </c>
-      <c r="F36" s="42" t="s">
-        <v>637</v>
-      </c>
-      <c r="G36" s="42" t="s">
-        <v>638</v>
-      </c>
-      <c r="H36" s="42" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="37" ht="60" spans="1:8">
-      <c r="A37" s="43"/>
-      <c r="B37" s="43"/>
-      <c r="C37" s="43"/>
-      <c r="D37" s="42"/>
-      <c r="E37" s="42" t="s">
-        <v>640</v>
-      </c>
-      <c r="F37" s="42" t="s">
-        <v>641</v>
-      </c>
-      <c r="G37" s="42" t="s">
-        <v>642</v>
-      </c>
-      <c r="H37" s="42" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="44"/>
-      <c r="B38" s="44"/>
-      <c r="C38" s="44"/>
-      <c r="D38" s="44"/>
-      <c r="E38" s="44"/>
-      <c r="F38" s="44"/>
-      <c r="G38" s="44"/>
-      <c r="H38" s="44"/>
+    <row r="36" ht="54" customHeight="1" spans="1:11">
+      <c r="A36" s="39"/>
+      <c r="B36" s="39"/>
+      <c r="C36" s="39"/>
+      <c r="D36" s="39"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="39"/>
+      <c r="G36" s="39"/>
+      <c r="H36" s="39"/>
+      <c r="I36" s="39" t="s">
+        <v>688</v>
+      </c>
+      <c r="J36" s="39" t="s">
+        <v>689</v>
+      </c>
+      <c r="K36" s="39">
+        <f>4.8*1000*5%*5</f>
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="38" ht="60" spans="1:8">
+      <c r="A38" s="40" t="s">
+        <v>591</v>
+      </c>
+      <c r="B38" s="40" t="s">
+        <v>693</v>
+      </c>
+      <c r="C38" s="40" t="s">
+        <v>694</v>
+      </c>
+      <c r="D38" s="41" t="s">
+        <v>695</v>
+      </c>
+      <c r="E38" s="41" t="s">
+        <v>696</v>
+      </c>
+      <c r="F38" s="41" t="s">
+        <v>697</v>
+      </c>
+      <c r="G38" s="41" t="s">
+        <v>698</v>
+      </c>
+      <c r="H38" s="41" t="s">
+        <v>699</v>
+      </c>
     </row>
     <row r="39" ht="60" spans="1:8">
-      <c r="A39" s="45" t="s">
-        <v>597</v>
-      </c>
-      <c r="B39" s="45" t="s">
-        <v>644</v>
-      </c>
-      <c r="C39" s="45" t="s">
-        <v>645</v>
-      </c>
-      <c r="D39" s="45" t="s">
-        <v>646</v>
-      </c>
-      <c r="E39" s="46" t="s">
-        <v>647</v>
-      </c>
-      <c r="F39" s="46" t="s">
-        <v>648</v>
-      </c>
-      <c r="G39" s="46" t="s">
-        <v>649</v>
-      </c>
-      <c r="H39" s="47"/>
-    </row>
-    <row r="40" ht="60" spans="1:8">
-      <c r="A40" s="48"/>
-      <c r="B40" s="48"/>
-      <c r="C40" s="48"/>
-      <c r="D40" s="48"/>
-      <c r="E40" s="46" t="s">
-        <v>650</v>
-      </c>
-      <c r="F40" s="46" t="s">
-        <v>651</v>
-      </c>
-      <c r="G40" s="46"/>
-      <c r="H40" s="47"/>
+      <c r="A39" s="42"/>
+      <c r="B39" s="42"/>
+      <c r="C39" s="42"/>
+      <c r="D39" s="41"/>
+      <c r="E39" s="41" t="s">
+        <v>700</v>
+      </c>
+      <c r="F39" s="41" t="s">
+        <v>701</v>
+      </c>
+      <c r="G39" s="41" t="s">
+        <v>702</v>
+      </c>
+      <c r="H39" s="41" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="43"/>
+      <c r="B40" s="43"/>
+      <c r="C40" s="43"/>
+      <c r="D40" s="43"/>
+      <c r="E40" s="43"/>
+      <c r="F40" s="43"/>
+      <c r="G40" s="43"/>
+      <c r="H40" s="43"/>
     </row>
     <row r="41" ht="60" spans="1:8">
-      <c r="A41" s="49"/>
-      <c r="B41" s="49"/>
-      <c r="C41" s="49"/>
-      <c r="D41" s="49"/>
-      <c r="E41" s="46" t="s">
-        <v>652</v>
-      </c>
-      <c r="F41" s="46" t="s">
-        <v>653</v>
-      </c>
-      <c r="G41" s="46" t="s">
-        <v>654</v>
-      </c>
-      <c r="H41" s="47"/>
+      <c r="A41" s="40" t="s">
+        <v>603</v>
+      </c>
+      <c r="B41" s="40" t="s">
+        <v>704</v>
+      </c>
+      <c r="C41" s="40" t="s">
+        <v>705</v>
+      </c>
+      <c r="D41" s="40" t="s">
+        <v>706</v>
+      </c>
+      <c r="E41" s="41" t="s">
+        <v>707</v>
+      </c>
+      <c r="F41" s="41" t="s">
+        <v>708</v>
+      </c>
+      <c r="G41" s="41" t="s">
+        <v>709</v>
+      </c>
+      <c r="H41" s="44"/>
+    </row>
+    <row r="42" ht="60" spans="1:8">
+      <c r="A42" s="45"/>
+      <c r="B42" s="45"/>
+      <c r="C42" s="45"/>
+      <c r="D42" s="45"/>
+      <c r="E42" s="41" t="s">
+        <v>710</v>
+      </c>
+      <c r="F42" s="41" t="s">
+        <v>711</v>
+      </c>
+      <c r="G42" s="41"/>
+      <c r="H42" s="44"/>
+    </row>
+    <row r="43" ht="60" spans="1:8">
+      <c r="A43" s="42"/>
+      <c r="B43" s="42"/>
+      <c r="C43" s="42"/>
+      <c r="D43" s="42"/>
+      <c r="E43" s="41" t="s">
+        <v>712</v>
+      </c>
+      <c r="F43" s="41" t="s">
+        <v>713</v>
+      </c>
+      <c r="G43" s="41" t="s">
+        <v>714</v>
+      </c>
+      <c r="H43" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A31:A32"/>
     <mergeCell ref="A33:A34"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A39:A41"/>
-    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A41:A43"/>
     <mergeCell ref="B33:B34"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="B39:B41"/>
-    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="B41:B43"/>
     <mergeCell ref="C33:C34"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="C39:C41"/>
-    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="C41:C43"/>
     <mergeCell ref="D33:D34"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="D41:D43"/>
     <mergeCell ref="E33:E34"/>
-    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="E35:E36"/>
     <mergeCell ref="F33:F34"/>
-    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="F35:F36"/>
     <mergeCell ref="G33:G34"/>
-    <mergeCell ref="H31:H32"/>
+    <mergeCell ref="G35:G36"/>
     <mergeCell ref="H33:H34"/>
+    <mergeCell ref="H35:H36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I52"/>
@@ -8827,42 +10581,42 @@
   <sheetData>
     <row r="1" s="2" customFormat="1" spans="1:9">
       <c r="A1" s="6" t="s">
-        <v>655</v>
+        <v>715</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>656</v>
+        <v>716</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>657</v>
+        <v>717</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>658</v>
+        <v>718</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>659</v>
+        <v>719</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>660</v>
+        <v>720</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>661</v>
+        <v>721</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>662</v>
+        <v>722</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="10" t="s">
-        <v>663</v>
+        <v>617</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="D2" s="12">
         <v>0</v>
@@ -8888,13 +10642,13 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="10" t="s">
-        <v>663</v>
+        <v>617</v>
       </c>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
       <c r="D3" s="16"/>
       <c r="E3" s="13" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="F3" s="13">
         <v>4</v>
@@ -8910,7 +10664,7 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="10" t="s">
-        <v>663</v>
+        <v>617</v>
       </c>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -8932,13 +10686,13 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="10" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>664</v>
+        <v>723</v>
       </c>
       <c r="D5" s="18">
         <v>0.5</v>
@@ -8964,7 +10718,7 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="10" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
@@ -8986,13 +10740,13 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="10" t="s">
-        <v>665</v>
+        <v>724</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>666</v>
+        <v>725</v>
       </c>
       <c r="D7" s="18">
         <v>0.5</v>
@@ -9018,7 +10772,7 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="10" t="s">
-        <v>665</v>
+        <v>724</v>
       </c>
       <c r="B8" s="16"/>
       <c r="C8" s="16"/>
@@ -9040,7 +10794,7 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="10" t="s">
-        <v>665</v>
+        <v>724</v>
       </c>
       <c r="B9" s="17"/>
       <c r="C9" s="17"/>
@@ -9062,13 +10816,13 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="10" t="s">
-        <v>611</v>
+        <v>674</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>615</v>
+        <v>627</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="D10" s="12">
         <v>0</v>
@@ -9094,7 +10848,7 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="10" t="s">
-        <v>611</v>
+        <v>674</v>
       </c>
       <c r="B11" s="16"/>
       <c r="C11" s="16"/>
@@ -9116,7 +10870,7 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="10" t="s">
-        <v>611</v>
+        <v>674</v>
       </c>
       <c r="B12" s="17"/>
       <c r="C12" s="17"/>
@@ -9138,16 +10892,16 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="10" t="s">
-        <v>667</v>
+        <v>726</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>668</v>
+        <v>727</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>669</v>
+        <v>728</v>
       </c>
       <c r="E13" s="13" t="s">
         <v>198</v>
@@ -9170,13 +10924,13 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="10" t="s">
-        <v>667</v>
+        <v>726</v>
       </c>
       <c r="B14" s="16"/>
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="13" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="F14" s="19">
         <v>0.2</v>
@@ -9192,7 +10946,7 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="10" t="s">
-        <v>667</v>
+        <v>726</v>
       </c>
       <c r="B15" s="16"/>
       <c r="C15" s="16"/>
@@ -9214,7 +10968,7 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="10" t="s">
-        <v>667</v>
+        <v>726</v>
       </c>
       <c r="B16" s="17"/>
       <c r="C16" s="17"/>
@@ -9236,13 +10990,13 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="10" t="s">
-        <v>670</v>
+        <v>729</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>615</v>
+        <v>627</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>671</v>
+        <v>730</v>
       </c>
       <c r="D17" s="18">
         <v>0.5</v>
@@ -9268,13 +11022,13 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="10" t="s">
-        <v>670</v>
+        <v>729</v>
       </c>
       <c r="B18" s="16"/>
       <c r="C18" s="16"/>
       <c r="D18" s="16"/>
       <c r="E18" s="13" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="F18" s="13">
         <v>1</v>
@@ -9290,7 +11044,7 @@
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="10" t="s">
-        <v>670</v>
+        <v>729</v>
       </c>
       <c r="B19" s="17"/>
       <c r="C19" s="17"/>
@@ -9312,13 +11066,13 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="20" t="s">
-        <v>672</v>
+        <v>731</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="D20" s="21"/>
       <c r="E20" s="13" t="s">
@@ -9341,7 +11095,7 @@
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="10" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="B21" s="22"/>
       <c r="C21" s="22"/>
@@ -9366,7 +11120,7 @@
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="10" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="B22" s="16"/>
       <c r="C22" s="16"/>
@@ -9391,7 +11145,7 @@
     </row>
     <row r="23" customFormat="1" spans="1:9">
       <c r="A23" s="10" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="B23" s="17"/>
       <c r="C23" s="17"/>
@@ -9417,7 +11171,7 @@
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="10" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -9443,7 +11197,7 @@
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="10" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="B25" s="17"/>
       <c r="C25" s="17"/>
@@ -9468,7 +11222,7 @@
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="10" t="s">
-        <v>673</v>
+        <v>618</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -9493,7 +11247,7 @@
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="10" t="s">
-        <v>673</v>
+        <v>618</v>
       </c>
       <c r="B27" s="16"/>
       <c r="C27" s="16"/>
@@ -9519,7 +11273,7 @@
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="10" t="s">
-        <v>673</v>
+        <v>618</v>
       </c>
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
@@ -9541,7 +11295,7 @@
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="10" t="s">
-        <v>673</v>
+        <v>618</v>
       </c>
       <c r="B29" s="16"/>
       <c r="C29" s="16"/>
@@ -9566,7 +11320,7 @@
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="10" t="s">
-        <v>673</v>
+        <v>618</v>
       </c>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
@@ -9591,7 +11345,7 @@
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="10" t="s">
-        <v>674</v>
+        <v>732</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -9616,7 +11370,7 @@
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="10" t="s">
-        <v>674</v>
+        <v>732</v>
       </c>
       <c r="B32" s="16"/>
       <c r="C32" s="16"/>
@@ -9641,7 +11395,7 @@
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="10" t="s">
-        <v>674</v>
+        <v>732</v>
       </c>
       <c r="B33" s="17"/>
       <c r="C33" s="17"/>
@@ -9666,7 +11420,7 @@
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="10" t="s">
-        <v>675</v>
+        <v>733</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -9688,7 +11442,7 @@
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="10" t="s">
-        <v>675</v>
+        <v>733</v>
       </c>
       <c r="B35" s="16"/>
       <c r="C35" s="16"/>
@@ -9711,13 +11465,13 @@
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="10" t="s">
-        <v>675</v>
+        <v>733</v>
       </c>
       <c r="B36" s="17"/>
       <c r="C36" s="17"/>
       <c r="D36" s="17"/>
       <c r="E36" s="13" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="F36" s="13">
         <v>2</v>
@@ -9733,7 +11487,7 @@
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="10" t="s">
-        <v>676</v>
+        <v>734</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -9759,7 +11513,7 @@
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="10" t="s">
-        <v>676</v>
+        <v>734</v>
       </c>
       <c r="B38" s="16"/>
       <c r="C38" s="16"/>
@@ -9781,7 +11535,7 @@
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="10" t="s">
-        <v>676</v>
+        <v>734</v>
       </c>
       <c r="B39" s="17"/>
       <c r="C39" s="17"/>
@@ -9803,7 +11557,7 @@
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="10" t="s">
-        <v>612</v>
+        <v>675</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -9829,7 +11583,7 @@
     </row>
     <row r="41" spans="1:9">
       <c r="A41" s="10" t="s">
-        <v>612</v>
+        <v>675</v>
       </c>
       <c r="B41" s="16"/>
       <c r="C41" s="16"/>
@@ -9851,7 +11605,7 @@
     </row>
     <row r="42" spans="1:9">
       <c r="A42" s="10" t="s">
-        <v>612</v>
+        <v>675</v>
       </c>
       <c r="B42" s="16"/>
       <c r="C42" s="16"/>
@@ -9873,7 +11627,7 @@
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="10" t="s">
-        <v>612</v>
+        <v>675</v>
       </c>
       <c r="B43" s="17"/>
       <c r="C43" s="17"/>
@@ -9895,42 +11649,42 @@
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>677</v>
+        <v>735</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>678</v>
+        <v>736</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="3" t="s">
-        <v>679</v>
+        <v>737</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="3" t="s">
-        <v>680</v>
+        <v>738</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="3" t="s">
-        <v>681</v>
+        <v>739</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="3" t="s">
-        <v>682</v>
+        <v>740</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="3" t="s">
-        <v>683</v>
+        <v>741</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>684</v>
+        <v>742</v>
       </c>
     </row>
   </sheetData>
@@ -9978,260 +11732,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="2"/>
-  <cols>
-    <col min="1" max="1" width="18.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="15.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="11.8571428571429" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>685</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>686</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>688</v>
-      </c>
-      <c r="C2" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>690</v>
-      </c>
-      <c r="C3" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>581</v>
-      </c>
-      <c r="C4" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>583</v>
-      </c>
-      <c r="C5" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>694</v>
-      </c>
-      <c r="C6" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>696</v>
-      </c>
-      <c r="C7" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>698</v>
-      </c>
-      <c r="C8" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>700</v>
-      </c>
-      <c r="C9" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>702</v>
-      </c>
-      <c r="C10" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>704</v>
-      </c>
-      <c r="C11" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>706</v>
-      </c>
-      <c r="C12" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>708</v>
-      </c>
-      <c r="C13" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>710</v>
-      </c>
-      <c r="C14" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" t="s">
-        <v>674</v>
-      </c>
-      <c r="B15">
-        <v>4</v>
-      </c>
-      <c r="C15" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" t="s">
-        <v>713</v>
-      </c>
-      <c r="C16" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>529</v>
-      </c>
-      <c r="B18">
-        <v>3</v>
-      </c>
-      <c r="C18" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>716</v>
-      </c>
-      <c r="B19">
-        <v>3</v>
-      </c>
-      <c r="C19" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" t="s">
-        <v>387</v>
-      </c>
-      <c r="C20" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" t="s">
-        <v>719</v>
-      </c>
-      <c r="C21" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" t="s">
-        <v>721</v>
-      </c>
-      <c r="B22" t="s">
-        <v>722</v>
-      </c>
-      <c r="C22" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" t="s">
-        <v>724</v>
-      </c>
-      <c r="C23" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" t="s">
-        <v>726</v>
-      </c>
-      <c r="C24" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" t="s">
-        <v>728</v>
-      </c>
-      <c r="C25" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" t="s">
-        <v>730</v>
-      </c>
-      <c r="C26" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" t="s">
-        <v>732</v>
-      </c>
-      <c r="C27" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" t="s">
-        <v>734</v>
-      </c>
-      <c r="C28" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" t="s">
-        <v>736</v>
-      </c>
-      <c r="C29" t="s">
-        <v>737</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-</worksheet>
 </file>
--- a/data/excel/Thiết kế game.xlsx
+++ b/data/excel/Thiết kế game.xlsx
@@ -7166,7 +7166,8 @@
         <v>125</v>
       </c>
       <c r="C32" s="36">
-        <v>7583</v>
+        <f>ROUND(4106*(50.5*4147.2+66.5*8270+66*L32)/1239658.6,0)</f>
+        <v>9385</v>
       </c>
       <c r="D32" s="14">
         <v>4</v>
@@ -7247,7 +7248,8 @@
         <v>100</v>
       </c>
       <c r="C35" s="36">
-        <v>5748</v>
+        <f>ROUND(4106*(67*4147.2+67*8270+66*L35)/1239658.6,0)</f>
+        <v>7219</v>
       </c>
       <c r="D35" s="14">
         <v>5</v>
@@ -7265,16 +7267,18 @@
       <c r="I35" s="13" t="s">
         <v>464</v>
       </c>
-      <c r="J35" s="13" t="s">
-        <v>1147</v>
+      <c r="J35" s="13" t="inlineStr">
+        <is>
+          <t>1.654*1000*SL</t>
+        </is>
       </c>
       <c r="K35" s="64">
         <f>1.654*1000*5</f>
         <v>8270</v>
       </c>
       <c r="L35" s="65">
-        <f>8279*1.975*1.25</f>
-        <v>20438.78125</v>
+        <f>8270*1.975*1.25</f>
+        <v>20416.5625</v>
       </c>
     </row>
     <row r="36" s="52" customFormat="1" ht="32" customHeight="1" spans="1:12">
@@ -10911,8 +10915,10 @@
       <c r="B9" s="147" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="147" t="s">
-        <v>39</v>
+      <c r="C9" s="147" t="inlineStr">
+        <is>
+          <t>Initialize each skill's remaining cooldown to its applicable cooldown duration, unless an explicit effect overrides it. Both teams begin cooldown recovery at the end of global turn 1, even if their first team turn has not occurred.</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="30" spans="1:3">
@@ -11917,8 +11923,10 @@
       <c r="B103" s="147" t="s">
         <v>229</v>
       </c>
-      <c r="C103" s="147" t="s">
-        <v>230</v>
+      <c r="C103" s="147" t="inlineStr">
+        <is>
+          <t>For a landed hit, use zero mitigation if Penetration succeeds; otherwise use the target's Final Defense mitigation. A critical hit multiplies damage by 1 + Final Critical Damage Bonus. Resolve applicable damage adjustments for each recipient, then multiply secondary-target final damage by (1 - Sub-target Damage Penalty). This penalty does not reduce Attack.</t>
+        </is>
       </c>
     </row>
     <row r="104" ht="30" spans="1:3">
@@ -12122,8 +12130,10 @@
       <c r="B122" s="147" t="s">
         <v>272</v>
       </c>
-      <c r="C122" s="147" t="s">
-        <v>273</v>
+      <c r="C122" s="147" t="inlineStr">
+        <is>
+          <t>At the end of every global turn, starting with global turn 1, apply default cooldown recovery to both teams. The team acting second also receives recovery at the end of global turn 1; a skill initialized with cooldown 1 is therefore ready on global turn 2, subject to its other casting requirements.</t>
+        </is>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -14158,7 +14168,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R176"/>
+  <dimension ref="A1:R186"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7142857142857" customWidth="1"/>
@@ -15875,8 +15885,73 @@
       </c>
     </row>
     <row r="176" spans="1:1">
-      <c r="A176" t="s">
-        <v>839</v>
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Mana reference: active SATK 8,270 without Stun Count; AP cost 100; mana cost 4,106; cooldown 3 global turns. CP/stat and status pricing retain the separate 5,800-SATK +1-Stun-Count reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Mana timing: evaluate 200 own team turns for each starting order. Both teams recover cooldown at the end of global turn 1. Start with 0 AP; recover 100 AP per own team turn; ignore MP exhaustion for pricing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Action priority: skill being priced, then reference active, then normal attack. Do not recast while the skill duration remains active. Apply listed AP costs and ordinary action-slot eligibility; a completed expensive action may leave AP negative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Reference totals: acting first gives 101 normals + 99 actives = 1,237,597.20 SATK equivalent; acting second gives 100 normals + 100 actives = 1,241,720.00. Mean reference value = 1,239,658.60.</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Mana Cost = 4,106 * Mean Total SATK Equivalent With Skill / 1,239,658.60. Average both starting orders. Skill SATK equivalent already includes assigned effects and area value; do not apply them again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>War Cry: AP 125, cooldown 4, duration 6, SATK equivalent 31,426. First: 51 normals, 66 reference actives, 66 War Cry casts, 17 skipped turns. Second: 50 normals, 67 reference actives, 66 War Cry casts, 17 skipped turns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>War Cry: mean total value 2,833,504.60; mana 9,385.140302; selected cost 9,385 MP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>God-King Slayer: AP 100, cooldown 5, instant; SATK equivalent = 8,270 * 1.975 * 1.25 = 20,416.5625. Both starting orders give 67 normals, 67 reference actives and 66 God-King Slayer casts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>God-King Slayer: total value 2,179,445.525; mana 7,218.764364; selected cost 7,219 MP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>These two Soldier mana costs use the updated cooldown timing and both starting orders. Other character mana entries have not been recalculated in this revision. Action counts are fixed for the listed AP costs, cooldowns and durations; recalculate them when those inputs change.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -16953,8 +17028,10 @@
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="91" t="s">
-        <v>873</v>
+      <c r="A51" s="91" t="inlineStr">
+        <is>
+          <t>Calculate damage separately against each recipient using its own mitigation and applicable damage modifiers. Then apply the listed Sub-target Damage Penalty to the secondary target's final damage: Final Sub-target Damage = Final Damage Before This Penalty * (1 - Penalty). A 50% penalty leaves 50% damage; a 75% penalty leaves 25%. This penalty does not reduce Attack or SATK. The primary target receives no sub-target penalty.</t>
+        </is>
       </c>
     </row>
     <row r="52" spans="1:1">
@@ -16973,8 +17050,10 @@
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" t="s">
-        <v>877</v>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Weapon Attack Target, Area of Attack, and Sub-target Damage Penalty apply only to normal attacks. Each skill defines its own targeting, area, and sub-target damage penalty; weapon rules are not inherited unless the skill explicitly states otherwise.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/excel/Thiết kế game.xlsx
+++ b/data/excel/Thiết kế game.xlsx
@@ -5473,7 +5473,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="150">
+  <cellXfs count="154">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -5838,6 +5838,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyNumberFormat="1">
+      <alignment wrapText="1" vertical="top"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyNumberFormat="1">
+      <alignment wrapText="1" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -14168,7 +14177,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R186"/>
+  <dimension ref="A1:R206"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7142857142857" customWidth="1"/>
@@ -15954,7 +15963,239 @@
         </is>
       </c>
     </row>
+    <row r="188" ht="28" customHeight="1">
+      <c r="A188" s="151" t="inlineStr">
+        <is>
+          <t>8. CP Review — Cooldown Recovery from Global Turn 1 — 2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="44" customHeight="1">
+      <c r="A189" s="151" t="inlineStr">
+        <is>
+          <t>Decision: keep all selected CP per stat and status coefficients. Analytic magnitude prices and explicit budget conventions are unchanged. The two new stun estimates differ from selected prices by less than 2%; retain 1,850 and 9,600 CP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="42" customHeight="1">
+      <c r="A190" s="151" t="inlineStr">
+        <is>
+          <t>Stat / tested increase</t>
+        </is>
+      </c>
+      <c r="B190" s="151" t="inlineStr">
+        <is>
+          <t>Selected CP</t>
+        </is>
+      </c>
+      <c r="C190" s="151" t="inlineStr">
+        <is>
+          <t>Old timing test</t>
+        </is>
+      </c>
+      <c r="D190" s="151" t="inlineStr">
+        <is>
+          <t>New timing test</t>
+        </is>
+      </c>
+      <c r="E190" s="151" t="inlineStr">
+        <is>
+          <t>New minus selected</t>
+        </is>
+      </c>
+      <c r="F190" s="151" t="inlineStr">
+        <is>
+          <t>Change vs selected</t>
+        </is>
+      </c>
+      <c r="G190" s="151" t="inlineStr">
+        <is>
+          <t>New estimate 95% interval</t>
+        </is>
+      </c>
+      <c r="H190" s="151" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="44" customHeight="1">
+      <c r="A191" s="151" t="inlineStr">
+        <is>
+          <t>Stun Threshold: 4 to 5</t>
+        </is>
+      </c>
+      <c r="B191" s="152">
+        <v>1850</v>
+      </c>
+      <c r="C191" s="152">
+        <v>1969.0</v>
+      </c>
+      <c r="D191" s="152">
+        <v>1866.0</v>
+      </c>
+      <c r="E191" s="152">
+        <f>D191-B191</f>
+        <v>16.0</v>
+      </c>
+      <c r="F191" s="153">
+        <f>E191/B191</f>
+        <v>0.008648648648648649</v>
+      </c>
+      <c r="G191" s="151" t="inlineStr">
+        <is>
+          <t>1,577.34 to 2,154.66</t>
+        </is>
+      </c>
+      <c r="H191" s="151" t="inlineStr">
+        <is>
+          <t>Keep selected CP</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="44" customHeight="1">
+      <c r="A192" s="151" t="inlineStr">
+        <is>
+          <t>Attack Stun Count: 0 to 1</t>
+        </is>
+      </c>
+      <c r="B192" s="152">
+        <v>9600</v>
+      </c>
+      <c r="C192" s="152">
+        <v>9702.0</v>
+      </c>
+      <c r="D192" s="152">
+        <v>9444.0</v>
+      </c>
+      <c r="E192" s="152">
+        <f>D192-B192</f>
+        <v>-156.0</v>
+      </c>
+      <c r="F192" s="153">
+        <f>E192/B192</f>
+        <v>-0.01625</v>
+      </c>
+      <c r="G192" s="151" t="inlineStr">
+        <is>
+          <t>9,115.55 to 9,772.45</t>
+        </is>
+      </c>
+      <c r="H192" s="151" t="inlineStr">
+        <is>
+          <t>Keep selected CP</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="44" customHeight="1">
+      <c r="A194" s="151" t="inlineStr">
+        <is>
+          <t>Comparison design: 100 battles per configuration, 50 per starting order, matched seed base 20261026. Use per-side/action random streams. CP = mean paired change in (A remaining HP - B remaining HP), with 1 HP = 1 CP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="44" customHeight="1">
+      <c r="A195" s="151" t="inlineStr">
+        <is>
+          <t>Current-timing sensitivity tests: HP 50,000; MP 41,060; active SATK 5,800, AP 100, MP cost 4,106, cooldown 3; passive Attack Effectiveness +20%. Normal-first alternating completed actions; normal fallback if active unavailable. Same rules except initial cooldown recovery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="44" customHeight="1">
+      <c r="A196" s="151" t="inlineStr">
+        <is>
+          <t>Threshold test: only B applies stun, through normal and active count 1; A threshold changes 4 to 5. Normal-count test: only A applies stun; A active count stays 1 and normal count changes 0 to 1. Stun/count duration 3 global turns; one stack per target per global turn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="44" customHeight="1">
+      <c r="A197" s="151" t="inlineStr">
+        <is>
+          <t>Original benchmark reproduction (no cooldown/MP limits): threshold 1,852.00 CP and normal count 9,579.00 CP, exactly reproducing the original results. The original selected prices remain 1,850 and 9,600. Do not confuse this unrestricted benchmark with the additional cooldown-constrained tests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="44" customHeight="1">
+      <c r="A198" s="151" t="inlineStr">
+        <is>
+          <t>Cooldown-rule-only effect with CD/MP fixed: threshold 1,969 -&gt; 1,866 CP (-103.00; approx. 95% paired interval -265.69 to +59.69). Normal count 9,702 -&gt; 9,444 CP (-258.00; interval -501.94 to -14.06). The latter indicates a small timing effect in this sample; it does not justify replacing the selected 9,600 budget with a precise sample estimate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="44" customHeight="1">
+      <c r="A199" s="151" t="inlineStr">
+        <is>
+          <t>Uncertainty: approximate 95% intervals use 1.984 times the standard error from 100 paired trials. Both current selected prices lie within the intervals of the corresponding new estimates. Samples are reference-scenario evidence, not universal prices for all characters or teams.</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="44" customHeight="1">
+      <c r="A200" s="151" t="inlineStr">
+        <is>
+          <t>Analytic stat prices unchanged: HP, MP package, Attack, Defense, Skill Defense, MHR, Penetration, CHC, CDB, Skill Points package, Evasion, Healing Amplification, Block Chance and Counterattack Chance. AP Recovery and Accuracy retain their explicit budget conventions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="44" customHeight="1">
+      <c r="A201" s="151" t="inlineStr">
+        <is>
+          <t>Status coefficients unchanged: Rage/Intimidated, Calm/Weaken, Fortify/Sunder, Resistance/Exposure, Haste/Slow, Onslaught/Falter, Blind, Precision/Doubt, Shield, Block Chance, Counterattack Chance, Vulnerable/Durable, Chill and Break. These price magnitude, not duration or actual cast counts. Blank coefficients remain unpriced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="44" customHeight="1">
+      <c r="A202" s="151" t="inlineStr">
+        <is>
+          <t>Why formulas do not change: the CP reference remains one normal action alternating with one active, with mixed damage 2,486.80 per completed action. It excludes initial cooldown delays. Changing this reference to a finite combat schedule would be a separate repricing decision, not an automatic consequence of the new cooldown rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="44" customHeight="1">
+      <c r="A203" s="151" t="inlineStr">
+        <is>
+          <t>Cadence check without stun or MP exhaustion, active-first when ready: over 20 own turns, old timing gives 11 normals + 9 actives for either starting side. New timing gives 11 + 9 for the first side, 10 + 10 for the second. Average damage changes 2,445.48 -&gt; 2,466.14 (+0.84%). This diagnostic is not the selected 2,486.80 magnitude reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="44" customHeight="1">
+      <c r="A204" s="151" t="inlineStr">
+        <is>
+          <t>Over 200 own turns, the analogous damage diagnostic changes 2,482.668 -&gt; 2,484.734 (+0.08%). This check excludes MP exhaustion; MP pricing itself retains the separate 10-usable-cast package assumption.</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="44" customHeight="1">
+      <c r="A205" s="151" t="inlineStr">
+        <is>
+          <t>Engine validation: confirmed that both teams recover cooldown at end of global turn 1; a cooldown-1 skill is ready for the second team on global turn 2. Duration/count expiration and cooldown assigned on casting remain unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="44" customHeight="1">
+      <c r="A206" s="151" t="inlineStr">
+        <is>
+          <t>Source audit: the original simulation-based coefficients excluded mana/cooldown. New tests supplement, rather than silently replace, those valuation assumptions. No character stats, skill mana costs, spec nodes or selected CP totals are changed in this review.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="A188:H188"/>
+    <mergeCell ref="A189:H189"/>
+    <mergeCell ref="A194:H194"/>
+    <mergeCell ref="A195:H195"/>
+    <mergeCell ref="A196:H196"/>
+    <mergeCell ref="A197:H197"/>
+    <mergeCell ref="A198:H198"/>
+    <mergeCell ref="A199:H199"/>
+    <mergeCell ref="A200:H200"/>
+    <mergeCell ref="A201:H201"/>
+    <mergeCell ref="A202:H202"/>
+    <mergeCell ref="A203:H203"/>
+    <mergeCell ref="A204:H204"/>
+    <mergeCell ref="A205:H205"/>
+    <mergeCell ref="A206:H206"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
@@ -17815,16 +18056,20 @@
       <c r="A57" s="86" t="s">
         <v>991</v>
       </c>
-      <c r="B57" s="86" t="s">
-        <v>992</v>
+      <c r="B57" s="86" t="inlineStr">
+        <is>
+          <t>These coefficients price effect magnitude. They exclude duration, uptime, recipient count, cast frequency, and resource costs. They are independent of the 200-team-turn mana-cost method. Stun value is not added to the mixed-damage denominator. Reviewed 2026-10-29 after the global-turn-1 cooldown change: coefficients retained; see Balanced Dummy section 8.</t>
+        </is>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="86" t="s">
         <v>993</v>
       </c>
-      <c r="B58" s="86" t="s">
-        <v>994</v>
+      <c r="B58" s="86" t="inlineStr">
+        <is>
+          <t>Each +1 active SATK adds 0.25 mixed damage. CP per SATK = 50,000 * 0.25 / 2,486.80 = 5.02654013. Point per 100 CP = 19.8944. Modifier per 100 CP = 19.8944 / 5,800 = 0.34300690%. This prices the SATK increase only; the skill keeps +1 Stun Count. SATK is not an additional basic-stat CP entry.</t>
+        </is>
       </c>
     </row>
     <row r="59" spans="1:2">
